--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-18.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="103">
   <si>
     <t>League</t>
   </si>
@@ -254,6 +254,75 @@
   </si>
   <si>
     <t>SnapshotTS</t>
+  </si>
+  <si>
+    <t>Ecuadorian Serie A</t>
+  </si>
+  <si>
+    <t>Argentinian Primera Division</t>
+  </si>
+  <si>
+    <t>Chilean Primera B</t>
+  </si>
+  <si>
+    <t>Chilean Primera Division</t>
+  </si>
+  <si>
+    <t>Mexican Liga MX</t>
+  </si>
+  <si>
+    <t>2026-08-18</t>
+  </si>
+  <si>
+    <t>00:00:00</t>
+  </si>
+  <si>
+    <t>00:30:00</t>
+  </si>
+  <si>
+    <t>01:00:00</t>
+  </si>
+  <si>
+    <t>03:00:00</t>
+  </si>
+  <si>
+    <t>Macara</t>
+  </si>
+  <si>
+    <t>Gimnasia Mendoza</t>
+  </si>
+  <si>
+    <t>Deportes Temuco</t>
+  </si>
+  <si>
+    <t>Palestino</t>
+  </si>
+  <si>
+    <t>Necaxa</t>
+  </si>
+  <si>
+    <t>Pachuca</t>
+  </si>
+  <si>
+    <t>Univ Catolica (Ecu)</t>
+  </si>
+  <si>
+    <t>Talleres</t>
+  </si>
+  <si>
+    <t>Deportes Recoleta</t>
+  </si>
+  <si>
+    <t>Huachipato</t>
+  </si>
+  <si>
+    <t>Leon</t>
+  </si>
+  <si>
+    <t>Puebla</t>
+  </si>
+  <si>
+    <t>2026-08-16 00:24:53</t>
   </si>
 </sst>
 </file>
@@ -585,7 +654,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB1"/>
+  <dimension ref="A1:CB7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -830,6 +899,1458 @@
         <v>79</v>
       </c>
     </row>
+    <row r="2" spans="1:80">
+      <c r="A2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F2">
+        <v>1.01</v>
+      </c>
+      <c r="G2">
+        <v>1000</v>
+      </c>
+      <c r="H2">
+        <v>1.01</v>
+      </c>
+      <c r="I2">
+        <v>1000</v>
+      </c>
+      <c r="J2">
+        <v>1.01</v>
+      </c>
+      <c r="K2">
+        <v>1000</v>
+      </c>
+      <c r="L2">
+        <v>1.01</v>
+      </c>
+      <c r="M2">
+        <v>1.01</v>
+      </c>
+      <c r="N2">
+        <v>1.01</v>
+      </c>
+      <c r="O2">
+        <v>1.38</v>
+      </c>
+      <c r="P2">
+        <v>1.24</v>
+      </c>
+      <c r="Q2">
+        <v>1.01</v>
+      </c>
+      <c r="R2">
+        <v>1.18</v>
+      </c>
+      <c r="S2">
+        <v>1.01</v>
+      </c>
+      <c r="T2">
+        <v>1.01</v>
+      </c>
+      <c r="U2">
+        <v>1.01</v>
+      </c>
+      <c r="V2">
+        <v>1.01</v>
+      </c>
+      <c r="W2">
+        <v>1.01</v>
+      </c>
+      <c r="X2">
+        <v>1000</v>
+      </c>
+      <c r="Y2">
+        <v>1000</v>
+      </c>
+      <c r="Z2">
+        <v>1000</v>
+      </c>
+      <c r="AA2">
+        <v>1000</v>
+      </c>
+      <c r="AB2">
+        <v>1000</v>
+      </c>
+      <c r="AC2">
+        <v>1000</v>
+      </c>
+      <c r="AD2">
+        <v>1000</v>
+      </c>
+      <c r="AE2">
+        <v>1000</v>
+      </c>
+      <c r="AF2">
+        <v>1000</v>
+      </c>
+      <c r="AG2">
+        <v>1000</v>
+      </c>
+      <c r="AH2">
+        <v>1000</v>
+      </c>
+      <c r="AI2">
+        <v>1000</v>
+      </c>
+      <c r="AJ2">
+        <v>1000</v>
+      </c>
+      <c r="AK2">
+        <v>1000</v>
+      </c>
+      <c r="AL2">
+        <v>1000</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>1000</v>
+      </c>
+      <c r="AO2">
+        <v>1000</v>
+      </c>
+      <c r="AP2">
+        <v>1.01</v>
+      </c>
+      <c r="AQ2">
+        <v>1.01</v>
+      </c>
+      <c r="AR2">
+        <v>1.01</v>
+      </c>
+      <c r="AS2">
+        <v>1.01</v>
+      </c>
+      <c r="AT2">
+        <v>1.01</v>
+      </c>
+      <c r="AU2">
+        <v>1.01</v>
+      </c>
+      <c r="AV2">
+        <v>1.01</v>
+      </c>
+      <c r="AW2">
+        <v>1.01</v>
+      </c>
+      <c r="AX2">
+        <v>1.01</v>
+      </c>
+      <c r="AY2">
+        <v>1.01</v>
+      </c>
+      <c r="AZ2">
+        <v>1.01</v>
+      </c>
+      <c r="BA2">
+        <v>1.01</v>
+      </c>
+      <c r="BB2">
+        <v>1.01</v>
+      </c>
+      <c r="BC2">
+        <v>1.01</v>
+      </c>
+      <c r="BD2">
+        <v>1.01</v>
+      </c>
+      <c r="BE2">
+        <v>1.01</v>
+      </c>
+      <c r="BF2">
+        <v>1.01</v>
+      </c>
+      <c r="BG2">
+        <v>1.01</v>
+      </c>
+      <c r="BH2">
+        <v>1000</v>
+      </c>
+      <c r="BI2">
+        <v>1.01</v>
+      </c>
+      <c r="BJ2">
+        <v>1000</v>
+      </c>
+      <c r="BK2">
+        <v>1.01</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>1.01</v>
+      </c>
+      <c r="BN2">
+        <v>1000</v>
+      </c>
+      <c r="BO2">
+        <v>1.01</v>
+      </c>
+      <c r="BP2">
+        <v>1000</v>
+      </c>
+      <c r="BQ2">
+        <v>1.01</v>
+      </c>
+      <c r="BR2">
+        <v>1000</v>
+      </c>
+      <c r="BS2">
+        <v>1.01</v>
+      </c>
+      <c r="BT2">
+        <v>1000</v>
+      </c>
+      <c r="BU2">
+        <v>1.01</v>
+      </c>
+      <c r="BV2">
+        <v>1000</v>
+      </c>
+      <c r="BW2">
+        <v>1.01</v>
+      </c>
+      <c r="BX2">
+        <v>1000</v>
+      </c>
+      <c r="BY2">
+        <v>1.01</v>
+      </c>
+      <c r="BZ2">
+        <v>1000</v>
+      </c>
+      <c r="CA2">
+        <v>1.01</v>
+      </c>
+      <c r="CB2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="3" spans="1:80">
+      <c r="A3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E3" t="s">
+        <v>97</v>
+      </c>
+      <c r="F3">
+        <v>2.8</v>
+      </c>
+      <c r="G3">
+        <v>3.4</v>
+      </c>
+      <c r="H3">
+        <v>2.7</v>
+      </c>
+      <c r="I3">
+        <v>3.45</v>
+      </c>
+      <c r="J3">
+        <v>2.8</v>
+      </c>
+      <c r="K3">
+        <v>3.05</v>
+      </c>
+      <c r="L3">
+        <v>1.59</v>
+      </c>
+      <c r="M3">
+        <v>1.01</v>
+      </c>
+      <c r="N3">
+        <v>2.36</v>
+      </c>
+      <c r="O3">
+        <v>1.56</v>
+      </c>
+      <c r="P3">
+        <v>1.31</v>
+      </c>
+      <c r="Q3">
+        <v>2.96</v>
+      </c>
+      <c r="R3">
+        <v>1.12</v>
+      </c>
+      <c r="S3">
+        <v>6</v>
+      </c>
+      <c r="T3">
+        <v>1.01</v>
+      </c>
+      <c r="U3">
+        <v>1.01</v>
+      </c>
+      <c r="V3">
+        <v>1.41</v>
+      </c>
+      <c r="W3">
+        <v>1.42</v>
+      </c>
+      <c r="X3">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Y3">
+        <v>1000</v>
+      </c>
+      <c r="Z3">
+        <v>1000</v>
+      </c>
+      <c r="AA3">
+        <v>1000</v>
+      </c>
+      <c r="AB3">
+        <v>1000</v>
+      </c>
+      <c r="AC3">
+        <v>1000</v>
+      </c>
+      <c r="AD3">
+        <v>1000</v>
+      </c>
+      <c r="AE3">
+        <v>1000</v>
+      </c>
+      <c r="AF3">
+        <v>1000</v>
+      </c>
+      <c r="AG3">
+        <v>1000</v>
+      </c>
+      <c r="AH3">
+        <v>1000</v>
+      </c>
+      <c r="AI3">
+        <v>1000</v>
+      </c>
+      <c r="AJ3">
+        <v>1000</v>
+      </c>
+      <c r="AK3">
+        <v>1000</v>
+      </c>
+      <c r="AL3">
+        <v>1000</v>
+      </c>
+      <c r="AM3">
+        <v>1000</v>
+      </c>
+      <c r="AN3">
+        <v>1000</v>
+      </c>
+      <c r="AO3">
+        <v>1000</v>
+      </c>
+      <c r="AP3">
+        <v>4.6</v>
+      </c>
+      <c r="AQ3">
+        <v>1.12</v>
+      </c>
+      <c r="AR3">
+        <v>1.12</v>
+      </c>
+      <c r="AS3">
+        <v>1.12</v>
+      </c>
+      <c r="AT3">
+        <v>1.12</v>
+      </c>
+      <c r="AU3">
+        <v>1.12</v>
+      </c>
+      <c r="AV3">
+        <v>1.12</v>
+      </c>
+      <c r="AW3">
+        <v>1.12</v>
+      </c>
+      <c r="AX3">
+        <v>1.12</v>
+      </c>
+      <c r="AY3">
+        <v>1.12</v>
+      </c>
+      <c r="AZ3">
+        <v>1.12</v>
+      </c>
+      <c r="BA3">
+        <v>1.12</v>
+      </c>
+      <c r="BB3">
+        <v>1.12</v>
+      </c>
+      <c r="BC3">
+        <v>1.12</v>
+      </c>
+      <c r="BD3">
+        <v>1.12</v>
+      </c>
+      <c r="BE3">
+        <v>1.12</v>
+      </c>
+      <c r="BF3">
+        <v>1.12</v>
+      </c>
+      <c r="BG3">
+        <v>1.12</v>
+      </c>
+      <c r="BH3">
+        <v>1000</v>
+      </c>
+      <c r="BI3">
+        <v>1.01</v>
+      </c>
+      <c r="BJ3">
+        <v>1000</v>
+      </c>
+      <c r="BK3">
+        <v>1.01</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
+        <v>1.01</v>
+      </c>
+      <c r="BN3">
+        <v>1000</v>
+      </c>
+      <c r="BO3">
+        <v>1.01</v>
+      </c>
+      <c r="BP3">
+        <v>1000</v>
+      </c>
+      <c r="BQ3">
+        <v>1.01</v>
+      </c>
+      <c r="BR3">
+        <v>1000</v>
+      </c>
+      <c r="BS3">
+        <v>1.01</v>
+      </c>
+      <c r="BT3">
+        <v>1000</v>
+      </c>
+      <c r="BU3">
+        <v>1.01</v>
+      </c>
+      <c r="BV3">
+        <v>1000</v>
+      </c>
+      <c r="BW3">
+        <v>1.01</v>
+      </c>
+      <c r="BX3">
+        <v>1000</v>
+      </c>
+      <c r="BY3">
+        <v>1.01</v>
+      </c>
+      <c r="BZ3">
+        <v>1000</v>
+      </c>
+      <c r="CA3">
+        <v>1.01</v>
+      </c>
+      <c r="CB3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="4" spans="1:80">
+      <c r="A4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E4" t="s">
+        <v>98</v>
+      </c>
+      <c r="F4">
+        <v>2.06</v>
+      </c>
+      <c r="G4">
+        <v>2.4</v>
+      </c>
+      <c r="H4">
+        <v>3.15</v>
+      </c>
+      <c r="I4">
+        <v>4.1</v>
+      </c>
+      <c r="J4">
+        <v>3.35</v>
+      </c>
+      <c r="K4">
+        <v>5.1</v>
+      </c>
+      <c r="L4">
+        <v>1.01</v>
+      </c>
+      <c r="M4">
+        <v>1.01</v>
+      </c>
+      <c r="N4">
+        <v>3.6</v>
+      </c>
+      <c r="O4">
+        <v>1.01</v>
+      </c>
+      <c r="P4">
+        <v>1.98</v>
+      </c>
+      <c r="Q4">
+        <v>1.79</v>
+      </c>
+      <c r="R4">
+        <v>1.36</v>
+      </c>
+      <c r="S4">
+        <v>2.76</v>
+      </c>
+      <c r="T4">
+        <v>1.01</v>
+      </c>
+      <c r="U4">
+        <v>1.01</v>
+      </c>
+      <c r="V4">
+        <v>1.32</v>
+      </c>
+      <c r="W4">
+        <v>1.71</v>
+      </c>
+      <c r="X4">
+        <v>1000</v>
+      </c>
+      <c r="Y4">
+        <v>1000</v>
+      </c>
+      <c r="Z4">
+        <v>1000</v>
+      </c>
+      <c r="AA4">
+        <v>1000</v>
+      </c>
+      <c r="AB4">
+        <v>1000</v>
+      </c>
+      <c r="AC4">
+        <v>1000</v>
+      </c>
+      <c r="AD4">
+        <v>1000</v>
+      </c>
+      <c r="AE4">
+        <v>1000</v>
+      </c>
+      <c r="AF4">
+        <v>1000</v>
+      </c>
+      <c r="AG4">
+        <v>1000</v>
+      </c>
+      <c r="AH4">
+        <v>1000</v>
+      </c>
+      <c r="AI4">
+        <v>1000</v>
+      </c>
+      <c r="AJ4">
+        <v>1000</v>
+      </c>
+      <c r="AK4">
+        <v>1000</v>
+      </c>
+      <c r="AL4">
+        <v>1000</v>
+      </c>
+      <c r="AM4">
+        <v>1000</v>
+      </c>
+      <c r="AN4">
+        <v>1000</v>
+      </c>
+      <c r="AO4">
+        <v>1000</v>
+      </c>
+      <c r="AP4">
+        <v>1.01</v>
+      </c>
+      <c r="AQ4">
+        <v>1.01</v>
+      </c>
+      <c r="AR4">
+        <v>1.01</v>
+      </c>
+      <c r="AS4">
+        <v>1.01</v>
+      </c>
+      <c r="AT4">
+        <v>1.01</v>
+      </c>
+      <c r="AU4">
+        <v>1.01</v>
+      </c>
+      <c r="AV4">
+        <v>1.01</v>
+      </c>
+      <c r="AW4">
+        <v>1.01</v>
+      </c>
+      <c r="AX4">
+        <v>1.01</v>
+      </c>
+      <c r="AY4">
+        <v>1.01</v>
+      </c>
+      <c r="AZ4">
+        <v>1.01</v>
+      </c>
+      <c r="BA4">
+        <v>1.01</v>
+      </c>
+      <c r="BB4">
+        <v>1.01</v>
+      </c>
+      <c r="BC4">
+        <v>1.01</v>
+      </c>
+      <c r="BD4">
+        <v>1.01</v>
+      </c>
+      <c r="BE4">
+        <v>1.01</v>
+      </c>
+      <c r="BF4">
+        <v>1.01</v>
+      </c>
+      <c r="BG4">
+        <v>1.01</v>
+      </c>
+      <c r="BH4">
+        <v>4.4</v>
+      </c>
+      <c r="BI4">
+        <v>2.72</v>
+      </c>
+      <c r="BJ4">
+        <v>1000</v>
+      </c>
+      <c r="BK4">
+        <v>1.3</v>
+      </c>
+      <c r="BL4">
+        <v>1000</v>
+      </c>
+      <c r="BM4">
+        <v>1.3</v>
+      </c>
+      <c r="BN4">
+        <v>1000</v>
+      </c>
+      <c r="BO4">
+        <v>1.3</v>
+      </c>
+      <c r="BP4">
+        <v>1000</v>
+      </c>
+      <c r="BQ4">
+        <v>1.3</v>
+      </c>
+      <c r="BR4">
+        <v>1000</v>
+      </c>
+      <c r="BS4">
+        <v>1.3</v>
+      </c>
+      <c r="BT4">
+        <v>1000</v>
+      </c>
+      <c r="BU4">
+        <v>1.3</v>
+      </c>
+      <c r="BV4">
+        <v>1000</v>
+      </c>
+      <c r="BW4">
+        <v>1.3</v>
+      </c>
+      <c r="BX4">
+        <v>1000</v>
+      </c>
+      <c r="BY4">
+        <v>1.3</v>
+      </c>
+      <c r="BZ4">
+        <v>1000</v>
+      </c>
+      <c r="CA4">
+        <v>1.3</v>
+      </c>
+      <c r="CB4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="5" spans="1:80">
+      <c r="A5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C5" t="s">
+        <v>87</v>
+      </c>
+      <c r="D5" t="s">
+        <v>93</v>
+      </c>
+      <c r="E5" t="s">
+        <v>99</v>
+      </c>
+      <c r="F5">
+        <v>1.77</v>
+      </c>
+      <c r="G5">
+        <v>1.93</v>
+      </c>
+      <c r="H5">
+        <v>4.4</v>
+      </c>
+      <c r="I5">
+        <v>5.1</v>
+      </c>
+      <c r="J5">
+        <v>3.85</v>
+      </c>
+      <c r="K5">
+        <v>4.8</v>
+      </c>
+      <c r="L5">
+        <v>1.31</v>
+      </c>
+      <c r="M5">
+        <v>1.05</v>
+      </c>
+      <c r="N5">
+        <v>4.3</v>
+      </c>
+      <c r="O5">
+        <v>1.25</v>
+      </c>
+      <c r="P5">
+        <v>2.12</v>
+      </c>
+      <c r="Q5">
+        <v>1.73</v>
+      </c>
+      <c r="R5">
+        <v>1.43</v>
+      </c>
+      <c r="S5">
+        <v>2.9</v>
+      </c>
+      <c r="T5">
+        <v>1.63</v>
+      </c>
+      <c r="U5">
+        <v>2.18</v>
+      </c>
+      <c r="V5">
+        <v>1.24</v>
+      </c>
+      <c r="W5">
+        <v>2.08</v>
+      </c>
+      <c r="X5">
+        <v>21</v>
+      </c>
+      <c r="Y5">
+        <v>19.5</v>
+      </c>
+      <c r="Z5">
+        <v>42</v>
+      </c>
+      <c r="AA5">
+        <v>120</v>
+      </c>
+      <c r="AB5">
+        <v>12</v>
+      </c>
+      <c r="AC5">
+        <v>9.6</v>
+      </c>
+      <c r="AD5">
+        <v>21</v>
+      </c>
+      <c r="AE5">
+        <v>65</v>
+      </c>
+      <c r="AF5">
+        <v>14.5</v>
+      </c>
+      <c r="AG5">
+        <v>12</v>
+      </c>
+      <c r="AH5">
+        <v>19</v>
+      </c>
+      <c r="AI5">
+        <v>65</v>
+      </c>
+      <c r="AJ5">
+        <v>22</v>
+      </c>
+      <c r="AK5">
+        <v>19.5</v>
+      </c>
+      <c r="AL5">
+        <v>34</v>
+      </c>
+      <c r="AM5">
+        <v>100</v>
+      </c>
+      <c r="AN5">
+        <v>12.5</v>
+      </c>
+      <c r="AO5">
+        <v>65</v>
+      </c>
+      <c r="AP5">
+        <v>14</v>
+      </c>
+      <c r="AQ5">
+        <v>14</v>
+      </c>
+      <c r="AR5">
+        <v>1.01</v>
+      </c>
+      <c r="AS5">
+        <v>1.01</v>
+      </c>
+      <c r="AT5">
+        <v>8</v>
+      </c>
+      <c r="AU5">
+        <v>7.8</v>
+      </c>
+      <c r="AV5">
+        <v>14</v>
+      </c>
+      <c r="AW5">
+        <v>1.01</v>
+      </c>
+      <c r="AX5">
+        <v>9.4</v>
+      </c>
+      <c r="AY5">
+        <v>8</v>
+      </c>
+      <c r="AZ5">
+        <v>15</v>
+      </c>
+      <c r="BA5">
+        <v>1.01</v>
+      </c>
+      <c r="BB5">
+        <v>15.5</v>
+      </c>
+      <c r="BC5">
+        <v>15.5</v>
+      </c>
+      <c r="BD5">
+        <v>21</v>
+      </c>
+      <c r="BE5">
+        <v>1.01</v>
+      </c>
+      <c r="BF5">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BG5">
+        <v>1.01</v>
+      </c>
+      <c r="BH5">
+        <v>4.3</v>
+      </c>
+      <c r="BI5">
+        <v>3.1</v>
+      </c>
+      <c r="BJ5">
+        <v>11</v>
+      </c>
+      <c r="BK5">
+        <v>3.7</v>
+      </c>
+      <c r="BL5">
+        <v>1000</v>
+      </c>
+      <c r="BM5">
+        <v>5.4</v>
+      </c>
+      <c r="BN5">
+        <v>5.3</v>
+      </c>
+      <c r="BO5">
+        <v>3.75</v>
+      </c>
+      <c r="BP5">
+        <v>14.5</v>
+      </c>
+      <c r="BQ5">
+        <v>4</v>
+      </c>
+      <c r="BR5">
+        <v>28</v>
+      </c>
+      <c r="BS5">
+        <v>4.7</v>
+      </c>
+      <c r="BT5">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BU5">
+        <v>3.5</v>
+      </c>
+      <c r="BV5">
+        <v>42</v>
+      </c>
+      <c r="BW5">
+        <v>5</v>
+      </c>
+      <c r="BX5">
+        <v>48</v>
+      </c>
+      <c r="BY5">
+        <v>5</v>
+      </c>
+      <c r="BZ5">
+        <v>22</v>
+      </c>
+      <c r="CA5">
+        <v>4.5</v>
+      </c>
+      <c r="CB5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="6" spans="1:80">
+      <c r="A6" t="s">
+        <v>84</v>
+      </c>
+      <c r="B6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C6" t="s">
+        <v>88</v>
+      </c>
+      <c r="D6" t="s">
+        <v>94</v>
+      </c>
+      <c r="E6" t="s">
+        <v>100</v>
+      </c>
+      <c r="F6">
+        <v>2.34</v>
+      </c>
+      <c r="G6">
+        <v>2.46</v>
+      </c>
+      <c r="H6">
+        <v>3</v>
+      </c>
+      <c r="I6">
+        <v>3.3</v>
+      </c>
+      <c r="J6">
+        <v>3.7</v>
+      </c>
+      <c r="K6">
+        <v>3.95</v>
+      </c>
+      <c r="L6">
+        <v>1.01</v>
+      </c>
+      <c r="M6">
+        <v>1.05</v>
+      </c>
+      <c r="N6">
+        <v>4.5</v>
+      </c>
+      <c r="O6">
+        <v>1.25</v>
+      </c>
+      <c r="P6">
+        <v>2.2</v>
+      </c>
+      <c r="Q6">
+        <v>1.74</v>
+      </c>
+      <c r="R6">
+        <v>1.47</v>
+      </c>
+      <c r="S6">
+        <v>2.84</v>
+      </c>
+      <c r="T6">
+        <v>1.52</v>
+      </c>
+      <c r="U6">
+        <v>2.38</v>
+      </c>
+      <c r="V6">
+        <v>1.44</v>
+      </c>
+      <c r="W6">
+        <v>1.68</v>
+      </c>
+      <c r="X6">
+        <v>23</v>
+      </c>
+      <c r="Y6">
+        <v>18.5</v>
+      </c>
+      <c r="Z6">
+        <v>29</v>
+      </c>
+      <c r="AA6">
+        <v>65</v>
+      </c>
+      <c r="AB6">
+        <v>15</v>
+      </c>
+      <c r="AC6">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD6">
+        <v>17</v>
+      </c>
+      <c r="AE6">
+        <v>40</v>
+      </c>
+      <c r="AF6">
+        <v>21</v>
+      </c>
+      <c r="AG6">
+        <v>14</v>
+      </c>
+      <c r="AH6">
+        <v>19</v>
+      </c>
+      <c r="AI6">
+        <v>48</v>
+      </c>
+      <c r="AJ6">
+        <v>38</v>
+      </c>
+      <c r="AK6">
+        <v>29</v>
+      </c>
+      <c r="AL6">
+        <v>40</v>
+      </c>
+      <c r="AM6">
+        <v>85</v>
+      </c>
+      <c r="AN6">
+        <v>18.5</v>
+      </c>
+      <c r="AO6">
+        <v>30</v>
+      </c>
+      <c r="AP6">
+        <v>16.5</v>
+      </c>
+      <c r="AQ6">
+        <v>13</v>
+      </c>
+      <c r="AR6">
+        <v>20</v>
+      </c>
+      <c r="AS6">
+        <v>4.4</v>
+      </c>
+      <c r="AT6">
+        <v>11</v>
+      </c>
+      <c r="AU6">
+        <v>7.8</v>
+      </c>
+      <c r="AV6">
+        <v>12</v>
+      </c>
+      <c r="AW6">
+        <v>4.2</v>
+      </c>
+      <c r="AX6">
+        <v>14.5</v>
+      </c>
+      <c r="AY6">
+        <v>10</v>
+      </c>
+      <c r="AZ6">
+        <v>13.5</v>
+      </c>
+      <c r="BA6">
+        <v>4.3</v>
+      </c>
+      <c r="BB6">
+        <v>4.2</v>
+      </c>
+      <c r="BC6">
+        <v>20</v>
+      </c>
+      <c r="BD6">
+        <v>4.2</v>
+      </c>
+      <c r="BE6">
+        <v>4.4</v>
+      </c>
+      <c r="BF6">
+        <v>11</v>
+      </c>
+      <c r="BG6">
+        <v>18</v>
+      </c>
+      <c r="BH6">
+        <v>1000</v>
+      </c>
+      <c r="BI6">
+        <v>1.01</v>
+      </c>
+      <c r="BJ6">
+        <v>1000</v>
+      </c>
+      <c r="BK6">
+        <v>1.01</v>
+      </c>
+      <c r="BL6">
+        <v>1000</v>
+      </c>
+      <c r="BM6">
+        <v>1.01</v>
+      </c>
+      <c r="BN6">
+        <v>1000</v>
+      </c>
+      <c r="BO6">
+        <v>1.01</v>
+      </c>
+      <c r="BP6">
+        <v>1000</v>
+      </c>
+      <c r="BQ6">
+        <v>1.01</v>
+      </c>
+      <c r="BR6">
+        <v>1000</v>
+      </c>
+      <c r="BS6">
+        <v>1.01</v>
+      </c>
+      <c r="BT6">
+        <v>1000</v>
+      </c>
+      <c r="BU6">
+        <v>1.01</v>
+      </c>
+      <c r="BV6">
+        <v>1000</v>
+      </c>
+      <c r="BW6">
+        <v>1.01</v>
+      </c>
+      <c r="BX6">
+        <v>1000</v>
+      </c>
+      <c r="BY6">
+        <v>1.01</v>
+      </c>
+      <c r="BZ6">
+        <v>1000</v>
+      </c>
+      <c r="CA6">
+        <v>1.01</v>
+      </c>
+      <c r="CB6" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="7" spans="1:80">
+      <c r="A7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D7" t="s">
+        <v>95</v>
+      </c>
+      <c r="E7" t="s">
+        <v>101</v>
+      </c>
+      <c r="F7">
+        <v>1.54</v>
+      </c>
+      <c r="G7">
+        <v>1.55</v>
+      </c>
+      <c r="H7">
+        <v>6.6</v>
+      </c>
+      <c r="I7">
+        <v>7.8</v>
+      </c>
+      <c r="J7">
+        <v>4.5</v>
+      </c>
+      <c r="K7">
+        <v>5.1</v>
+      </c>
+      <c r="L7">
+        <v>1.29</v>
+      </c>
+      <c r="M7">
+        <v>1.01</v>
+      </c>
+      <c r="N7">
+        <v>2.36</v>
+      </c>
+      <c r="O7">
+        <v>1.21</v>
+      </c>
+      <c r="P7">
+        <v>2.02</v>
+      </c>
+      <c r="Q7">
+        <v>1.6</v>
+      </c>
+      <c r="R7">
+        <v>1.4</v>
+      </c>
+      <c r="S7">
+        <v>2.42</v>
+      </c>
+      <c r="T7">
+        <v>1.01</v>
+      </c>
+      <c r="U7">
+        <v>1.01</v>
+      </c>
+      <c r="V7">
+        <v>1.14</v>
+      </c>
+      <c r="W7">
+        <v>2.8</v>
+      </c>
+      <c r="X7">
+        <v>1000</v>
+      </c>
+      <c r="Y7">
+        <v>1000</v>
+      </c>
+      <c r="Z7">
+        <v>1000</v>
+      </c>
+      <c r="AA7">
+        <v>1000</v>
+      </c>
+      <c r="AB7">
+        <v>1000</v>
+      </c>
+      <c r="AC7">
+        <v>1000</v>
+      </c>
+      <c r="AD7">
+        <v>1000</v>
+      </c>
+      <c r="AE7">
+        <v>1000</v>
+      </c>
+      <c r="AF7">
+        <v>1000</v>
+      </c>
+      <c r="AG7">
+        <v>1000</v>
+      </c>
+      <c r="AH7">
+        <v>1000</v>
+      </c>
+      <c r="AI7">
+        <v>1000</v>
+      </c>
+      <c r="AJ7">
+        <v>1000</v>
+      </c>
+      <c r="AK7">
+        <v>1000</v>
+      </c>
+      <c r="AL7">
+        <v>1000</v>
+      </c>
+      <c r="AM7">
+        <v>1000</v>
+      </c>
+      <c r="AN7">
+        <v>1000</v>
+      </c>
+      <c r="AO7">
+        <v>1000</v>
+      </c>
+      <c r="AP7">
+        <v>16.5</v>
+      </c>
+      <c r="AQ7">
+        <v>18.5</v>
+      </c>
+      <c r="AR7">
+        <v>38</v>
+      </c>
+      <c r="AS7">
+        <v>40</v>
+      </c>
+      <c r="AT7">
+        <v>7.6</v>
+      </c>
+      <c r="AU7">
+        <v>8.6</v>
+      </c>
+      <c r="AV7">
+        <v>19</v>
+      </c>
+      <c r="AW7">
+        <v>40</v>
+      </c>
+      <c r="AX7">
+        <v>7.6</v>
+      </c>
+      <c r="AY7">
+        <v>8.6</v>
+      </c>
+      <c r="AZ7">
+        <v>16.5</v>
+      </c>
+      <c r="BA7">
+        <v>40</v>
+      </c>
+      <c r="BB7">
+        <v>10</v>
+      </c>
+      <c r="BC7">
+        <v>11</v>
+      </c>
+      <c r="BD7">
+        <v>24</v>
+      </c>
+      <c r="BE7">
+        <v>40</v>
+      </c>
+      <c r="BF7">
+        <v>1.01</v>
+      </c>
+      <c r="BG7">
+        <v>1.01</v>
+      </c>
+      <c r="BH7">
+        <v>1000</v>
+      </c>
+      <c r="BI7">
+        <v>1.01</v>
+      </c>
+      <c r="BJ7">
+        <v>1000</v>
+      </c>
+      <c r="BK7">
+        <v>1.01</v>
+      </c>
+      <c r="BL7">
+        <v>1000</v>
+      </c>
+      <c r="BM7">
+        <v>1.01</v>
+      </c>
+      <c r="BN7">
+        <v>1000</v>
+      </c>
+      <c r="BO7">
+        <v>1.01</v>
+      </c>
+      <c r="BP7">
+        <v>1000</v>
+      </c>
+      <c r="BQ7">
+        <v>1.01</v>
+      </c>
+      <c r="BR7">
+        <v>1000</v>
+      </c>
+      <c r="BS7">
+        <v>1.01</v>
+      </c>
+      <c r="BT7">
+        <v>1000</v>
+      </c>
+      <c r="BU7">
+        <v>1.01</v>
+      </c>
+      <c r="BV7">
+        <v>1000</v>
+      </c>
+      <c r="BW7">
+        <v>1.01</v>
+      </c>
+      <c r="BX7">
+        <v>1000</v>
+      </c>
+      <c r="BY7">
+        <v>1.01</v>
+      </c>
+      <c r="BZ7">
+        <v>1000</v>
+      </c>
+      <c r="CA7">
+        <v>1.01</v>
+      </c>
+      <c r="CB7" t="s">
+        <v>102</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-18.xlsx
@@ -322,7 +322,7 @@
     <t>Puebla</t>
   </si>
   <si>
-    <t>2026-08-16 00:24:53</t>
+    <t>2026-08-16 02:41:26</t>
   </si>
 </sst>
 </file>
@@ -943,7 +943,7 @@
         <v>1.01</v>
       </c>
       <c r="O2">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P2">
         <v>1.24</v>
@@ -1158,22 +1158,22 @@
         <v>97</v>
       </c>
       <c r="F3">
-        <v>2.8</v>
+        <v>2.96</v>
       </c>
       <c r="G3">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="H3">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="I3">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="J3">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="K3">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="L3">
         <v>1.59</v>
@@ -1182,16 +1182,16 @@
         <v>1.01</v>
       </c>
       <c r="N3">
-        <v>2.36</v>
+        <v>1.98</v>
       </c>
       <c r="O3">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="P3">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="Q3">
-        <v>2.96</v>
+        <v>2.78</v>
       </c>
       <c r="R3">
         <v>1.12</v>
@@ -1206,52 +1206,52 @@
         <v>1.01</v>
       </c>
       <c r="V3">
+        <v>1.46</v>
+      </c>
+      <c r="W3">
         <v>1.41</v>
-      </c>
-      <c r="W3">
-        <v>1.42</v>
       </c>
       <c r="X3">
         <v>9.199999999999999</v>
       </c>
       <c r="Y3">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z3">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AA3">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB3">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC3">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD3">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AE3">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF3">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AG3">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AH3">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI3">
         <v>1000</v>
       </c>
       <c r="AJ3">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AK3">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AL3">
         <v>1000</v>
@@ -1260,64 +1260,64 @@
         <v>1000</v>
       </c>
       <c r="AN3">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AO3">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AP3">
         <v>4.6</v>
       </c>
       <c r="AQ3">
-        <v>1.12</v>
+        <v>6.4</v>
       </c>
       <c r="AR3">
-        <v>1.12</v>
+        <v>13</v>
       </c>
       <c r="AS3">
-        <v>1.12</v>
+        <v>3</v>
       </c>
       <c r="AT3">
-        <v>1.12</v>
+        <v>6.8</v>
       </c>
       <c r="AU3">
-        <v>1.12</v>
+        <v>5.8</v>
       </c>
       <c r="AV3">
-        <v>1.12</v>
+        <v>10.5</v>
       </c>
       <c r="AW3">
-        <v>1.12</v>
+        <v>3</v>
       </c>
       <c r="AX3">
-        <v>1.12</v>
+        <v>14</v>
       </c>
       <c r="AY3">
-        <v>1.12</v>
+        <v>11</v>
       </c>
       <c r="AZ3">
-        <v>1.12</v>
+        <v>19</v>
       </c>
       <c r="BA3">
-        <v>1.12</v>
+        <v>3.1</v>
       </c>
       <c r="BB3">
-        <v>1.12</v>
+        <v>3</v>
       </c>
       <c r="BC3">
-        <v>1.12</v>
+        <v>3</v>
       </c>
       <c r="BD3">
-        <v>1.12</v>
+        <v>3.1</v>
       </c>
       <c r="BE3">
-        <v>1.12</v>
+        <v>3.1</v>
       </c>
       <c r="BF3">
-        <v>1.12</v>
+        <v>3.05</v>
       </c>
       <c r="BG3">
-        <v>1.12</v>
+        <v>3</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1400,22 +1400,22 @@
         <v>98</v>
       </c>
       <c r="F4">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="G4">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="H4">
         <v>3.15</v>
       </c>
       <c r="I4">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="J4">
         <v>3.35</v>
       </c>
       <c r="K4">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="L4">
         <v>1.01</v>
@@ -1433,13 +1433,13 @@
         <v>1.98</v>
       </c>
       <c r="Q4">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="R4">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="S4">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="T4">
         <v>1.01</v>
@@ -1448,10 +1448,10 @@
         <v>1.01</v>
       </c>
       <c r="V4">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W4">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="X4">
         <v>1000</v>
@@ -1666,13 +1666,13 @@
         <v>1.05</v>
       </c>
       <c r="N5">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="O5">
         <v>1.25</v>
       </c>
       <c r="P5">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="Q5">
         <v>1.73</v>
@@ -1681,13 +1681,13 @@
         <v>1.43</v>
       </c>
       <c r="S5">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="T5">
         <v>1.63</v>
       </c>
       <c r="U5">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V5">
         <v>1.24</v>
@@ -1893,7 +1893,7 @@
         <v>3</v>
       </c>
       <c r="I6">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J6">
         <v>3.7</v>
@@ -1920,7 +1920,7 @@
         <v>1.74</v>
       </c>
       <c r="R6">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S6">
         <v>2.84</v>
@@ -1932,7 +1932,7 @@
         <v>2.38</v>
       </c>
       <c r="V6">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W6">
         <v>1.68</v>
@@ -1944,10 +1944,10 @@
         <v>18.5</v>
       </c>
       <c r="Z6">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AA6">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB6">
         <v>15</v>
@@ -1956,7 +1956,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD6">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE6">
         <v>40</v>
@@ -1971,7 +1971,7 @@
         <v>19</v>
       </c>
       <c r="AI6">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ6">
         <v>38</v>
@@ -1989,7 +1989,7 @@
         <v>18.5</v>
       </c>
       <c r="AO6">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AP6">
         <v>16.5</v>
@@ -2001,7 +2001,7 @@
         <v>20</v>
       </c>
       <c r="AS6">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AT6">
         <v>11</v>
@@ -2013,7 +2013,7 @@
         <v>12</v>
       </c>
       <c r="AW6">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AX6">
         <v>14.5</v>
@@ -2025,19 +2025,19 @@
         <v>13.5</v>
       </c>
       <c r="BA6">
+        <v>4.4</v>
+      </c>
+      <c r="BB6">
         <v>4.3</v>
-      </c>
-      <c r="BB6">
-        <v>4.2</v>
       </c>
       <c r="BC6">
         <v>20</v>
       </c>
       <c r="BD6">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BE6">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BF6">
         <v>11</v>
@@ -2144,7 +2144,7 @@
         <v>5.1</v>
       </c>
       <c r="L7">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="M7">
         <v>1.01</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-18.xlsx
@@ -322,7 +322,7 @@
     <t>Puebla</t>
   </si>
   <si>
-    <t>2026-08-16 02:41:26</t>
+    <t>2026-08-16 04:57:44</t>
   </si>
 </sst>
 </file>
@@ -916,46 +916,46 @@
         <v>96</v>
       </c>
       <c r="F2">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="G2">
         <v>1000</v>
       </c>
       <c r="H2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="I2">
-        <v>1000</v>
+        <v>2.66</v>
       </c>
       <c r="J2">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="K2">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="L2">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M2">
         <v>1.01</v>
       </c>
       <c r="N2">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="O2">
         <v>1.39</v>
       </c>
       <c r="P2">
-        <v>1.24</v>
+        <v>1.58</v>
       </c>
       <c r="Q2">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="R2">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="S2">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="T2">
         <v>1.01</v>
@@ -967,7 +967,7 @@
         <v>1.01</v>
       </c>
       <c r="W2">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="X2">
         <v>1000</v>
@@ -1164,7 +1164,7 @@
         <v>3.45</v>
       </c>
       <c r="H3">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="I3">
         <v>3.2</v>
@@ -1173,7 +1173,7 @@
         <v>2.82</v>
       </c>
       <c r="K3">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="L3">
         <v>1.59</v>
@@ -1182,19 +1182,19 @@
         <v>1.01</v>
       </c>
       <c r="N3">
-        <v>1.98</v>
+        <v>2.38</v>
       </c>
       <c r="O3">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="P3">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="Q3">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="R3">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S3">
         <v>6</v>
@@ -1209,7 +1209,7 @@
         <v>1.46</v>
       </c>
       <c r="W3">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="X3">
         <v>9.199999999999999</v>
@@ -1654,10 +1654,10 @@
         <v>5.1</v>
       </c>
       <c r="J5">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="K5">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="L5">
         <v>1.31</v>
@@ -1672,10 +1672,10 @@
         <v>1.25</v>
       </c>
       <c r="P5">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="Q5">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="R5">
         <v>1.43</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-18.xlsx
@@ -322,7 +322,7 @@
     <t>Puebla</t>
   </si>
   <si>
-    <t>2026-08-16 04:57:44</t>
+    <t>2026-08-16 07:14:29</t>
   </si>
 </sst>
 </file>
@@ -916,22 +916,22 @@
         <v>96</v>
       </c>
       <c r="F2">
-        <v>1.62</v>
+        <v>3.45</v>
       </c>
       <c r="G2">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="H2">
-        <v>1.04</v>
+        <v>2.16</v>
       </c>
       <c r="I2">
-        <v>2.66</v>
+        <v>2.44</v>
       </c>
       <c r="J2">
-        <v>1.6</v>
+        <v>3.15</v>
       </c>
       <c r="K2">
-        <v>500</v>
+        <v>4.1</v>
       </c>
       <c r="L2">
         <v>1.36</v>
@@ -940,16 +940,16 @@
         <v>1.01</v>
       </c>
       <c r="N2">
-        <v>1.02</v>
+        <v>3.05</v>
       </c>
       <c r="O2">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="P2">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="Q2">
-        <v>1.97</v>
+        <v>2.12</v>
       </c>
       <c r="R2">
         <v>1.22</v>
@@ -967,115 +967,115 @@
         <v>1.01</v>
       </c>
       <c r="W2">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="X2">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y2">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z2">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AA2">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AB2">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AC2">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD2">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE2">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF2">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AG2">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AH2">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI2">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ2">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AK2">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL2">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM2">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN2">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AO2">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AP2">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AQ2">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AR2">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AS2">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="AT2">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AU2">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV2">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AW2">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AX2">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AY2">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AZ2">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BA2">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BB2">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BC2">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BD2">
-        <v>1.01</v>
+        <v>44</v>
       </c>
       <c r="BE2">
-        <v>1.01</v>
+        <v>85</v>
       </c>
       <c r="BF2">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="BG2">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1161,10 +1161,10 @@
         <v>2.96</v>
       </c>
       <c r="G3">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="H3">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="I3">
         <v>3.2</v>
@@ -1173,7 +1173,7 @@
         <v>2.82</v>
       </c>
       <c r="K3">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="L3">
         <v>1.59</v>
@@ -1182,19 +1182,19 @@
         <v>1.01</v>
       </c>
       <c r="N3">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="O3">
         <v>1.6</v>
       </c>
       <c r="P3">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="Q3">
-        <v>2.76</v>
+        <v>2.66</v>
       </c>
       <c r="R3">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="S3">
         <v>6</v>
@@ -1209,49 +1209,49 @@
         <v>1.46</v>
       </c>
       <c r="W3">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="X3">
         <v>9.199999999999999</v>
       </c>
       <c r="Y3">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Z3">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AA3">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AB3">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AC3">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AD3">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AE3">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AF3">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AG3">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AH3">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AI3">
         <v>1000</v>
       </c>
       <c r="AJ3">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AK3">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AL3">
         <v>1000</v>
@@ -1260,64 +1260,64 @@
         <v>1000</v>
       </c>
       <c r="AN3">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AO3">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AP3">
         <v>4.6</v>
       </c>
       <c r="AQ3">
-        <v>6.4</v>
+        <v>1.12</v>
       </c>
       <c r="AR3">
-        <v>13</v>
+        <v>1.12</v>
       </c>
       <c r="AS3">
-        <v>3</v>
+        <v>1.12</v>
       </c>
       <c r="AT3">
-        <v>6.8</v>
+        <v>1.12</v>
       </c>
       <c r="AU3">
-        <v>5.8</v>
+        <v>1.12</v>
       </c>
       <c r="AV3">
-        <v>10.5</v>
+        <v>1.12</v>
       </c>
       <c r="AW3">
-        <v>3</v>
+        <v>1.12</v>
       </c>
       <c r="AX3">
-        <v>14</v>
+        <v>1.12</v>
       </c>
       <c r="AY3">
-        <v>11</v>
+        <v>1.12</v>
       </c>
       <c r="AZ3">
-        <v>19</v>
+        <v>1.12</v>
       </c>
       <c r="BA3">
-        <v>3.1</v>
+        <v>1.12</v>
       </c>
       <c r="BB3">
-        <v>3</v>
+        <v>1.12</v>
       </c>
       <c r="BC3">
-        <v>3</v>
+        <v>1.12</v>
       </c>
       <c r="BD3">
-        <v>3.1</v>
+        <v>1.12</v>
       </c>
       <c r="BE3">
-        <v>3.1</v>
+        <v>1.12</v>
       </c>
       <c r="BF3">
-        <v>3.05</v>
+        <v>1.12</v>
       </c>
       <c r="BG3">
-        <v>3</v>
+        <v>1.12</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1412,7 +1412,7 @@
         <v>4.3</v>
       </c>
       <c r="J4">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K4">
         <v>5.5</v>
@@ -1654,7 +1654,7 @@
         <v>5.1</v>
       </c>
       <c r="J5">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K5">
         <v>4.4</v>
@@ -1666,16 +1666,16 @@
         <v>1.05</v>
       </c>
       <c r="N5">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O5">
         <v>1.25</v>
       </c>
       <c r="P5">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="Q5">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="R5">
         <v>1.43</v>
@@ -1884,22 +1884,22 @@
         <v>100</v>
       </c>
       <c r="F6">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="G6">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="H6">
+        <v>2.96</v>
+      </c>
+      <c r="I6">
         <v>3</v>
       </c>
-      <c r="I6">
-        <v>3.25</v>
-      </c>
       <c r="J6">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K6">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L6">
         <v>1.01</v>
@@ -1914,7 +1914,7 @@
         <v>1.25</v>
       </c>
       <c r="P6">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q6">
         <v>1.74</v>
@@ -1932,34 +1932,34 @@
         <v>2.38</v>
       </c>
       <c r="V6">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W6">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="X6">
         <v>23</v>
       </c>
       <c r="Y6">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="Z6">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AA6">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB6">
         <v>15</v>
       </c>
       <c r="AC6">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD6">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE6">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AF6">
         <v>21</v>
@@ -1971,7 +1971,7 @@
         <v>19</v>
       </c>
       <c r="AI6">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ6">
         <v>38</v>
@@ -1989,19 +1989,19 @@
         <v>18.5</v>
       </c>
       <c r="AO6">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AP6">
         <v>16.5</v>
       </c>
       <c r="AQ6">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR6">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AS6">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AT6">
         <v>11</v>
@@ -2010,10 +2010,10 @@
         <v>7.8</v>
       </c>
       <c r="AV6">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AW6">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AX6">
         <v>14.5</v>
@@ -2025,22 +2025,22 @@
         <v>13.5</v>
       </c>
       <c r="BA6">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BB6">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BC6">
         <v>20</v>
       </c>
       <c r="BD6">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BE6">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BF6">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BG6">
         <v>18</v>
@@ -2132,13 +2132,13 @@
         <v>1.55</v>
       </c>
       <c r="H7">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="I7">
-        <v>7.8</v>
+        <v>11</v>
       </c>
       <c r="J7">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="K7">
         <v>5.1</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-18.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="107">
   <si>
     <t>League</t>
   </si>
@@ -271,6 +271,9 @@
     <t>Mexican Liga MX</t>
   </si>
   <si>
+    <t>Chinese Super League</t>
+  </si>
+  <si>
     <t>2026-08-18</t>
   </si>
   <si>
@@ -286,6 +289,9 @@
     <t>03:00:00</t>
   </si>
   <si>
+    <t>11:35:00</t>
+  </si>
+  <si>
     <t>Macara</t>
   </si>
   <si>
@@ -304,6 +310,9 @@
     <t>Pachuca</t>
   </si>
   <si>
+    <t>Shanghai Shenhua</t>
+  </si>
+  <si>
     <t>Univ Catolica (Ecu)</t>
   </si>
   <si>
@@ -322,7 +331,10 @@
     <t>Puebla</t>
   </si>
   <si>
-    <t>2026-08-16 07:14:29</t>
+    <t>Beijing Guoan</t>
+  </si>
+  <si>
+    <t>2026-08-16 09:30:03</t>
   </si>
 </sst>
 </file>
@@ -654,7 +666,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB7"/>
+  <dimension ref="A1:CB8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -904,22 +916,22 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F2">
         <v>3.45</v>
       </c>
       <c r="G2">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="H2">
         <v>2.16</v>
@@ -928,13 +940,13 @@
         <v>2.44</v>
       </c>
       <c r="J2">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K2">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="L2">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M2">
         <v>1.01</v>
@@ -943,10 +955,10 @@
         <v>3.05</v>
       </c>
       <c r="O2">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="P2">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q2">
         <v>2.12</v>
@@ -958,10 +970,10 @@
         <v>3.35</v>
       </c>
       <c r="T2">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U2">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V2">
         <v>1.01</v>
@@ -1033,7 +1045,7 @@
         <v>10</v>
       </c>
       <c r="AS2">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="AT2">
         <v>9</v>
@@ -1057,22 +1069,22 @@
         <v>14</v>
       </c>
       <c r="BA2">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BB2">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BC2">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BD2">
-        <v>44</v>
+        <v>1.01</v>
       </c>
       <c r="BE2">
-        <v>85</v>
+        <v>1.01</v>
       </c>
       <c r="BF2">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BG2">
         <v>16.5</v>
@@ -1081,64 +1093,64 @@
         <v>1000</v>
       </c>
       <c r="BI2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ2">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BK2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN2">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BO2">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BP2">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BQ2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT2">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU2">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BV2">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BW2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ2">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="CA2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1146,16 +1158,16 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="F3">
         <v>2.96</v>
@@ -1164,10 +1176,10 @@
         <v>3.4</v>
       </c>
       <c r="H3">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="I3">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="J3">
         <v>2.82</v>
@@ -1182,16 +1194,16 @@
         <v>1.01</v>
       </c>
       <c r="N3">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="O3">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="P3">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="Q3">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="R3">
         <v>1.12</v>
@@ -1200,13 +1212,13 @@
         <v>6</v>
       </c>
       <c r="T3">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U3">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="V3">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W3">
         <v>1.42</v>
@@ -1323,64 +1335,64 @@
         <v>1000</v>
       </c>
       <c r="BI3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ3">
         <v>1000</v>
       </c>
       <c r="BK3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN3">
         <v>1000</v>
       </c>
       <c r="BO3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP3">
         <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT3">
         <v>1000</v>
       </c>
       <c r="BU3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB3" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1388,25 +1400,25 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E4" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="G4">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="H4">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="I4">
         <v>4.3</v>
@@ -1415,22 +1427,22 @@
         <v>3.45</v>
       </c>
       <c r="K4">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="L4">
         <v>1.01</v>
       </c>
       <c r="M4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N4">
         <v>3.6</v>
       </c>
       <c r="O4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="P4">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q4">
         <v>1.78</v>
@@ -1442,16 +1454,16 @@
         <v>2.74</v>
       </c>
       <c r="T4">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="U4">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="V4">
         <v>1.3</v>
       </c>
       <c r="W4">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="X4">
         <v>1000</v>
@@ -1622,7 +1634,7 @@
         <v>1.3</v>
       </c>
       <c r="CB4" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1630,16 +1642,16 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E5" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="F5">
         <v>1.77</v>
@@ -1657,7 +1669,7 @@
         <v>3.85</v>
       </c>
       <c r="K5">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L5">
         <v>1.31</v>
@@ -1666,13 +1678,13 @@
         <v>1.05</v>
       </c>
       <c r="N5">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="O5">
         <v>1.25</v>
       </c>
       <c r="P5">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="Q5">
         <v>1.73</v>
@@ -1864,7 +1876,7 @@
         <v>4.5</v>
       </c>
       <c r="CB5" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1872,34 +1884,34 @@
         <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E6" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F6">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="G6">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="H6">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="J6">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K6">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L6">
         <v>1.01</v>
@@ -1923,190 +1935,190 @@
         <v>1.48</v>
       </c>
       <c r="S6">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="T6">
-        <v>1.52</v>
+        <v>1.64</v>
       </c>
       <c r="U6">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="V6">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W6">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="X6">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Y6">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z6">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA6">
         <v>55</v>
       </c>
       <c r="AB6">
+        <v>14.5</v>
+      </c>
+      <c r="AC6">
+        <v>9</v>
+      </c>
+      <c r="AD6">
         <v>15</v>
       </c>
-      <c r="AC6">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD6">
-        <v>15.5</v>
-      </c>
       <c r="AE6">
+        <v>34</v>
+      </c>
+      <c r="AF6">
+        <v>20</v>
+      </c>
+      <c r="AG6">
+        <v>13</v>
+      </c>
+      <c r="AH6">
+        <v>18.5</v>
+      </c>
+      <c r="AI6">
+        <v>42</v>
+      </c>
+      <c r="AJ6">
         <v>36</v>
       </c>
-      <c r="AF6">
-        <v>21</v>
-      </c>
-      <c r="AG6">
-        <v>14</v>
-      </c>
-      <c r="AH6">
-        <v>19</v>
-      </c>
-      <c r="AI6">
-        <v>44</v>
-      </c>
-      <c r="AJ6">
+      <c r="AK6">
+        <v>28</v>
+      </c>
+      <c r="AL6">
         <v>38</v>
       </c>
-      <c r="AK6">
-        <v>29</v>
-      </c>
-      <c r="AL6">
-        <v>40</v>
-      </c>
       <c r="AM6">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AN6">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AO6">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AP6">
         <v>16.5</v>
       </c>
       <c r="AQ6">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AR6">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AS6">
-        <v>4.7</v>
+        <v>40</v>
       </c>
       <c r="AT6">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AU6">
         <v>7.8</v>
       </c>
       <c r="AV6">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW6">
-        <v>4.5</v>
+        <v>26</v>
       </c>
       <c r="AX6">
+        <v>16</v>
+      </c>
+      <c r="AY6">
+        <v>10.5</v>
+      </c>
+      <c r="AZ6">
         <v>14.5</v>
       </c>
-      <c r="AY6">
-        <v>10</v>
-      </c>
-      <c r="AZ6">
-        <v>13.5</v>
-      </c>
       <c r="BA6">
-        <v>4.6</v>
+        <v>32</v>
       </c>
       <c r="BB6">
-        <v>4.6</v>
+        <v>30</v>
       </c>
       <c r="BC6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD6">
-        <v>4.6</v>
+        <v>29</v>
       </c>
       <c r="BE6">
-        <v>4.9</v>
+        <v>60</v>
       </c>
       <c r="BF6">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="BG6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BH6">
         <v>1000</v>
       </c>
       <c r="BI6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ6">
         <v>1000</v>
       </c>
       <c r="BK6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN6">
         <v>1000</v>
       </c>
       <c r="BO6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP6">
         <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT6">
         <v>1000</v>
       </c>
       <c r="BU6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ6">
         <v>1000</v>
       </c>
       <c r="CA6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB6" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2114,16 +2126,16 @@
         <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D7" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E7" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F7">
         <v>1.54</v>
@@ -2138,7 +2150,7 @@
         <v>11</v>
       </c>
       <c r="J7">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K7">
         <v>5.1</v>
@@ -2168,10 +2180,10 @@
         <v>2.42</v>
       </c>
       <c r="T7">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U7">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V7">
         <v>1.14</v>
@@ -2291,64 +2303,306 @@
         <v>1000</v>
       </c>
       <c r="BI7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ7">
         <v>1000</v>
       </c>
       <c r="BK7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN7">
         <v>1000</v>
       </c>
       <c r="BO7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP7">
         <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT7">
         <v>1000</v>
       </c>
       <c r="BU7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV7">
         <v>1000</v>
       </c>
       <c r="BW7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ7">
         <v>1000</v>
       </c>
       <c r="CA7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB7" t="s">
-        <v>102</v>
+        <v>106</v>
+      </c>
+    </row>
+    <row r="8" spans="1:80">
+      <c r="A8" t="s">
+        <v>85</v>
+      </c>
+      <c r="B8" t="s">
+        <v>86</v>
+      </c>
+      <c r="C8" t="s">
+        <v>91</v>
+      </c>
+      <c r="D8" t="s">
+        <v>98</v>
+      </c>
+      <c r="E8" t="s">
+        <v>105</v>
+      </c>
+      <c r="F8">
+        <v>2.14</v>
+      </c>
+      <c r="G8">
+        <v>2.34</v>
+      </c>
+      <c r="H8">
+        <v>2.9</v>
+      </c>
+      <c r="I8">
+        <v>3.7</v>
+      </c>
+      <c r="J8">
+        <v>3.3</v>
+      </c>
+      <c r="K8">
+        <v>5.4</v>
+      </c>
+      <c r="L8">
+        <v>1.01</v>
+      </c>
+      <c r="M8">
+        <v>1.01</v>
+      </c>
+      <c r="N8">
+        <v>2.86</v>
+      </c>
+      <c r="O8">
+        <v>1.11</v>
+      </c>
+      <c r="P8">
+        <v>2.86</v>
+      </c>
+      <c r="Q8">
+        <v>1.39</v>
+      </c>
+      <c r="R8">
+        <v>1.81</v>
+      </c>
+      <c r="S8">
+        <v>1.98</v>
+      </c>
+      <c r="T8">
+        <v>1.11</v>
+      </c>
+      <c r="U8">
+        <v>1.11</v>
+      </c>
+      <c r="V8">
+        <v>1.41</v>
+      </c>
+      <c r="W8">
+        <v>1.74</v>
+      </c>
+      <c r="X8">
+        <v>1000</v>
+      </c>
+      <c r="Y8">
+        <v>1000</v>
+      </c>
+      <c r="Z8">
+        <v>1000</v>
+      </c>
+      <c r="AA8">
+        <v>1000</v>
+      </c>
+      <c r="AB8">
+        <v>1000</v>
+      </c>
+      <c r="AC8">
+        <v>1000</v>
+      </c>
+      <c r="AD8">
+        <v>1000</v>
+      </c>
+      <c r="AE8">
+        <v>1000</v>
+      </c>
+      <c r="AF8">
+        <v>1000</v>
+      </c>
+      <c r="AG8">
+        <v>1000</v>
+      </c>
+      <c r="AH8">
+        <v>1000</v>
+      </c>
+      <c r="AI8">
+        <v>1000</v>
+      </c>
+      <c r="AJ8">
+        <v>1000</v>
+      </c>
+      <c r="AK8">
+        <v>1000</v>
+      </c>
+      <c r="AL8">
+        <v>1000</v>
+      </c>
+      <c r="AM8">
+        <v>1000</v>
+      </c>
+      <c r="AN8">
+        <v>1000</v>
+      </c>
+      <c r="AO8">
+        <v>1000</v>
+      </c>
+      <c r="AP8">
+        <v>26</v>
+      </c>
+      <c r="AQ8">
+        <v>18</v>
+      </c>
+      <c r="AR8">
+        <v>19.5</v>
+      </c>
+      <c r="AS8">
+        <v>38</v>
+      </c>
+      <c r="AT8">
+        <v>15.5</v>
+      </c>
+      <c r="AU8">
+        <v>9</v>
+      </c>
+      <c r="AV8">
+        <v>10.5</v>
+      </c>
+      <c r="AW8">
+        <v>19.5</v>
+      </c>
+      <c r="AX8">
+        <v>15.5</v>
+      </c>
+      <c r="AY8">
+        <v>9</v>
+      </c>
+      <c r="AZ8">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BA8">
+        <v>19.5</v>
+      </c>
+      <c r="BB8">
+        <v>23</v>
+      </c>
+      <c r="BC8">
+        <v>14</v>
+      </c>
+      <c r="BD8">
+        <v>17.5</v>
+      </c>
+      <c r="BE8">
+        <v>26</v>
+      </c>
+      <c r="BF8">
+        <v>1.01</v>
+      </c>
+      <c r="BG8">
+        <v>1.01</v>
+      </c>
+      <c r="BH8">
+        <v>1000</v>
+      </c>
+      <c r="BI8">
+        <v>1.04</v>
+      </c>
+      <c r="BJ8">
+        <v>1000</v>
+      </c>
+      <c r="BK8">
+        <v>1.04</v>
+      </c>
+      <c r="BL8">
+        <v>1000</v>
+      </c>
+      <c r="BM8">
+        <v>1.04</v>
+      </c>
+      <c r="BN8">
+        <v>1000</v>
+      </c>
+      <c r="BO8">
+        <v>1.04</v>
+      </c>
+      <c r="BP8">
+        <v>1000</v>
+      </c>
+      <c r="BQ8">
+        <v>1.04</v>
+      </c>
+      <c r="BR8">
+        <v>1000</v>
+      </c>
+      <c r="BS8">
+        <v>1.04</v>
+      </c>
+      <c r="BT8">
+        <v>1000</v>
+      </c>
+      <c r="BU8">
+        <v>1.04</v>
+      </c>
+      <c r="BV8">
+        <v>1000</v>
+      </c>
+      <c r="BW8">
+        <v>1.04</v>
+      </c>
+      <c r="BX8">
+        <v>1000</v>
+      </c>
+      <c r="BY8">
+        <v>1.04</v>
+      </c>
+      <c r="BZ8">
+        <v>1000</v>
+      </c>
+      <c r="CA8">
+        <v>1.04</v>
+      </c>
+      <c r="CB8" t="s">
+        <v>106</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-18.xlsx
@@ -334,7 +334,7 @@
     <t>Beijing Guoan</t>
   </si>
   <si>
-    <t>2026-08-16 09:30:03</t>
+    <t>2026-08-16 11:46:01</t>
   </si>
 </sst>
 </file>
@@ -928,16 +928,16 @@
         <v>99</v>
       </c>
       <c r="F2">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="G2">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="H2">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="I2">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="J2">
         <v>3.2</v>
@@ -946,16 +946,16 @@
         <v>3.6</v>
       </c>
       <c r="L2">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="M2">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N2">
         <v>3.05</v>
       </c>
       <c r="O2">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="P2">
         <v>1.71</v>
@@ -964,22 +964,22 @@
         <v>2.12</v>
       </c>
       <c r="R2">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="S2">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="T2">
-        <v>1.11</v>
+        <v>1.86</v>
       </c>
       <c r="U2">
-        <v>1.11</v>
+        <v>1.95</v>
       </c>
       <c r="V2">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="W2">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="X2">
         <v>14</v>
@@ -994,7 +994,7 @@
         <v>38</v>
       </c>
       <c r="AB2">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC2">
         <v>9.199999999999999</v>
@@ -1018,10 +1018,10 @@
         <v>55</v>
       </c>
       <c r="AJ2">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AK2">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AL2">
         <v>75</v>
@@ -1090,25 +1090,25 @@
         <v>16.5</v>
       </c>
       <c r="BH2">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="BI2">
-        <v>1.04</v>
+        <v>2.5</v>
       </c>
       <c r="BJ2">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="BK2">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BN2">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO2">
         <v>4.4</v>
@@ -1117,37 +1117,37 @@
         <v>48</v>
       </c>
       <c r="BQ2">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BR2">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BS2">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BT2">
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="BU2">
-        <v>3.35</v>
+        <v>4.3</v>
       </c>
       <c r="BV2">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="BW2">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BX2">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="BY2">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BZ2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="CA2">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="CB2" t="s">
         <v>106</v>
@@ -1170,166 +1170,166 @@
         <v>100</v>
       </c>
       <c r="F3">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="H3">
-        <v>2.6</v>
+        <v>2.86</v>
       </c>
       <c r="I3">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="J3">
         <v>2.82</v>
       </c>
       <c r="K3">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="L3">
         <v>1.59</v>
       </c>
       <c r="M3">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="N3">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="O3">
         <v>1.64</v>
       </c>
       <c r="P3">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="Q3">
-        <v>2.68</v>
+        <v>2.98</v>
       </c>
       <c r="R3">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="S3">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="T3">
-        <v>1.11</v>
+        <v>2.24</v>
       </c>
       <c r="U3">
-        <v>1.54</v>
+        <v>1.7</v>
       </c>
       <c r="V3">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W3">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="X3">
-        <v>9.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="Y3">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="Z3">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AA3">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB3">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC3">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="AD3">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AE3">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF3">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AG3">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH3">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AI3">
         <v>1000</v>
       </c>
       <c r="AJ3">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AK3">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AL3">
         <v>1000</v>
       </c>
       <c r="AM3">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AN3">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AO3">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AP3">
         <v>4.6</v>
       </c>
       <c r="AQ3">
-        <v>1.12</v>
+        <v>7</v>
       </c>
       <c r="AR3">
-        <v>1.12</v>
+        <v>15.5</v>
       </c>
       <c r="AS3">
-        <v>1.12</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT3">
-        <v>1.12</v>
+        <v>7.2</v>
       </c>
       <c r="AU3">
-        <v>1.12</v>
+        <v>6.2</v>
       </c>
       <c r="AV3">
-        <v>1.12</v>
+        <v>12.5</v>
       </c>
       <c r="AW3">
-        <v>1.12</v>
+        <v>8.6</v>
       </c>
       <c r="AX3">
-        <v>1.12</v>
+        <v>6.8</v>
       </c>
       <c r="AY3">
-        <v>1.12</v>
+        <v>13</v>
       </c>
       <c r="AZ3">
-        <v>1.12</v>
+        <v>18.5</v>
       </c>
       <c r="BA3">
-        <v>1.12</v>
+        <v>10.5</v>
       </c>
       <c r="BB3">
-        <v>1.12</v>
+        <v>9</v>
       </c>
       <c r="BC3">
-        <v>1.12</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD3">
-        <v>1.12</v>
+        <v>10.5</v>
       </c>
       <c r="BE3">
-        <v>1.12</v>
+        <v>10</v>
       </c>
       <c r="BF3">
-        <v>1.12</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG3">
-        <v>1.12</v>
+        <v>9</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1424,22 +1424,22 @@
         <v>4.3</v>
       </c>
       <c r="J4">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="K4">
         <v>4.2</v>
       </c>
       <c r="L4">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M4">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="N4">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="O4">
-        <v>1.04</v>
+        <v>1.26</v>
       </c>
       <c r="P4">
         <v>2</v>
@@ -1454,10 +1454,10 @@
         <v>2.74</v>
       </c>
       <c r="T4">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="U4">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="V4">
         <v>1.3</v>
@@ -1469,13 +1469,13 @@
         <v>1000</v>
       </c>
       <c r="Y4">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Z4">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA4">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB4">
         <v>1000</v>
@@ -1484,13 +1484,13 @@
         <v>1000</v>
       </c>
       <c r="AD4">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AE4">
         <v>1000</v>
       </c>
       <c r="AF4">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AG4">
         <v>1000</v>
@@ -1502,64 +1502,64 @@
         <v>1000</v>
       </c>
       <c r="AJ4">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK4">
         <v>1000</v>
       </c>
       <c r="AL4">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM4">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN4">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AO4">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AP4">
         <v>1.01</v>
       </c>
       <c r="AQ4">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AR4">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AS4">
         <v>1.01</v>
       </c>
       <c r="AT4">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AU4">
         <v>1.01</v>
       </c>
       <c r="AV4">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AW4">
         <v>1.01</v>
       </c>
       <c r="AX4">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AY4">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AZ4">
         <v>1.01</v>
       </c>
       <c r="BA4">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BB4">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BC4">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BD4">
         <v>1.01</v>
@@ -1568,70 +1568,70 @@
         <v>1.01</v>
       </c>
       <c r="BF4">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BG4">
         <v>1.01</v>
       </c>
       <c r="BH4">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="BI4">
-        <v>2.72</v>
+        <v>3.2</v>
       </c>
       <c r="BJ4">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BK4">
-        <v>1.3</v>
+        <v>4.9</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN4">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BO4">
-        <v>1.3</v>
+        <v>4.1</v>
       </c>
       <c r="BP4">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BQ4">
-        <v>1.3</v>
+        <v>6</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>1.3</v>
+        <v>7.4</v>
       </c>
       <c r="BT4">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BU4">
-        <v>1.3</v>
+        <v>5.4</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>1.3</v>
+        <v>7.4</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>1.3</v>
+        <v>7.8</v>
       </c>
       <c r="BZ4">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="CA4">
-        <v>1.3</v>
+        <v>7</v>
       </c>
       <c r="CB4" t="s">
         <v>106</v>
@@ -1687,7 +1687,7 @@
         <v>2.12</v>
       </c>
       <c r="Q5">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="R5">
         <v>1.43</v>
@@ -1696,10 +1696,10 @@
         <v>2.86</v>
       </c>
       <c r="T5">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="U5">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="V5">
         <v>1.24</v>
@@ -1714,28 +1714,28 @@
         <v>19.5</v>
       </c>
       <c r="Z5">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AA5">
         <v>120</v>
       </c>
       <c r="AB5">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AC5">
         <v>9.6</v>
       </c>
       <c r="AD5">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AE5">
         <v>65</v>
       </c>
       <c r="AF5">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AG5">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH5">
         <v>19</v>
@@ -1765,31 +1765,31 @@
         <v>14</v>
       </c>
       <c r="AQ5">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AR5">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="AS5">
         <v>1.01</v>
       </c>
       <c r="AT5">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AU5">
         <v>7.8</v>
       </c>
       <c r="AV5">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AW5">
         <v>1.01</v>
       </c>
       <c r="AX5">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AY5">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ5">
         <v>15</v>
@@ -1798,7 +1798,7 @@
         <v>1.01</v>
       </c>
       <c r="BB5">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BC5">
         <v>15.5</v>
@@ -1810,7 +1810,7 @@
         <v>1.01</v>
       </c>
       <c r="BF5">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BG5">
         <v>1.01</v>
@@ -1899,7 +1899,7 @@
         <v>2.44</v>
       </c>
       <c r="G6">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="H6">
         <v>2.98</v>
@@ -1926,7 +1926,7 @@
         <v>1.25</v>
       </c>
       <c r="P6">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q6">
         <v>1.74</v>
@@ -1941,7 +1941,7 @@
         <v>1.64</v>
       </c>
       <c r="U6">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="V6">
         <v>1.49</v>
@@ -1980,7 +1980,7 @@
         <v>13</v>
       </c>
       <c r="AH6">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI6">
         <v>42</v>
@@ -2147,10 +2147,10 @@
         <v>6.4</v>
       </c>
       <c r="I7">
-        <v>11</v>
+        <v>8.6</v>
       </c>
       <c r="J7">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="K7">
         <v>5.1</v>
@@ -2383,16 +2383,16 @@
         <v>2.14</v>
       </c>
       <c r="G8">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="H8">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="I8">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="J8">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="K8">
         <v>5.4</v>
@@ -2431,7 +2431,7 @@
         <v>1.41</v>
       </c>
       <c r="W8">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="X8">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-18.xlsx
@@ -334,7 +334,7 @@
     <t>Beijing Guoan</t>
   </si>
   <si>
-    <t>2026-08-16 11:46:01</t>
+    <t>2026-08-16 13:59:19</t>
   </si>
 </sst>
 </file>
@@ -1045,7 +1045,7 @@
         <v>10</v>
       </c>
       <c r="AS2">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AT2">
         <v>9</v>
@@ -1069,22 +1069,22 @@
         <v>14</v>
       </c>
       <c r="BA2">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BB2">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BC2">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BD2">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BE2">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BF2">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BG2">
         <v>16.5</v>
@@ -1111,7 +1111,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BO2">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BP2">
         <v>48</v>
@@ -1182,10 +1182,10 @@
         <v>3.1</v>
       </c>
       <c r="J3">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="K3">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="L3">
         <v>1.59</v>
@@ -1194,16 +1194,16 @@
         <v>1.15</v>
       </c>
       <c r="N3">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="O3">
         <v>1.64</v>
       </c>
       <c r="P3">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="Q3">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="R3">
         <v>1.16</v>
@@ -1218,10 +1218,10 @@
         <v>1.7</v>
       </c>
       <c r="V3">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W3">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X3">
         <v>7.4</v>
@@ -1245,7 +1245,7 @@
         <v>20</v>
       </c>
       <c r="AE3">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="AF3">
         <v>28</v>
@@ -1254,19 +1254,19 @@
         <v>15.5</v>
       </c>
       <c r="AH3">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AI3">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ3">
         <v>90</v>
       </c>
       <c r="AK3">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AL3">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AM3">
         <v>270</v>
@@ -1275,10 +1275,10 @@
         <v>100</v>
       </c>
       <c r="AO3">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="AP3">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="AQ3">
         <v>7</v>
@@ -1287,7 +1287,7 @@
         <v>15.5</v>
       </c>
       <c r="AS3">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AT3">
         <v>7.2</v>
@@ -1299,10 +1299,10 @@
         <v>12.5</v>
       </c>
       <c r="AW3">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AX3">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AY3">
         <v>13</v>
@@ -1311,25 +1311,25 @@
         <v>18.5</v>
       </c>
       <c r="BA3">
+        <v>11</v>
+      </c>
+      <c r="BB3">
         <v>10.5</v>
       </c>
-      <c r="BB3">
-        <v>9</v>
-      </c>
       <c r="BC3">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BD3">
+        <v>11.5</v>
+      </c>
+      <c r="BE3">
+        <v>12</v>
+      </c>
+      <c r="BF3">
+        <v>11</v>
+      </c>
+      <c r="BG3">
         <v>10.5</v>
-      </c>
-      <c r="BE3">
-        <v>10</v>
-      </c>
-      <c r="BF3">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BG3">
-        <v>9</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1421,13 +1421,13 @@
         <v>3.3</v>
       </c>
       <c r="I4">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="J4">
         <v>3.35</v>
       </c>
       <c r="K4">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="L4">
         <v>1.32</v>
@@ -1448,28 +1448,28 @@
         <v>1.78</v>
       </c>
       <c r="R4">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="S4">
-        <v>2.74</v>
+        <v>2.98</v>
       </c>
       <c r="T4">
         <v>1.67</v>
       </c>
       <c r="U4">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V4">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W4">
         <v>1.75</v>
       </c>
       <c r="X4">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Y4">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="Z4">
         <v>34</v>
@@ -1478,34 +1478,34 @@
         <v>80</v>
       </c>
       <c r="AB4">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AC4">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD4">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AE4">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AF4">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AG4">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH4">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI4">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ4">
         <v>34</v>
       </c>
       <c r="AK4">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL4">
         <v>42</v>
@@ -1514,43 +1514,43 @@
         <v>100</v>
       </c>
       <c r="AN4">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AO4">
         <v>44</v>
       </c>
       <c r="AP4">
+        <v>12.5</v>
+      </c>
+      <c r="AQ4">
+        <v>12.5</v>
+      </c>
+      <c r="AR4">
         <v>1.01</v>
-      </c>
-      <c r="AQ4">
-        <v>11</v>
-      </c>
-      <c r="AR4">
-        <v>19</v>
       </c>
       <c r="AS4">
         <v>1.01</v>
       </c>
       <c r="AT4">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU4">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV4">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW4">
         <v>1.01</v>
       </c>
       <c r="AX4">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AY4">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ4">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BA4">
         <v>32</v>
@@ -1559,7 +1559,7 @@
         <v>19</v>
       </c>
       <c r="BC4">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="BD4">
         <v>1.01</v>
@@ -1568,7 +1568,7 @@
         <v>1.01</v>
       </c>
       <c r="BF4">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BG4">
         <v>1.01</v>
@@ -1583,7 +1583,7 @@
         <v>9.6</v>
       </c>
       <c r="BK4">
-        <v>4.9</v>
+        <v>7.2</v>
       </c>
       <c r="BL4">
         <v>1000</v>
@@ -1613,7 +1613,7 @@
         <v>7.4</v>
       </c>
       <c r="BU4">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BV4">
         <v>1000</v>
@@ -1654,7 +1654,7 @@
         <v>102</v>
       </c>
       <c r="F5">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="G5">
         <v>1.93</v>
@@ -1684,10 +1684,10 @@
         <v>1.25</v>
       </c>
       <c r="P5">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="Q5">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="R5">
         <v>1.43</v>
@@ -1699,7 +1699,7 @@
         <v>1.69</v>
       </c>
       <c r="U5">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="V5">
         <v>1.24</v>
@@ -1908,7 +1908,7 @@
         <v>3.05</v>
       </c>
       <c r="J6">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K6">
         <v>3.9</v>
@@ -1920,28 +1920,28 @@
         <v>1.05</v>
       </c>
       <c r="N6">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="O6">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="P6">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="Q6">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="R6">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="S6">
-        <v>2.86</v>
+        <v>2.7</v>
       </c>
       <c r="T6">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="U6">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="V6">
         <v>1.49</v>
@@ -1953,16 +1953,16 @@
         <v>21</v>
       </c>
       <c r="Y6">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Z6">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AA6">
         <v>55</v>
       </c>
       <c r="AB6">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AC6">
         <v>9</v>
@@ -1977,7 +1977,7 @@
         <v>20</v>
       </c>
       <c r="AG6">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH6">
         <v>18</v>
@@ -1989,25 +1989,25 @@
         <v>36</v>
       </c>
       <c r="AK6">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL6">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM6">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN6">
         <v>18</v>
       </c>
       <c r="AO6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AP6">
         <v>16.5</v>
       </c>
       <c r="AQ6">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AR6">
         <v>19</v>
@@ -2016,7 +2016,7 @@
         <v>40</v>
       </c>
       <c r="AT6">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU6">
         <v>7.8</v>
@@ -2034,10 +2034,10 @@
         <v>10.5</v>
       </c>
       <c r="AZ6">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA6">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="BB6">
         <v>30</v>
@@ -2046,16 +2046,16 @@
         <v>21</v>
       </c>
       <c r="BD6">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="BE6">
-        <v>60</v>
+        <v>7</v>
       </c>
       <c r="BF6">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BG6">
-        <v>19</v>
+        <v>5.6</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -2144,58 +2144,58 @@
         <v>1.55</v>
       </c>
       <c r="H7">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="I7">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="J7">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="K7">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L7">
         <v>1.01</v>
       </c>
       <c r="M7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N7">
-        <v>2.36</v>
+        <v>4.6</v>
       </c>
       <c r="O7">
         <v>1.21</v>
       </c>
       <c r="P7">
-        <v>2.02</v>
+        <v>2.22</v>
       </c>
       <c r="Q7">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="R7">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="S7">
-        <v>2.42</v>
+        <v>2.68</v>
       </c>
       <c r="T7">
-        <v>1.11</v>
+        <v>1.8</v>
       </c>
       <c r="U7">
-        <v>1.11</v>
+        <v>2.04</v>
       </c>
       <c r="V7">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W7">
         <v>2.8</v>
       </c>
       <c r="X7">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y7">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z7">
         <v>1000</v>
@@ -2204,100 +2204,100 @@
         <v>1000</v>
       </c>
       <c r="AB7">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AC7">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AD7">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE7">
         <v>1000</v>
       </c>
       <c r="AF7">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AG7">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH7">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI7">
         <v>1000</v>
       </c>
       <c r="AJ7">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AK7">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL7">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM7">
         <v>1000</v>
       </c>
       <c r="AN7">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO7">
         <v>1000</v>
       </c>
       <c r="AP7">
-        <v>16.5</v>
+        <v>2.54</v>
       </c>
       <c r="AQ7">
-        <v>18.5</v>
+        <v>2.6</v>
       </c>
       <c r="AR7">
-        <v>38</v>
+        <v>2.74</v>
       </c>
       <c r="AS7">
-        <v>40</v>
+        <v>2.74</v>
       </c>
       <c r="AT7">
-        <v>7.6</v>
+        <v>2.28</v>
       </c>
       <c r="AU7">
-        <v>8.6</v>
+        <v>2.26</v>
       </c>
       <c r="AV7">
-        <v>19</v>
+        <v>2.6</v>
       </c>
       <c r="AW7">
-        <v>40</v>
+        <v>2.74</v>
       </c>
       <c r="AX7">
-        <v>7.6</v>
+        <v>2.24</v>
       </c>
       <c r="AY7">
-        <v>8.6</v>
+        <v>2.3</v>
       </c>
       <c r="AZ7">
-        <v>16.5</v>
+        <v>2.56</v>
       </c>
       <c r="BA7">
-        <v>40</v>
+        <v>2.74</v>
       </c>
       <c r="BB7">
-        <v>10</v>
+        <v>2.4</v>
       </c>
       <c r="BC7">
+        <v>2.44</v>
+      </c>
+      <c r="BD7">
+        <v>2.66</v>
+      </c>
+      <c r="BE7">
+        <v>2.74</v>
+      </c>
+      <c r="BF7">
+        <v>4.3</v>
+      </c>
+      <c r="BG7">
         <v>11</v>
-      </c>
-      <c r="BD7">
-        <v>24</v>
-      </c>
-      <c r="BE7">
-        <v>40</v>
-      </c>
-      <c r="BF7">
-        <v>1.01</v>
-      </c>
-      <c r="BG7">
-        <v>1.01</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2389,7 +2389,7 @@
         <v>2.88</v>
       </c>
       <c r="I8">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="J8">
         <v>4</v>
@@ -2416,19 +2416,19 @@
         <v>1.39</v>
       </c>
       <c r="R8">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="S8">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="T8">
-        <v>1.11</v>
+        <v>1.35</v>
       </c>
       <c r="U8">
-        <v>1.11</v>
+        <v>2.62</v>
       </c>
       <c r="V8">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="W8">
         <v>1.73</v>
@@ -2452,7 +2452,7 @@
         <v>1000</v>
       </c>
       <c r="AD8">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AE8">
         <v>1000</v>
@@ -2464,10 +2464,10 @@
         <v>1000</v>
       </c>
       <c r="AH8">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AI8">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AJ8">
         <v>1000</v>
@@ -2488,58 +2488,58 @@
         <v>1000</v>
       </c>
       <c r="AP8">
-        <v>26</v>
+        <v>1.16</v>
       </c>
       <c r="AQ8">
-        <v>18</v>
+        <v>1.16</v>
       </c>
       <c r="AR8">
-        <v>19.5</v>
+        <v>1.16</v>
       </c>
       <c r="AS8">
-        <v>38</v>
+        <v>1.16</v>
       </c>
       <c r="AT8">
-        <v>15.5</v>
+        <v>1.16</v>
       </c>
       <c r="AU8">
-        <v>9</v>
+        <v>1.16</v>
       </c>
       <c r="AV8">
+        <v>11</v>
+      </c>
+      <c r="AW8">
+        <v>1.16</v>
+      </c>
+      <c r="AX8">
+        <v>1.16</v>
+      </c>
+      <c r="AY8">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ8">
         <v>10.5</v>
       </c>
-      <c r="AW8">
-        <v>19.5</v>
-      </c>
-      <c r="AX8">
-        <v>15.5</v>
-      </c>
-      <c r="AY8">
-        <v>9</v>
-      </c>
-      <c r="AZ8">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BA8">
-        <v>19.5</v>
+        <v>1.13</v>
       </c>
       <c r="BB8">
-        <v>23</v>
+        <v>1.16</v>
       </c>
       <c r="BC8">
-        <v>14</v>
+        <v>1.16</v>
       </c>
       <c r="BD8">
-        <v>17.5</v>
+        <v>1.16</v>
       </c>
       <c r="BE8">
-        <v>26</v>
+        <v>1.16</v>
       </c>
       <c r="BF8">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BG8">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BH8">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-18.xlsx
@@ -334,7 +334,7 @@
     <t>Beijing Guoan</t>
   </si>
   <si>
-    <t>2026-08-16 13:59:19</t>
+    <t>2026-08-16 16:10:32</t>
   </si>
 </sst>
 </file>
@@ -985,22 +985,22 @@
         <v>14</v>
       </c>
       <c r="Y2">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Z2">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AA2">
         <v>38</v>
       </c>
       <c r="AB2">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AC2">
         <v>9.199999999999999</v>
       </c>
       <c r="AD2">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AE2">
         <v>34</v>
@@ -1045,7 +1045,7 @@
         <v>10</v>
       </c>
       <c r="AS2">
-        <v>3.95</v>
+        <v>23</v>
       </c>
       <c r="AT2">
         <v>9</v>
@@ -1057,37 +1057,37 @@
         <v>8.4</v>
       </c>
       <c r="AW2">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AX2">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AY2">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AZ2">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="BA2">
-        <v>4.1</v>
+        <v>34</v>
       </c>
       <c r="BB2">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BC2">
-        <v>4.1</v>
+        <v>36</v>
       </c>
       <c r="BD2">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BE2">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BF2">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BG2">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BH2">
         <v>3.6</v>
@@ -1173,37 +1173,37 @@
         <v>3</v>
       </c>
       <c r="G3">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="H3">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="I3">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J3">
         <v>2.88</v>
       </c>
       <c r="K3">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="L3">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="M3">
         <v>1.15</v>
       </c>
       <c r="N3">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="O3">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="P3">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="Q3">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="R3">
         <v>1.16</v>
@@ -1212,124 +1212,124 @@
         <v>6.4</v>
       </c>
       <c r="T3">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="U3">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="V3">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W3">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="X3">
         <v>7.4</v>
       </c>
       <c r="Y3">
+        <v>7.8</v>
+      </c>
+      <c r="Z3">
+        <v>20</v>
+      </c>
+      <c r="AA3">
+        <v>70</v>
+      </c>
+      <c r="AB3">
         <v>8</v>
-      </c>
-      <c r="Z3">
-        <v>18</v>
-      </c>
-      <c r="AA3">
-        <v>75</v>
-      </c>
-      <c r="AB3">
-        <v>8.199999999999999</v>
       </c>
       <c r="AC3">
         <v>7</v>
       </c>
       <c r="AD3">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AE3">
-        <v>50</v>
+        <v>160</v>
       </c>
       <c r="AF3">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="AG3">
-        <v>15.5</v>
+        <v>19.5</v>
       </c>
       <c r="AH3">
         <v>34</v>
       </c>
       <c r="AI3">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AJ3">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AK3">
-        <v>55</v>
+        <v>210</v>
       </c>
       <c r="AL3">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AM3">
         <v>270</v>
       </c>
       <c r="AN3">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AO3">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AP3">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AQ3">
         <v>7</v>
       </c>
       <c r="AR3">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AS3">
-        <v>10.5</v>
+        <v>27</v>
       </c>
       <c r="AT3">
         <v>7.2</v>
       </c>
       <c r="AU3">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV3">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AW3">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="AX3">
-        <v>7.6</v>
+        <v>16</v>
       </c>
       <c r="AY3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ3">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="BA3">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="BB3">
-        <v>10.5</v>
+        <v>28</v>
       </c>
       <c r="BC3">
-        <v>10.5</v>
+        <v>27</v>
       </c>
       <c r="BD3">
-        <v>11.5</v>
+        <v>60</v>
       </c>
       <c r="BE3">
-        <v>12</v>
+        <v>95</v>
       </c>
       <c r="BF3">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="BG3">
-        <v>10.5</v>
+        <v>30</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1430,7 +1430,7 @@
         <v>4</v>
       </c>
       <c r="L4">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="M4">
         <v>1.06</v>
@@ -1526,7 +1526,7 @@
         <v>12.5</v>
       </c>
       <c r="AR4">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AS4">
         <v>1.01</v>
@@ -1562,7 +1562,7 @@
         <v>18.5</v>
       </c>
       <c r="BD4">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE4">
         <v>1.01</v>
@@ -1678,7 +1678,7 @@
         <v>1.05</v>
       </c>
       <c r="N5">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="O5">
         <v>1.25</v>
@@ -1771,7 +1771,7 @@
         <v>28</v>
       </c>
       <c r="AS5">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AT5">
         <v>8.6</v>
@@ -1783,7 +1783,7 @@
         <v>15.5</v>
       </c>
       <c r="AW5">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AX5">
         <v>10.5</v>
@@ -1795,7 +1795,7 @@
         <v>15</v>
       </c>
       <c r="BA5">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BB5">
         <v>17</v>
@@ -1807,13 +1807,13 @@
         <v>21</v>
       </c>
       <c r="BE5">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BF5">
         <v>9</v>
       </c>
       <c r="BG5">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BH5">
         <v>4.3</v>
@@ -1905,7 +1905,7 @@
         <v>2.98</v>
       </c>
       <c r="I6">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="J6">
         <v>3.85</v>
@@ -1914,55 +1914,55 @@
         <v>3.9</v>
       </c>
       <c r="L6">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M6">
         <v>1.05</v>
       </c>
       <c r="N6">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O6">
         <v>1.23</v>
       </c>
       <c r="P6">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="Q6">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="R6">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S6">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="T6">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="U6">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="V6">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W6">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="X6">
         <v>21</v>
       </c>
       <c r="Y6">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z6">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AA6">
         <v>55</v>
       </c>
       <c r="AB6">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AC6">
         <v>9</v>
@@ -1974,7 +1974,7 @@
         <v>34</v>
       </c>
       <c r="AF6">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AG6">
         <v>12</v>
@@ -1995,16 +1995,16 @@
         <v>36</v>
       </c>
       <c r="AM6">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AN6">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AO6">
         <v>27</v>
       </c>
       <c r="AP6">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AQ6">
         <v>13.5</v>
@@ -2019,7 +2019,7 @@
         <v>12</v>
       </c>
       <c r="AU6">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV6">
         <v>11.5</v>
@@ -2037,7 +2037,7 @@
         <v>14</v>
       </c>
       <c r="BA6">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="BB6">
         <v>30</v>
@@ -2046,76 +2046,76 @@
         <v>21</v>
       </c>
       <c r="BD6">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="BE6">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="BF6">
         <v>13</v>
       </c>
       <c r="BG6">
+        <v>18</v>
+      </c>
+      <c r="BH6">
+        <v>4.1</v>
+      </c>
+      <c r="BI6">
+        <v>3.25</v>
+      </c>
+      <c r="BJ6">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK6">
         <v>5.6</v>
       </c>
-      <c r="BH6">
-        <v>1000</v>
-      </c>
-      <c r="BI6">
-        <v>1.04</v>
-      </c>
-      <c r="BJ6">
-        <v>1000</v>
-      </c>
-      <c r="BK6">
-        <v>1.04</v>
-      </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>1.04</v>
+        <v>13</v>
       </c>
       <c r="BN6">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BO6">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BP6">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BQ6">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BR6">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS6">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BT6">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU6">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BV6">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BW6">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX6">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BY6">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BZ6">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="CA6">
-        <v>1.04</v>
+        <v>13.5</v>
       </c>
       <c r="CB6" t="s">
         <v>106</v>
@@ -2150,7 +2150,7 @@
         <v>7.6</v>
       </c>
       <c r="J7">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K7">
         <v>5</v>
@@ -2159,28 +2159,28 @@
         <v>1.01</v>
       </c>
       <c r="M7">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="N7">
         <v>4.6</v>
       </c>
       <c r="O7">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="P7">
         <v>2.22</v>
       </c>
       <c r="Q7">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="R7">
         <v>1.51</v>
       </c>
       <c r="S7">
-        <v>2.68</v>
+        <v>2.82</v>
       </c>
       <c r="T7">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="U7">
         <v>2.04</v>
@@ -2198,106 +2198,106 @@
         <v>950</v>
       </c>
       <c r="Z7">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AA7">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AB7">
-        <v>13.5</v>
+        <v>9.4</v>
       </c>
       <c r="AC7">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AD7">
         <v>950</v>
       </c>
       <c r="AE7">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF7">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AG7">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="AH7">
         <v>950</v>
       </c>
       <c r="AI7">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ7">
-        <v>19.5</v>
+        <v>14.5</v>
       </c>
       <c r="AK7">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="AL7">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="AM7">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN7">
+        <v>7.4</v>
+      </c>
+      <c r="AO7">
+        <v>140</v>
+      </c>
+      <c r="AP7">
+        <v>17</v>
+      </c>
+      <c r="AQ7">
+        <v>21</v>
+      </c>
+      <c r="AR7">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS7">
+        <v>10</v>
+      </c>
+      <c r="AT7">
         <v>8.199999999999999</v>
       </c>
-      <c r="AO7">
-        <v>1000</v>
-      </c>
-      <c r="AP7">
-        <v>2.54</v>
-      </c>
-      <c r="AQ7">
-        <v>2.6</v>
-      </c>
-      <c r="AR7">
-        <v>2.74</v>
-      </c>
-      <c r="AS7">
-        <v>2.74</v>
-      </c>
-      <c r="AT7">
-        <v>2.28</v>
-      </c>
       <c r="AU7">
-        <v>2.26</v>
+        <v>9.4</v>
       </c>
       <c r="AV7">
-        <v>2.6</v>
+        <v>7.6</v>
       </c>
       <c r="AW7">
-        <v>2.74</v>
+        <v>9.6</v>
       </c>
       <c r="AX7">
-        <v>2.24</v>
+        <v>8.6</v>
       </c>
       <c r="AY7">
-        <v>2.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ7">
-        <v>2.56</v>
+        <v>7</v>
       </c>
       <c r="BA7">
-        <v>2.74</v>
+        <v>9.6</v>
       </c>
       <c r="BB7">
-        <v>2.4</v>
+        <v>12.5</v>
       </c>
       <c r="BC7">
-        <v>2.44</v>
+        <v>13.5</v>
       </c>
       <c r="BD7">
-        <v>2.66</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE7">
-        <v>2.74</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF7">
-        <v>4.3</v>
+        <v>6.4</v>
       </c>
       <c r="BG7">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2380,40 +2380,40 @@
         <v>105</v>
       </c>
       <c r="F8">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G8">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="H8">
         <v>2.88</v>
       </c>
       <c r="I8">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="J8">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="K8">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="L8">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="M8">
         <v>1.01</v>
       </c>
       <c r="N8">
-        <v>2.86</v>
+        <v>7.2</v>
       </c>
       <c r="O8">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="P8">
-        <v>2.86</v>
+        <v>3.05</v>
       </c>
       <c r="Q8">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="R8">
         <v>1.85</v>
@@ -2422,133 +2422,133 @@
         <v>2</v>
       </c>
       <c r="T8">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="U8">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="V8">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W8">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="X8">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="Y8">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Z8">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA8">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB8">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AC8">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AD8">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AE8">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF8">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AG8">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH8">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI8">
+        <v>34</v>
+      </c>
+      <c r="AJ8">
         <v>36</v>
       </c>
-      <c r="AJ8">
-        <v>1000</v>
-      </c>
       <c r="AK8">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL8">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AM8">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AN8">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AO8">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AP8">
-        <v>1.16</v>
+        <v>4.5</v>
       </c>
       <c r="AQ8">
-        <v>1.16</v>
+        <v>19</v>
       </c>
       <c r="AR8">
-        <v>1.16</v>
+        <v>21</v>
       </c>
       <c r="AS8">
-        <v>1.16</v>
+        <v>4.6</v>
       </c>
       <c r="AT8">
-        <v>1.16</v>
+        <v>15</v>
       </c>
       <c r="AU8">
-        <v>1.16</v>
+        <v>9</v>
       </c>
       <c r="AV8">
         <v>11</v>
       </c>
       <c r="AW8">
-        <v>1.16</v>
+        <v>20</v>
       </c>
       <c r="AX8">
-        <v>1.16</v>
+        <v>16</v>
       </c>
       <c r="AY8">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ8">
+        <v>11</v>
+      </c>
+      <c r="BA8">
+        <v>21</v>
+      </c>
+      <c r="BB8">
+        <v>4.4</v>
+      </c>
+      <c r="BC8">
+        <v>15</v>
+      </c>
+      <c r="BD8">
+        <v>18</v>
+      </c>
+      <c r="BE8">
+        <v>4.6</v>
+      </c>
+      <c r="BF8">
+        <v>6.8</v>
+      </c>
+      <c r="BG8">
         <v>10.5</v>
       </c>
-      <c r="BA8">
-        <v>1.13</v>
-      </c>
-      <c r="BB8">
-        <v>1.16</v>
-      </c>
-      <c r="BC8">
-        <v>1.16</v>
-      </c>
-      <c r="BD8">
-        <v>1.16</v>
-      </c>
-      <c r="BE8">
-        <v>1.16</v>
-      </c>
-      <c r="BF8">
-        <v>1.16</v>
-      </c>
-      <c r="BG8">
-        <v>1.16</v>
-      </c>
       <c r="BH8">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BI8">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BJ8">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BK8">
         <v>1.04</v>
@@ -2560,13 +2560,13 @@
         <v>1.04</v>
       </c>
       <c r="BN8">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BO8">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BP8">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BQ8">
         <v>1.04</v>
@@ -2578,10 +2578,10 @@
         <v>1.04</v>
       </c>
       <c r="BT8">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BU8">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BV8">
         <v>1000</v>
@@ -2596,7 +2596,7 @@
         <v>1.04</v>
       </c>
       <c r="BZ8">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="CA8">
         <v>1.04</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-18.xlsx
@@ -334,7 +334,7 @@
     <t>Beijing Guoan</t>
   </si>
   <si>
-    <t>2026-08-16 16:10:32</t>
+    <t>2026-08-16 18:21:03</t>
   </si>
 </sst>
 </file>
@@ -949,28 +949,28 @@
         <v>1.45</v>
       </c>
       <c r="M2">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N2">
         <v>3.05</v>
       </c>
       <c r="O2">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="P2">
         <v>1.71</v>
       </c>
       <c r="Q2">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R2">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="S2">
         <v>4</v>
       </c>
       <c r="T2">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U2">
         <v>1.95</v>
@@ -994,13 +994,13 @@
         <v>38</v>
       </c>
       <c r="AB2">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AC2">
         <v>9.199999999999999</v>
       </c>
       <c r="AD2">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE2">
         <v>34</v>
@@ -1015,7 +1015,7 @@
         <v>24</v>
       </c>
       <c r="AI2">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AJ2">
         <v>90</v>
@@ -1072,7 +1072,7 @@
         <v>34</v>
       </c>
       <c r="BB2">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BC2">
         <v>36</v>
@@ -1081,7 +1081,7 @@
         <v>4.7</v>
       </c>
       <c r="BE2">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BF2">
         <v>4.7</v>
@@ -1179,7 +1179,7 @@
         <v>2.88</v>
       </c>
       <c r="I3">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="J3">
         <v>2.88</v>
@@ -1194,10 +1194,10 @@
         <v>1.15</v>
       </c>
       <c r="N3">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="O3">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="P3">
         <v>1.45</v>
@@ -1332,13 +1332,13 @@
         <v>30</v>
       </c>
       <c r="BH3">
-        <v>1000</v>
+        <v>2.52</v>
       </c>
       <c r="BI3">
-        <v>1.04</v>
+        <v>2.14</v>
       </c>
       <c r="BJ3">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK3">
         <v>1.04</v>
@@ -1350,10 +1350,10 @@
         <v>1.04</v>
       </c>
       <c r="BN3">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BO3">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BP3">
         <v>1000</v>
@@ -1368,10 +1368,10 @@
         <v>1.04</v>
       </c>
       <c r="BT3">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BU3">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BV3">
         <v>1000</v>
@@ -1896,76 +1896,76 @@
         <v>103</v>
       </c>
       <c r="F6">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="G6">
         <v>2.48</v>
       </c>
       <c r="H6">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="I6">
         <v>3</v>
       </c>
       <c r="J6">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K6">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L6">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="M6">
         <v>1.05</v>
       </c>
       <c r="N6">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="O6">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="P6">
-        <v>2.32</v>
+        <v>2.24</v>
       </c>
       <c r="Q6">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="R6">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="S6">
-        <v>2.72</v>
+        <v>2.88</v>
       </c>
       <c r="T6">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="U6">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="V6">
         <v>1.5</v>
       </c>
       <c r="W6">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="X6">
         <v>21</v>
       </c>
       <c r="Y6">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="Z6">
         <v>26</v>
       </c>
       <c r="AA6">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AB6">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AC6">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD6">
         <v>15</v>
@@ -1980,10 +1980,10 @@
         <v>12</v>
       </c>
       <c r="AH6">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI6">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ6">
         <v>36</v>
@@ -1995,7 +1995,7 @@
         <v>36</v>
       </c>
       <c r="AM6">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AN6">
         <v>18.5</v>
@@ -2004,7 +2004,7 @@
         <v>27</v>
       </c>
       <c r="AP6">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AQ6">
         <v>13.5</v>
@@ -2019,7 +2019,7 @@
         <v>12</v>
       </c>
       <c r="AU6">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AV6">
         <v>11.5</v>
@@ -2028,7 +2028,7 @@
         <v>26</v>
       </c>
       <c r="AX6">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AY6">
         <v>10.5</v>
@@ -2058,40 +2058,40 @@
         <v>18</v>
       </c>
       <c r="BH6">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="BI6">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="BJ6">
         <v>8.800000000000001</v>
       </c>
       <c r="BK6">
+        <v>5.7</v>
+      </c>
+      <c r="BL6">
+        <v>1000</v>
+      </c>
+      <c r="BM6">
+        <v>14</v>
+      </c>
+      <c r="BN6">
         <v>5.6</v>
       </c>
-      <c r="BL6">
-        <v>1000</v>
-      </c>
-      <c r="BM6">
-        <v>13</v>
-      </c>
-      <c r="BN6">
-        <v>5.7</v>
-      </c>
       <c r="BO6">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BP6">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BQ6">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BR6">
         <v>26</v>
       </c>
       <c r="BS6">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BT6">
         <v>6.4</v>
@@ -2100,22 +2100,22 @@
         <v>4.8</v>
       </c>
       <c r="BV6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BW6">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BX6">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BY6">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ6">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="CA6">
-        <v>13.5</v>
+        <v>9</v>
       </c>
       <c r="CB6" t="s">
         <v>106</v>
@@ -2144,7 +2144,7 @@
         <v>1.55</v>
       </c>
       <c r="H7">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="I7">
         <v>7.6</v>
@@ -2153,7 +2153,7 @@
         <v>4.4</v>
       </c>
       <c r="K7">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L7">
         <v>1.01</v>
@@ -2171,10 +2171,10 @@
         <v>2.22</v>
       </c>
       <c r="Q7">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="R7">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="S7">
         <v>2.82</v>
@@ -2389,7 +2389,7 @@
         <v>2.88</v>
       </c>
       <c r="I8">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="J8">
         <v>4.2</v>
@@ -2410,7 +2410,7 @@
         <v>1.13</v>
       </c>
       <c r="P8">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="Q8">
         <v>1.41</v>
@@ -2428,7 +2428,7 @@
         <v>3</v>
       </c>
       <c r="V8">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="W8">
         <v>1.74</v>
@@ -2437,7 +2437,7 @@
         <v>42</v>
       </c>
       <c r="Y8">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Z8">
         <v>34</v>
@@ -2449,7 +2449,7 @@
         <v>23</v>
       </c>
       <c r="AC8">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD8">
         <v>17.5</v>
@@ -2458,13 +2458,13 @@
         <v>32</v>
       </c>
       <c r="AF8">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AG8">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH8">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AI8">
         <v>34</v>
@@ -2476,7 +2476,7 @@
         <v>24</v>
       </c>
       <c r="AL8">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AM8">
         <v>50</v>
@@ -2485,22 +2485,22 @@
         <v>10</v>
       </c>
       <c r="AO8">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AP8">
-        <v>4.5</v>
+        <v>5.9</v>
       </c>
       <c r="AQ8">
-        <v>19</v>
+        <v>5.4</v>
       </c>
       <c r="AR8">
         <v>21</v>
       </c>
       <c r="AS8">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="AT8">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AU8">
         <v>9</v>
@@ -2524,7 +2524,7 @@
         <v>21</v>
       </c>
       <c r="BB8">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
       <c r="BC8">
         <v>15</v>
@@ -2533,10 +2533,10 @@
         <v>18</v>
       </c>
       <c r="BE8">
-        <v>4.6</v>
+        <v>5.9</v>
       </c>
       <c r="BF8">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BG8">
         <v>10.5</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-18.xlsx
@@ -334,7 +334,7 @@
     <t>Beijing Guoan</t>
   </si>
   <si>
-    <t>2026-08-16 18:21:03</t>
+    <t>2026-08-16 20:35:58</t>
   </si>
 </sst>
 </file>
@@ -928,25 +928,25 @@
         <v>99</v>
       </c>
       <c r="F2">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="G2">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="H2">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="I2">
-        <v>2.42</v>
+        <v>2.56</v>
       </c>
       <c r="J2">
         <v>3.2</v>
       </c>
       <c r="K2">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L2">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M2">
         <v>1.09</v>
@@ -961,16 +961,16 @@
         <v>1.71</v>
       </c>
       <c r="Q2">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R2">
         <v>1.25</v>
       </c>
       <c r="S2">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T2">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="U2">
         <v>1.95</v>
@@ -979,7 +979,7 @@
         <v>1.6</v>
       </c>
       <c r="W2">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="X2">
         <v>14</v>
@@ -1006,10 +1006,10 @@
         <v>34</v>
       </c>
       <c r="AF2">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AG2">
-        <v>19</v>
+        <v>15.5</v>
       </c>
       <c r="AH2">
         <v>24</v>
@@ -1030,7 +1030,7 @@
         <v>150</v>
       </c>
       <c r="AN2">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AO2">
         <v>28</v>
@@ -1060,10 +1060,10 @@
         <v>20</v>
       </c>
       <c r="AX2">
-        <v>19</v>
+        <v>15.5</v>
       </c>
       <c r="AY2">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AZ2">
         <v>16.5</v>
@@ -1072,31 +1072,31 @@
         <v>34</v>
       </c>
       <c r="BB2">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BC2">
         <v>36</v>
       </c>
       <c r="BD2">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BE2">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BF2">
-        <v>4.7</v>
+        <v>34</v>
       </c>
       <c r="BG2">
         <v>17</v>
       </c>
       <c r="BH2">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BI2">
         <v>2.5</v>
       </c>
       <c r="BJ2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK2">
         <v>6.2</v>
@@ -1105,16 +1105,16 @@
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BN2">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BO2">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="BP2">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="BQ2">
         <v>4.5</v>
@@ -1126,25 +1126,25 @@
         <v>4.7</v>
       </c>
       <c r="BT2">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BU2">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BV2">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BW2">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BX2">
+        <v>44</v>
+      </c>
+      <c r="BY2">
+        <v>4.7</v>
+      </c>
+      <c r="BZ2">
         <v>42</v>
-      </c>
-      <c r="BY2">
-        <v>4.6</v>
-      </c>
-      <c r="BZ2">
-        <v>40</v>
       </c>
       <c r="CA2">
         <v>4.6</v>
@@ -1176,10 +1176,10 @@
         <v>3.2</v>
       </c>
       <c r="H3">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="J3">
         <v>2.88</v>
@@ -1194,7 +1194,7 @@
         <v>1.15</v>
       </c>
       <c r="N3">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="O3">
         <v>1.66</v>
@@ -1221,7 +1221,7 @@
         <v>1.5</v>
       </c>
       <c r="W3">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="X3">
         <v>7.4</v>
@@ -1245,13 +1245,13 @@
         <v>18.5</v>
       </c>
       <c r="AE3">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AF3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG3">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AH3">
         <v>34</v>
@@ -1263,7 +1263,7 @@
         <v>85</v>
       </c>
       <c r="AK3">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AL3">
         <v>1000</v>
@@ -1272,7 +1272,7 @@
         <v>270</v>
       </c>
       <c r="AN3">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AO3">
         <v>1000</v>
@@ -1293,7 +1293,7 @@
         <v>7.2</v>
       </c>
       <c r="AU3">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV3">
         <v>12</v>
@@ -1308,7 +1308,7 @@
         <v>12</v>
       </c>
       <c r="AZ3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA3">
         <v>38</v>
@@ -1335,19 +1335,19 @@
         <v>2.52</v>
       </c>
       <c r="BI3">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="BJ3">
         <v>12</v>
       </c>
       <c r="BK3">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.04</v>
+        <v>16.5</v>
       </c>
       <c r="BN3">
         <v>5.9</v>
@@ -1359,13 +1359,13 @@
         <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>1.04</v>
+        <v>13.5</v>
       </c>
       <c r="BT3">
         <v>5.7</v>
@@ -1377,19 +1377,19 @@
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.04</v>
+        <v>13.5</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>1.04</v>
+        <v>13.5</v>
       </c>
       <c r="CB3" t="s">
         <v>106</v>
@@ -1430,7 +1430,7 @@
         <v>4</v>
       </c>
       <c r="L4">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="M4">
         <v>1.06</v>
@@ -1442,10 +1442,10 @@
         <v>1.26</v>
       </c>
       <c r="P4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q4">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="R4">
         <v>1.4</v>
@@ -1654,10 +1654,10 @@
         <v>102</v>
       </c>
       <c r="F5">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="G5">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="H5">
         <v>4.4</v>
@@ -1666,7 +1666,7 @@
         <v>5.1</v>
       </c>
       <c r="J5">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K5">
         <v>4.3</v>
@@ -1684,7 +1684,7 @@
         <v>1.25</v>
       </c>
       <c r="P5">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="Q5">
         <v>1.73</v>
@@ -1699,13 +1699,13 @@
         <v>1.69</v>
       </c>
       <c r="U5">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="V5">
         <v>1.24</v>
       </c>
       <c r="W5">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="X5">
         <v>21</v>
@@ -1920,7 +1920,7 @@
         <v>1.05</v>
       </c>
       <c r="N6">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O6">
         <v>1.25</v>
@@ -1935,7 +1935,7 @@
         <v>1.49</v>
       </c>
       <c r="S6">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="T6">
         <v>1.65</v>
@@ -1953,7 +1953,7 @@
         <v>21</v>
       </c>
       <c r="Y6">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="Z6">
         <v>26</v>
@@ -2061,7 +2061,7 @@
         <v>3.95</v>
       </c>
       <c r="BI6">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="BJ6">
         <v>8.800000000000001</v>
@@ -2153,7 +2153,7 @@
         <v>4.4</v>
       </c>
       <c r="K7">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L7">
         <v>1.01</v>
@@ -2165,31 +2165,31 @@
         <v>4.6</v>
       </c>
       <c r="O7">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P7">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="Q7">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R7">
         <v>1.5</v>
       </c>
       <c r="S7">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="T7">
         <v>1.86</v>
       </c>
       <c r="U7">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V7">
         <v>1.15</v>
       </c>
       <c r="W7">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="X7">
         <v>950</v>
@@ -2207,7 +2207,7 @@
         <v>9.4</v>
       </c>
       <c r="AC7">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AD7">
         <v>950</v>
@@ -2216,7 +2216,7 @@
         <v>120</v>
       </c>
       <c r="AF7">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AG7">
         <v>10.5</v>
@@ -2228,7 +2228,7 @@
         <v>110</v>
       </c>
       <c r="AJ7">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AK7">
         <v>16</v>
@@ -2240,7 +2240,7 @@
         <v>140</v>
       </c>
       <c r="AN7">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AO7">
         <v>140</v>
@@ -2252,10 +2252,10 @@
         <v>21</v>
       </c>
       <c r="AR7">
-        <v>9.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="AS7">
-        <v>10</v>
+        <v>6.8</v>
       </c>
       <c r="AT7">
         <v>8.199999999999999</v>
@@ -2264,10 +2264,10 @@
         <v>9.4</v>
       </c>
       <c r="AV7">
-        <v>7.6</v>
+        <v>5.6</v>
       </c>
       <c r="AW7">
-        <v>9.6</v>
+        <v>6.6</v>
       </c>
       <c r="AX7">
         <v>8.6</v>
@@ -2276,10 +2276,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ7">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="BA7">
-        <v>9.6</v>
+        <v>6.4</v>
       </c>
       <c r="BB7">
         <v>12.5</v>
@@ -2288,16 +2288,16 @@
         <v>13.5</v>
       </c>
       <c r="BD7">
-        <v>8.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="BE7">
-        <v>9.800000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="BF7">
         <v>6.4</v>
       </c>
       <c r="BG7">
-        <v>9.800000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2380,16 +2380,16 @@
         <v>105</v>
       </c>
       <c r="F8">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="G8">
-        <v>2.34</v>
+        <v>2.24</v>
       </c>
       <c r="H8">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="I8">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="J8">
         <v>4.2</v>
@@ -2428,16 +2428,16 @@
         <v>3</v>
       </c>
       <c r="V8">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W8">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="X8">
         <v>42</v>
       </c>
       <c r="Y8">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Z8">
         <v>34</v>
@@ -2458,10 +2458,10 @@
         <v>32</v>
       </c>
       <c r="AF8">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG8">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH8">
         <v>15</v>
@@ -2470,10 +2470,10 @@
         <v>34</v>
       </c>
       <c r="AJ8">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK8">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL8">
         <v>25</v>
@@ -2482,16 +2482,16 @@
         <v>50</v>
       </c>
       <c r="AN8">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AO8">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AP8">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AQ8">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AR8">
         <v>21</v>
@@ -2524,7 +2524,7 @@
         <v>21</v>
       </c>
       <c r="BB8">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BC8">
         <v>15</v>
@@ -2536,7 +2536,7 @@
         <v>5.9</v>
       </c>
       <c r="BF8">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BG8">
         <v>10.5</v>
@@ -2560,13 +2560,13 @@
         <v>1.04</v>
       </c>
       <c r="BN8">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BO8">
         <v>4.7</v>
       </c>
       <c r="BP8">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BQ8">
         <v>1.04</v>
@@ -2581,7 +2581,7 @@
         <v>7.2</v>
       </c>
       <c r="BU8">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BV8">
         <v>1000</v>
@@ -2596,7 +2596,7 @@
         <v>1.04</v>
       </c>
       <c r="BZ8">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="CA8">
         <v>1.04</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-18.xlsx
@@ -334,7 +334,7 @@
     <t>Beijing Guoan</t>
   </si>
   <si>
-    <t>2026-08-16 20:35:58</t>
+    <t>2026-08-16 22:47:13</t>
   </si>
 </sst>
 </file>
@@ -931,13 +931,13 @@
         <v>3.25</v>
       </c>
       <c r="G2">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="I2">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="J2">
         <v>3.2</v>
@@ -955,16 +955,16 @@
         <v>3.05</v>
       </c>
       <c r="O2">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="P2">
         <v>1.71</v>
       </c>
       <c r="Q2">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R2">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S2">
         <v>4.1</v>
@@ -979,13 +979,13 @@
         <v>1.6</v>
       </c>
       <c r="W2">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="X2">
         <v>14</v>
       </c>
       <c r="Y2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Z2">
         <v>16.5</v>
@@ -994,7 +994,7 @@
         <v>38</v>
       </c>
       <c r="AB2">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AC2">
         <v>9.199999999999999</v>
@@ -1006,10 +1006,10 @@
         <v>34</v>
       </c>
       <c r="AF2">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AG2">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH2">
         <v>24</v>
@@ -1072,16 +1072,16 @@
         <v>34</v>
       </c>
       <c r="BB2">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BC2">
         <v>36</v>
       </c>
       <c r="BD2">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BE2">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BF2">
         <v>34</v>
@@ -1105,16 +1105,16 @@
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BN2">
         <v>7.8</v>
       </c>
       <c r="BO2">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="BP2">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BQ2">
         <v>4.5</v>
@@ -1123,7 +1123,7 @@
         <v>70</v>
       </c>
       <c r="BS2">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BT2">
         <v>6.2</v>
@@ -1141,7 +1141,7 @@
         <v>44</v>
       </c>
       <c r="BY2">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BZ2">
         <v>42</v>
@@ -1185,7 +1185,7 @@
         <v>2.88</v>
       </c>
       <c r="K3">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="L3">
         <v>1.66</v>
@@ -1197,13 +1197,13 @@
         <v>2.44</v>
       </c>
       <c r="O3">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="P3">
         <v>1.45</v>
       </c>
       <c r="Q3">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="R3">
         <v>1.16</v>
@@ -1212,7 +1212,7 @@
         <v>6.4</v>
       </c>
       <c r="T3">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="U3">
         <v>1.71</v>
@@ -1239,7 +1239,7 @@
         <v>8</v>
       </c>
       <c r="AC3">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AD3">
         <v>18.5</v>
@@ -1263,7 +1263,7 @@
         <v>85</v>
       </c>
       <c r="AK3">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AL3">
         <v>1000</v>
@@ -1272,7 +1272,7 @@
         <v>270</v>
       </c>
       <c r="AN3">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AO3">
         <v>1000</v>
@@ -1296,7 +1296,7 @@
         <v>6.2</v>
       </c>
       <c r="AV3">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AW3">
         <v>26</v>
@@ -1308,7 +1308,7 @@
         <v>12</v>
       </c>
       <c r="AZ3">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="BA3">
         <v>38</v>
@@ -1427,7 +1427,7 @@
         <v>3.35</v>
       </c>
       <c r="K4">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="L4">
         <v>1.32</v>
@@ -1439,13 +1439,13 @@
         <v>3.95</v>
       </c>
       <c r="O4">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="R4">
         <v>1.4</v>
@@ -1481,7 +1481,7 @@
         <v>12.5</v>
       </c>
       <c r="AC4">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD4">
         <v>16</v>
@@ -1535,13 +1535,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AU4">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AV4">
         <v>11.5</v>
       </c>
       <c r="AW4">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="AX4">
         <v>12</v>
@@ -1562,7 +1562,7 @@
         <v>18.5</v>
       </c>
       <c r="BD4">
-        <v>1.03</v>
+        <v>27</v>
       </c>
       <c r="BE4">
         <v>1.01</v>
@@ -1660,7 +1660,7 @@
         <v>1.9</v>
       </c>
       <c r="H5">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I5">
         <v>5.1</v>
@@ -1696,13 +1696,13 @@
         <v>2.86</v>
       </c>
       <c r="T5">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
       <c r="U5">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="V5">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W5">
         <v>2.1</v>
@@ -1759,7 +1759,7 @@
         <v>12.5</v>
       </c>
       <c r="AO5">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AP5">
         <v>14</v>
@@ -1902,10 +1902,10 @@
         <v>2.48</v>
       </c>
       <c r="H6">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="J6">
         <v>3.8</v>
@@ -1929,13 +1929,13 @@
         <v>2.24</v>
       </c>
       <c r="Q6">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="R6">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S6">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="T6">
         <v>1.65</v>
@@ -1944,10 +1944,10 @@
         <v>2.46</v>
       </c>
       <c r="V6">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W6">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="X6">
         <v>21</v>
@@ -1959,28 +1959,28 @@
         <v>26</v>
       </c>
       <c r="AA6">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB6">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AC6">
         <v>8.800000000000001</v>
       </c>
       <c r="AD6">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AE6">
         <v>34</v>
       </c>
       <c r="AF6">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AG6">
         <v>12</v>
       </c>
       <c r="AH6">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AI6">
         <v>40</v>
@@ -1989,7 +1989,7 @@
         <v>36</v>
       </c>
       <c r="AK6">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AL6">
         <v>36</v>
@@ -2004,7 +2004,7 @@
         <v>27</v>
       </c>
       <c r="AP6">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AQ6">
         <v>13.5</v>
@@ -2028,7 +2028,7 @@
         <v>26</v>
       </c>
       <c r="AX6">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AY6">
         <v>10.5</v>
@@ -2061,61 +2061,61 @@
         <v>3.95</v>
       </c>
       <c r="BI6">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="BJ6">
         <v>8.800000000000001</v>
       </c>
       <c r="BK6">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BN6">
         <v>5.6</v>
       </c>
       <c r="BO6">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="BP6">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BQ6">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BR6">
         <v>26</v>
       </c>
       <c r="BS6">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT6">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BU6">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BV6">
         <v>22</v>
       </c>
       <c r="BW6">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX6">
         <v>30</v>
       </c>
       <c r="BY6">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BZ6">
         <v>19.5</v>
       </c>
       <c r="CA6">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="CB6" t="s">
         <v>106</v>
@@ -2150,7 +2150,7 @@
         <v>7.6</v>
       </c>
       <c r="J7">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K7">
         <v>4.8</v>
@@ -2189,7 +2189,7 @@
         <v>1.15</v>
       </c>
       <c r="W7">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="X7">
         <v>950</v>
@@ -2264,7 +2264,7 @@
         <v>9.4</v>
       </c>
       <c r="AV7">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AW7">
         <v>6.6</v>
@@ -2279,7 +2279,7 @@
         <v>5.5</v>
       </c>
       <c r="BA7">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB7">
         <v>12.5</v>
@@ -2297,7 +2297,7 @@
         <v>6.4</v>
       </c>
       <c r="BG7">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2380,19 +2380,19 @@
         <v>105</v>
       </c>
       <c r="F8">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="G8">
         <v>2.24</v>
       </c>
       <c r="H8">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I8">
         <v>3.25</v>
       </c>
       <c r="J8">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K8">
         <v>4.7</v>
@@ -2401,7 +2401,7 @@
         <v>1.2</v>
       </c>
       <c r="M8">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N8">
         <v>7.2</v>
@@ -2413,16 +2413,16 @@
         <v>3.1</v>
       </c>
       <c r="Q8">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="R8">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="S8">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="T8">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="U8">
         <v>3</v>
@@ -2449,7 +2449,7 @@
         <v>23</v>
       </c>
       <c r="AC8">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AD8">
         <v>17.5</v>
@@ -2497,28 +2497,28 @@
         <v>21</v>
       </c>
       <c r="AS8">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AT8">
         <v>17</v>
       </c>
       <c r="AU8">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AV8">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AW8">
         <v>20</v>
       </c>
       <c r="AX8">
-        <v>16</v>
+        <v>5.2</v>
       </c>
       <c r="AY8">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AZ8">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BA8">
         <v>21</v>
@@ -2527,19 +2527,19 @@
         <v>5.6</v>
       </c>
       <c r="BC8">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BD8">
         <v>18</v>
       </c>
       <c r="BE8">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BF8">
         <v>7.4</v>
       </c>
       <c r="BG8">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BH8">
         <v>5.3</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-18.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="115">
   <si>
     <t>League</t>
   </si>
@@ -274,6 +274,12 @@
     <t>Chinese Super League</t>
   </si>
   <si>
+    <t>CONMEBOL Copa Libertadores</t>
+  </si>
+  <si>
+    <t>Brazilian Serie B</t>
+  </si>
+  <si>
     <t>2026-08-18</t>
   </si>
   <si>
@@ -292,6 +298,12 @@
     <t>11:35:00</t>
   </si>
   <si>
+    <t>22:00:00</t>
+  </si>
+  <si>
+    <t>22:30:00</t>
+  </si>
+  <si>
     <t>Macara</t>
   </si>
   <si>
@@ -313,6 +325,12 @@
     <t>Shanghai Shenhua</t>
   </si>
   <si>
+    <t>Independiente Rivadavia</t>
+  </si>
+  <si>
+    <t>Londrina</t>
+  </si>
+  <si>
     <t>Univ Catolica (Ecu)</t>
   </si>
   <si>
@@ -334,7 +352,13 @@
     <t>Beijing Guoan</t>
   </si>
   <si>
-    <t>2026-08-16 22:47:13</t>
+    <t>Fluminense</t>
+  </si>
+  <si>
+    <t>Atletico GO</t>
+  </si>
+  <si>
+    <t>2026-08-17 00:56:53</t>
   </si>
 </sst>
 </file>
@@ -666,7 +690,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB8"/>
+  <dimension ref="A1:CB10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -916,16 +940,16 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D2" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E2" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="F2">
         <v>3.25</v>
@@ -1150,7 +1174,7 @@
         <v>4.6</v>
       </c>
       <c r="CB2" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1158,25 +1182,25 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D3" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="E3" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="F3">
         <v>3</v>
       </c>
       <c r="G3">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="H3">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="I3">
         <v>3.05</v>
@@ -1212,7 +1236,7 @@
         <v>6.4</v>
       </c>
       <c r="T3">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="U3">
         <v>1.71</v>
@@ -1254,10 +1278,10 @@
         <v>19</v>
       </c>
       <c r="AH3">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AI3">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="AJ3">
         <v>85</v>
@@ -1266,7 +1290,7 @@
         <v>210</v>
       </c>
       <c r="AL3">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="AM3">
         <v>270</v>
@@ -1392,7 +1416,7 @@
         <v>13.5</v>
       </c>
       <c r="CB3" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1400,31 +1424,31 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E4" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="F4">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="G4">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="H4">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="I4">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="J4">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K4">
         <v>4.2</v>
@@ -1436,76 +1460,76 @@
         <v>1.06</v>
       </c>
       <c r="N4">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="O4">
         <v>1.28</v>
       </c>
       <c r="P4">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="Q4">
+        <v>1.79</v>
+      </c>
+      <c r="R4">
+        <v>1.39</v>
+      </c>
+      <c r="S4">
+        <v>3</v>
+      </c>
+      <c r="T4">
+        <v>1.68</v>
+      </c>
+      <c r="U4">
+        <v>2.16</v>
+      </c>
+      <c r="V4">
+        <v>1.32</v>
+      </c>
+      <c r="W4">
         <v>1.78</v>
       </c>
-      <c r="R4">
-        <v>1.4</v>
-      </c>
-      <c r="S4">
-        <v>2.98</v>
-      </c>
-      <c r="T4">
-        <v>1.67</v>
-      </c>
-      <c r="U4">
-        <v>2.18</v>
-      </c>
-      <c r="V4">
-        <v>1.33</v>
-      </c>
-      <c r="W4">
-        <v>1.75</v>
-      </c>
       <c r="X4">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Y4">
         <v>16</v>
       </c>
       <c r="Z4">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AA4">
         <v>80</v>
       </c>
       <c r="AB4">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AC4">
         <v>9</v>
       </c>
       <c r="AD4">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AE4">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AF4">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG4">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH4">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AI4">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AJ4">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AK4">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AL4">
         <v>42</v>
@@ -1526,61 +1550,61 @@
         <v>12.5</v>
       </c>
       <c r="AR4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS4">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AT4">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU4">
         <v>7.2</v>
       </c>
       <c r="AV4">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW4">
         <v>32</v>
       </c>
       <c r="AX4">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AY4">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ4">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BA4">
         <v>32</v>
       </c>
       <c r="BB4">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BC4">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BD4">
         <v>27</v>
       </c>
       <c r="BE4">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BF4">
         <v>12</v>
       </c>
       <c r="BG4">
-        <v>1.01</v>
+        <v>29</v>
       </c>
       <c r="BH4">
         <v>3.8</v>
       </c>
       <c r="BI4">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BJ4">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK4">
         <v>7.2</v>
@@ -1589,37 +1613,37 @@
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN4">
         <v>5.3</v>
       </c>
       <c r="BO4">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BP4">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BQ4">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BR4">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BS4">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BT4">
         <v>7.4</v>
       </c>
       <c r="BU4">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BX4">
         <v>1000</v>
@@ -1631,10 +1655,10 @@
         <v>24</v>
       </c>
       <c r="CA4">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="CB4" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1642,19 +1666,19 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D5" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E5" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="F5">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="G5">
         <v>1.9</v>
@@ -1687,7 +1711,7 @@
         <v>2.12</v>
       </c>
       <c r="Q5">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="R5">
         <v>1.43</v>
@@ -1876,7 +1900,7 @@
         <v>4.5</v>
       </c>
       <c r="CB5" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1884,16 +1908,16 @@
         <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C6" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D6" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E6" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="F6">
         <v>2.42</v>
@@ -1902,16 +1926,16 @@
         <v>2.48</v>
       </c>
       <c r="H6">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="I6">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J6">
         <v>3.8</v>
       </c>
       <c r="K6">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L6">
         <v>1.28</v>
@@ -1920,22 +1944,22 @@
         <v>1.05</v>
       </c>
       <c r="N6">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="O6">
         <v>1.25</v>
       </c>
       <c r="P6">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="Q6">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R6">
         <v>1.5</v>
       </c>
       <c r="S6">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="T6">
         <v>1.65</v>
@@ -1950,13 +1974,13 @@
         <v>1.68</v>
       </c>
       <c r="X6">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y6">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Z6">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AA6">
         <v>55</v>
@@ -2028,7 +2052,7 @@
         <v>26</v>
       </c>
       <c r="AX6">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AY6">
         <v>10.5</v>
@@ -2052,28 +2076,28 @@
         <v>55</v>
       </c>
       <c r="BF6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BG6">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BH6">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BI6">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="BJ6">
         <v>8.800000000000001</v>
       </c>
       <c r="BK6">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BN6">
         <v>5.6</v>
@@ -2082,43 +2106,43 @@
         <v>4.2</v>
       </c>
       <c r="BP6">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BQ6">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BR6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BS6">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BT6">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BU6">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BV6">
         <v>22</v>
       </c>
       <c r="BW6">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BX6">
         <v>30</v>
       </c>
       <c r="BY6">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ6">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="CA6">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="CB6" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2126,16 +2150,16 @@
         <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C7" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D7" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="E7" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="F7">
         <v>1.54</v>
@@ -2144,13 +2168,13 @@
         <v>1.55</v>
       </c>
       <c r="H7">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="I7">
         <v>7.6</v>
       </c>
       <c r="J7">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K7">
         <v>4.8</v>
@@ -2165,7 +2189,7 @@
         <v>4.6</v>
       </c>
       <c r="O7">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P7">
         <v>2.26</v>
@@ -2180,7 +2204,7 @@
         <v>2.84</v>
       </c>
       <c r="T7">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U7">
         <v>2.06</v>
@@ -2189,7 +2213,7 @@
         <v>1.15</v>
       </c>
       <c r="W7">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="X7">
         <v>950</v>
@@ -2252,13 +2276,13 @@
         <v>21</v>
       </c>
       <c r="AR7">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AS7">
         <v>6.8</v>
       </c>
       <c r="AT7">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AU7">
         <v>9.4</v>
@@ -2273,7 +2297,7 @@
         <v>8.6</v>
       </c>
       <c r="AY7">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ7">
         <v>5.5</v>
@@ -2297,7 +2321,7 @@
         <v>6.4</v>
       </c>
       <c r="BG7">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2360,7 +2384,7 @@
         <v>1.04</v>
       </c>
       <c r="CB7" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2368,28 +2392,28 @@
         <v>85</v>
       </c>
       <c r="B8" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C8" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D8" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="E8" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="F8">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="G8">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="H8">
         <v>3.05</v>
       </c>
       <c r="I8">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="J8">
         <v>4.3</v>
@@ -2422,16 +2446,16 @@
         <v>2.02</v>
       </c>
       <c r="T8">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="U8">
         <v>3</v>
       </c>
       <c r="V8">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W8">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="X8">
         <v>42</v>
@@ -2446,7 +2470,7 @@
         <v>55</v>
       </c>
       <c r="AB8">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AC8">
         <v>13.5</v>
@@ -2461,7 +2485,7 @@
         <v>24</v>
       </c>
       <c r="AG8">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AH8">
         <v>15</v>
@@ -2485,19 +2509,19 @@
         <v>9.6</v>
       </c>
       <c r="AO8">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AP8">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="AQ8">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="AR8">
         <v>21</v>
       </c>
       <c r="AS8">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="AT8">
         <v>17</v>
@@ -2512,7 +2536,7 @@
         <v>20</v>
       </c>
       <c r="AX8">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="AY8">
         <v>11</v>
@@ -2524,7 +2548,7 @@
         <v>21</v>
       </c>
       <c r="BB8">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BC8">
         <v>17</v>
@@ -2533,13 +2557,13 @@
         <v>18</v>
       </c>
       <c r="BE8">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BF8">
         <v>7.4</v>
       </c>
       <c r="BG8">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BH8">
         <v>5.3</v>
@@ -2551,58 +2575,542 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BK8">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>1.04</v>
+        <v>13.5</v>
       </c>
       <c r="BN8">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BO8">
         <v>4.7</v>
       </c>
       <c r="BP8">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BR8">
         <v>1000</v>
       </c>
       <c r="BS8">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT8">
         <v>7.2</v>
       </c>
       <c r="BU8">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BV8">
         <v>1000</v>
       </c>
       <c r="BW8">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BZ8">
         <v>11.5</v>
       </c>
       <c r="CA8">
+        <v>7</v>
+      </c>
+      <c r="CB8" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="9" spans="1:80">
+      <c r="A9" t="s">
+        <v>86</v>
+      </c>
+      <c r="B9" t="s">
+        <v>88</v>
+      </c>
+      <c r="C9" t="s">
+        <v>94</v>
+      </c>
+      <c r="D9" t="s">
+        <v>103</v>
+      </c>
+      <c r="E9" t="s">
+        <v>112</v>
+      </c>
+      <c r="F9">
+        <v>2.4</v>
+      </c>
+      <c r="G9">
+        <v>2.6</v>
+      </c>
+      <c r="H9">
+        <v>3.45</v>
+      </c>
+      <c r="I9">
+        <v>3.95</v>
+      </c>
+      <c r="J9">
+        <v>2.92</v>
+      </c>
+      <c r="K9">
+        <v>3.2</v>
+      </c>
+      <c r="L9">
+        <v>1.01</v>
+      </c>
+      <c r="M9">
+        <v>1.14</v>
+      </c>
+      <c r="N9">
+        <v>2.42</v>
+      </c>
+      <c r="O9">
+        <v>1.6</v>
+      </c>
+      <c r="P9">
+        <v>1.46</v>
+      </c>
+      <c r="Q9">
+        <v>2.8</v>
+      </c>
+      <c r="R9">
+        <v>1.18</v>
+      </c>
+      <c r="S9">
+        <v>5.9</v>
+      </c>
+      <c r="T9">
+        <v>2.2</v>
+      </c>
+      <c r="U9">
+        <v>1.68</v>
+      </c>
+      <c r="V9">
+        <v>1.33</v>
+      </c>
+      <c r="W9">
+        <v>1.62</v>
+      </c>
+      <c r="X9">
+        <v>9</v>
+      </c>
+      <c r="Y9">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Z9">
+        <v>28</v>
+      </c>
+      <c r="AA9">
+        <v>100</v>
+      </c>
+      <c r="AB9">
+        <v>7.4</v>
+      </c>
+      <c r="AC9">
+        <v>7.6</v>
+      </c>
+      <c r="AD9">
+        <v>17.5</v>
+      </c>
+      <c r="AE9">
+        <v>75</v>
+      </c>
+      <c r="AF9">
+        <v>15</v>
+      </c>
+      <c r="AG9">
+        <v>13.5</v>
+      </c>
+      <c r="AH9">
+        <v>950</v>
+      </c>
+      <c r="AI9">
+        <v>110</v>
+      </c>
+      <c r="AJ9">
+        <v>46</v>
+      </c>
+      <c r="AK9">
+        <v>46</v>
+      </c>
+      <c r="AL9">
+        <v>75</v>
+      </c>
+      <c r="AM9">
+        <v>260</v>
+      </c>
+      <c r="AN9">
+        <v>55</v>
+      </c>
+      <c r="AO9">
+        <v>110</v>
+      </c>
+      <c r="AP9">
+        <v>7</v>
+      </c>
+      <c r="AQ9">
+        <v>8</v>
+      </c>
+      <c r="AR9">
+        <v>20</v>
+      </c>
+      <c r="AS9">
+        <v>7.2</v>
+      </c>
+      <c r="AT9">
+        <v>6</v>
+      </c>
+      <c r="AU9">
+        <v>6.2</v>
+      </c>
+      <c r="AV9">
+        <v>14</v>
+      </c>
+      <c r="AW9">
+        <v>7</v>
+      </c>
+      <c r="AX9">
+        <v>12</v>
+      </c>
+      <c r="AY9">
+        <v>10.5</v>
+      </c>
+      <c r="AZ9">
+        <v>21</v>
+      </c>
+      <c r="BA9">
+        <v>7.2</v>
+      </c>
+      <c r="BB9">
+        <v>6.6</v>
+      </c>
+      <c r="BC9">
+        <v>6.6</v>
+      </c>
+      <c r="BD9">
+        <v>7</v>
+      </c>
+      <c r="BE9">
+        <v>7.6</v>
+      </c>
+      <c r="BF9">
+        <v>6.8</v>
+      </c>
+      <c r="BG9">
+        <v>7.2</v>
+      </c>
+      <c r="BH9">
+        <v>1000</v>
+      </c>
+      <c r="BI9">
         <v>1.04</v>
       </c>
-      <c r="CB8" t="s">
-        <v>106</v>
+      <c r="BJ9">
+        <v>1000</v>
+      </c>
+      <c r="BK9">
+        <v>1.04</v>
+      </c>
+      <c r="BL9">
+        <v>1000</v>
+      </c>
+      <c r="BM9">
+        <v>1.04</v>
+      </c>
+      <c r="BN9">
+        <v>1000</v>
+      </c>
+      <c r="BO9">
+        <v>1.04</v>
+      </c>
+      <c r="BP9">
+        <v>1000</v>
+      </c>
+      <c r="BQ9">
+        <v>1.04</v>
+      </c>
+      <c r="BR9">
+        <v>1000</v>
+      </c>
+      <c r="BS9">
+        <v>1.04</v>
+      </c>
+      <c r="BT9">
+        <v>1000</v>
+      </c>
+      <c r="BU9">
+        <v>1.04</v>
+      </c>
+      <c r="BV9">
+        <v>1000</v>
+      </c>
+      <c r="BW9">
+        <v>1.04</v>
+      </c>
+      <c r="BX9">
+        <v>1000</v>
+      </c>
+      <c r="BY9">
+        <v>1.04</v>
+      </c>
+      <c r="BZ9">
+        <v>1000</v>
+      </c>
+      <c r="CA9">
+        <v>1.04</v>
+      </c>
+      <c r="CB9" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="10" spans="1:80">
+      <c r="A10" t="s">
+        <v>87</v>
+      </c>
+      <c r="B10" t="s">
+        <v>88</v>
+      </c>
+      <c r="C10" t="s">
+        <v>95</v>
+      </c>
+      <c r="D10" t="s">
+        <v>104</v>
+      </c>
+      <c r="E10" t="s">
+        <v>113</v>
+      </c>
+      <c r="F10">
+        <v>2.8</v>
+      </c>
+      <c r="G10">
+        <v>3.25</v>
+      </c>
+      <c r="H10">
+        <v>2.64</v>
+      </c>
+      <c r="I10">
+        <v>2.96</v>
+      </c>
+      <c r="J10">
+        <v>2.82</v>
+      </c>
+      <c r="K10">
+        <v>3.6</v>
+      </c>
+      <c r="L10">
+        <v>1.44</v>
+      </c>
+      <c r="M10">
+        <v>1.09</v>
+      </c>
+      <c r="N10">
+        <v>3.3</v>
+      </c>
+      <c r="O10">
+        <v>1.38</v>
+      </c>
+      <c r="P10">
+        <v>1.76</v>
+      </c>
+      <c r="Q10">
+        <v>2.16</v>
+      </c>
+      <c r="R10">
+        <v>1.28</v>
+      </c>
+      <c r="S10">
+        <v>4</v>
+      </c>
+      <c r="T10">
+        <v>1.84</v>
+      </c>
+      <c r="U10">
+        <v>2</v>
+      </c>
+      <c r="V10">
+        <v>1.51</v>
+      </c>
+      <c r="W10">
+        <v>1.44</v>
+      </c>
+      <c r="X10">
+        <v>13.5</v>
+      </c>
+      <c r="Y10">
+        <v>10</v>
+      </c>
+      <c r="Z10">
+        <v>18</v>
+      </c>
+      <c r="AA10">
+        <v>50</v>
+      </c>
+      <c r="AB10">
+        <v>10.5</v>
+      </c>
+      <c r="AC10">
+        <v>7.6</v>
+      </c>
+      <c r="AD10">
+        <v>13</v>
+      </c>
+      <c r="AE10">
+        <v>40</v>
+      </c>
+      <c r="AF10">
+        <v>24</v>
+      </c>
+      <c r="AG10">
+        <v>13.5</v>
+      </c>
+      <c r="AH10">
+        <v>19</v>
+      </c>
+      <c r="AI10">
+        <v>60</v>
+      </c>
+      <c r="AJ10">
+        <v>60</v>
+      </c>
+      <c r="AK10">
+        <v>46</v>
+      </c>
+      <c r="AL10">
+        <v>60</v>
+      </c>
+      <c r="AM10">
+        <v>140</v>
+      </c>
+      <c r="AN10">
+        <v>46</v>
+      </c>
+      <c r="AO10">
+        <v>36</v>
+      </c>
+      <c r="AP10">
+        <v>10</v>
+      </c>
+      <c r="AQ10">
+        <v>8.4</v>
+      </c>
+      <c r="AR10">
+        <v>15</v>
+      </c>
+      <c r="AS10">
+        <v>8</v>
+      </c>
+      <c r="AT10">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU10">
+        <v>6.6</v>
+      </c>
+      <c r="AV10">
+        <v>11</v>
+      </c>
+      <c r="AW10">
+        <v>25</v>
+      </c>
+      <c r="AX10">
+        <v>14.5</v>
+      </c>
+      <c r="AY10">
+        <v>11.5</v>
+      </c>
+      <c r="AZ10">
+        <v>16</v>
+      </c>
+      <c r="BA10">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB10">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC10">
+        <v>27</v>
+      </c>
+      <c r="BD10">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE10">
+        <v>9</v>
+      </c>
+      <c r="BF10">
+        <v>30</v>
+      </c>
+      <c r="BG10">
+        <v>27</v>
+      </c>
+      <c r="BH10">
+        <v>1000</v>
+      </c>
+      <c r="BI10">
+        <v>1.04</v>
+      </c>
+      <c r="BJ10">
+        <v>1000</v>
+      </c>
+      <c r="BK10">
+        <v>1.04</v>
+      </c>
+      <c r="BL10">
+        <v>1000</v>
+      </c>
+      <c r="BM10">
+        <v>1.04</v>
+      </c>
+      <c r="BN10">
+        <v>1000</v>
+      </c>
+      <c r="BO10">
+        <v>1.04</v>
+      </c>
+      <c r="BP10">
+        <v>1000</v>
+      </c>
+      <c r="BQ10">
+        <v>1.04</v>
+      </c>
+      <c r="BR10">
+        <v>1000</v>
+      </c>
+      <c r="BS10">
+        <v>1.04</v>
+      </c>
+      <c r="BT10">
+        <v>1000</v>
+      </c>
+      <c r="BU10">
+        <v>1.04</v>
+      </c>
+      <c r="BV10">
+        <v>1000</v>
+      </c>
+      <c r="BW10">
+        <v>1.04</v>
+      </c>
+      <c r="BX10">
+        <v>1000</v>
+      </c>
+      <c r="BY10">
+        <v>1.04</v>
+      </c>
+      <c r="BZ10">
+        <v>1000</v>
+      </c>
+      <c r="CA10">
+        <v>1.04</v>
+      </c>
+      <c r="CB10" t="s">
+        <v>114</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-18.xlsx
@@ -358,7 +358,7 @@
     <t>Atletico GO</t>
   </si>
   <si>
-    <t>2026-08-17 00:56:53</t>
+    <t>2026-08-17 03:05:56</t>
   </si>
 </sst>
 </file>
@@ -952,7 +952,7 @@
         <v>105</v>
       </c>
       <c r="F2">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="G2">
         <v>4</v>
@@ -961,52 +961,52 @@
         <v>2.3</v>
       </c>
       <c r="I2">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="J2">
         <v>3.2</v>
       </c>
       <c r="K2">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="L2">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M2">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N2">
         <v>3.05</v>
       </c>
       <c r="O2">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="P2">
         <v>1.71</v>
       </c>
       <c r="Q2">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R2">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S2">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="T2">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="U2">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="V2">
         <v>1.6</v>
       </c>
       <c r="W2">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="X2">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y2">
         <v>10.5</v>
@@ -1033,7 +1033,7 @@
         <v>30</v>
       </c>
       <c r="AG2">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AH2">
         <v>24</v>
@@ -1048,7 +1048,7 @@
         <v>60</v>
       </c>
       <c r="AL2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AM2">
         <v>150</v>
@@ -1096,16 +1096,16 @@
         <v>34</v>
       </c>
       <c r="BB2">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BC2">
         <v>36</v>
       </c>
       <c r="BD2">
+        <v>4.8</v>
+      </c>
+      <c r="BE2">
         <v>5</v>
-      </c>
-      <c r="BE2">
-        <v>5.2</v>
       </c>
       <c r="BF2">
         <v>34</v>
@@ -1117,10 +1117,10 @@
         <v>3.55</v>
       </c>
       <c r="BI2">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="BJ2">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BK2">
         <v>6.2</v>
@@ -1129,7 +1129,7 @@
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="BN2">
         <v>7.8</v>
@@ -1138,19 +1138,19 @@
         <v>4.9</v>
       </c>
       <c r="BP2">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BQ2">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BR2">
         <v>70</v>
       </c>
       <c r="BS2">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="BT2">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="BU2">
         <v>4.5</v>
@@ -1159,19 +1159,19 @@
         <v>19.5</v>
       </c>
       <c r="BW2">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BX2">
         <v>44</v>
       </c>
       <c r="BY2">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="BZ2">
         <v>42</v>
       </c>
       <c r="CA2">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="CB2" t="s">
         <v>114</v>
@@ -1194,16 +1194,16 @@
         <v>106</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="G3">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="H3">
         <v>2.88</v>
       </c>
       <c r="I3">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="J3">
         <v>2.88</v>
@@ -1212,16 +1212,16 @@
         <v>3</v>
       </c>
       <c r="L3">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="M3">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="N3">
         <v>2.44</v>
       </c>
       <c r="O3">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="P3">
         <v>1.45</v>
@@ -1230,10 +1230,10 @@
         <v>3.05</v>
       </c>
       <c r="R3">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="S3">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="T3">
         <v>2.32</v>
@@ -1245,7 +1245,7 @@
         <v>1.5</v>
       </c>
       <c r="W3">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="X3">
         <v>7.4</v>
@@ -1266,7 +1266,7 @@
         <v>6.8</v>
       </c>
       <c r="AD3">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE3">
         <v>150</v>
@@ -1275,13 +1275,13 @@
         <v>23</v>
       </c>
       <c r="AG3">
-        <v>19</v>
+        <v>15.5</v>
       </c>
       <c r="AH3">
         <v>32</v>
       </c>
       <c r="AI3">
-        <v>990</v>
+        <v>970</v>
       </c>
       <c r="AJ3">
         <v>85</v>
@@ -1290,7 +1290,7 @@
         <v>210</v>
       </c>
       <c r="AL3">
-        <v>990</v>
+        <v>980</v>
       </c>
       <c r="AM3">
         <v>270</v>
@@ -1299,22 +1299,22 @@
         <v>1000</v>
       </c>
       <c r="AO3">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AP3">
         <v>6.6</v>
       </c>
       <c r="AQ3">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AR3">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AS3">
         <v>27</v>
       </c>
       <c r="AT3">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU3">
         <v>6.2</v>
@@ -1329,7 +1329,7 @@
         <v>16</v>
       </c>
       <c r="AY3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ3">
         <v>19</v>
@@ -1338,7 +1338,7 @@
         <v>38</v>
       </c>
       <c r="BB3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BC3">
         <v>27</v>
@@ -1356,7 +1356,7 @@
         <v>30</v>
       </c>
       <c r="BH3">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="BI3">
         <v>2.2</v>
@@ -1365,13 +1365,13 @@
         <v>12</v>
       </c>
       <c r="BK3">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>16.5</v>
+        <v>12</v>
       </c>
       <c r="BN3">
         <v>5.9</v>
@@ -1380,40 +1380,40 @@
         <v>4.7</v>
       </c>
       <c r="BP3">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BQ3">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BT3">
         <v>5.7</v>
       </c>
       <c r="BU3">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>13.5</v>
+        <v>2.12</v>
       </c>
       <c r="CB3" t="s">
         <v>114</v>
@@ -1436,46 +1436,46 @@
         <v>107</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="G4">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="H4">
         <v>3.45</v>
       </c>
       <c r="I4">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="J4">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K4">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="L4">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="M4">
         <v>1.06</v>
       </c>
       <c r="N4">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="O4">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P4">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="Q4">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="R4">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="S4">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="T4">
         <v>1.68</v>
@@ -1484,10 +1484,10 @@
         <v>2.16</v>
       </c>
       <c r="V4">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="W4">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="X4">
         <v>19</v>
@@ -1517,13 +1517,13 @@
         <v>15</v>
       </c>
       <c r="AG4">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH4">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AI4">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ4">
         <v>28</v>
@@ -1544,58 +1544,58 @@
         <v>44</v>
       </c>
       <c r="AP4">
-        <v>12.5</v>
+        <v>5.3</v>
       </c>
       <c r="AQ4">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AR4">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="AS4">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT4">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AU4">
-        <v>7.2</v>
+        <v>4</v>
       </c>
       <c r="AV4">
+        <v>5.1</v>
+      </c>
+      <c r="AW4">
+        <v>6.4</v>
+      </c>
+      <c r="AX4">
+        <v>5</v>
+      </c>
+      <c r="AY4">
+        <v>8</v>
+      </c>
+      <c r="AZ4">
         <v>12</v>
       </c>
-      <c r="AW4">
-        <v>32</v>
-      </c>
-      <c r="AX4">
-        <v>11.5</v>
-      </c>
-      <c r="AY4">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ4">
-        <v>13</v>
-      </c>
       <c r="BA4">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="BB4">
-        <v>21</v>
+        <v>5.9</v>
       </c>
       <c r="BC4">
-        <v>18</v>
+        <v>5.6</v>
       </c>
       <c r="BD4">
-        <v>27</v>
+        <v>6.2</v>
       </c>
       <c r="BE4">
         <v>6.8</v>
       </c>
       <c r="BF4">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="BG4">
-        <v>29</v>
+        <v>6.2</v>
       </c>
       <c r="BH4">
         <v>3.8</v>
@@ -1678,7 +1678,7 @@
         <v>108</v>
       </c>
       <c r="F5">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="G5">
         <v>1.9</v>
@@ -1687,37 +1687,37 @@
         <v>4.5</v>
       </c>
       <c r="I5">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="J5">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K5">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="L5">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="M5">
         <v>1.05</v>
       </c>
       <c r="N5">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="O5">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P5">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="Q5">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="R5">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="S5">
-        <v>2.86</v>
+        <v>3.05</v>
       </c>
       <c r="T5">
         <v>1.63</v>
@@ -1726,178 +1726,178 @@
         <v>2.2</v>
       </c>
       <c r="V5">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="W5">
         <v>2.1</v>
       </c>
       <c r="X5">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Y5">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="Z5">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="AA5">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AB5">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AC5">
-        <v>9.6</v>
+        <v>17</v>
       </c>
       <c r="AD5">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AE5">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AF5">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="AG5">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AH5">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AI5">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ5">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="AK5">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AL5">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="AM5">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN5">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AO5">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AP5">
-        <v>14</v>
+        <v>1.51</v>
       </c>
       <c r="AQ5">
-        <v>15.5</v>
+        <v>1.44</v>
       </c>
       <c r="AR5">
-        <v>28</v>
+        <v>1.49</v>
       </c>
       <c r="AS5">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="AT5">
-        <v>8.6</v>
+        <v>1.39</v>
       </c>
       <c r="AU5">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="AV5">
-        <v>15.5</v>
+        <v>1.51</v>
       </c>
       <c r="AW5">
-        <v>6.6</v>
+        <v>1.51</v>
       </c>
       <c r="AX5">
-        <v>10.5</v>
+        <v>1.42</v>
       </c>
       <c r="AY5">
-        <v>8.800000000000001</v>
+        <v>1.42</v>
       </c>
       <c r="AZ5">
-        <v>15</v>
+        <v>1.46</v>
       </c>
       <c r="BA5">
-        <v>6.6</v>
+        <v>1.51</v>
       </c>
       <c r="BB5">
-        <v>17</v>
+        <v>1.46</v>
       </c>
       <c r="BC5">
-        <v>15.5</v>
+        <v>1.46</v>
       </c>
       <c r="BD5">
-        <v>21</v>
+        <v>1.48</v>
       </c>
       <c r="BE5">
-        <v>6.8</v>
+        <v>1.51</v>
       </c>
       <c r="BF5">
-        <v>9</v>
+        <v>3.5</v>
       </c>
       <c r="BG5">
-        <v>6.6</v>
+        <v>4.9</v>
       </c>
       <c r="BH5">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="BI5">
-        <v>3.1</v>
+        <v>1.04</v>
       </c>
       <c r="BJ5">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK5">
-        <v>3.7</v>
+        <v>1.04</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BN5">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="BO5">
-        <v>3.75</v>
+        <v>1.04</v>
       </c>
       <c r="BP5">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="BR5">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BS5">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BT5">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BU5">
-        <v>3.5</v>
+        <v>1.04</v>
       </c>
       <c r="BV5">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BW5">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="BX5">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BY5">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="BZ5">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="CA5">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="CB5" t="s">
         <v>114</v>
@@ -1938,31 +1938,31 @@
         <v>3.9</v>
       </c>
       <c r="L6">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="M6">
         <v>1.05</v>
       </c>
       <c r="N6">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O6">
         <v>1.25</v>
       </c>
       <c r="P6">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q6">
         <v>1.76</v>
       </c>
       <c r="R6">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="S6">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="T6">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="U6">
         <v>2.46</v>
@@ -1971,13 +1971,13 @@
         <v>1.48</v>
       </c>
       <c r="W6">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="X6">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Y6">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="Z6">
         <v>23</v>
@@ -1986,16 +1986,16 @@
         <v>55</v>
       </c>
       <c r="AB6">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC6">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD6">
         <v>13.5</v>
       </c>
       <c r="AE6">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF6">
         <v>21</v>
@@ -2028,7 +2028,7 @@
         <v>27</v>
       </c>
       <c r="AP6">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AQ6">
         <v>13.5</v>
@@ -2043,7 +2043,7 @@
         <v>12</v>
       </c>
       <c r="AU6">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV6">
         <v>11.5</v>
@@ -2103,7 +2103,7 @@
         <v>5.6</v>
       </c>
       <c r="BO6">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BP6">
         <v>17</v>
@@ -2121,7 +2121,7 @@
         <v>6.4</v>
       </c>
       <c r="BU6">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BV6">
         <v>22</v>
@@ -2165,49 +2165,49 @@
         <v>1.54</v>
       </c>
       <c r="G7">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="H7">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="I7">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J7">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K7">
         <v>4.8</v>
       </c>
       <c r="L7">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M7">
         <v>1.05</v>
       </c>
       <c r="N7">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="O7">
         <v>1.24</v>
       </c>
       <c r="P7">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q7">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R7">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S7">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="T7">
         <v>1.87</v>
       </c>
       <c r="U7">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V7">
         <v>1.15</v>
@@ -2267,7 +2267,7 @@
         <v>8.4</v>
       </c>
       <c r="AO7">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AP7">
         <v>17</v>
@@ -2276,10 +2276,10 @@
         <v>21</v>
       </c>
       <c r="AR7">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AS7">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AT7">
         <v>8.4</v>
@@ -2288,10 +2288,10 @@
         <v>9.4</v>
       </c>
       <c r="AV7">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AW7">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX7">
         <v>8.6</v>
@@ -2300,7 +2300,7 @@
         <v>9</v>
       </c>
       <c r="AZ7">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BA7">
         <v>6.6</v>
@@ -2315,73 +2315,73 @@
         <v>6.2</v>
       </c>
       <c r="BE7">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF7">
         <v>6.4</v>
       </c>
       <c r="BG7">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH7">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BI7">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="BJ7">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK7">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BN7">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BO7">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="BP7">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BQ7">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="BR7">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BS7">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BT7">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BU7">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="BV7">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BW7">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BX7">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BY7">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BZ7">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="CA7">
-        <v>1.04</v>
+        <v>3.8</v>
       </c>
       <c r="CB7" t="s">
         <v>114</v>
@@ -2410,7 +2410,7 @@
         <v>2.22</v>
       </c>
       <c r="H8">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I8">
         <v>3.3</v>
@@ -2488,7 +2488,7 @@
         <v>14.5</v>
       </c>
       <c r="AH8">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AI8">
         <v>34</v>
@@ -2500,7 +2500,7 @@
         <v>23</v>
       </c>
       <c r="AL8">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AM8">
         <v>50</v>
@@ -2509,7 +2509,7 @@
         <v>9.6</v>
       </c>
       <c r="AO8">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AP8">
         <v>5.5</v>
@@ -2646,19 +2646,19 @@
         <v>112</v>
       </c>
       <c r="F9">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="G9">
         <v>2.6</v>
       </c>
       <c r="H9">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="I9">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="J9">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="K9">
         <v>3.2</v>
@@ -2670,7 +2670,7 @@
         <v>1.14</v>
       </c>
       <c r="N9">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="O9">
         <v>1.6</v>
@@ -2691,10 +2691,10 @@
         <v>2.2</v>
       </c>
       <c r="U9">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="V9">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="W9">
         <v>1.62</v>
@@ -2706,25 +2706,25 @@
         <v>9.800000000000001</v>
       </c>
       <c r="Z9">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AA9">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AB9">
         <v>7.4</v>
       </c>
       <c r="AC9">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD9">
         <v>17.5</v>
       </c>
       <c r="AE9">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AF9">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AG9">
         <v>13.5</v>
@@ -2733,25 +2733,25 @@
         <v>950</v>
       </c>
       <c r="AI9">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AJ9">
         <v>46</v>
       </c>
       <c r="AK9">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AL9">
         <v>75</v>
       </c>
       <c r="AM9">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AN9">
         <v>55</v>
       </c>
       <c r="AO9">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AP9">
         <v>7</v>
@@ -2760,13 +2760,13 @@
         <v>8</v>
       </c>
       <c r="AR9">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AS9">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AT9">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AU9">
         <v>6.2</v>
@@ -2775,7 +2775,7 @@
         <v>14</v>
       </c>
       <c r="AW9">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AX9">
         <v>12</v>
@@ -2787,25 +2787,25 @@
         <v>21</v>
       </c>
       <c r="BA9">
+        <v>7.6</v>
+      </c>
+      <c r="BB9">
+        <v>7</v>
+      </c>
+      <c r="BC9">
+        <v>7</v>
+      </c>
+      <c r="BD9">
+        <v>7.4</v>
+      </c>
+      <c r="BE9">
+        <v>8</v>
+      </c>
+      <c r="BF9">
         <v>7.2</v>
       </c>
-      <c r="BB9">
-        <v>6.6</v>
-      </c>
-      <c r="BC9">
-        <v>6.6</v>
-      </c>
-      <c r="BD9">
-        <v>7</v>
-      </c>
-      <c r="BE9">
+      <c r="BG9">
         <v>7.6</v>
-      </c>
-      <c r="BF9">
-        <v>6.8</v>
-      </c>
-      <c r="BG9">
-        <v>7.2</v>
       </c>
       <c r="BH9">
         <v>1000</v>
@@ -2888,7 +2888,7 @@
         <v>113</v>
       </c>
       <c r="F10">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="G10">
         <v>3.25</v>
@@ -2897,73 +2897,73 @@
         <v>2.64</v>
       </c>
       <c r="I10">
-        <v>2.96</v>
+        <v>3.15</v>
       </c>
       <c r="J10">
-        <v>2.82</v>
+        <v>2.68</v>
       </c>
       <c r="K10">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="L10">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="M10">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N10">
         <v>3.3</v>
       </c>
       <c r="O10">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P10">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="Q10">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="R10">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S10">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="T10">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="U10">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V10">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="W10">
         <v>1.44</v>
       </c>
       <c r="X10">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y10">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z10">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA10">
         <v>50</v>
       </c>
       <c r="AB10">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC10">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AD10">
         <v>13</v>
       </c>
       <c r="AE10">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF10">
         <v>24</v>
@@ -2972,13 +2972,13 @@
         <v>13.5</v>
       </c>
       <c r="AH10">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI10">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ10">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AK10">
         <v>46</v>
@@ -2987,7 +2987,7 @@
         <v>60</v>
       </c>
       <c r="AM10">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN10">
         <v>46</v>
@@ -2996,58 +2996,58 @@
         <v>36</v>
       </c>
       <c r="AP10">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AQ10">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR10">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AS10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AT10">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AU10">
         <v>6.6</v>
       </c>
       <c r="AV10">
+        <v>10.5</v>
+      </c>
+      <c r="AW10">
+        <v>6.6</v>
+      </c>
+      <c r="AX10">
+        <v>16.5</v>
+      </c>
+      <c r="AY10">
         <v>11</v>
       </c>
-      <c r="AW10">
-        <v>25</v>
-      </c>
-      <c r="AX10">
-        <v>14.5</v>
-      </c>
-      <c r="AY10">
-        <v>11.5</v>
-      </c>
       <c r="AZ10">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BA10">
-        <v>8.199999999999999</v>
+        <v>36</v>
       </c>
       <c r="BB10">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="BC10">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BD10">
-        <v>8.199999999999999</v>
+        <v>38</v>
       </c>
       <c r="BE10">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="BF10">
-        <v>30</v>
+        <v>6.6</v>
       </c>
       <c r="BG10">
-        <v>27</v>
+        <v>6.4</v>
       </c>
       <c r="BH10">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-18.xlsx
@@ -358,7 +358,7 @@
     <t>Atletico GO</t>
   </si>
   <si>
-    <t>2026-08-17 03:05:56</t>
+    <t>2026-08-17 05:14:50</t>
   </si>
 </sst>
 </file>
@@ -952,16 +952,16 @@
         <v>105</v>
       </c>
       <c r="F2">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="H2">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="I2">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="J2">
         <v>3.2</v>
@@ -970,13 +970,13 @@
         <v>3.45</v>
       </c>
       <c r="L2">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M2">
         <v>1.1</v>
       </c>
       <c r="N2">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O2">
         <v>1.41</v>
@@ -985,10 +985,10 @@
         <v>1.71</v>
       </c>
       <c r="Q2">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R2">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S2">
         <v>4.3</v>
@@ -1000,10 +1000,10 @@
         <v>1.96</v>
       </c>
       <c r="V2">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="W2">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="X2">
         <v>13.5</v>
@@ -1024,7 +1024,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD2">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AE2">
         <v>34</v>
@@ -1048,37 +1048,37 @@
         <v>60</v>
       </c>
       <c r="AL2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM2">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AN2">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AO2">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AP2">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ2">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="AR2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AS2">
         <v>23</v>
       </c>
       <c r="AT2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AU2">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV2">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AW2">
         <v>20</v>
@@ -1087,25 +1087,25 @@
         <v>15.5</v>
       </c>
       <c r="AY2">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AZ2">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA2">
-        <v>34</v>
+        <v>4.5</v>
       </c>
       <c r="BB2">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="BC2">
-        <v>36</v>
+        <v>4.5</v>
       </c>
       <c r="BD2">
+        <v>4.6</v>
+      </c>
+      <c r="BE2">
         <v>4.8</v>
-      </c>
-      <c r="BE2">
-        <v>5</v>
       </c>
       <c r="BF2">
         <v>34</v>
@@ -1123,13 +1123,13 @@
         <v>12.5</v>
       </c>
       <c r="BK2">
-        <v>6.2</v>
+        <v>3.6</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="BN2">
         <v>7.8</v>
@@ -1138,40 +1138,40 @@
         <v>4.9</v>
       </c>
       <c r="BP2">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BQ2">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="BR2">
         <v>70</v>
       </c>
       <c r="BS2">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="BT2">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BU2">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="BV2">
-        <v>19.5</v>
+        <v>26</v>
       </c>
       <c r="BW2">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="BX2">
         <v>44</v>
       </c>
       <c r="BY2">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="BZ2">
         <v>42</v>
       </c>
       <c r="CA2">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="CB2" t="s">
         <v>114</v>
@@ -1197,55 +1197,55 @@
         <v>3.05</v>
       </c>
       <c r="G3">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="H3">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="I3">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="J3">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="K3">
         <v>3</v>
       </c>
       <c r="L3">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="M3">
         <v>1.16</v>
       </c>
       <c r="N3">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="O3">
         <v>1.66</v>
       </c>
       <c r="P3">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="Q3">
         <v>3.05</v>
       </c>
       <c r="R3">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="S3">
         <v>6.8</v>
       </c>
       <c r="T3">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="U3">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="V3">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W3">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="X3">
         <v>7.4</v>
@@ -1260,19 +1260,19 @@
         <v>70</v>
       </c>
       <c r="AB3">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC3">
         <v>6.8</v>
       </c>
       <c r="AD3">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE3">
         <v>150</v>
       </c>
       <c r="AF3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG3">
         <v>15.5</v>
@@ -1281,7 +1281,7 @@
         <v>32</v>
       </c>
       <c r="AI3">
-        <v>970</v>
+        <v>960</v>
       </c>
       <c r="AJ3">
         <v>85</v>
@@ -1290,7 +1290,7 @@
         <v>210</v>
       </c>
       <c r="AL3">
-        <v>980</v>
+        <v>970</v>
       </c>
       <c r="AM3">
         <v>270</v>
@@ -1299,19 +1299,19 @@
         <v>1000</v>
       </c>
       <c r="AO3">
-        <v>950</v>
+        <v>930</v>
       </c>
       <c r="AP3">
         <v>6.6</v>
       </c>
       <c r="AQ3">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AR3">
         <v>15</v>
       </c>
       <c r="AS3">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="AT3">
         <v>7.4</v>
@@ -1320,7 +1320,7 @@
         <v>6.2</v>
       </c>
       <c r="AV3">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AW3">
         <v>26</v>
@@ -1329,7 +1329,7 @@
         <v>16</v>
       </c>
       <c r="AY3">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AZ3">
         <v>19</v>
@@ -1353,28 +1353,28 @@
         <v>48</v>
       </c>
       <c r="BG3">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="BH3">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="BI3">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="BJ3">
         <v>12</v>
       </c>
       <c r="BK3">
-        <v>7.2</v>
+        <v>9.4</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>12</v>
+        <v>16.5</v>
       </c>
       <c r="BN3">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BO3">
         <v>4.7</v>
@@ -1389,13 +1389,13 @@
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BT3">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BU3">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BV3">
         <v>1000</v>
@@ -1407,13 +1407,13 @@
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>2.12</v>
+        <v>13.5</v>
       </c>
       <c r="CB3" t="s">
         <v>114</v>
@@ -1442,13 +1442,13 @@
         <v>2.26</v>
       </c>
       <c r="H4">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="I4">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="J4">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K4">
         <v>4</v>
@@ -1460,13 +1460,13 @@
         <v>1.06</v>
       </c>
       <c r="N4">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O4">
         <v>1.27</v>
       </c>
       <c r="P4">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q4">
         <v>1.84</v>
@@ -1481,7 +1481,7 @@
         <v>1.68</v>
       </c>
       <c r="U4">
-        <v>2.16</v>
+        <v>2.38</v>
       </c>
       <c r="V4">
         <v>1.35</v>
@@ -1496,94 +1496,94 @@
         <v>16</v>
       </c>
       <c r="Z4">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AA4">
         <v>80</v>
       </c>
       <c r="AB4">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC4">
         <v>9</v>
       </c>
       <c r="AD4">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE4">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF4">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AG4">
         <v>13</v>
       </c>
       <c r="AH4">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI4">
         <v>55</v>
       </c>
       <c r="AJ4">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AK4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL4">
         <v>42</v>
       </c>
       <c r="AM4">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AN4">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AO4">
         <v>44</v>
       </c>
       <c r="AP4">
-        <v>5.3</v>
+        <v>12.5</v>
       </c>
       <c r="AQ4">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AR4">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="AS4">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AT4">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU4">
-        <v>4</v>
+        <v>7.2</v>
       </c>
       <c r="AV4">
-        <v>5.1</v>
+        <v>12.5</v>
       </c>
       <c r="AW4">
-        <v>6.4</v>
+        <v>32</v>
       </c>
       <c r="AX4">
-        <v>5</v>
+        <v>12.5</v>
       </c>
       <c r="AY4">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="AZ4">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BA4">
         <v>20</v>
       </c>
       <c r="BB4">
-        <v>5.9</v>
+        <v>20</v>
       </c>
       <c r="BC4">
-        <v>5.6</v>
+        <v>18.5</v>
       </c>
       <c r="BD4">
         <v>6.2</v>
@@ -1592,19 +1592,19 @@
         <v>6.8</v>
       </c>
       <c r="BF4">
-        <v>5</v>
+        <v>11.5</v>
       </c>
       <c r="BG4">
-        <v>6.2</v>
+        <v>26</v>
       </c>
       <c r="BH4">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BI4">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BJ4">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BK4">
         <v>7.2</v>
@@ -1613,7 +1613,7 @@
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN4">
         <v>5.3</v>
@@ -1622,40 +1622,40 @@
         <v>4</v>
       </c>
       <c r="BP4">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BQ4">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BR4">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BS4">
+        <v>7.8</v>
+      </c>
+      <c r="BT4">
         <v>7.2</v>
       </c>
-      <c r="BT4">
-        <v>7.4</v>
-      </c>
       <c r="BU4">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BZ4">
         <v>24</v>
       </c>
       <c r="CA4">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="CB4" t="s">
         <v>114</v>
@@ -1690,7 +1690,7 @@
         <v>4.7</v>
       </c>
       <c r="J5">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K5">
         <v>4.1</v>
@@ -1711,7 +1711,7 @@
         <v>2.18</v>
       </c>
       <c r="Q5">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R5">
         <v>1.46</v>
@@ -1723,7 +1723,7 @@
         <v>1.63</v>
       </c>
       <c r="U5">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V5">
         <v>1.27</v>
@@ -1732,172 +1732,172 @@
         <v>2.1</v>
       </c>
       <c r="X5">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y5">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="Z5">
+        <v>42</v>
+      </c>
+      <c r="AA5">
+        <v>110</v>
+      </c>
+      <c r="AB5">
+        <v>11</v>
+      </c>
+      <c r="AC5">
+        <v>9.6</v>
+      </c>
+      <c r="AD5">
+        <v>19</v>
+      </c>
+      <c r="AE5">
+        <v>65</v>
+      </c>
+      <c r="AF5">
+        <v>13</v>
+      </c>
+      <c r="AG5">
+        <v>12</v>
+      </c>
+      <c r="AH5">
+        <v>18.5</v>
+      </c>
+      <c r="AI5">
+        <v>65</v>
+      </c>
+      <c r="AJ5">
+        <v>22</v>
+      </c>
+      <c r="AK5">
+        <v>19.5</v>
+      </c>
+      <c r="AL5">
+        <v>38</v>
+      </c>
+      <c r="AM5">
         <v>100</v>
       </c>
-      <c r="AA5">
-        <v>1000</v>
-      </c>
-      <c r="AB5">
+      <c r="AN5">
+        <v>11</v>
+      </c>
+      <c r="AO5">
+        <v>60</v>
+      </c>
+      <c r="AP5">
+        <v>14</v>
+      </c>
+      <c r="AQ5">
+        <v>15.5</v>
+      </c>
+      <c r="AR5">
+        <v>24</v>
+      </c>
+      <c r="AS5">
+        <v>6.8</v>
+      </c>
+      <c r="AT5">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU5">
+        <v>7.8</v>
+      </c>
+      <c r="AV5">
+        <v>15.5</v>
+      </c>
+      <c r="AW5">
+        <v>36</v>
+      </c>
+      <c r="AX5">
+        <v>10.5</v>
+      </c>
+      <c r="AY5">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ5">
+        <v>15</v>
+      </c>
+      <c r="BA5">
+        <v>36</v>
+      </c>
+      <c r="BB5">
         <v>17</v>
       </c>
-      <c r="AC5">
-        <v>17</v>
-      </c>
-      <c r="AD5">
-        <v>1000</v>
-      </c>
-      <c r="AE5">
-        <v>1000</v>
-      </c>
-      <c r="AF5">
-        <v>23</v>
-      </c>
-      <c r="AG5">
-        <v>970</v>
-      </c>
-      <c r="AH5">
-        <v>970</v>
-      </c>
-      <c r="AI5">
-        <v>1000</v>
-      </c>
-      <c r="AJ5">
-        <v>40</v>
-      </c>
-      <c r="AK5">
-        <v>970</v>
-      </c>
-      <c r="AL5">
-        <v>70</v>
-      </c>
-      <c r="AM5">
-        <v>1000</v>
-      </c>
-      <c r="AN5">
-        <v>1000</v>
-      </c>
-      <c r="AO5">
-        <v>1000</v>
-      </c>
-      <c r="AP5">
-        <v>1.51</v>
-      </c>
-      <c r="AQ5">
-        <v>1.44</v>
-      </c>
-      <c r="AR5">
-        <v>1.49</v>
-      </c>
-      <c r="AS5">
-        <v>5.7</v>
-      </c>
-      <c r="AT5">
-        <v>1.39</v>
-      </c>
-      <c r="AU5">
+      <c r="BC5">
+        <v>15.5</v>
+      </c>
+      <c r="BD5">
+        <v>21</v>
+      </c>
+      <c r="BE5">
+        <v>6.8</v>
+      </c>
+      <c r="BF5">
+        <v>9</v>
+      </c>
+      <c r="BG5">
+        <v>36</v>
+      </c>
+      <c r="BH5">
+        <v>4.3</v>
+      </c>
+      <c r="BI5">
+        <v>3.1</v>
+      </c>
+      <c r="BJ5">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK5">
+        <v>7.4</v>
+      </c>
+      <c r="BL5">
+        <v>120</v>
+      </c>
+      <c r="BM5">
+        <v>7.6</v>
+      </c>
+      <c r="BN5">
+        <v>4.9</v>
+      </c>
+      <c r="BO5">
+        <v>4</v>
+      </c>
+      <c r="BP5">
+        <v>13</v>
+      </c>
+      <c r="BQ5">
+        <v>9.6</v>
+      </c>
+      <c r="BR5">
+        <v>26</v>
+      </c>
+      <c r="BS5">
         <v>6.2</v>
       </c>
-      <c r="AV5">
-        <v>1.51</v>
-      </c>
-      <c r="AW5">
-        <v>1.51</v>
-      </c>
-      <c r="AX5">
-        <v>1.42</v>
-      </c>
-      <c r="AY5">
-        <v>1.42</v>
-      </c>
-      <c r="AZ5">
-        <v>1.46</v>
-      </c>
-      <c r="BA5">
-        <v>1.51</v>
-      </c>
-      <c r="BB5">
-        <v>1.46</v>
-      </c>
-      <c r="BC5">
-        <v>1.46</v>
-      </c>
-      <c r="BD5">
-        <v>1.48</v>
-      </c>
-      <c r="BE5">
-        <v>1.51</v>
-      </c>
-      <c r="BF5">
-        <v>3.5</v>
-      </c>
-      <c r="BG5">
-        <v>4.9</v>
-      </c>
-      <c r="BH5">
-        <v>1000</v>
-      </c>
-      <c r="BI5">
-        <v>1.04</v>
-      </c>
-      <c r="BJ5">
-        <v>1000</v>
-      </c>
-      <c r="BK5">
-        <v>1.04</v>
-      </c>
-      <c r="BL5">
-        <v>1000</v>
-      </c>
-      <c r="BM5">
-        <v>1.04</v>
-      </c>
-      <c r="BN5">
-        <v>1000</v>
-      </c>
-      <c r="BO5">
-        <v>1.04</v>
-      </c>
-      <c r="BP5">
-        <v>1000</v>
-      </c>
-      <c r="BQ5">
-        <v>1.04</v>
-      </c>
-      <c r="BR5">
-        <v>1000</v>
-      </c>
-      <c r="BS5">
-        <v>1.04</v>
-      </c>
       <c r="BT5">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BU5">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BV5">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BW5">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BX5">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY5">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BZ5">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="CA5">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="CB5" t="s">
         <v>114</v>
@@ -1938,7 +1938,7 @@
         <v>3.9</v>
       </c>
       <c r="L6">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="M6">
         <v>1.05</v>
@@ -1956,7 +1956,7 @@
         <v>1.76</v>
       </c>
       <c r="R6">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S6">
         <v>2.94</v>
@@ -1971,7 +1971,7 @@
         <v>1.48</v>
       </c>
       <c r="W6">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="X6">
         <v>18</v>
@@ -1986,16 +1986,16 @@
         <v>55</v>
       </c>
       <c r="AB6">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC6">
         <v>8.6</v>
       </c>
       <c r="AD6">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE6">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF6">
         <v>21</v>
@@ -2016,7 +2016,7 @@
         <v>25</v>
       </c>
       <c r="AL6">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM6">
         <v>80</v>
@@ -2028,7 +2028,7 @@
         <v>27</v>
       </c>
       <c r="AP6">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AQ6">
         <v>13.5</v>
@@ -2103,7 +2103,7 @@
         <v>5.6</v>
       </c>
       <c r="BO6">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BP6">
         <v>17</v>
@@ -2165,13 +2165,13 @@
         <v>1.54</v>
       </c>
       <c r="G7">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="H7">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="I7">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="J7">
         <v>4.5</v>
@@ -2186,7 +2186,7 @@
         <v>1.05</v>
       </c>
       <c r="N7">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="O7">
         <v>1.24</v>
@@ -2261,7 +2261,7 @@
         <v>40</v>
       </c>
       <c r="AM7">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN7">
         <v>8.4</v>
@@ -2270,7 +2270,7 @@
         <v>130</v>
       </c>
       <c r="AP7">
-        <v>17</v>
+        <v>5.4</v>
       </c>
       <c r="AQ7">
         <v>21</v>
@@ -2279,7 +2279,7 @@
         <v>6.8</v>
       </c>
       <c r="AS7">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AT7">
         <v>8.4</v>
@@ -2291,10 +2291,10 @@
         <v>5.8</v>
       </c>
       <c r="AW7">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AX7">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY7">
         <v>9</v>
@@ -2315,16 +2315,16 @@
         <v>6.2</v>
       </c>
       <c r="BE7">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BF7">
         <v>6.4</v>
       </c>
       <c r="BG7">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BH7">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BI7">
         <v>3.1</v>
@@ -2333,13 +2333,13 @@
         <v>12.5</v>
       </c>
       <c r="BK7">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BN7">
         <v>4.9</v>
@@ -2351,37 +2351,37 @@
         <v>11.5</v>
       </c>
       <c r="BQ7">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BR7">
         <v>28</v>
       </c>
       <c r="BS7">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BT7">
         <v>12.5</v>
       </c>
       <c r="BU7">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BV7">
         <v>70</v>
       </c>
       <c r="BW7">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BX7">
         <v>70</v>
       </c>
       <c r="BY7">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BZ7">
         <v>18.5</v>
       </c>
       <c r="CA7">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="CB7" t="s">
         <v>114</v>
@@ -2410,10 +2410,10 @@
         <v>2.22</v>
       </c>
       <c r="H8">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="I8">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="J8">
         <v>4.3</v>
@@ -2461,13 +2461,13 @@
         <v>42</v>
       </c>
       <c r="Y8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Z8">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AA8">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AB8">
         <v>22</v>
@@ -2476,19 +2476,19 @@
         <v>13.5</v>
       </c>
       <c r="AD8">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AE8">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AF8">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AG8">
         <v>14.5</v>
       </c>
       <c r="AH8">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AI8">
         <v>34</v>
@@ -2500,31 +2500,31 @@
         <v>23</v>
       </c>
       <c r="AL8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AM8">
         <v>50</v>
       </c>
       <c r="AN8">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO8">
+        <v>17</v>
+      </c>
+      <c r="AP8">
+        <v>5.1</v>
+      </c>
+      <c r="AQ8">
+        <v>18</v>
+      </c>
+      <c r="AR8">
+        <v>5</v>
+      </c>
+      <c r="AS8">
+        <v>5.3</v>
+      </c>
+      <c r="AT8">
         <v>16</v>
-      </c>
-      <c r="AP8">
-        <v>5.5</v>
-      </c>
-      <c r="AQ8">
-        <v>5.1</v>
-      </c>
-      <c r="AR8">
-        <v>21</v>
-      </c>
-      <c r="AS8">
-        <v>5.7</v>
-      </c>
-      <c r="AT8">
-        <v>17</v>
       </c>
       <c r="AU8">
         <v>10.5</v>
@@ -2533,34 +2533,34 @@
         <v>13</v>
       </c>
       <c r="AW8">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="AX8">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="AY8">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ8">
         <v>12.5</v>
       </c>
       <c r="BA8">
+        <v>5</v>
+      </c>
+      <c r="BB8">
         <v>21</v>
       </c>
-      <c r="BB8">
-        <v>5.4</v>
-      </c>
       <c r="BC8">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="BD8">
         <v>18</v>
       </c>
       <c r="BE8">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="BF8">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BG8">
         <v>13</v>
@@ -2575,55 +2575,55 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BK8">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BN8">
         <v>5.9</v>
       </c>
       <c r="BO8">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BP8">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BQ8">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="BR8">
         <v>1000</v>
       </c>
       <c r="BS8">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BT8">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BU8">
         <v>5.7</v>
       </c>
       <c r="BV8">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BW8">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX8">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BY8">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ8">
         <v>11.5</v>
       </c>
       <c r="CA8">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="CB8" t="s">
         <v>114</v>
@@ -2646,7 +2646,7 @@
         <v>112</v>
       </c>
       <c r="F9">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="G9">
         <v>2.6</v>
@@ -2658,19 +2658,19 @@
         <v>3.7</v>
       </c>
       <c r="J9">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="K9">
         <v>3.2</v>
       </c>
       <c r="L9">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="M9">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="N9">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="O9">
         <v>1.6</v>
@@ -2700,46 +2700,46 @@
         <v>1.62</v>
       </c>
       <c r="X9">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y9">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="Z9">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AA9">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AB9">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AC9">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD9">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AE9">
         <v>70</v>
       </c>
       <c r="AF9">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AG9">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AH9">
-        <v>950</v>
+        <v>29</v>
       </c>
       <c r="AI9">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AJ9">
+        <v>50</v>
+      </c>
+      <c r="AK9">
         <v>46</v>
-      </c>
-      <c r="AK9">
-        <v>44</v>
       </c>
       <c r="AL9">
         <v>75</v>
@@ -2751,19 +2751,19 @@
         <v>55</v>
       </c>
       <c r="AO9">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AP9">
         <v>7</v>
       </c>
       <c r="AQ9">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AR9">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AS9">
-        <v>7.6</v>
+        <v>5.5</v>
       </c>
       <c r="AT9">
         <v>6.6</v>
@@ -2772,100 +2772,100 @@
         <v>6.2</v>
       </c>
       <c r="AV9">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AW9">
-        <v>7.4</v>
+        <v>5.4</v>
       </c>
       <c r="AX9">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AY9">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ9">
         <v>21</v>
       </c>
       <c r="BA9">
-        <v>7.6</v>
+        <v>5.5</v>
       </c>
       <c r="BB9">
-        <v>7</v>
+        <v>5.2</v>
       </c>
       <c r="BC9">
-        <v>7</v>
+        <v>5.2</v>
       </c>
       <c r="BD9">
-        <v>7.4</v>
+        <v>5.4</v>
       </c>
       <c r="BE9">
-        <v>8</v>
+        <v>5.7</v>
       </c>
       <c r="BF9">
-        <v>7.2</v>
+        <v>5.3</v>
       </c>
       <c r="BG9">
-        <v>7.6</v>
+        <v>5.5</v>
       </c>
       <c r="BH9">
-        <v>1000</v>
+        <v>2.66</v>
       </c>
       <c r="BI9">
-        <v>1.04</v>
+        <v>2.2</v>
       </c>
       <c r="BJ9">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK9">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BN9">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BO9">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BP9">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BQ9">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BR9">
         <v>1000</v>
       </c>
       <c r="BS9">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BT9">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU9">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BV9">
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BZ9">
         <v>1000</v>
       </c>
       <c r="CA9">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="CB9" t="s">
         <v>114</v>
@@ -2888,64 +2888,64 @@
         <v>113</v>
       </c>
       <c r="F10">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="G10">
         <v>3.25</v>
       </c>
       <c r="H10">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="I10">
-        <v>3.15</v>
+        <v>2.96</v>
       </c>
       <c r="J10">
-        <v>2.68</v>
+        <v>2.82</v>
       </c>
       <c r="K10">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L10">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M10">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N10">
         <v>3.3</v>
       </c>
       <c r="O10">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P10">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="Q10">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="R10">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S10">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="T10">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="U10">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="V10">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="W10">
         <v>1.44</v>
       </c>
       <c r="X10">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y10">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z10">
         <v>19</v>
@@ -2954,7 +2954,7 @@
         <v>50</v>
       </c>
       <c r="AB10">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC10">
         <v>8</v>
@@ -2963,7 +2963,7 @@
         <v>13</v>
       </c>
       <c r="AE10">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AF10">
         <v>24</v>
@@ -2972,13 +2972,13 @@
         <v>13.5</v>
       </c>
       <c r="AH10">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AI10">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AJ10">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AK10">
         <v>46</v>
@@ -2987,67 +2987,67 @@
         <v>60</v>
       </c>
       <c r="AM10">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AN10">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AO10">
         <v>36</v>
       </c>
       <c r="AP10">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AQ10">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AR10">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AS10">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AT10">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU10">
         <v>6.6</v>
       </c>
       <c r="AV10">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW10">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX10">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AY10">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ10">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA10">
-        <v>36</v>
+        <v>7.4</v>
       </c>
       <c r="BB10">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BC10">
         <v>29</v>
       </c>
       <c r="BD10">
-        <v>38</v>
+        <v>7.4</v>
       </c>
       <c r="BE10">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BF10">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BG10">
-        <v>6.4</v>
+        <v>27</v>
       </c>
       <c r="BH10">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-18.xlsx
@@ -358,7 +358,7 @@
     <t>Atletico GO</t>
   </si>
   <si>
-    <t>2026-08-17 05:14:50</t>
+    <t>2026-08-17 07:24:14</t>
   </si>
 </sst>
 </file>
@@ -952,55 +952,55 @@
         <v>105</v>
       </c>
       <c r="F2">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="G2">
         <v>3.65</v>
       </c>
       <c r="H2">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="I2">
-        <v>2.54</v>
+        <v>2.42</v>
       </c>
       <c r="J2">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K2">
         <v>3.45</v>
       </c>
       <c r="L2">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="M2">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N2">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="O2">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="P2">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="Q2">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="R2">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S2">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="T2">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="U2">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="V2">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W2">
         <v>1.37</v>
@@ -1024,7 +1024,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD2">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE2">
         <v>34</v>
@@ -1051,16 +1051,16 @@
         <v>75</v>
       </c>
       <c r="AM2">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AN2">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AO2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AP2">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AQ2">
         <v>7.8</v>
@@ -1090,37 +1090,37 @@
         <v>13</v>
       </c>
       <c r="AZ2">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="BA2">
-        <v>4.5</v>
+        <v>28</v>
       </c>
       <c r="BB2">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BC2">
-        <v>4.5</v>
+        <v>28</v>
       </c>
       <c r="BD2">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BE2">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BF2">
-        <v>34</v>
+        <v>4.7</v>
       </c>
       <c r="BG2">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="BH2">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BI2">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="BJ2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK2">
         <v>3.6</v>
@@ -1129,7 +1129,7 @@
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BN2">
         <v>7.8</v>
@@ -1141,7 +1141,7 @@
         <v>36</v>
       </c>
       <c r="BQ2">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BR2">
         <v>70</v>
@@ -1162,16 +1162,16 @@
         <v>4</v>
       </c>
       <c r="BX2">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BY2">
         <v>4.6</v>
       </c>
       <c r="BZ2">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="CA2">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="CB2" t="s">
         <v>114</v>
@@ -1194,19 +1194,19 @@
         <v>106</v>
       </c>
       <c r="F3">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="G3">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="H3">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="I3">
         <v>2.96</v>
       </c>
       <c r="J3">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="K3">
         <v>3</v>
@@ -1221,7 +1221,7 @@
         <v>2.46</v>
       </c>
       <c r="O3">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="P3">
         <v>1.46</v>
@@ -1245,7 +1245,7 @@
         <v>1.51</v>
       </c>
       <c r="W3">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="X3">
         <v>7.4</v>
@@ -1281,7 +1281,7 @@
         <v>32</v>
       </c>
       <c r="AI3">
-        <v>960</v>
+        <v>950</v>
       </c>
       <c r="AJ3">
         <v>85</v>
@@ -1290,7 +1290,7 @@
         <v>210</v>
       </c>
       <c r="AL3">
-        <v>970</v>
+        <v>960</v>
       </c>
       <c r="AM3">
         <v>270</v>
@@ -1302,10 +1302,10 @@
         <v>930</v>
       </c>
       <c r="AP3">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AQ3">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AR3">
         <v>15</v>
@@ -1320,7 +1320,7 @@
         <v>6.2</v>
       </c>
       <c r="AV3">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AW3">
         <v>26</v>
@@ -1338,7 +1338,7 @@
         <v>38</v>
       </c>
       <c r="BB3">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BC3">
         <v>27</v>
@@ -1356,7 +1356,7 @@
         <v>44</v>
       </c>
       <c r="BH3">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="BI3">
         <v>2.22</v>
@@ -1371,7 +1371,7 @@
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>16.5</v>
+        <v>12.5</v>
       </c>
       <c r="BN3">
         <v>6</v>
@@ -1383,13 +1383,13 @@
         <v>32</v>
       </c>
       <c r="BQ3">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="BT3">
         <v>5.6</v>
@@ -1407,13 +1407,13 @@
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>13.5</v>
+        <v>2.14</v>
       </c>
       <c r="CB3" t="s">
         <v>114</v>
@@ -1439,7 +1439,7 @@
         <v>2.06</v>
       </c>
       <c r="G4">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="H4">
         <v>3.35</v>
@@ -1448,7 +1448,7 @@
         <v>3.9</v>
       </c>
       <c r="J4">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K4">
         <v>4</v>
@@ -1460,22 +1460,22 @@
         <v>1.06</v>
       </c>
       <c r="N4">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O4">
         <v>1.27</v>
       </c>
       <c r="P4">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q4">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="R4">
         <v>1.42</v>
       </c>
       <c r="S4">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="T4">
         <v>1.68</v>
@@ -1487,10 +1487,10 @@
         <v>1.35</v>
       </c>
       <c r="W4">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="X4">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="Y4">
         <v>16</v>
@@ -1529,16 +1529,16 @@
         <v>34</v>
       </c>
       <c r="AK4">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AL4">
         <v>42</v>
       </c>
       <c r="AM4">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AN4">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AO4">
         <v>44</v>
@@ -1553,7 +1553,7 @@
         <v>21</v>
       </c>
       <c r="AS4">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT4">
         <v>9.199999999999999</v>
@@ -1580,7 +1580,7 @@
         <v>20</v>
       </c>
       <c r="BB4">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BC4">
         <v>18.5</v>
@@ -1589,16 +1589,16 @@
         <v>6.2</v>
       </c>
       <c r="BE4">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BF4">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BG4">
         <v>26</v>
       </c>
       <c r="BH4">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BI4">
         <v>3.2</v>
@@ -1613,13 +1613,13 @@
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BN4">
         <v>5.3</v>
       </c>
       <c r="BO4">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BP4">
         <v>16</v>
@@ -1631,7 +1631,7 @@
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BT4">
         <v>7.2</v>
@@ -1649,13 +1649,13 @@
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ4">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="CA4">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="CB4" t="s">
         <v>114</v>
@@ -1678,10 +1678,10 @@
         <v>108</v>
       </c>
       <c r="F5">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="G5">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="H5">
         <v>4.5</v>
@@ -1690,46 +1690,46 @@
         <v>4.7</v>
       </c>
       <c r="J5">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K5">
         <v>4.1</v>
       </c>
       <c r="L5">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="M5">
         <v>1.05</v>
       </c>
       <c r="N5">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O5">
         <v>1.26</v>
       </c>
       <c r="P5">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q5">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="R5">
         <v>1.46</v>
       </c>
       <c r="S5">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="T5">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="U5">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V5">
         <v>1.27</v>
       </c>
       <c r="W5">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="X5">
         <v>21</v>
@@ -1768,10 +1768,10 @@
         <v>65</v>
       </c>
       <c r="AJ5">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK5">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AL5">
         <v>38</v>
@@ -1795,7 +1795,7 @@
         <v>24</v>
       </c>
       <c r="AS5">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AT5">
         <v>8.800000000000001</v>
@@ -1831,7 +1831,7 @@
         <v>21</v>
       </c>
       <c r="BE5">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BF5">
         <v>9</v>
@@ -1855,16 +1855,16 @@
         <v>120</v>
       </c>
       <c r="BM5">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BN5">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BO5">
         <v>4</v>
       </c>
       <c r="BP5">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BQ5">
         <v>9.6</v>
@@ -1873,7 +1873,7 @@
         <v>26</v>
       </c>
       <c r="BS5">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BT5">
         <v>8.4</v>
@@ -1885,19 +1885,19 @@
         <v>38</v>
       </c>
       <c r="BW5">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BX5">
         <v>48</v>
       </c>
       <c r="BY5">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BZ5">
         <v>20</v>
       </c>
       <c r="CA5">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="CB5" t="s">
         <v>114</v>
@@ -1926,7 +1926,7 @@
         <v>2.48</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="I6">
         <v>3.05</v>
@@ -1944,13 +1944,13 @@
         <v>1.05</v>
       </c>
       <c r="N6">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O6">
         <v>1.25</v>
       </c>
       <c r="P6">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q6">
         <v>1.76</v>
@@ -1971,7 +1971,7 @@
         <v>1.48</v>
       </c>
       <c r="W6">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="X6">
         <v>18</v>
@@ -1986,7 +1986,7 @@
         <v>55</v>
       </c>
       <c r="AB6">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC6">
         <v>8.6</v>
@@ -2019,7 +2019,7 @@
         <v>34</v>
       </c>
       <c r="AM6">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN6">
         <v>18.5</v>
@@ -2043,7 +2043,7 @@
         <v>12</v>
       </c>
       <c r="AU6">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV6">
         <v>11.5</v>
@@ -2094,7 +2094,7 @@
         <v>5.7</v>
       </c>
       <c r="BL6">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BM6">
         <v>14</v>
@@ -2103,7 +2103,7 @@
         <v>5.6</v>
       </c>
       <c r="BO6">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="BP6">
         <v>17</v>
@@ -2121,7 +2121,7 @@
         <v>6.4</v>
       </c>
       <c r="BU6">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="BV6">
         <v>22</v>
@@ -2162,70 +2162,70 @@
         <v>110</v>
       </c>
       <c r="F7">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="G7">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="H7">
+        <v>6.4</v>
+      </c>
+      <c r="I7">
         <v>7</v>
       </c>
-      <c r="I7">
-        <v>7.6</v>
-      </c>
       <c r="J7">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K7">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="L7">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M7">
         <v>1.05</v>
       </c>
       <c r="N7">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="O7">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="P7">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="Q7">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="R7">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="S7">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="T7">
         <v>1.87</v>
       </c>
       <c r="U7">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="V7">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="W7">
-        <v>2.78</v>
+        <v>2.66</v>
       </c>
       <c r="X7">
-        <v>950</v>
+        <v>24</v>
       </c>
       <c r="Y7">
-        <v>950</v>
+        <v>25</v>
       </c>
       <c r="Z7">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AA7">
-        <v>240</v>
+        <v>210</v>
       </c>
       <c r="AB7">
         <v>9.4</v>
@@ -2237,25 +2237,25 @@
         <v>950</v>
       </c>
       <c r="AE7">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AF7">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG7">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH7">
-        <v>950</v>
+        <v>24</v>
       </c>
       <c r="AI7">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AJ7">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AK7">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AL7">
         <v>40</v>
@@ -2264,46 +2264,46 @@
         <v>130</v>
       </c>
       <c r="AN7">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AO7">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AP7">
+        <v>14</v>
+      </c>
+      <c r="AQ7">
         <v>5.4</v>
       </c>
-      <c r="AQ7">
-        <v>21</v>
-      </c>
       <c r="AR7">
-        <v>6.8</v>
+        <v>42</v>
       </c>
       <c r="AS7">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="AT7">
         <v>8.4</v>
       </c>
       <c r="AU7">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV7">
-        <v>5.8</v>
+        <v>19</v>
       </c>
       <c r="AW7">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AX7">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AY7">
         <v>9</v>
       </c>
       <c r="AZ7">
-        <v>5.6</v>
+        <v>18</v>
       </c>
       <c r="BA7">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BB7">
         <v>12.5</v>
@@ -2312,19 +2312,19 @@
         <v>13.5</v>
       </c>
       <c r="BD7">
+        <v>24</v>
+      </c>
+      <c r="BE7">
         <v>6.2</v>
       </c>
-      <c r="BE7">
-        <v>6.6</v>
-      </c>
       <c r="BF7">
+        <v>6.8</v>
+      </c>
+      <c r="BG7">
         <v>6.4</v>
       </c>
-      <c r="BG7">
-        <v>6.6</v>
-      </c>
       <c r="BH7">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BI7">
         <v>3.1</v>
@@ -2333,25 +2333,25 @@
         <v>12.5</v>
       </c>
       <c r="BK7">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BN7">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BO7">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BP7">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BQ7">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BR7">
         <v>28</v>
@@ -2360,28 +2360,28 @@
         <v>4</v>
       </c>
       <c r="BT7">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BU7">
         <v>3.4</v>
       </c>
       <c r="BV7">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BW7">
         <v>4.4</v>
       </c>
       <c r="BX7">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BY7">
         <v>4.4</v>
       </c>
       <c r="BZ7">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="CA7">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="CB7" t="s">
         <v>114</v>
@@ -2407,10 +2407,10 @@
         <v>2.1</v>
       </c>
       <c r="G8">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="H8">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="I8">
         <v>3.35</v>
@@ -2422,121 +2422,121 @@
         <v>4.7</v>
       </c>
       <c r="L8">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="M8">
         <v>1.02</v>
       </c>
       <c r="N8">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="O8">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="P8">
         <v>3.1</v>
       </c>
       <c r="Q8">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="R8">
         <v>1.86</v>
       </c>
       <c r="S8">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="T8">
         <v>1.45</v>
       </c>
       <c r="U8">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="V8">
         <v>1.43</v>
       </c>
       <c r="W8">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="X8">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="Y8">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Z8">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA8">
-        <v>60</v>
+        <v>380</v>
       </c>
       <c r="AB8">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AC8">
+        <v>12.5</v>
+      </c>
+      <c r="AD8">
+        <v>17.5</v>
+      </c>
+      <c r="AE8">
+        <v>32</v>
+      </c>
+      <c r="AF8">
+        <v>20</v>
+      </c>
+      <c r="AG8">
         <v>13.5</v>
       </c>
-      <c r="AD8">
-        <v>18</v>
-      </c>
-      <c r="AE8">
-        <v>34</v>
-      </c>
-      <c r="AF8">
-        <v>22</v>
-      </c>
-      <c r="AG8">
-        <v>14.5</v>
-      </c>
       <c r="AH8">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI8">
         <v>34</v>
       </c>
       <c r="AJ8">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK8">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AL8">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AM8">
         <v>50</v>
       </c>
       <c r="AN8">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO8">
         <v>17</v>
       </c>
       <c r="AP8">
-        <v>5.1</v>
+        <v>28</v>
       </c>
       <c r="AQ8">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AR8">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="AS8">
-        <v>5.3</v>
+        <v>40</v>
       </c>
       <c r="AT8">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AU8">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AV8">
         <v>13</v>
       </c>
       <c r="AW8">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="AX8">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY8">
         <v>10.5</v>
@@ -2545,25 +2545,25 @@
         <v>12.5</v>
       </c>
       <c r="BA8">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="BB8">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BC8">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BD8">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BE8">
-        <v>5.2</v>
+        <v>34</v>
       </c>
       <c r="BF8">
         <v>7.2</v>
       </c>
       <c r="BG8">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BH8">
         <v>5.3</v>
@@ -2575,34 +2575,34 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BK8">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BN8">
         <v>5.9</v>
       </c>
       <c r="BO8">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BP8">
         <v>13.5</v>
       </c>
       <c r="BQ8">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BR8">
         <v>1000</v>
       </c>
       <c r="BS8">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BT8">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BU8">
         <v>5.7</v>
@@ -2611,19 +2611,19 @@
         <v>21</v>
       </c>
       <c r="BW8">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BX8">
         <v>24</v>
       </c>
       <c r="BY8">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BZ8">
         <v>11.5</v>
       </c>
       <c r="CA8">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="CB8" t="s">
         <v>114</v>
@@ -2664,7 +2664,7 @@
         <v>3.2</v>
       </c>
       <c r="L9">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="M9">
         <v>1.12</v>
@@ -2676,10 +2676,10 @@
         <v>1.6</v>
       </c>
       <c r="P9">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="Q9">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="R9">
         <v>1.18</v>
@@ -2688,7 +2688,7 @@
         <v>5.9</v>
       </c>
       <c r="T9">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="U9">
         <v>1.69</v>
@@ -2706,7 +2706,7 @@
         <v>10.5</v>
       </c>
       <c r="Z9">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA9">
         <v>90</v>
@@ -2718,7 +2718,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD9">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AE9">
         <v>70</v>
@@ -2727,7 +2727,7 @@
         <v>17</v>
       </c>
       <c r="AG9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH9">
         <v>29</v>
@@ -2748,10 +2748,10 @@
         <v>250</v>
       </c>
       <c r="AN9">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AO9">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AP9">
         <v>7</v>
@@ -2763,7 +2763,7 @@
         <v>19</v>
       </c>
       <c r="AS9">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="AT9">
         <v>6.6</v>
@@ -2772,40 +2772,40 @@
         <v>6.2</v>
       </c>
       <c r="AV9">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AW9">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="AX9">
         <v>12.5</v>
       </c>
       <c r="AY9">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ9">
         <v>21</v>
       </c>
       <c r="BA9">
+        <v>6</v>
+      </c>
+      <c r="BB9">
+        <v>5.6</v>
+      </c>
+      <c r="BC9">
         <v>5.5</v>
       </c>
-      <c r="BB9">
-        <v>5.2</v>
-      </c>
-      <c r="BC9">
-        <v>5.2</v>
-      </c>
       <c r="BD9">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BE9">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BF9">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BG9">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BH9">
         <v>2.66</v>
@@ -2891,19 +2891,19 @@
         <v>2.8</v>
       </c>
       <c r="G10">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="H10">
         <v>2.72</v>
       </c>
       <c r="I10">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="J10">
         <v>2.82</v>
       </c>
       <c r="K10">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="L10">
         <v>1.44</v>
@@ -2915,7 +2915,7 @@
         <v>3.3</v>
       </c>
       <c r="O10">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P10">
         <v>1.76</v>
@@ -2933,13 +2933,13 @@
         <v>1.84</v>
       </c>
       <c r="U10">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="V10">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W10">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="X10">
         <v>13.5</v>
@@ -2954,13 +2954,13 @@
         <v>50</v>
       </c>
       <c r="AB10">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC10">
         <v>8</v>
       </c>
       <c r="AD10">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE10">
         <v>40</v>
@@ -2972,7 +2972,7 @@
         <v>13.5</v>
       </c>
       <c r="AH10">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AI10">
         <v>60</v>
@@ -2987,7 +2987,7 @@
         <v>60</v>
       </c>
       <c r="AM10">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN10">
         <v>44</v>
@@ -2999,25 +2999,25 @@
         <v>10</v>
       </c>
       <c r="AQ10">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR10">
         <v>15</v>
       </c>
       <c r="AS10">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AT10">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AU10">
         <v>6.6</v>
       </c>
       <c r="AV10">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AW10">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AX10">
         <v>14.5</v>
@@ -3029,25 +3029,25 @@
         <v>16</v>
       </c>
       <c r="BA10">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB10">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BC10">
         <v>29</v>
       </c>
       <c r="BD10">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE10">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF10">
         <v>7.2</v>
       </c>
       <c r="BG10">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BH10">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-18.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="119">
   <si>
     <t>League</t>
   </si>
@@ -271,6 +271,9 @@
     <t>Mexican Liga MX</t>
   </si>
   <si>
+    <t>Costa Rican Primera Division</t>
+  </si>
+  <si>
     <t>Chinese Super League</t>
   </si>
   <si>
@@ -292,6 +295,9 @@
     <t>01:00:00</t>
   </si>
   <si>
+    <t>02:00:00</t>
+  </si>
+  <si>
     <t>03:00:00</t>
   </si>
   <si>
@@ -319,6 +325,9 @@
     <t>Necaxa</t>
   </si>
   <si>
+    <t>Sporting San Jose FC</t>
+  </si>
+  <si>
     <t>Pachuca</t>
   </si>
   <si>
@@ -346,6 +355,9 @@
     <t>Leon</t>
   </si>
   <si>
+    <t>Escorpiones FC</t>
+  </si>
+  <si>
     <t>Puebla</t>
   </si>
   <si>
@@ -358,7 +370,7 @@
     <t>Atletico GO</t>
   </si>
   <si>
-    <t>2026-08-17 07:24:14</t>
+    <t>2026-08-17 09:33:37</t>
   </si>
 </sst>
 </file>
@@ -690,7 +702,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB10"/>
+  <dimension ref="A1:CB11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -940,70 +952,70 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="F2">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="G2">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="H2">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="I2">
-        <v>2.42</v>
+        <v>2.26</v>
       </c>
       <c r="J2">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K2">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L2">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="M2">
         <v>1.09</v>
       </c>
       <c r="N2">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O2">
         <v>1.39</v>
       </c>
       <c r="P2">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="Q2">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R2">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S2">
         <v>4.1</v>
       </c>
       <c r="T2">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="U2">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="V2">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="W2">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="X2">
         <v>13.5</v>
@@ -1024,7 +1036,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE2">
         <v>34</v>
@@ -1036,40 +1048,40 @@
         <v>18</v>
       </c>
       <c r="AH2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI2">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ2">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AK2">
         <v>60</v>
       </c>
       <c r="AL2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AM2">
         <v>150</v>
       </c>
       <c r="AN2">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AO2">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AP2">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="AQ2">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AR2">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AS2">
-        <v>23</v>
+        <v>4.5</v>
       </c>
       <c r="AT2">
         <v>10</v>
@@ -1078,10 +1090,10 @@
         <v>6.6</v>
       </c>
       <c r="AV2">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AW2">
-        <v>20</v>
+        <v>4.5</v>
       </c>
       <c r="AX2">
         <v>15.5</v>
@@ -1090,91 +1102,91 @@
         <v>13</v>
       </c>
       <c r="AZ2">
-        <v>12.5</v>
+        <v>17</v>
       </c>
       <c r="BA2">
         <v>28</v>
       </c>
       <c r="BB2">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BC2">
         <v>28</v>
       </c>
       <c r="BD2">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BE2">
+        <v>5</v>
+      </c>
+      <c r="BF2">
         <v>4.9</v>
       </c>
-      <c r="BF2">
-        <v>4.7</v>
-      </c>
       <c r="BG2">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BH2">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BI2">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="BJ2">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BK2">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
+        <v>5.3</v>
+      </c>
+      <c r="BN2">
+        <v>7.4</v>
+      </c>
+      <c r="BO2">
+        <v>5.5</v>
+      </c>
+      <c r="BP2">
+        <v>44</v>
+      </c>
+      <c r="BQ2">
+        <v>4.9</v>
+      </c>
+      <c r="BR2">
+        <v>60</v>
+      </c>
+      <c r="BS2">
         <v>5</v>
       </c>
-      <c r="BN2">
-        <v>7.8</v>
-      </c>
-      <c r="BO2">
-        <v>4.9</v>
-      </c>
-      <c r="BP2">
-        <v>36</v>
-      </c>
-      <c r="BQ2">
-        <v>4.5</v>
-      </c>
-      <c r="BR2">
-        <v>70</v>
-      </c>
-      <c r="BS2">
-        <v>4.6</v>
-      </c>
       <c r="BT2">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="BU2">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="BV2">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="BW2">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BX2">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BY2">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BZ2">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="CA2">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="CB2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1182,34 +1194,34 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E3" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F3">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="G3">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="H3">
+        <v>2.76</v>
+      </c>
+      <c r="I3">
+        <v>2.84</v>
+      </c>
+      <c r="J3">
         <v>2.88</v>
       </c>
-      <c r="I3">
-        <v>2.96</v>
-      </c>
-      <c r="J3">
-        <v>2.9</v>
-      </c>
       <c r="K3">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="L3">
         <v>1.67</v>
@@ -1218,16 +1230,16 @@
         <v>1.16</v>
       </c>
       <c r="N3">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="O3">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="P3">
         <v>1.46</v>
       </c>
       <c r="Q3">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="R3">
         <v>1.16</v>
@@ -1236,112 +1248,112 @@
         <v>6.8</v>
       </c>
       <c r="T3">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="U3">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V3">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="W3">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="X3">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="Y3">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="Z3">
-        <v>20</v>
+        <v>15.5</v>
       </c>
       <c r="AA3">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="AB3">
         <v>8.199999999999999</v>
       </c>
       <c r="AC3">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AD3">
-        <v>17.5</v>
+        <v>14</v>
       </c>
       <c r="AE3">
-        <v>150</v>
+        <v>48</v>
       </c>
       <c r="AF3">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG3">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AH3">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AI3">
-        <v>950</v>
+        <v>85</v>
       </c>
       <c r="AJ3">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AK3">
-        <v>210</v>
+        <v>60</v>
       </c>
       <c r="AL3">
-        <v>960</v>
+        <v>95</v>
       </c>
       <c r="AM3">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="AN3">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AO3">
-        <v>930</v>
+        <v>60</v>
       </c>
       <c r="AP3">
         <v>6.8</v>
       </c>
       <c r="AQ3">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AR3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AS3">
         <v>36</v>
       </c>
       <c r="AT3">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AU3">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV3">
         <v>12.5</v>
       </c>
       <c r="AW3">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="AX3">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AY3">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AZ3">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="BA3">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="BB3">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="BC3">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="BD3">
         <v>60</v>
@@ -1353,10 +1365,10 @@
         <v>48</v>
       </c>
       <c r="BG3">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="BH3">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="BI3">
         <v>2.22</v>
@@ -1365,34 +1377,34 @@
         <v>12</v>
       </c>
       <c r="BK3">
-        <v>9.4</v>
+        <v>7.4</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
+        <v>2.2</v>
+      </c>
+      <c r="BN3">
+        <v>6.2</v>
+      </c>
+      <c r="BO3">
+        <v>4.9</v>
+      </c>
+      <c r="BP3">
+        <v>1000</v>
+      </c>
+      <c r="BQ3">
         <v>12.5</v>
       </c>
-      <c r="BN3">
-        <v>6</v>
-      </c>
-      <c r="BO3">
-        <v>4.7</v>
-      </c>
-      <c r="BP3">
-        <v>32</v>
-      </c>
-      <c r="BQ3">
-        <v>12</v>
-      </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>11</v>
+        <v>2.14</v>
       </c>
       <c r="BT3">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BU3">
         <v>5</v>
@@ -1401,13 +1413,13 @@
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
@@ -1416,7 +1428,7 @@
         <v>2.14</v>
       </c>
       <c r="CB3" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1424,16 +1436,16 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E4" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="F4">
         <v>2.06</v>
@@ -1442,7 +1454,7 @@
         <v>2.22</v>
       </c>
       <c r="H4">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="I4">
         <v>3.9</v>
@@ -1451,10 +1463,10 @@
         <v>3.65</v>
       </c>
       <c r="K4">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L4">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M4">
         <v>1.06</v>
@@ -1466,16 +1478,16 @@
         <v>1.27</v>
       </c>
       <c r="P4">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q4">
         <v>1.81</v>
       </c>
       <c r="R4">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S4">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T4">
         <v>1.68</v>
@@ -1487,7 +1499,7 @@
         <v>1.35</v>
       </c>
       <c r="W4">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="X4">
         <v>19.5</v>
@@ -1511,22 +1523,22 @@
         <v>16</v>
       </c>
       <c r="AE4">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF4">
         <v>15.5</v>
       </c>
       <c r="AG4">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH4">
         <v>17.5</v>
       </c>
       <c r="AI4">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AJ4">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AK4">
         <v>26</v>
@@ -1535,13 +1547,13 @@
         <v>42</v>
       </c>
       <c r="AM4">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="AN4">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AO4">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AP4">
         <v>12.5</v>
@@ -1553,7 +1565,7 @@
         <v>21</v>
       </c>
       <c r="AS4">
-        <v>6.8</v>
+        <v>46</v>
       </c>
       <c r="AT4">
         <v>9.199999999999999</v>
@@ -1577,19 +1589,19 @@
         <v>14</v>
       </c>
       <c r="BA4">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="BB4">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="BC4">
         <v>18.5</v>
       </c>
       <c r="BD4">
-        <v>6.2</v>
+        <v>24</v>
       </c>
       <c r="BE4">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="BF4">
         <v>11</v>
@@ -1601,13 +1613,13 @@
         <v>3.8</v>
       </c>
       <c r="BI4">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="BJ4">
         <v>9.6</v>
       </c>
       <c r="BK4">
-        <v>7.2</v>
+        <v>5</v>
       </c>
       <c r="BL4">
         <v>1000</v>
@@ -1658,7 +1670,7 @@
         <v>7.2</v>
       </c>
       <c r="CB4" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1666,34 +1678,34 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F5">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="G5">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="H5">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I5">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J5">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K5">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L5">
         <v>1.38</v>
@@ -1714,7 +1726,7 @@
         <v>1.78</v>
       </c>
       <c r="R5">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="S5">
         <v>3</v>
@@ -1726,10 +1738,10 @@
         <v>2.2</v>
       </c>
       <c r="V5">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W5">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="X5">
         <v>21</v>
@@ -1744,7 +1756,7 @@
         <v>110</v>
       </c>
       <c r="AB5">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC5">
         <v>9.6</v>
@@ -1756,7 +1768,7 @@
         <v>65</v>
       </c>
       <c r="AF5">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG5">
         <v>12</v>
@@ -1774,13 +1786,13 @@
         <v>19</v>
       </c>
       <c r="AL5">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM5">
         <v>100</v>
       </c>
       <c r="AN5">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AO5">
         <v>60</v>
@@ -1792,13 +1804,13 @@
         <v>15.5</v>
       </c>
       <c r="AR5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS5">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AT5">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AU5">
         <v>7.8</v>
@@ -1813,7 +1825,7 @@
         <v>10.5</v>
       </c>
       <c r="AY5">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ5">
         <v>15</v>
@@ -1828,10 +1840,10 @@
         <v>15.5</v>
       </c>
       <c r="BD5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BE5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BF5">
         <v>9</v>
@@ -1840,10 +1852,10 @@
         <v>36</v>
       </c>
       <c r="BH5">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BI5">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BJ5">
         <v>9.800000000000001</v>
@@ -1855,7 +1867,7 @@
         <v>120</v>
       </c>
       <c r="BM5">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BN5">
         <v>4.8</v>
@@ -1870,10 +1882,10 @@
         <v>9.6</v>
       </c>
       <c r="BR5">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BS5">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BT5">
         <v>8.4</v>
@@ -1885,22 +1897,22 @@
         <v>38</v>
       </c>
       <c r="BW5">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BX5">
         <v>48</v>
       </c>
       <c r="BY5">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BZ5">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="CA5">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="CB5" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1908,97 +1920,97 @@
         <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D6" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E6" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="F6">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="G6">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="H6">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="I6">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="J6">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K6">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L6">
         <v>1.35</v>
       </c>
       <c r="M6">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N6">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="O6">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="P6">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="Q6">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="R6">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="S6">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="T6">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="U6">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="V6">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="W6">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="X6">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Y6">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="Z6">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AA6">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AB6">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AC6">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD6">
         <v>13</v>
       </c>
       <c r="AE6">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AF6">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AG6">
         <v>12</v>
@@ -2013,25 +2025,25 @@
         <v>36</v>
       </c>
       <c r="AK6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL6">
         <v>34</v>
       </c>
       <c r="AM6">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AN6">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AO6">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AP6">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AQ6">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR6">
         <v>19</v>
@@ -2043,7 +2055,7 @@
         <v>12</v>
       </c>
       <c r="AU6">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV6">
         <v>11.5</v>
@@ -2073,31 +2085,31 @@
         <v>28</v>
       </c>
       <c r="BE6">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BF6">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BG6">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BH6">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BI6">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="BJ6">
         <v>8.800000000000001</v>
       </c>
       <c r="BK6">
-        <v>5.7</v>
+        <v>4.6</v>
       </c>
       <c r="BL6">
         <v>90</v>
       </c>
       <c r="BM6">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="BN6">
         <v>5.6</v>
@@ -2106,527 +2118,527 @@
         <v>5</v>
       </c>
       <c r="BP6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BQ6">
-        <v>8.4</v>
+        <v>6.4</v>
       </c>
       <c r="BR6">
         <v>27</v>
       </c>
       <c r="BS6">
-        <v>10</v>
+        <v>7.2</v>
       </c>
       <c r="BT6">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BU6">
         <v>5.7</v>
       </c>
       <c r="BV6">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BW6">
-        <v>9.4</v>
+        <v>6.6</v>
       </c>
       <c r="BX6">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BY6">
-        <v>10.5</v>
+        <v>7.4</v>
       </c>
       <c r="BZ6">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="CA6">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB6" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:80">
       <c r="A7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D7" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E7" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F7">
-        <v>1.59</v>
+        <v>1.18</v>
       </c>
       <c r="G7">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="H7">
-        <v>6.4</v>
+        <v>2.3</v>
       </c>
       <c r="I7">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J7">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="K7">
-        <v>4.6</v>
+        <v>950</v>
       </c>
       <c r="L7">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="M7">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N7">
-        <v>4.7</v>
+        <v>1.24</v>
       </c>
       <c r="O7">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="P7">
-        <v>2.26</v>
+        <v>1.24</v>
       </c>
       <c r="Q7">
-        <v>1.76</v>
+        <v>1.01</v>
       </c>
       <c r="R7">
-        <v>1.49</v>
+        <v>1.18</v>
       </c>
       <c r="S7">
-        <v>2.94</v>
+        <v>1.01</v>
       </c>
       <c r="T7">
-        <v>1.87</v>
+        <v>1.11</v>
       </c>
       <c r="U7">
-        <v>2.08</v>
+        <v>1.11</v>
       </c>
       <c r="V7">
         <v>1.17</v>
       </c>
       <c r="W7">
-        <v>2.66</v>
+        <v>2.24</v>
       </c>
       <c r="X7">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Y7">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="Z7">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AA7">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AB7">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AC7">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AD7">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AE7">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AF7">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AG7">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AH7">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI7">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AJ7">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AK7">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AL7">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AM7">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN7">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AO7">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AP7">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR7">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="AS7">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AT7">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU7">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AV7">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="AW7">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AX7">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AY7">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BA7">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BB7">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC7">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD7">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BE7">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BF7">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BG7">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH7">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BI7">
-        <v>3.1</v>
+        <v>1.04</v>
       </c>
       <c r="BJ7">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK7">
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>4.6</v>
+        <v>1.04</v>
       </c>
       <c r="BN7">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BO7">
-        <v>3.3</v>
+        <v>1.04</v>
       </c>
       <c r="BP7">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>3.4</v>
+        <v>1.04</v>
       </c>
       <c r="BR7">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BS7">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="BT7">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BU7">
-        <v>3.4</v>
+        <v>1.04</v>
       </c>
       <c r="BV7">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BW7">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="BX7">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BY7">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="BZ7">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="CA7">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="CB7" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="8" spans="1:80">
       <c r="A8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D8" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E8" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="F8">
-        <v>2.1</v>
+        <v>1.59</v>
       </c>
       <c r="G8">
-        <v>2.18</v>
+        <v>1.6</v>
       </c>
       <c r="H8">
-        <v>3.15</v>
+        <v>6.4</v>
       </c>
       <c r="I8">
-        <v>3.35</v>
+        <v>6.8</v>
       </c>
       <c r="J8">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K8">
+        <v>4.6</v>
+      </c>
+      <c r="L8">
+        <v>1.34</v>
+      </c>
+      <c r="M8">
+        <v>1.05</v>
+      </c>
+      <c r="N8">
         <v>4.7</v>
       </c>
-      <c r="L8">
+      <c r="O8">
         <v>1.25</v>
       </c>
-      <c r="M8">
-        <v>1.02</v>
-      </c>
-      <c r="N8">
-        <v>7.4</v>
-      </c>
-      <c r="O8">
-        <v>1.14</v>
-      </c>
       <c r="P8">
-        <v>3.1</v>
+        <v>2.24</v>
       </c>
       <c r="Q8">
-        <v>1.44</v>
+        <v>1.76</v>
       </c>
       <c r="R8">
+        <v>1.48</v>
+      </c>
+      <c r="S8">
+        <v>2.94</v>
+      </c>
+      <c r="T8">
         <v>1.86</v>
       </c>
-      <c r="S8">
-        <v>2.08</v>
-      </c>
-      <c r="T8">
-        <v>1.45</v>
-      </c>
       <c r="U8">
-        <v>3.05</v>
+        <v>2.06</v>
       </c>
       <c r="V8">
-        <v>1.43</v>
+        <v>1.17</v>
       </c>
       <c r="W8">
-        <v>1.84</v>
+        <v>2.66</v>
       </c>
       <c r="X8">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="Y8">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Z8">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AA8">
-        <v>380</v>
+        <v>210</v>
       </c>
       <c r="AB8">
+        <v>9.4</v>
+      </c>
+      <c r="AC8">
+        <v>10.5</v>
+      </c>
+      <c r="AD8">
+        <v>950</v>
+      </c>
+      <c r="AE8">
+        <v>110</v>
+      </c>
+      <c r="AF8">
+        <v>10.5</v>
+      </c>
+      <c r="AG8">
+        <v>10</v>
+      </c>
+      <c r="AH8">
         <v>21</v>
       </c>
-      <c r="AC8">
-        <v>12.5</v>
-      </c>
-      <c r="AD8">
-        <v>17.5</v>
-      </c>
-      <c r="AE8">
-        <v>32</v>
-      </c>
-      <c r="AF8">
-        <v>20</v>
-      </c>
-      <c r="AG8">
-        <v>13.5</v>
-      </c>
-      <c r="AH8">
+      <c r="AI8">
+        <v>95</v>
+      </c>
+      <c r="AJ8">
+        <v>18.5</v>
+      </c>
+      <c r="AK8">
         <v>16.5</v>
       </c>
-      <c r="AI8">
-        <v>34</v>
-      </c>
-      <c r="AJ8">
-        <v>32</v>
-      </c>
-      <c r="AK8">
-        <v>21</v>
-      </c>
       <c r="AL8">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="AM8">
-        <v>50</v>
+        <v>130</v>
       </c>
       <c r="AN8">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AO8">
+        <v>120</v>
+      </c>
+      <c r="AP8">
         <v>17</v>
       </c>
-      <c r="AP8">
-        <v>28</v>
-      </c>
       <c r="AQ8">
-        <v>16.5</v>
+        <v>7.2</v>
       </c>
       <c r="AR8">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="AS8">
-        <v>40</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT8">
-        <v>14</v>
+        <v>8.4</v>
       </c>
       <c r="AU8">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV8">
+        <v>7.2</v>
+      </c>
+      <c r="AW8">
+        <v>9</v>
+      </c>
+      <c r="AX8">
+        <v>9</v>
+      </c>
+      <c r="AY8">
+        <v>9</v>
+      </c>
+      <c r="AZ8">
+        <v>18</v>
+      </c>
+      <c r="BA8">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB8">
         <v>13</v>
-      </c>
-      <c r="AW8">
-        <v>22</v>
-      </c>
-      <c r="AX8">
-        <v>14</v>
-      </c>
-      <c r="AY8">
-        <v>10.5</v>
-      </c>
-      <c r="AZ8">
-        <v>12.5</v>
-      </c>
-      <c r="BA8">
-        <v>23</v>
-      </c>
-      <c r="BB8">
-        <v>19</v>
       </c>
       <c r="BC8">
         <v>13.5</v>
       </c>
       <c r="BD8">
-        <v>20</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE8">
-        <v>34</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF8">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BG8">
-        <v>13.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH8">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="BI8">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="BJ8">
-        <v>8.199999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="BK8">
+        <v>3.85</v>
+      </c>
+      <c r="BL8">
+        <v>1000</v>
+      </c>
+      <c r="BM8">
         <v>5.4</v>
       </c>
-      <c r="BL8">
-        <v>1000</v>
-      </c>
-      <c r="BM8">
-        <v>12.5</v>
-      </c>
       <c r="BN8">
-        <v>5.9</v>
+        <v>4.3</v>
       </c>
       <c r="BO8">
-        <v>4.7</v>
+        <v>3.3</v>
       </c>
       <c r="BP8">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BQ8">
-        <v>7.2</v>
+        <v>3.8</v>
       </c>
       <c r="BR8">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BS8">
-        <v>8.6</v>
+        <v>4.6</v>
       </c>
       <c r="BT8">
-        <v>7.2</v>
+        <v>12</v>
       </c>
       <c r="BU8">
-        <v>5.7</v>
+        <v>3.8</v>
       </c>
       <c r="BV8">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="BW8">
-        <v>9</v>
+        <v>5.1</v>
       </c>
       <c r="BX8">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="BY8">
-        <v>9.6</v>
+        <v>5.1</v>
       </c>
       <c r="BZ8">
-        <v>11.5</v>
+        <v>19</v>
       </c>
       <c r="CA8">
-        <v>6.6</v>
+        <v>4.3</v>
       </c>
       <c r="CB8" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2634,241 +2646,241 @@
         <v>86</v>
       </c>
       <c r="B9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D9" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E9" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="F9">
-        <v>2.48</v>
+        <v>2.08</v>
       </c>
       <c r="G9">
-        <v>2.6</v>
+        <v>2.16</v>
       </c>
       <c r="H9">
+        <v>3.2</v>
+      </c>
+      <c r="I9">
         <v>3.4</v>
       </c>
-      <c r="I9">
-        <v>3.7</v>
-      </c>
       <c r="J9">
-        <v>2.94</v>
+        <v>4.3</v>
       </c>
       <c r="K9">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="L9">
-        <v>1.54</v>
+        <v>1.25</v>
       </c>
       <c r="M9">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="N9">
-        <v>2.46</v>
+        <v>7.4</v>
       </c>
       <c r="O9">
-        <v>1.6</v>
+        <v>1.14</v>
       </c>
       <c r="P9">
-        <v>1.48</v>
+        <v>3.1</v>
       </c>
       <c r="Q9">
-        <v>2.78</v>
+        <v>1.44</v>
       </c>
       <c r="R9">
-        <v>1.18</v>
+        <v>1.87</v>
       </c>
       <c r="S9">
-        <v>5.9</v>
+        <v>2.08</v>
       </c>
       <c r="T9">
-        <v>2.22</v>
+        <v>1.45</v>
       </c>
       <c r="U9">
-        <v>1.69</v>
+        <v>3.05</v>
       </c>
       <c r="V9">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="W9">
-        <v>1.62</v>
+        <v>1.87</v>
       </c>
       <c r="X9">
-        <v>9.199999999999999</v>
+        <v>80</v>
       </c>
       <c r="Y9">
+        <v>27</v>
+      </c>
+      <c r="Z9">
+        <v>50</v>
+      </c>
+      <c r="AA9">
+        <v>450</v>
+      </c>
+      <c r="AB9">
+        <v>21</v>
+      </c>
+      <c r="AC9">
+        <v>12.5</v>
+      </c>
+      <c r="AD9">
+        <v>17.5</v>
+      </c>
+      <c r="AE9">
+        <v>32</v>
+      </c>
+      <c r="AF9">
+        <v>22</v>
+      </c>
+      <c r="AG9">
+        <v>12.5</v>
+      </c>
+      <c r="AH9">
+        <v>16.5</v>
+      </c>
+      <c r="AI9">
+        <v>34</v>
+      </c>
+      <c r="AJ9">
+        <v>32</v>
+      </c>
+      <c r="AK9">
+        <v>19.5</v>
+      </c>
+      <c r="AL9">
+        <v>26</v>
+      </c>
+      <c r="AM9">
+        <v>50</v>
+      </c>
+      <c r="AN9">
+        <v>8</v>
+      </c>
+      <c r="AO9">
+        <v>17.5</v>
+      </c>
+      <c r="AP9">
+        <v>23</v>
+      </c>
+      <c r="AQ9">
+        <v>17</v>
+      </c>
+      <c r="AR9">
+        <v>19.5</v>
+      </c>
+      <c r="AS9">
+        <v>29</v>
+      </c>
+      <c r="AT9">
+        <v>14</v>
+      </c>
+      <c r="AU9">
+        <v>10</v>
+      </c>
+      <c r="AV9">
+        <v>13</v>
+      </c>
+      <c r="AW9">
+        <v>19</v>
+      </c>
+      <c r="AX9">
+        <v>14</v>
+      </c>
+      <c r="AY9">
         <v>10.5</v>
       </c>
-      <c r="Z9">
-        <v>26</v>
-      </c>
-      <c r="AA9">
-        <v>90</v>
-      </c>
-      <c r="AB9">
-        <v>7.6</v>
-      </c>
-      <c r="AC9">
+      <c r="AZ9">
+        <v>12.5</v>
+      </c>
+      <c r="BA9">
+        <v>20</v>
+      </c>
+      <c r="BB9">
+        <v>18.5</v>
+      </c>
+      <c r="BC9">
+        <v>13.5</v>
+      </c>
+      <c r="BD9">
+        <v>20</v>
+      </c>
+      <c r="BE9">
+        <v>25</v>
+      </c>
+      <c r="BF9">
+        <v>7.4</v>
+      </c>
+      <c r="BG9">
+        <v>14.5</v>
+      </c>
+      <c r="BH9">
+        <v>5.3</v>
+      </c>
+      <c r="BI9">
+        <v>4.2</v>
+      </c>
+      <c r="BJ9">
         <v>8.199999999999999</v>
       </c>
-      <c r="AD9">
-        <v>17</v>
-      </c>
-      <c r="AE9">
-        <v>70</v>
-      </c>
-      <c r="AF9">
-        <v>17</v>
-      </c>
-      <c r="AG9">
-        <v>14</v>
-      </c>
-      <c r="AH9">
-        <v>29</v>
-      </c>
-      <c r="AI9">
-        <v>110</v>
-      </c>
-      <c r="AJ9">
-        <v>50</v>
-      </c>
-      <c r="AK9">
-        <v>46</v>
-      </c>
-      <c r="AL9">
-        <v>75</v>
-      </c>
-      <c r="AM9">
-        <v>250</v>
-      </c>
-      <c r="AN9">
-        <v>50</v>
-      </c>
-      <c r="AO9">
-        <v>100</v>
-      </c>
-      <c r="AP9">
-        <v>7</v>
-      </c>
-      <c r="AQ9">
-        <v>7.8</v>
-      </c>
-      <c r="AR9">
-        <v>19</v>
-      </c>
-      <c r="AS9">
-        <v>5.9</v>
-      </c>
-      <c r="AT9">
-        <v>6.6</v>
-      </c>
-      <c r="AU9">
-        <v>6.2</v>
-      </c>
-      <c r="AV9">
+      <c r="BK9">
+        <v>5.5</v>
+      </c>
+      <c r="BL9">
+        <v>1000</v>
+      </c>
+      <c r="BM9">
+        <v>13</v>
+      </c>
+      <c r="BN9">
+        <v>5.8</v>
+      </c>
+      <c r="BO9">
+        <v>5.2</v>
+      </c>
+      <c r="BP9">
         <v>13.5</v>
       </c>
-      <c r="AW9">
-        <v>5.8</v>
-      </c>
-      <c r="AX9">
-        <v>12.5</v>
-      </c>
-      <c r="AY9">
-        <v>11</v>
-      </c>
-      <c r="AZ9">
+      <c r="BQ9">
+        <v>10.5</v>
+      </c>
+      <c r="BR9">
+        <v>1000</v>
+      </c>
+      <c r="BS9">
+        <v>9</v>
+      </c>
+      <c r="BT9">
+        <v>7.2</v>
+      </c>
+      <c r="BU9">
+        <v>5</v>
+      </c>
+      <c r="BV9">
         <v>21</v>
       </c>
-      <c r="BA9">
-        <v>6</v>
-      </c>
-      <c r="BB9">
-        <v>5.6</v>
-      </c>
-      <c r="BC9">
-        <v>5.5</v>
-      </c>
-      <c r="BD9">
-        <v>5.8</v>
-      </c>
-      <c r="BE9">
-        <v>6.2</v>
-      </c>
-      <c r="BF9">
-        <v>5.6</v>
-      </c>
-      <c r="BG9">
-        <v>5.9</v>
-      </c>
-      <c r="BH9">
-        <v>2.66</v>
-      </c>
-      <c r="BI9">
-        <v>2.2</v>
-      </c>
-      <c r="BJ9">
-        <v>12</v>
-      </c>
-      <c r="BK9">
-        <v>5.8</v>
-      </c>
-      <c r="BL9">
-        <v>1000</v>
-      </c>
-      <c r="BM9">
-        <v>10.5</v>
-      </c>
-      <c r="BN9">
-        <v>5.4</v>
-      </c>
-      <c r="BO9">
-        <v>4.1</v>
-      </c>
-      <c r="BP9">
-        <v>25</v>
-      </c>
-      <c r="BQ9">
-        <v>7.8</v>
-      </c>
-      <c r="BR9">
-        <v>1000</v>
-      </c>
-      <c r="BS9">
+      <c r="BW9">
         <v>9.4</v>
       </c>
-      <c r="BT9">
+      <c r="BX9">
+        <v>24</v>
+      </c>
+      <c r="BY9">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BZ9">
+        <v>11.5</v>
+      </c>
+      <c r="CA9">
         <v>6.8</v>
       </c>
-      <c r="BU9">
-        <v>5.1</v>
-      </c>
-      <c r="BV9">
-        <v>1000</v>
-      </c>
-      <c r="BW9">
-        <v>8.6</v>
-      </c>
-      <c r="BX9">
-        <v>1000</v>
-      </c>
-      <c r="BY9">
-        <v>9.6</v>
-      </c>
-      <c r="BZ9">
-        <v>1000</v>
-      </c>
-      <c r="CA9">
-        <v>9.4</v>
-      </c>
       <c r="CB9" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2876,241 +2888,483 @@
         <v>87</v>
       </c>
       <c r="B10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D10" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E10" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="F10">
-        <v>2.8</v>
+        <v>2.48</v>
       </c>
       <c r="G10">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="H10">
-        <v>2.72</v>
+        <v>3.4</v>
       </c>
       <c r="I10">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="J10">
-        <v>2.82</v>
+        <v>2.96</v>
       </c>
       <c r="K10">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="L10">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="M10">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="N10">
-        <v>3.3</v>
+        <v>2.48</v>
       </c>
       <c r="O10">
+        <v>1.6</v>
+      </c>
+      <c r="P10">
+        <v>1.48</v>
+      </c>
+      <c r="Q10">
+        <v>2.78</v>
+      </c>
+      <c r="R10">
+        <v>1.18</v>
+      </c>
+      <c r="S10">
+        <v>5.9</v>
+      </c>
+      <c r="T10">
+        <v>2.2</v>
+      </c>
+      <c r="U10">
+        <v>1.7</v>
+      </c>
+      <c r="V10">
         <v>1.37</v>
       </c>
-      <c r="P10">
-        <v>1.76</v>
-      </c>
-      <c r="Q10">
-        <v>2.16</v>
-      </c>
-      <c r="R10">
-        <v>1.28</v>
-      </c>
-      <c r="S10">
-        <v>4</v>
-      </c>
-      <c r="T10">
-        <v>1.84</v>
-      </c>
-      <c r="U10">
-        <v>2.08</v>
-      </c>
-      <c r="V10">
-        <v>1.5</v>
-      </c>
       <c r="W10">
-        <v>1.45</v>
+        <v>1.62</v>
       </c>
       <c r="X10">
-        <v>13.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y10">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Z10">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="AA10">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="AB10">
-        <v>11</v>
+        <v>7.6</v>
       </c>
       <c r="AC10">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD10">
-        <v>12.5</v>
+        <v>17</v>
       </c>
       <c r="AE10">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="AF10">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="AG10">
         <v>13.5</v>
       </c>
       <c r="AH10">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="AI10">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="AJ10">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AK10">
         <v>46</v>
       </c>
       <c r="AL10">
+        <v>75</v>
+      </c>
+      <c r="AM10">
+        <v>250</v>
+      </c>
+      <c r="AN10">
+        <v>50</v>
+      </c>
+      <c r="AO10">
+        <v>100</v>
+      </c>
+      <c r="AP10">
+        <v>7</v>
+      </c>
+      <c r="AQ10">
+        <v>7.8</v>
+      </c>
+      <c r="AR10">
+        <v>19</v>
+      </c>
+      <c r="AS10">
+        <v>6</v>
+      </c>
+      <c r="AT10">
+        <v>6.6</v>
+      </c>
+      <c r="AU10">
+        <v>6.2</v>
+      </c>
+      <c r="AV10">
+        <v>13.5</v>
+      </c>
+      <c r="AW10">
+        <v>5.9</v>
+      </c>
+      <c r="AX10">
+        <v>12.5</v>
+      </c>
+      <c r="AY10">
+        <v>11</v>
+      </c>
+      <c r="AZ10">
+        <v>21</v>
+      </c>
+      <c r="BA10">
+        <v>6</v>
+      </c>
+      <c r="BB10">
+        <v>5.7</v>
+      </c>
+      <c r="BC10">
+        <v>32</v>
+      </c>
+      <c r="BD10">
+        <v>6</v>
+      </c>
+      <c r="BE10">
+        <v>6.2</v>
+      </c>
+      <c r="BF10">
+        <v>5.7</v>
+      </c>
+      <c r="BG10">
+        <v>6</v>
+      </c>
+      <c r="BH10">
+        <v>2.68</v>
+      </c>
+      <c r="BI10">
+        <v>2.22</v>
+      </c>
+      <c r="BJ10">
+        <v>12</v>
+      </c>
+      <c r="BK10">
+        <v>5.8</v>
+      </c>
+      <c r="BL10">
+        <v>1000</v>
+      </c>
+      <c r="BM10">
+        <v>10.5</v>
+      </c>
+      <c r="BN10">
+        <v>5.4</v>
+      </c>
+      <c r="BO10">
+        <v>4.1</v>
+      </c>
+      <c r="BP10">
+        <v>1000</v>
+      </c>
+      <c r="BQ10">
+        <v>7.6</v>
+      </c>
+      <c r="BR10">
+        <v>1000</v>
+      </c>
+      <c r="BS10">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BT10">
+        <v>6.8</v>
+      </c>
+      <c r="BU10">
+        <v>5.1</v>
+      </c>
+      <c r="BV10">
+        <v>1000</v>
+      </c>
+      <c r="BW10">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BX10">
+        <v>1000</v>
+      </c>
+      <c r="BY10">
+        <v>9.6</v>
+      </c>
+      <c r="BZ10">
+        <v>1000</v>
+      </c>
+      <c r="CA10">
+        <v>9.6</v>
+      </c>
+      <c r="CB10" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="11" spans="1:80">
+      <c r="A11" t="s">
+        <v>88</v>
+      </c>
+      <c r="B11" t="s">
+        <v>89</v>
+      </c>
+      <c r="C11" t="s">
+        <v>97</v>
+      </c>
+      <c r="D11" t="s">
+        <v>107</v>
+      </c>
+      <c r="E11" t="s">
+        <v>117</v>
+      </c>
+      <c r="F11">
+        <v>2.8</v>
+      </c>
+      <c r="G11">
+        <v>3.2</v>
+      </c>
+      <c r="H11">
+        <v>2.58</v>
+      </c>
+      <c r="I11">
+        <v>3</v>
+      </c>
+      <c r="J11">
+        <v>2.84</v>
+      </c>
+      <c r="K11">
+        <v>3.65</v>
+      </c>
+      <c r="L11">
+        <v>1.01</v>
+      </c>
+      <c r="M11">
+        <v>1.09</v>
+      </c>
+      <c r="N11">
+        <v>3.3</v>
+      </c>
+      <c r="O11">
+        <v>1.39</v>
+      </c>
+      <c r="P11">
+        <v>1.76</v>
+      </c>
+      <c r="Q11">
+        <v>2.16</v>
+      </c>
+      <c r="R11">
+        <v>1.28</v>
+      </c>
+      <c r="S11">
+        <v>4</v>
+      </c>
+      <c r="T11">
+        <v>1.84</v>
+      </c>
+      <c r="U11">
+        <v>2.08</v>
+      </c>
+      <c r="V11">
+        <v>1.5</v>
+      </c>
+      <c r="W11">
+        <v>1.45</v>
+      </c>
+      <c r="X11">
+        <v>13.5</v>
+      </c>
+      <c r="Y11">
+        <v>10</v>
+      </c>
+      <c r="Z11">
+        <v>19</v>
+      </c>
+      <c r="AA11">
+        <v>50</v>
+      </c>
+      <c r="AB11">
+        <v>11</v>
+      </c>
+      <c r="AC11">
+        <v>8</v>
+      </c>
+      <c r="AD11">
+        <v>12.5</v>
+      </c>
+      <c r="AE11">
+        <v>38</v>
+      </c>
+      <c r="AF11">
+        <v>24</v>
+      </c>
+      <c r="AG11">
+        <v>13.5</v>
+      </c>
+      <c r="AH11">
+        <v>23</v>
+      </c>
+      <c r="AI11">
         <v>60</v>
       </c>
-      <c r="AM10">
+      <c r="AJ11">
+        <v>60</v>
+      </c>
+      <c r="AK11">
+        <v>46</v>
+      </c>
+      <c r="AL11">
+        <v>60</v>
+      </c>
+      <c r="AM11">
         <v>130</v>
       </c>
-      <c r="AN10">
+      <c r="AN11">
         <v>44</v>
       </c>
-      <c r="AO10">
-        <v>36</v>
-      </c>
-      <c r="AP10">
+      <c r="AO11">
+        <v>32</v>
+      </c>
+      <c r="AP11">
         <v>10</v>
       </c>
-      <c r="AQ10">
+      <c r="AQ11">
         <v>8.800000000000001</v>
       </c>
-      <c r="AR10">
+      <c r="AR11">
         <v>15</v>
       </c>
-      <c r="AS10">
+      <c r="AS11">
         <v>7.4</v>
       </c>
-      <c r="AT10">
+      <c r="AT11">
         <v>9.4</v>
       </c>
-      <c r="AU10">
+      <c r="AU11">
         <v>6.6</v>
       </c>
-      <c r="AV10">
+      <c r="AV11">
         <v>10.5</v>
       </c>
-      <c r="AW10">
+      <c r="AW11">
         <v>7</v>
       </c>
-      <c r="AX10">
-        <v>14.5</v>
-      </c>
-      <c r="AY10">
+      <c r="AX11">
+        <v>6</v>
+      </c>
+      <c r="AY11">
         <v>11.5</v>
       </c>
-      <c r="AZ10">
+      <c r="AZ11">
         <v>16</v>
       </c>
-      <c r="BA10">
+      <c r="BA11">
         <v>7.6</v>
       </c>
-      <c r="BB10">
+      <c r="BB11">
         <v>7.6</v>
       </c>
-      <c r="BC10">
+      <c r="BC11">
         <v>29</v>
       </c>
-      <c r="BD10">
+      <c r="BD11">
         <v>7.6</v>
       </c>
-      <c r="BE10">
+      <c r="BE11">
         <v>8.199999999999999</v>
       </c>
-      <c r="BF10">
+      <c r="BF11">
         <v>7.2</v>
       </c>
-      <c r="BG10">
+      <c r="BG11">
         <v>26</v>
       </c>
-      <c r="BH10">
-        <v>1000</v>
-      </c>
-      <c r="BI10">
+      <c r="BH11">
+        <v>1000</v>
+      </c>
+      <c r="BI11">
         <v>1.04</v>
       </c>
-      <c r="BJ10">
-        <v>1000</v>
-      </c>
-      <c r="BK10">
+      <c r="BJ11">
+        <v>1000</v>
+      </c>
+      <c r="BK11">
         <v>1.04</v>
       </c>
-      <c r="BL10">
-        <v>1000</v>
-      </c>
-      <c r="BM10">
+      <c r="BL11">
+        <v>1000</v>
+      </c>
+      <c r="BM11">
         <v>1.04</v>
       </c>
-      <c r="BN10">
-        <v>1000</v>
-      </c>
-      <c r="BO10">
+      <c r="BN11">
+        <v>1000</v>
+      </c>
+      <c r="BO11">
         <v>1.04</v>
       </c>
-      <c r="BP10">
-        <v>1000</v>
-      </c>
-      <c r="BQ10">
+      <c r="BP11">
+        <v>1000</v>
+      </c>
+      <c r="BQ11">
         <v>1.04</v>
       </c>
-      <c r="BR10">
-        <v>1000</v>
-      </c>
-      <c r="BS10">
+      <c r="BR11">
+        <v>1000</v>
+      </c>
+      <c r="BS11">
         <v>1.04</v>
       </c>
-      <c r="BT10">
-        <v>1000</v>
-      </c>
-      <c r="BU10">
+      <c r="BT11">
+        <v>1000</v>
+      </c>
+      <c r="BU11">
         <v>1.04</v>
       </c>
-      <c r="BV10">
-        <v>1000</v>
-      </c>
-      <c r="BW10">
+      <c r="BV11">
+        <v>1000</v>
+      </c>
+      <c r="BW11">
         <v>1.04</v>
       </c>
-      <c r="BX10">
-        <v>1000</v>
-      </c>
-      <c r="BY10">
+      <c r="BX11">
+        <v>1000</v>
+      </c>
+      <c r="BY11">
         <v>1.04</v>
       </c>
-      <c r="BZ10">
-        <v>1000</v>
-      </c>
-      <c r="CA10">
+      <c r="BZ11">
+        <v>1000</v>
+      </c>
+      <c r="CA11">
         <v>1.04</v>
       </c>
-      <c r="CB10" t="s">
-        <v>114</v>
+      <c r="CB11" t="s">
+        <v>118</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-18.xlsx
@@ -370,7 +370,7 @@
     <t>Atletico GO</t>
   </si>
   <si>
-    <t>2026-08-17 09:33:37</t>
+    <t>2026-08-17 11:42:58</t>
   </si>
 </sst>
 </file>
@@ -964,226 +964,226 @@
         <v>108</v>
       </c>
       <c r="F2">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="G2">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="I2">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="J2">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="K2">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L2">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="M2">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N2">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="O2">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="P2">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="Q2">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="R2">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="S2">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="T2">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="U2">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="V2">
         <v>1.65</v>
       </c>
       <c r="W2">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="X2">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="Y2">
+        <v>8</v>
+      </c>
+      <c r="Z2">
+        <v>13</v>
+      </c>
+      <c r="AA2">
+        <v>34</v>
+      </c>
+      <c r="AB2">
+        <v>12.5</v>
+      </c>
+      <c r="AC2">
+        <v>7.6</v>
+      </c>
+      <c r="AD2">
+        <v>11.5</v>
+      </c>
+      <c r="AE2">
+        <v>36</v>
+      </c>
+      <c r="AF2">
+        <v>28</v>
+      </c>
+      <c r="AG2">
+        <v>19.5</v>
+      </c>
+      <c r="AH2">
+        <v>24</v>
+      </c>
+      <c r="AI2">
+        <v>60</v>
+      </c>
+      <c r="AJ2">
+        <v>120</v>
+      </c>
+      <c r="AK2">
+        <v>80</v>
+      </c>
+      <c r="AL2">
+        <v>90</v>
+      </c>
+      <c r="AM2">
+        <v>170</v>
+      </c>
+      <c r="AN2">
+        <v>100</v>
+      </c>
+      <c r="AO2">
+        <v>25</v>
+      </c>
+      <c r="AP2">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ2">
+        <v>7.2</v>
+      </c>
+      <c r="AR2">
+        <v>11</v>
+      </c>
+      <c r="AS2">
+        <v>20</v>
+      </c>
+      <c r="AT2">
         <v>10.5</v>
-      </c>
-      <c r="Z2">
-        <v>16.5</v>
-      </c>
-      <c r="AA2">
-        <v>38</v>
-      </c>
-      <c r="AB2">
-        <v>14</v>
-      </c>
-      <c r="AC2">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD2">
-        <v>11</v>
-      </c>
-      <c r="AE2">
-        <v>34</v>
-      </c>
-      <c r="AF2">
-        <v>30</v>
-      </c>
-      <c r="AG2">
-        <v>18</v>
-      </c>
-      <c r="AH2">
-        <v>23</v>
-      </c>
-      <c r="AI2">
-        <v>55</v>
-      </c>
-      <c r="AJ2">
-        <v>110</v>
-      </c>
-      <c r="AK2">
-        <v>60</v>
-      </c>
-      <c r="AL2">
-        <v>80</v>
-      </c>
-      <c r="AM2">
-        <v>150</v>
-      </c>
-      <c r="AN2">
-        <v>85</v>
-      </c>
-      <c r="AO2">
-        <v>28</v>
-      </c>
-      <c r="AP2">
-        <v>10.5</v>
-      </c>
-      <c r="AQ2">
-        <v>7.6</v>
-      </c>
-      <c r="AR2">
-        <v>11.5</v>
-      </c>
-      <c r="AS2">
-        <v>4.5</v>
-      </c>
-      <c r="AT2">
-        <v>10</v>
       </c>
       <c r="AU2">
         <v>6.6</v>
       </c>
       <c r="AV2">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW2">
-        <v>4.5</v>
+        <v>18.5</v>
       </c>
       <c r="AX2">
-        <v>15.5</v>
+        <v>21</v>
       </c>
       <c r="AY2">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AZ2">
         <v>17</v>
       </c>
       <c r="BA2">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BB2">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="BC2">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="BD2">
-        <v>4.9</v>
+        <v>44</v>
       </c>
       <c r="BE2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="BF2">
-        <v>4.9</v>
+        <v>46</v>
       </c>
       <c r="BG2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BH2">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="BI2">
-        <v>2.56</v>
+        <v>2.46</v>
       </c>
       <c r="BJ2">
         <v>12.5</v>
       </c>
       <c r="BK2">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="BN2">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BO2">
         <v>5.5</v>
       </c>
       <c r="BP2">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BQ2">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="BR2">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BS2">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="BT2">
         <v>5.5</v>
       </c>
       <c r="BU2">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BV2">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BW2">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="BX2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BY2">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="BZ2">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="CA2">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="CB2" t="s">
         <v>118</v>
@@ -1215,64 +1215,64 @@
         <v>2.76</v>
       </c>
       <c r="I3">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="J3">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="K3">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="L3">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="M3">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="N3">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="O3">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="P3">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="Q3">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R3">
         <v>1.16</v>
       </c>
       <c r="S3">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="T3">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="U3">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="V3">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W3">
         <v>1.42</v>
       </c>
       <c r="X3">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="Y3">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="Z3">
         <v>15.5</v>
       </c>
       <c r="AA3">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AB3">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AC3">
         <v>6.6</v>
@@ -1281,16 +1281,16 @@
         <v>14</v>
       </c>
       <c r="AE3">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF3">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AG3">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AH3">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AI3">
         <v>85</v>
@@ -1299,25 +1299,25 @@
         <v>65</v>
       </c>
       <c r="AK3">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AL3">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AM3">
         <v>250</v>
       </c>
       <c r="AN3">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AO3">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP3">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AQ3">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AR3">
         <v>14</v>
@@ -1326,7 +1326,7 @@
         <v>36</v>
       </c>
       <c r="AT3">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AU3">
         <v>6.4</v>
@@ -1347,13 +1347,13 @@
         <v>24</v>
       </c>
       <c r="BA3">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="BB3">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BC3">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BD3">
         <v>60</v>
@@ -1365,67 +1365,67 @@
         <v>48</v>
       </c>
       <c r="BG3">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="BH3">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="BI3">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="BJ3">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK3">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>2.2</v>
+        <v>15.5</v>
       </c>
       <c r="BN3">
         <v>6.2</v>
       </c>
       <c r="BO3">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BP3">
         <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>2.14</v>
+        <v>13</v>
       </c>
       <c r="BT3">
         <v>5.4</v>
       </c>
       <c r="BU3">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="BZ3">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="CA3">
-        <v>2.14</v>
+        <v>13</v>
       </c>
       <c r="CB3" t="s">
         <v>118</v>
@@ -1448,22 +1448,22 @@
         <v>110</v>
       </c>
       <c r="F4">
-        <v>2.06</v>
+        <v>2.18</v>
       </c>
       <c r="G4">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="H4">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="I4">
+        <v>3.75</v>
+      </c>
+      <c r="J4">
+        <v>3.55</v>
+      </c>
+      <c r="K4">
         <v>3.9</v>
-      </c>
-      <c r="J4">
-        <v>3.65</v>
-      </c>
-      <c r="K4">
-        <v>4.1</v>
       </c>
       <c r="L4">
         <v>1.36</v>
@@ -1490,16 +1490,16 @@
         <v>3.1</v>
       </c>
       <c r="T4">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="U4">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="V4">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W4">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="X4">
         <v>19.5</v>
@@ -1508,7 +1508,7 @@
         <v>16</v>
       </c>
       <c r="Z4">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA4">
         <v>80</v>
@@ -1535,10 +1535,10 @@
         <v>17.5</v>
       </c>
       <c r="AI4">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ4">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AK4">
         <v>26</v>
@@ -1547,13 +1547,13 @@
         <v>42</v>
       </c>
       <c r="AM4">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN4">
         <v>15</v>
       </c>
       <c r="AO4">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AP4">
         <v>12.5</v>
@@ -1592,13 +1592,13 @@
         <v>32</v>
       </c>
       <c r="BB4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BC4">
         <v>18.5</v>
       </c>
       <c r="BD4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BE4">
         <v>55</v>
@@ -1690,226 +1690,226 @@
         <v>111</v>
       </c>
       <c r="F5">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="G5">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="H5">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="I5">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="J5">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K5">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L5">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="M5">
         <v>1.05</v>
       </c>
       <c r="N5">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="O5">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="P5">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q5">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="R5">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S5">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="T5">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="U5">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V5">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W5">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="X5">
         <v>21</v>
       </c>
       <c r="Y5">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="Z5">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AA5">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AB5">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC5">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AD5">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AE5">
         <v>65</v>
       </c>
       <c r="AF5">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AG5">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AH5">
         <v>18.5</v>
       </c>
       <c r="AI5">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ5">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AK5">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AL5">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AM5">
         <v>100</v>
       </c>
       <c r="AN5">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AO5">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AP5">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AQ5">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AR5">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AS5">
-        <v>7.8</v>
+        <v>55</v>
       </c>
       <c r="AT5">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AU5">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV5">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AW5">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AX5">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY5">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AZ5">
         <v>15</v>
       </c>
       <c r="BA5">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BB5">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BC5">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BD5">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BE5">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="BF5">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG5">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BH5">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BI5">
         <v>3.15</v>
       </c>
       <c r="BJ5">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BK5">
-        <v>7.4</v>
+        <v>3.7</v>
       </c>
       <c r="BL5">
         <v>120</v>
       </c>
       <c r="BM5">
-        <v>8.6</v>
+        <v>5.3</v>
       </c>
       <c r="BN5">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BO5">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="BP5">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BQ5">
-        <v>9.6</v>
+        <v>3.95</v>
       </c>
       <c r="BR5">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BS5">
-        <v>6.8</v>
+        <v>4.6</v>
       </c>
       <c r="BT5">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU5">
-        <v>6.2</v>
+        <v>3.55</v>
       </c>
       <c r="BV5">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="BW5">
-        <v>7.4</v>
+        <v>4.9</v>
       </c>
       <c r="BX5">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BY5">
-        <v>7.8</v>
+        <v>5</v>
       </c>
       <c r="BZ5">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="CA5">
-        <v>6.2</v>
+        <v>4.4</v>
       </c>
       <c r="CB5" t="s">
         <v>118</v>
@@ -1932,82 +1932,82 @@
         <v>112</v>
       </c>
       <c r="F6">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="G6">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="H6">
-        <v>2.9</v>
+        <v>2.74</v>
       </c>
       <c r="I6">
-        <v>2.96</v>
+        <v>2.8</v>
       </c>
       <c r="J6">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K6">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L6">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="M6">
         <v>1.06</v>
       </c>
       <c r="N6">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="O6">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="P6">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="Q6">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="R6">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="S6">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="T6">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="U6">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="V6">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="W6">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="X6">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y6">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Z6">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AA6">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AB6">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC6">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD6">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE6">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AF6">
         <v>18</v>
@@ -2016,142 +2016,142 @@
         <v>12</v>
       </c>
       <c r="AH6">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AI6">
+        <v>38</v>
+      </c>
+      <c r="AJ6">
         <v>40</v>
       </c>
-      <c r="AJ6">
-        <v>36</v>
-      </c>
       <c r="AK6">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AL6">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AM6">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AN6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ6">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AR6">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AS6">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AT6">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AU6">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV6">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AW6">
         <v>26</v>
       </c>
       <c r="AX6">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AY6">
         <v>10.5</v>
       </c>
       <c r="AZ6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA6">
         <v>32</v>
       </c>
       <c r="BB6">
+        <v>34</v>
+      </c>
+      <c r="BC6">
+        <v>24</v>
+      </c>
+      <c r="BD6">
+        <v>32</v>
+      </c>
+      <c r="BE6">
+        <v>55</v>
+      </c>
+      <c r="BF6">
+        <v>19.5</v>
+      </c>
+      <c r="BG6">
+        <v>20</v>
+      </c>
+      <c r="BH6">
+        <v>3.65</v>
+      </c>
+      <c r="BI6">
+        <v>3</v>
+      </c>
+      <c r="BJ6">
+        <v>9</v>
+      </c>
+      <c r="BK6">
+        <v>5.9</v>
+      </c>
+      <c r="BL6">
+        <v>100</v>
+      </c>
+      <c r="BM6">
+        <v>15</v>
+      </c>
+      <c r="BN6">
+        <v>5.8</v>
+      </c>
+      <c r="BO6">
+        <v>4.5</v>
+      </c>
+      <c r="BP6">
+        <v>19.5</v>
+      </c>
+      <c r="BQ6">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BR6">
         <v>30</v>
       </c>
-      <c r="BC6">
-        <v>21</v>
-      </c>
-      <c r="BD6">
-        <v>28</v>
-      </c>
-      <c r="BE6">
-        <v>60</v>
-      </c>
-      <c r="BF6">
-        <v>15.5</v>
-      </c>
-      <c r="BG6">
-        <v>19.5</v>
-      </c>
-      <c r="BH6">
-        <v>3.85</v>
-      </c>
-      <c r="BI6">
-        <v>3.05</v>
-      </c>
-      <c r="BJ6">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BK6">
-        <v>4.6</v>
-      </c>
-      <c r="BL6">
-        <v>90</v>
-      </c>
-      <c r="BM6">
-        <v>9</v>
-      </c>
-      <c r="BN6">
-        <v>5.6</v>
-      </c>
-      <c r="BO6">
-        <v>5</v>
-      </c>
-      <c r="BP6">
-        <v>18</v>
-      </c>
-      <c r="BQ6">
-        <v>6.4</v>
-      </c>
-      <c r="BR6">
-        <v>27</v>
-      </c>
       <c r="BS6">
-        <v>7.2</v>
+        <v>11</v>
       </c>
       <c r="BT6">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BU6">
-        <v>5.7</v>
+        <v>4.5</v>
       </c>
       <c r="BV6">
         <v>21</v>
       </c>
       <c r="BW6">
-        <v>6.6</v>
+        <v>9.6</v>
       </c>
       <c r="BX6">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BY6">
-        <v>7.4</v>
+        <v>11</v>
       </c>
       <c r="BZ6">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="CA6">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="CB6" t="s">
         <v>118</v>
@@ -2174,220 +2174,220 @@
         <v>113</v>
       </c>
       <c r="F7">
-        <v>1.18</v>
+        <v>1.64</v>
       </c>
       <c r="G7">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="H7">
-        <v>2.3</v>
+        <v>5.8</v>
       </c>
       <c r="I7">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="J7">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="K7">
-        <v>950</v>
+        <v>4.4</v>
       </c>
       <c r="L7">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M7">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N7">
-        <v>1.24</v>
+        <v>3.6</v>
       </c>
       <c r="O7">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="P7">
-        <v>1.24</v>
+        <v>1.91</v>
       </c>
       <c r="Q7">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="R7">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="S7">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="T7">
-        <v>1.11</v>
+        <v>1.95</v>
       </c>
       <c r="U7">
-        <v>1.11</v>
+        <v>1.92</v>
       </c>
       <c r="V7">
         <v>1.17</v>
       </c>
       <c r="W7">
-        <v>2.24</v>
+        <v>2.34</v>
       </c>
       <c r="X7">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Y7">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z7">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA7">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AB7">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC7">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD7">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AE7">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF7">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AG7">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH7">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI7">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ7">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AK7">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL7">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM7">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN7">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AO7">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AP7">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AQ7">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AR7">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="AS7">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AT7">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AU7">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AV7">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AW7">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="AX7">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AY7">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ7">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BA7">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BB7">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BC7">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BD7">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="BE7">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BF7">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BG7">
-        <v>1.01</v>
+        <v>60</v>
       </c>
       <c r="BH7">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="BI7">
-        <v>1.04</v>
+        <v>2.74</v>
       </c>
       <c r="BJ7">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK7">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>1.04</v>
+        <v>12.5</v>
       </c>
       <c r="BN7">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BO7">
-        <v>1.04</v>
+        <v>3.2</v>
       </c>
       <c r="BP7">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BQ7">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT7">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU7">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BV7">
         <v>1000</v>
       </c>
       <c r="BW7">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BZ7">
         <v>0</v>
@@ -2416,10 +2416,10 @@
         <v>114</v>
       </c>
       <c r="F8">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="G8">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="H8">
         <v>6.4</v>
@@ -2434,7 +2434,7 @@
         <v>4.6</v>
       </c>
       <c r="L8">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="M8">
         <v>1.05</v>
@@ -2446,34 +2446,34 @@
         <v>1.25</v>
       </c>
       <c r="P8">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q8">
         <v>1.76</v>
       </c>
       <c r="R8">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S8">
         <v>2.94</v>
       </c>
       <c r="T8">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="U8">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V8">
         <v>1.17</v>
       </c>
       <c r="W8">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="X8">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Y8">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Z8">
         <v>65</v>
@@ -2482,22 +2482,22 @@
         <v>210</v>
       </c>
       <c r="AB8">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AC8">
         <v>10.5</v>
       </c>
       <c r="AD8">
-        <v>950</v>
+        <v>25</v>
       </c>
       <c r="AE8">
         <v>110</v>
       </c>
       <c r="AF8">
+        <v>12</v>
+      </c>
+      <c r="AG8">
         <v>10.5</v>
-      </c>
-      <c r="AG8">
-        <v>10</v>
       </c>
       <c r="AH8">
         <v>21</v>
@@ -2506,13 +2506,13 @@
         <v>95</v>
       </c>
       <c r="AJ8">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="AK8">
         <v>16.5</v>
       </c>
       <c r="AL8">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AM8">
         <v>130</v>
@@ -2527,13 +2527,13 @@
         <v>17</v>
       </c>
       <c r="AQ8">
-        <v>7.2</v>
+        <v>20</v>
       </c>
       <c r="AR8">
-        <v>42</v>
+        <v>7.8</v>
       </c>
       <c r="AS8">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AT8">
         <v>8.4</v>
@@ -2542,10 +2542,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV8">
-        <v>7.2</v>
+        <v>21</v>
       </c>
       <c r="AW8">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX8">
         <v>9</v>
@@ -2557,46 +2557,46 @@
         <v>18</v>
       </c>
       <c r="BA8">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB8">
         <v>13</v>
       </c>
       <c r="BC8">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BD8">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="BE8">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BF8">
         <v>6.8</v>
       </c>
       <c r="BG8">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH8">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BI8">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BJ8">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BK8">
-        <v>3.85</v>
+        <v>3.35</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="BN8">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BO8">
         <v>3.3</v>
@@ -2605,37 +2605,37 @@
         <v>12</v>
       </c>
       <c r="BQ8">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="BR8">
         <v>28</v>
       </c>
       <c r="BS8">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="BT8">
         <v>12</v>
       </c>
       <c r="BU8">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="BV8">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BW8">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="BX8">
         <v>65</v>
       </c>
       <c r="BY8">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="BZ8">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="CA8">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="CB8" t="s">
         <v>118</v>
@@ -2688,16 +2688,16 @@
         <v>1.14</v>
       </c>
       <c r="P9">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="Q9">
         <v>1.44</v>
       </c>
       <c r="R9">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="S9">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="T9">
         <v>1.45</v>
@@ -2709,10 +2709,10 @@
         <v>1.42</v>
       </c>
       <c r="W9">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="X9">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="Y9">
         <v>27</v>
@@ -2721,13 +2721,13 @@
         <v>50</v>
       </c>
       <c r="AA9">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="AB9">
         <v>21</v>
       </c>
       <c r="AC9">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD9">
         <v>17.5</v>
@@ -2739,7 +2739,7 @@
         <v>22</v>
       </c>
       <c r="AG9">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH9">
         <v>16.5</v>
@@ -2760,10 +2760,10 @@
         <v>50</v>
       </c>
       <c r="AN9">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO9">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AP9">
         <v>23</v>
@@ -2799,10 +2799,10 @@
         <v>12.5</v>
       </c>
       <c r="BA9">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BB9">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BC9">
         <v>13.5</v>
@@ -2826,58 +2826,58 @@
         <v>4.2</v>
       </c>
       <c r="BJ9">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BK9">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BN9">
         <v>5.8</v>
       </c>
       <c r="BO9">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="BP9">
         <v>13.5</v>
       </c>
       <c r="BQ9">
-        <v>10.5</v>
+        <v>7</v>
       </c>
       <c r="BR9">
         <v>1000</v>
       </c>
       <c r="BS9">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BT9">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BU9">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="BV9">
         <v>21</v>
       </c>
       <c r="BW9">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX9">
         <v>24</v>
       </c>
       <c r="BY9">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ9">
         <v>11.5</v>
       </c>
       <c r="CA9">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="CB9" t="s">
         <v>118</v>
@@ -2900,13 +2900,13 @@
         <v>116</v>
       </c>
       <c r="F10">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="G10">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="H10">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="I10">
         <v>3.7</v>
@@ -2915,7 +2915,7 @@
         <v>2.96</v>
       </c>
       <c r="K10">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L10">
         <v>1.62</v>
@@ -2951,25 +2951,25 @@
         <v>1.37</v>
       </c>
       <c r="W10">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="X10">
         <v>9.199999999999999</v>
       </c>
       <c r="Y10">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Z10">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AA10">
         <v>90</v>
       </c>
       <c r="AB10">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AC10">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD10">
         <v>17</v>
@@ -2978,10 +2978,10 @@
         <v>70</v>
       </c>
       <c r="AF10">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AG10">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AH10">
         <v>29</v>
@@ -2990,19 +2990,19 @@
         <v>100</v>
       </c>
       <c r="AJ10">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AK10">
         <v>46</v>
       </c>
       <c r="AL10">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AM10">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="AN10">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AO10">
         <v>100</v>
@@ -3017,10 +3017,10 @@
         <v>19</v>
       </c>
       <c r="AS10">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AT10">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AU10">
         <v>6.2</v>
@@ -3029,7 +3029,7 @@
         <v>13.5</v>
       </c>
       <c r="AW10">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AX10">
         <v>12.5</v>
@@ -3041,25 +3041,25 @@
         <v>21</v>
       </c>
       <c r="BA10">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BB10">
-        <v>5.7</v>
+        <v>34</v>
       </c>
       <c r="BC10">
         <v>32</v>
       </c>
       <c r="BD10">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BE10">
         <v>6.2</v>
       </c>
       <c r="BF10">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BG10">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BH10">
         <v>2.68</v>
@@ -3142,25 +3142,25 @@
         <v>117</v>
       </c>
       <c r="F11">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="G11">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="H11">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="I11">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="J11">
-        <v>2.84</v>
+        <v>3.15</v>
       </c>
       <c r="K11">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="L11">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M11">
         <v>1.09</v>
@@ -3169,7 +3169,7 @@
         <v>3.3</v>
       </c>
       <c r="O11">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P11">
         <v>1.76</v>
@@ -3181,7 +3181,7 @@
         <v>1.28</v>
       </c>
       <c r="S11">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="T11">
         <v>1.84</v>
@@ -3190,16 +3190,16 @@
         <v>2.08</v>
       </c>
       <c r="V11">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W11">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="X11">
         <v>13.5</v>
       </c>
       <c r="Y11">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Z11">
         <v>19</v>
@@ -3247,7 +3247,7 @@
         <v>44</v>
       </c>
       <c r="AO11">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AP11">
         <v>10</v>
@@ -3259,7 +3259,7 @@
         <v>15</v>
       </c>
       <c r="AS11">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AT11">
         <v>9.4</v>
@@ -3271,10 +3271,10 @@
         <v>10.5</v>
       </c>
       <c r="AW11">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AX11">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="AY11">
         <v>11.5</v>
@@ -3283,85 +3283,85 @@
         <v>16</v>
       </c>
       <c r="BA11">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="BB11">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="BC11">
         <v>29</v>
       </c>
       <c r="BD11">
+        <v>7</v>
+      </c>
+      <c r="BE11">
         <v>7.6</v>
       </c>
-      <c r="BE11">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BF11">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BG11">
         <v>26</v>
       </c>
       <c r="BH11">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="BI11">
-        <v>1.04</v>
+        <v>2.58</v>
       </c>
       <c r="BJ11">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK11">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BN11">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BO11">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BP11">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BQ11">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BR11">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS11">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BT11">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU11">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BV11">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BW11">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BX11">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BY11">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BZ11">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="CA11">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="CB11" t="s">
         <v>118</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-18.xlsx
@@ -370,7 +370,7 @@
     <t>Atletico GO</t>
   </si>
   <si>
-    <t>2026-08-17 11:42:58</t>
+    <t>2026-08-17 13:52:13</t>
   </si>
 </sst>
 </file>
@@ -967,13 +967,13 @@
         <v>3.85</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="H2">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="I2">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="J2">
         <v>3.25</v>
@@ -988,7 +988,7 @@
         <v>1.1</v>
       </c>
       <c r="N2">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O2">
         <v>1.43</v>
@@ -1000,7 +1000,7 @@
         <v>2.28</v>
       </c>
       <c r="R2">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S2">
         <v>4.4</v>
@@ -1009,13 +1009,13 @@
         <v>1.97</v>
       </c>
       <c r="U2">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="V2">
         <v>1.65</v>
       </c>
       <c r="W2">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="X2">
         <v>11</v>
@@ -1057,7 +1057,7 @@
         <v>120</v>
       </c>
       <c r="AK2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AL2">
         <v>90</v>
@@ -1096,7 +1096,7 @@
         <v>18.5</v>
       </c>
       <c r="AX2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY2">
         <v>14.5</v>
@@ -1114,7 +1114,7 @@
         <v>42</v>
       </c>
       <c r="BD2">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BE2">
         <v>11</v>
@@ -1129,22 +1129,22 @@
         <v>3.5</v>
       </c>
       <c r="BI2">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="BJ2">
         <v>12.5</v>
       </c>
       <c r="BK2">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BN2">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BO2">
         <v>5.5</v>
@@ -1153,13 +1153,13 @@
         <v>46</v>
       </c>
       <c r="BQ2">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BR2">
         <v>65</v>
       </c>
       <c r="BS2">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BT2">
         <v>5.5</v>
@@ -1180,7 +1180,7 @@
         <v>4.5</v>
       </c>
       <c r="BZ2">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="CA2">
         <v>4.5</v>
@@ -1212,55 +1212,55 @@
         <v>3.35</v>
       </c>
       <c r="H3">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="I3">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="J3">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="K3">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="L3">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="M3">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="N3">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="O3">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="P3">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="Q3">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="R3">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="S3">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="T3">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="U3">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="V3">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W3">
         <v>1.42</v>
       </c>
       <c r="X3">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="Y3">
         <v>7.8</v>
@@ -1269,22 +1269,22 @@
         <v>15.5</v>
       </c>
       <c r="AA3">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AB3">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC3">
         <v>6.6</v>
       </c>
       <c r="AD3">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE3">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF3">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AG3">
         <v>15.5</v>
@@ -1293,7 +1293,7 @@
         <v>26</v>
       </c>
       <c r="AI3">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AJ3">
         <v>65</v>
@@ -1302,10 +1302,10 @@
         <v>55</v>
       </c>
       <c r="AL3">
+        <v>90</v>
+      </c>
+      <c r="AM3">
         <v>1000</v>
-      </c>
-      <c r="AM3">
-        <v>250</v>
       </c>
       <c r="AN3">
         <v>1000</v>
@@ -1314,7 +1314,7 @@
         <v>55</v>
       </c>
       <c r="AP3">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AQ3">
         <v>7.2</v>
@@ -1326,7 +1326,7 @@
         <v>36</v>
       </c>
       <c r="AT3">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU3">
         <v>6.4</v>
@@ -1335,7 +1335,7 @@
         <v>12.5</v>
       </c>
       <c r="AW3">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AX3">
         <v>17.5</v>
@@ -1344,16 +1344,16 @@
         <v>14</v>
       </c>
       <c r="AZ3">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BA3">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="BB3">
         <v>55</v>
       </c>
       <c r="BC3">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BD3">
         <v>60</v>
@@ -1365,25 +1365,25 @@
         <v>48</v>
       </c>
       <c r="BG3">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="BH3">
         <v>2.6</v>
       </c>
       <c r="BI3">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="BJ3">
         <v>11.5</v>
       </c>
       <c r="BK3">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BN3">
         <v>6.2</v>
@@ -1395,13 +1395,13 @@
         <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BT3">
         <v>5.4</v>
@@ -1413,19 +1413,19 @@
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BZ3">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="CA3">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="CB3" t="s">
         <v>118</v>
@@ -1448,172 +1448,172 @@
         <v>110</v>
       </c>
       <c r="F4">
-        <v>2.18</v>
+        <v>1.96</v>
       </c>
       <c r="G4">
-        <v>2.28</v>
+        <v>2.06</v>
       </c>
       <c r="H4">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="I4">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="J4">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="K4">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="L4">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M4">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N4">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O4">
         <v>1.27</v>
       </c>
       <c r="P4">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q4">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="R4">
         <v>1.43</v>
       </c>
       <c r="S4">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="T4">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="U4">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V4">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="W4">
-        <v>1.79</v>
+        <v>1.94</v>
       </c>
       <c r="X4">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="Y4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Z4">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AA4">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AB4">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC4">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AE4">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="AF4">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AG4">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH4">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AI4">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AJ4">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AK4">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AL4">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM4">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AN4">
+        <v>13</v>
+      </c>
+      <c r="AO4">
+        <v>50</v>
+      </c>
+      <c r="AP4">
+        <v>14.5</v>
+      </c>
+      <c r="AQ4">
+        <v>13.5</v>
+      </c>
+      <c r="AR4">
+        <v>23</v>
+      </c>
+      <c r="AS4">
+        <v>50</v>
+      </c>
+      <c r="AT4">
+        <v>8.6</v>
+      </c>
+      <c r="AU4">
+        <v>7.6</v>
+      </c>
+      <c r="AV4">
+        <v>14</v>
+      </c>
+      <c r="AW4">
+        <v>34</v>
+      </c>
+      <c r="AX4">
+        <v>10</v>
+      </c>
+      <c r="AY4">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ4">
         <v>15</v>
-      </c>
-      <c r="AO4">
-        <v>40</v>
-      </c>
-      <c r="AP4">
-        <v>12.5</v>
-      </c>
-      <c r="AQ4">
-        <v>12.5</v>
-      </c>
-      <c r="AR4">
-        <v>21</v>
-      </c>
-      <c r="AS4">
-        <v>46</v>
-      </c>
-      <c r="AT4">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU4">
-        <v>7.2</v>
-      </c>
-      <c r="AV4">
-        <v>12.5</v>
-      </c>
-      <c r="AW4">
-        <v>32</v>
-      </c>
-      <c r="AX4">
-        <v>12.5</v>
-      </c>
-      <c r="AY4">
-        <v>9.4</v>
-      </c>
-      <c r="AZ4">
-        <v>14</v>
       </c>
       <c r="BA4">
         <v>32</v>
       </c>
       <c r="BB4">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BC4">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="BD4">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BE4">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BF4">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="BG4">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BH4">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BI4">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BJ4">
         <v>9.6</v>
@@ -1628,28 +1628,28 @@
         <v>9.6</v>
       </c>
       <c r="BN4">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BO4">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BP4">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="BQ4">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BR4">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BS4">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BT4">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BU4">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BV4">
         <v>1000</v>
@@ -1664,10 +1664,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BZ4">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="CA4">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="CB4" t="s">
         <v>118</v>
@@ -1699,7 +1699,7 @@
         <v>4.9</v>
       </c>
       <c r="I5">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="J5">
         <v>4.1</v>
@@ -1708,37 +1708,37 @@
         <v>4.3</v>
       </c>
       <c r="L5">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M5">
         <v>1.05</v>
       </c>
       <c r="N5">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O5">
         <v>1.24</v>
       </c>
       <c r="P5">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="Q5">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="R5">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S5">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="T5">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="U5">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="V5">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W5">
         <v>2.24</v>
@@ -1750,31 +1750,31 @@
         <v>22</v>
       </c>
       <c r="Z5">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AA5">
         <v>120</v>
       </c>
       <c r="AB5">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC5">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD5">
         <v>20</v>
       </c>
       <c r="AE5">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF5">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG5">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AH5">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AI5">
         <v>60</v>
@@ -1783,22 +1783,22 @@
         <v>19</v>
       </c>
       <c r="AK5">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL5">
         <v>32</v>
       </c>
       <c r="AM5">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AN5">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AO5">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AP5">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AQ5">
         <v>17.5</v>
@@ -1807,10 +1807,10 @@
         <v>32</v>
       </c>
       <c r="AS5">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AT5">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AU5">
         <v>8.800000000000001</v>
@@ -1825,10 +1825,10 @@
         <v>11</v>
       </c>
       <c r="AY5">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ5">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA5">
         <v>40</v>
@@ -1840,13 +1840,13 @@
         <v>15</v>
       </c>
       <c r="BD5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BE5">
         <v>55</v>
       </c>
       <c r="BF5">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BG5">
         <v>40</v>
@@ -1855,58 +1855,58 @@
         <v>4.4</v>
       </c>
       <c r="BI5">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BJ5">
         <v>11</v>
       </c>
       <c r="BK5">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BL5">
         <v>120</v>
       </c>
       <c r="BM5">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BN5">
         <v>5.2</v>
       </c>
       <c r="BO5">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BP5">
         <v>13.5</v>
       </c>
       <c r="BQ5">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BR5">
         <v>27</v>
       </c>
       <c r="BS5">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BT5">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BU5">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BV5">
         <v>44</v>
       </c>
       <c r="BW5">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BX5">
         <v>50</v>
       </c>
       <c r="BY5">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BZ5">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="CA5">
         <v>4.4</v>
@@ -1932,25 +1932,25 @@
         <v>112</v>
       </c>
       <c r="F6">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="G6">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="H6">
         <v>2.74</v>
       </c>
       <c r="I6">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="J6">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K6">
         <v>3.8</v>
       </c>
       <c r="L6">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="M6">
         <v>1.06</v>
@@ -1962,10 +1962,10 @@
         <v>1.29</v>
       </c>
       <c r="P6">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="Q6">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R6">
         <v>1.43</v>
@@ -1980,16 +1980,16 @@
         <v>2.36</v>
       </c>
       <c r="V6">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W6">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="X6">
         <v>16.5</v>
       </c>
       <c r="Y6">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z6">
         <v>19</v>
@@ -2010,7 +2010,7 @@
         <v>29</v>
       </c>
       <c r="AF6">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AG6">
         <v>12</v>
@@ -2043,10 +2043,10 @@
         <v>15</v>
       </c>
       <c r="AQ6">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AR6">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AS6">
         <v>38</v>
@@ -2097,40 +2097,40 @@
         <v>3.65</v>
       </c>
       <c r="BI6">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="BJ6">
         <v>9</v>
       </c>
       <c r="BK6">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BL6">
         <v>100</v>
       </c>
       <c r="BM6">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BN6">
         <v>5.8</v>
       </c>
       <c r="BO6">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BP6">
         <v>19.5</v>
       </c>
       <c r="BQ6">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR6">
         <v>30</v>
       </c>
       <c r="BS6">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BT6">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BU6">
         <v>4.5</v>
@@ -2139,19 +2139,19 @@
         <v>21</v>
       </c>
       <c r="BW6">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX6">
         <v>32</v>
       </c>
       <c r="BY6">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BZ6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="CA6">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="CB6" t="s">
         <v>118</v>
@@ -2177,16 +2177,16 @@
         <v>1.64</v>
       </c>
       <c r="G7">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="H7">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="I7">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="J7">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K7">
         <v>4.4</v>
@@ -2201,31 +2201,31 @@
         <v>3.6</v>
       </c>
       <c r="O7">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P7">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="Q7">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="R7">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S7">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="T7">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="U7">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="V7">
         <v>1.17</v>
       </c>
       <c r="W7">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="X7">
         <v>17</v>
@@ -2237,16 +2237,16 @@
         <v>60</v>
       </c>
       <c r="AA7">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="AB7">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AC7">
         <v>9.800000000000001</v>
       </c>
       <c r="AD7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AE7">
         <v>120</v>
@@ -2270,40 +2270,40 @@
         <v>23</v>
       </c>
       <c r="AL7">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM7">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AN7">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="AO7">
         <v>160</v>
       </c>
       <c r="AP7">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AQ7">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AR7">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AS7">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AT7">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU7">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV7">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AW7">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AX7">
         <v>8.6</v>
@@ -2312,37 +2312,37 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA7">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BB7">
         <v>14</v>
       </c>
       <c r="BC7">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BD7">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="BE7">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BF7">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BG7">
-        <v>60</v>
+        <v>6.6</v>
       </c>
       <c r="BH7">
         <v>3.45</v>
       </c>
       <c r="BI7">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="BJ7">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BK7">
         <v>6</v>
@@ -2351,7 +2351,7 @@
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BN7">
         <v>4.2</v>
@@ -2360,28 +2360,28 @@
         <v>3.2</v>
       </c>
       <c r="BP7">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BQ7">
-        <v>8.4</v>
+        <v>5.9</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT7">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BU7">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BV7">
         <v>1000</v>
       </c>
       <c r="BW7">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BX7">
         <v>1000</v>
@@ -2416,7 +2416,7 @@
         <v>114</v>
       </c>
       <c r="F8">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="G8">
         <v>1.61</v>
@@ -2443,7 +2443,7 @@
         <v>4.7</v>
       </c>
       <c r="O8">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P8">
         <v>2.26</v>
@@ -2530,13 +2530,13 @@
         <v>20</v>
       </c>
       <c r="AR8">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS8">
         <v>8.6</v>
       </c>
       <c r="AT8">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU8">
         <v>9.199999999999999</v>
@@ -2548,7 +2548,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AX8">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY8">
         <v>9</v>
@@ -2557,7 +2557,7 @@
         <v>18</v>
       </c>
       <c r="BA8">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BB8">
         <v>13</v>
@@ -2566,7 +2566,7 @@
         <v>14</v>
       </c>
       <c r="BD8">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="BE8">
         <v>8.4</v>
@@ -2575,7 +2575,7 @@
         <v>6.8</v>
       </c>
       <c r="BG8">
-        <v>8.199999999999999</v>
+        <v>27</v>
       </c>
       <c r="BH8">
         <v>4.7</v>
@@ -2658,10 +2658,10 @@
         <v>115</v>
       </c>
       <c r="F9">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="G9">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="H9">
         <v>3.2</v>
@@ -2673,7 +2673,7 @@
         <v>4.3</v>
       </c>
       <c r="K9">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L9">
         <v>1.25</v>
@@ -2688,13 +2688,13 @@
         <v>1.14</v>
       </c>
       <c r="P9">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="Q9">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="R9">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="S9">
         <v>2.1</v>
@@ -2709,7 +2709,7 @@
         <v>1.42</v>
       </c>
       <c r="W9">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="X9">
         <v>75</v>
@@ -2721,13 +2721,13 @@
         <v>50</v>
       </c>
       <c r="AA9">
-        <v>440</v>
+        <v>420</v>
       </c>
       <c r="AB9">
         <v>21</v>
       </c>
       <c r="AC9">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD9">
         <v>17.5</v>
@@ -2760,7 +2760,7 @@
         <v>50</v>
       </c>
       <c r="AN9">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO9">
         <v>17</v>
@@ -2772,7 +2772,7 @@
         <v>17</v>
       </c>
       <c r="AR9">
-        <v>19.5</v>
+        <v>26</v>
       </c>
       <c r="AS9">
         <v>29</v>
@@ -2817,7 +2817,7 @@
         <v>7.4</v>
       </c>
       <c r="BG9">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="BH9">
         <v>5.3</v>
@@ -2930,7 +2930,7 @@
         <v>1.6</v>
       </c>
       <c r="P10">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="Q10">
         <v>2.78</v>
@@ -2945,7 +2945,7 @@
         <v>2.2</v>
       </c>
       <c r="U10">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="V10">
         <v>1.37</v>
@@ -2954,13 +2954,13 @@
         <v>1.6</v>
       </c>
       <c r="X10">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="Y10">
         <v>10</v>
       </c>
       <c r="Z10">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AA10">
         <v>90</v>
@@ -2969,7 +2969,7 @@
         <v>7.8</v>
       </c>
       <c r="AC10">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AD10">
         <v>17</v>
@@ -2978,13 +2978,13 @@
         <v>70</v>
       </c>
       <c r="AF10">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AG10">
         <v>15</v>
       </c>
       <c r="AH10">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AI10">
         <v>100</v>
@@ -3017,7 +3017,7 @@
         <v>19</v>
       </c>
       <c r="AS10">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="AT10">
         <v>6.4</v>
@@ -3026,10 +3026,10 @@
         <v>6.2</v>
       </c>
       <c r="AV10">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AW10">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AX10">
         <v>12.5</v>
@@ -3041,7 +3041,7 @@
         <v>21</v>
       </c>
       <c r="BA10">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BB10">
         <v>34</v>
@@ -3050,16 +3050,16 @@
         <v>32</v>
       </c>
       <c r="BD10">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BE10">
+        <v>7</v>
+      </c>
+      <c r="BF10">
         <v>6.2</v>
       </c>
-      <c r="BF10">
-        <v>5.6</v>
-      </c>
       <c r="BG10">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BH10">
         <v>2.68</v>
@@ -3142,13 +3142,13 @@
         <v>117</v>
       </c>
       <c r="F11">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="G11">
         <v>3.15</v>
       </c>
       <c r="H11">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="I11">
         <v>2.86</v>
@@ -3169,19 +3169,19 @@
         <v>3.3</v>
       </c>
       <c r="O11">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P11">
         <v>1.76</v>
       </c>
       <c r="Q11">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="R11">
         <v>1.28</v>
       </c>
       <c r="S11">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="T11">
         <v>1.84</v>
@@ -3190,7 +3190,7 @@
         <v>2.08</v>
       </c>
       <c r="V11">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W11">
         <v>1.46</v>
@@ -3199,7 +3199,7 @@
         <v>13.5</v>
       </c>
       <c r="Y11">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Z11">
         <v>19</v>
@@ -3259,7 +3259,7 @@
         <v>15</v>
       </c>
       <c r="AS11">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AT11">
         <v>9.4</v>
@@ -3271,7 +3271,7 @@
         <v>10.5</v>
       </c>
       <c r="AW11">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX11">
         <v>17</v>
@@ -3283,22 +3283,22 @@
         <v>16</v>
       </c>
       <c r="BA11">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BB11">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BC11">
         <v>29</v>
       </c>
       <c r="BD11">
+        <v>7.4</v>
+      </c>
+      <c r="BE11">
+        <v>7.8</v>
+      </c>
+      <c r="BF11">
         <v>7</v>
-      </c>
-      <c r="BE11">
-        <v>7.6</v>
-      </c>
-      <c r="BF11">
-        <v>6.8</v>
       </c>
       <c r="BG11">
         <v>26</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-18.xlsx
@@ -370,7 +370,7 @@
     <t>Atletico GO</t>
   </si>
   <si>
-    <t>2026-08-17 13:52:13</t>
+    <t>2026-08-17 16:01:02</t>
   </si>
 </sst>
 </file>
@@ -964,37 +964,37 @@
         <v>108</v>
       </c>
       <c r="F2">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="G2">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="H2">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="I2">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="J2">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="K2">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L2">
         <v>1.48</v>
       </c>
       <c r="M2">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N2">
         <v>3</v>
       </c>
       <c r="O2">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="P2">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="Q2">
         <v>2.28</v>
@@ -1006,46 +1006,46 @@
         <v>4.4</v>
       </c>
       <c r="T2">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="U2">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="V2">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="W2">
         <v>1.25</v>
       </c>
       <c r="X2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Y2">
         <v>8</v>
       </c>
       <c r="Z2">
+        <v>12</v>
+      </c>
+      <c r="AA2">
+        <v>32</v>
+      </c>
+      <c r="AB2">
         <v>13</v>
       </c>
-      <c r="AA2">
+      <c r="AC2">
+        <v>7.8</v>
+      </c>
+      <c r="AD2">
+        <v>11</v>
+      </c>
+      <c r="AE2">
         <v>34</v>
-      </c>
-      <c r="AB2">
-        <v>12.5</v>
-      </c>
-      <c r="AC2">
-        <v>7.6</v>
-      </c>
-      <c r="AD2">
-        <v>11.5</v>
-      </c>
-      <c r="AE2">
-        <v>36</v>
       </c>
       <c r="AF2">
         <v>28</v>
       </c>
       <c r="AG2">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AH2">
         <v>24</v>
@@ -1054,40 +1054,40 @@
         <v>60</v>
       </c>
       <c r="AJ2">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AK2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AL2">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AM2">
         <v>170</v>
       </c>
       <c r="AN2">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AO2">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AP2">
         <v>9.800000000000001</v>
       </c>
       <c r="AQ2">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AR2">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AS2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AT2">
         <v>10.5</v>
       </c>
       <c r="AU2">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV2">
         <v>9.800000000000001</v>
@@ -1096,13 +1096,13 @@
         <v>18.5</v>
       </c>
       <c r="AX2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY2">
         <v>14.5</v>
       </c>
       <c r="AZ2">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="BA2">
         <v>32</v>
@@ -1117,13 +1117,13 @@
         <v>46</v>
       </c>
       <c r="BE2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BF2">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BG2">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="BH2">
         <v>3.5</v>
@@ -1135,55 +1135,55 @@
         <v>12.5</v>
       </c>
       <c r="BK2">
-        <v>3.65</v>
+        <v>7.8</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BN2">
         <v>8.6</v>
       </c>
       <c r="BO2">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BP2">
         <v>46</v>
       </c>
       <c r="BQ2">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BR2">
         <v>65</v>
       </c>
       <c r="BS2">
+        <v>4.9</v>
+      </c>
+      <c r="BT2">
+        <v>5.4</v>
+      </c>
+      <c r="BU2">
+        <v>4.2</v>
+      </c>
+      <c r="BV2">
+        <v>18.5</v>
+      </c>
+      <c r="BW2">
+        <v>4.1</v>
+      </c>
+      <c r="BX2">
+        <v>40</v>
+      </c>
+      <c r="BY2">
         <v>4.7</v>
-      </c>
-      <c r="BT2">
-        <v>5.5</v>
-      </c>
-      <c r="BU2">
-        <v>3.65</v>
-      </c>
-      <c r="BV2">
-        <v>19.5</v>
-      </c>
-      <c r="BW2">
-        <v>4</v>
-      </c>
-      <c r="BX2">
-        <v>42</v>
-      </c>
-      <c r="BY2">
-        <v>4.5</v>
       </c>
       <c r="BZ2">
         <v>40</v>
       </c>
       <c r="CA2">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="CB2" t="s">
         <v>118</v>
@@ -1206,16 +1206,16 @@
         <v>109</v>
       </c>
       <c r="F3">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="G3">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="H3">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="I3">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="J3">
         <v>2.98</v>
@@ -1230,7 +1230,7 @@
         <v>1.14</v>
       </c>
       <c r="N3">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="O3">
         <v>1.61</v>
@@ -1239,19 +1239,19 @@
         <v>1.51</v>
       </c>
       <c r="Q3">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="R3">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S3">
         <v>6.2</v>
       </c>
       <c r="T3">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="U3">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="V3">
         <v>1.56</v>
@@ -1269,19 +1269,19 @@
         <v>15.5</v>
       </c>
       <c r="AA3">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AB3">
         <v>8.800000000000001</v>
       </c>
       <c r="AC3">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AD3">
         <v>13.5</v>
       </c>
       <c r="AE3">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AF3">
         <v>20</v>
@@ -1290,10 +1290,10 @@
         <v>15.5</v>
       </c>
       <c r="AH3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI3">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AJ3">
         <v>65</v>
@@ -1302,16 +1302,16 @@
         <v>55</v>
       </c>
       <c r="AL3">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AM3">
         <v>1000</v>
       </c>
       <c r="AN3">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AO3">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AP3">
         <v>7.4</v>
@@ -1323,7 +1323,7 @@
         <v>14</v>
       </c>
       <c r="AS3">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AT3">
         <v>8.199999999999999</v>
@@ -1335,7 +1335,7 @@
         <v>12.5</v>
       </c>
       <c r="AW3">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AX3">
         <v>17.5</v>
@@ -1362,49 +1362,49 @@
         <v>95</v>
       </c>
       <c r="BF3">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BG3">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="BH3">
         <v>2.6</v>
       </c>
       <c r="BI3">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="BJ3">
         <v>11.5</v>
       </c>
       <c r="BK3">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>16.5</v>
+        <v>2.3</v>
       </c>
       <c r="BN3">
         <v>6.2</v>
       </c>
       <c r="BO3">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BP3">
         <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>14.5</v>
+        <v>2.22</v>
       </c>
       <c r="BT3">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BU3">
         <v>4.8</v>
@@ -1413,19 +1413,19 @@
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>14.5</v>
+        <v>2.22</v>
       </c>
       <c r="CB3" t="s">
         <v>118</v>
@@ -1478,10 +1478,10 @@
         <v>1.27</v>
       </c>
       <c r="P4">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="Q4">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="R4">
         <v>1.43</v>
@@ -1490,7 +1490,7 @@
         <v>3.05</v>
       </c>
       <c r="T4">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="U4">
         <v>2.18</v>
@@ -1568,7 +1568,7 @@
         <v>50</v>
       </c>
       <c r="AT4">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU4">
         <v>7.6</v>
@@ -1589,7 +1589,7 @@
         <v>15</v>
       </c>
       <c r="BA4">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BB4">
         <v>18</v>
@@ -1598,7 +1598,7 @@
         <v>16.5</v>
       </c>
       <c r="BD4">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="BE4">
         <v>60</v>
@@ -1619,7 +1619,7 @@
         <v>9.6</v>
       </c>
       <c r="BK4">
-        <v>5</v>
+        <v>7.4</v>
       </c>
       <c r="BL4">
         <v>1000</v>
@@ -1649,7 +1649,7 @@
         <v>7.8</v>
       </c>
       <c r="BU4">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BV4">
         <v>1000</v>
@@ -1690,10 +1690,10 @@
         <v>111</v>
       </c>
       <c r="F5">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="G5">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="H5">
         <v>4.9</v>
@@ -1714,7 +1714,7 @@
         <v>1.05</v>
       </c>
       <c r="N5">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O5">
         <v>1.24</v>
@@ -1723,16 +1723,16 @@
         <v>2.32</v>
       </c>
       <c r="Q5">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="R5">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S5">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="T5">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="U5">
         <v>2.28</v>
@@ -1828,7 +1828,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ5">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BA5">
         <v>40</v>
@@ -1849,67 +1849,67 @@
         <v>8</v>
       </c>
       <c r="BG5">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="BH5">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="BI5">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="BJ5">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK5">
-        <v>3.75</v>
+        <v>5.4</v>
       </c>
       <c r="BL5">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="BM5">
-        <v>5.5</v>
+        <v>10.5</v>
       </c>
       <c r="BN5">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="BO5">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="BP5">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BQ5">
-        <v>4</v>
+        <v>5.9</v>
       </c>
       <c r="BR5">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="BS5">
-        <v>4.7</v>
+        <v>7.8</v>
       </c>
       <c r="BT5">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU5">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="BV5">
+        <v>38</v>
+      </c>
+      <c r="BW5">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BX5">
         <v>44</v>
       </c>
-      <c r="BW5">
-        <v>5.1</v>
-      </c>
-      <c r="BX5">
-        <v>50</v>
-      </c>
       <c r="BY5">
-        <v>5.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ5">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="CA5">
-        <v>4.4</v>
+        <v>7</v>
       </c>
       <c r="CB5" t="s">
         <v>118</v>
@@ -1935,16 +1935,16 @@
         <v>2.64</v>
       </c>
       <c r="G6">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="H6">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="I6">
         <v>2.78</v>
       </c>
       <c r="J6">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K6">
         <v>3.8</v>
@@ -1974,10 +1974,10 @@
         <v>3.2</v>
       </c>
       <c r="T6">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="U6">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="V6">
         <v>1.56</v>
@@ -2058,13 +2058,13 @@
         <v>7.6</v>
       </c>
       <c r="AV6">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW6">
         <v>26</v>
       </c>
       <c r="AX6">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AY6">
         <v>10.5</v>
@@ -2085,13 +2085,13 @@
         <v>32</v>
       </c>
       <c r="BE6">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BF6">
         <v>19.5</v>
       </c>
       <c r="BG6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BH6">
         <v>3.65</v>
@@ -2115,7 +2115,7 @@
         <v>5.8</v>
       </c>
       <c r="BO6">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="BP6">
         <v>19.5</v>
@@ -2133,7 +2133,7 @@
         <v>6</v>
       </c>
       <c r="BU6">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="BV6">
         <v>21</v>
@@ -2174,7 +2174,7 @@
         <v>113</v>
       </c>
       <c r="F7">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="G7">
         <v>1.7</v>
@@ -2189,7 +2189,7 @@
         <v>4</v>
       </c>
       <c r="K7">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L7">
         <v>1.4</v>
@@ -2216,7 +2216,7 @@
         <v>3.4</v>
       </c>
       <c r="T7">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="U7">
         <v>1.9</v>
@@ -2234,7 +2234,7 @@
         <v>22</v>
       </c>
       <c r="Z7">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA7">
         <v>240</v>
@@ -2252,7 +2252,7 @@
         <v>120</v>
       </c>
       <c r="AF7">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG7">
         <v>12</v>
@@ -2270,7 +2270,7 @@
         <v>23</v>
       </c>
       <c r="AL7">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AM7">
         <v>160</v>
@@ -2291,7 +2291,7 @@
         <v>38</v>
       </c>
       <c r="AS7">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AT7">
         <v>7</v>
@@ -2324,22 +2324,22 @@
         <v>15.5</v>
       </c>
       <c r="BD7">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="BE7">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BF7">
         <v>8.6</v>
       </c>
       <c r="BG7">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BH7">
         <v>3.45</v>
       </c>
       <c r="BI7">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="BJ7">
         <v>11.5</v>
@@ -2357,13 +2357,13 @@
         <v>4.2</v>
       </c>
       <c r="BO7">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="BP7">
         <v>11</v>
       </c>
       <c r="BQ7">
-        <v>5.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR7">
         <v>1000</v>
@@ -2416,10 +2416,10 @@
         <v>114</v>
       </c>
       <c r="F8">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="G8">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="H8">
         <v>6.4</v>
@@ -2431,7 +2431,7 @@
         <v>4.4</v>
       </c>
       <c r="K8">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L8">
         <v>1.33</v>
@@ -2455,7 +2455,7 @@
         <v>1.49</v>
       </c>
       <c r="S8">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="T8">
         <v>1.85</v>
@@ -2467,13 +2467,13 @@
         <v>1.17</v>
       </c>
       <c r="W8">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="X8">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="Y8">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="Z8">
         <v>65</v>
@@ -2482,7 +2482,7 @@
         <v>210</v>
       </c>
       <c r="AB8">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC8">
         <v>10.5</v>
@@ -2491,10 +2491,10 @@
         <v>25</v>
       </c>
       <c r="AE8">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AF8">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AG8">
         <v>10.5</v>
@@ -2509,13 +2509,13 @@
         <v>15.5</v>
       </c>
       <c r="AK8">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AL8">
         <v>32</v>
       </c>
       <c r="AM8">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AN8">
         <v>7.8</v>
@@ -2527,16 +2527,16 @@
         <v>17</v>
       </c>
       <c r="AQ8">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AR8">
-        <v>8.199999999999999</v>
+        <v>46</v>
       </c>
       <c r="AS8">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="AT8">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU8">
         <v>9.199999999999999</v>
@@ -2545,7 +2545,7 @@
         <v>21</v>
       </c>
       <c r="AW8">
-        <v>8.199999999999999</v>
+        <v>70</v>
       </c>
       <c r="AX8">
         <v>9.199999999999999</v>
@@ -2554,28 +2554,28 @@
         <v>9</v>
       </c>
       <c r="AZ8">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BA8">
-        <v>8.4</v>
+        <v>13</v>
       </c>
       <c r="BB8">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BC8">
+        <v>14.5</v>
+      </c>
+      <c r="BD8">
+        <v>28</v>
+      </c>
+      <c r="BE8">
         <v>14</v>
       </c>
-      <c r="BD8">
-        <v>23</v>
-      </c>
-      <c r="BE8">
-        <v>8.4</v>
-      </c>
       <c r="BF8">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BG8">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="BH8">
         <v>4.7</v>
@@ -2584,58 +2584,58 @@
         <v>3.15</v>
       </c>
       <c r="BJ8">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BK8">
-        <v>3.35</v>
+        <v>4.9</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>4.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN8">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="BO8">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="BP8">
-        <v>12</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BQ8">
-        <v>3.35</v>
+        <v>4.9</v>
       </c>
       <c r="BR8">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="BS8">
-        <v>4</v>
+        <v>6.8</v>
       </c>
       <c r="BT8">
-        <v>12</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU8">
-        <v>3.35</v>
+        <v>4.9</v>
       </c>
       <c r="BV8">
         <v>60</v>
       </c>
       <c r="BW8">
-        <v>4.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX8">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="BY8">
-        <v>4.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ8">
-        <v>19.5</v>
+        <v>16</v>
       </c>
       <c r="CA8">
-        <v>3.8</v>
+        <v>6</v>
       </c>
       <c r="CB8" t="s">
         <v>118</v>
@@ -2658,16 +2658,16 @@
         <v>115</v>
       </c>
       <c r="F9">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="G9">
         <v>2.18</v>
       </c>
       <c r="H9">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I9">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J9">
         <v>4.3</v>
@@ -2691,13 +2691,13 @@
         <v>3.1</v>
       </c>
       <c r="Q9">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="R9">
         <v>1.86</v>
       </c>
       <c r="S9">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="T9">
         <v>1.45</v>
@@ -2706,13 +2706,13 @@
         <v>3.05</v>
       </c>
       <c r="V9">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W9">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="X9">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="Y9">
         <v>27</v>
@@ -2727,7 +2727,7 @@
         <v>21</v>
       </c>
       <c r="AC9">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD9">
         <v>17.5</v>
@@ -2745,13 +2745,13 @@
         <v>16.5</v>
       </c>
       <c r="AI9">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="AJ9">
         <v>32</v>
       </c>
       <c r="AK9">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AL9">
         <v>26</v>
@@ -2760,7 +2760,7 @@
         <v>50</v>
       </c>
       <c r="AN9">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AO9">
         <v>17</v>
@@ -2772,13 +2772,13 @@
         <v>17</v>
       </c>
       <c r="AR9">
-        <v>26</v>
+        <v>19.5</v>
       </c>
       <c r="AS9">
         <v>29</v>
       </c>
       <c r="AT9">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AU9">
         <v>10</v>
@@ -2787,10 +2787,10 @@
         <v>13</v>
       </c>
       <c r="AW9">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AX9">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AY9">
         <v>10.5</v>
@@ -2805,7 +2805,7 @@
         <v>19</v>
       </c>
       <c r="BC9">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BD9">
         <v>20</v>
@@ -2814,7 +2814,7 @@
         <v>25</v>
       </c>
       <c r="BF9">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BG9">
         <v>12.5</v>
@@ -2912,7 +2912,7 @@
         <v>3.7</v>
       </c>
       <c r="J10">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="K10">
         <v>3.1</v>
@@ -2930,7 +2930,7 @@
         <v>1.6</v>
       </c>
       <c r="P10">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="Q10">
         <v>2.78</v>
@@ -2954,10 +2954,10 @@
         <v>1.6</v>
       </c>
       <c r="X10">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="Y10">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Z10">
         <v>24</v>
@@ -2978,7 +2978,7 @@
         <v>70</v>
       </c>
       <c r="AF10">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG10">
         <v>15</v>
@@ -3029,7 +3029,7 @@
         <v>12</v>
       </c>
       <c r="AW10">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX10">
         <v>12.5</v>
@@ -3041,10 +3041,10 @@
         <v>21</v>
       </c>
       <c r="BA10">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BB10">
-        <v>34</v>
+        <v>6.2</v>
       </c>
       <c r="BC10">
         <v>32</v>
@@ -3059,7 +3059,7 @@
         <v>6.2</v>
       </c>
       <c r="BG10">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH10">
         <v>2.68</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-18.xlsx
@@ -370,7 +370,7 @@
     <t>Atletico GO</t>
   </si>
   <si>
-    <t>2026-08-17 16:01:02</t>
+    <t>2026-08-17 18:08:56</t>
   </si>
 </sst>
 </file>
@@ -964,22 +964,22 @@
         <v>108</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="G2">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="H2">
+        <v>1.97</v>
+      </c>
+      <c r="I2">
         <v>2.04</v>
       </c>
-      <c r="I2">
-        <v>2.12</v>
-      </c>
       <c r="J2">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K2">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="L2">
         <v>1.48</v>
@@ -988,64 +988,64 @@
         <v>1.09</v>
       </c>
       <c r="N2">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="O2">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P2">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="Q2">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="R2">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="S2">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="T2">
         <v>1.98</v>
       </c>
       <c r="U2">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="V2">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="W2">
         <v>1.25</v>
       </c>
       <c r="X2">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Y2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z2">
         <v>12</v>
       </c>
       <c r="AA2">
+        <v>29</v>
+      </c>
+      <c r="AB2">
+        <v>14</v>
+      </c>
+      <c r="AC2">
+        <v>8</v>
+      </c>
+      <c r="AD2">
+        <v>10.5</v>
+      </c>
+      <c r="AE2">
+        <v>30</v>
+      </c>
+      <c r="AF2">
         <v>32</v>
       </c>
-      <c r="AB2">
-        <v>13</v>
-      </c>
-      <c r="AC2">
-        <v>7.8</v>
-      </c>
-      <c r="AD2">
-        <v>11</v>
-      </c>
-      <c r="AE2">
-        <v>34</v>
-      </c>
-      <c r="AF2">
-        <v>28</v>
-      </c>
       <c r="AG2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AH2">
         <v>24</v>
@@ -1054,22 +1054,22 @@
         <v>60</v>
       </c>
       <c r="AJ2">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="AK2">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AL2">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AM2">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AN2">
         <v>110</v>
       </c>
       <c r="AO2">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AP2">
         <v>9.800000000000001</v>
@@ -1078,22 +1078,22 @@
         <v>7</v>
       </c>
       <c r="AR2">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AS2">
         <v>19</v>
       </c>
       <c r="AT2">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU2">
         <v>6.8</v>
       </c>
       <c r="AV2">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW2">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AX2">
         <v>23</v>
@@ -1102,37 +1102,37 @@
         <v>14.5</v>
       </c>
       <c r="AZ2">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA2">
         <v>32</v>
       </c>
       <c r="BB2">
+        <v>60</v>
+      </c>
+      <c r="BC2">
+        <v>44</v>
+      </c>
+      <c r="BD2">
+        <v>50</v>
+      </c>
+      <c r="BE2">
+        <v>90</v>
+      </c>
+      <c r="BF2">
         <v>55</v>
-      </c>
-      <c r="BC2">
-        <v>42</v>
-      </c>
-      <c r="BD2">
-        <v>46</v>
-      </c>
-      <c r="BE2">
-        <v>12</v>
-      </c>
-      <c r="BF2">
-        <v>50</v>
       </c>
       <c r="BG2">
         <v>14</v>
       </c>
       <c r="BH2">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="BI2">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="BJ2">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BK2">
         <v>7.8</v>
@@ -1141,49 +1141,49 @@
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>5.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN2">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BO2">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BP2">
         <v>46</v>
       </c>
       <c r="BQ2">
-        <v>4.8</v>
+        <v>7.2</v>
       </c>
       <c r="BR2">
         <v>65</v>
       </c>
       <c r="BS2">
-        <v>4.9</v>
+        <v>7.6</v>
       </c>
       <c r="BT2">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="BU2">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="BV2">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BW2">
-        <v>4.1</v>
+        <v>5.8</v>
       </c>
       <c r="BX2">
         <v>40</v>
       </c>
       <c r="BY2">
-        <v>4.7</v>
+        <v>7.2</v>
       </c>
       <c r="BZ2">
         <v>40</v>
       </c>
       <c r="CA2">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="CB2" t="s">
         <v>118</v>
@@ -1206,37 +1206,37 @@
         <v>109</v>
       </c>
       <c r="F3">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="G3">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="H3">
         <v>2.72</v>
       </c>
       <c r="I3">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="J3">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="K3">
         <v>3</v>
       </c>
       <c r="L3">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="M3">
         <v>1.14</v>
       </c>
       <c r="N3">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="O3">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="P3">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="Q3">
         <v>2.88</v>
@@ -1245,16 +1245,16 @@
         <v>1.18</v>
       </c>
       <c r="S3">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="T3">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="U3">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="V3">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="W3">
         <v>1.42</v>
@@ -1263,16 +1263,16 @@
         <v>8</v>
       </c>
       <c r="Y3">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="Z3">
         <v>15.5</v>
       </c>
       <c r="AA3">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AB3">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC3">
         <v>6.8</v>
@@ -1281,10 +1281,10 @@
         <v>13.5</v>
       </c>
       <c r="AE3">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AF3">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AG3">
         <v>15.5</v>
@@ -1302,22 +1302,22 @@
         <v>55</v>
       </c>
       <c r="AL3">
-        <v>85</v>
+        <v>970</v>
       </c>
       <c r="AM3">
         <v>1000</v>
       </c>
       <c r="AN3">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AO3">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AP3">
         <v>7.4</v>
       </c>
       <c r="AQ3">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AR3">
         <v>14</v>
@@ -1344,7 +1344,7 @@
         <v>14</v>
       </c>
       <c r="AZ3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA3">
         <v>55</v>
@@ -1356,52 +1356,52 @@
         <v>46</v>
       </c>
       <c r="BD3">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BE3">
         <v>95</v>
       </c>
       <c r="BF3">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="BG3">
         <v>42</v>
       </c>
       <c r="BH3">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="BI3">
-        <v>2.32</v>
+        <v>2.48</v>
       </c>
       <c r="BJ3">
         <v>11.5</v>
       </c>
       <c r="BK3">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>2.3</v>
+        <v>17.5</v>
       </c>
       <c r="BN3">
         <v>6.2</v>
       </c>
       <c r="BO3">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BP3">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BQ3">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>2.22</v>
+        <v>14</v>
       </c>
       <c r="BT3">
         <v>5.3</v>
@@ -1410,10 +1410,10 @@
         <v>4.8</v>
       </c>
       <c r="BV3">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BW3">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BX3">
         <v>1000</v>
@@ -1425,7 +1425,7 @@
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>2.22</v>
+        <v>14</v>
       </c>
       <c r="CB3" t="s">
         <v>118</v>
@@ -1448,226 +1448,226 @@
         <v>110</v>
       </c>
       <c r="F4">
-        <v>1.96</v>
+        <v>2.42</v>
       </c>
       <c r="G4">
+        <v>2.56</v>
+      </c>
+      <c r="H4">
+        <v>2.98</v>
+      </c>
+      <c r="I4">
+        <v>3.2</v>
+      </c>
+      <c r="J4">
+        <v>3.6</v>
+      </c>
+      <c r="K4">
+        <v>3.75</v>
+      </c>
+      <c r="L4">
+        <v>1.38</v>
+      </c>
+      <c r="M4">
+        <v>1.06</v>
+      </c>
+      <c r="N4">
+        <v>4.2</v>
+      </c>
+      <c r="O4">
+        <v>1.29</v>
+      </c>
+      <c r="P4">
         <v>2.06</v>
       </c>
-      <c r="H4">
-        <v>3.8</v>
-      </c>
-      <c r="I4">
-        <v>4.2</v>
-      </c>
-      <c r="J4">
-        <v>3.7</v>
-      </c>
-      <c r="K4">
-        <v>4</v>
-      </c>
-      <c r="L4">
-        <v>1.37</v>
-      </c>
-      <c r="M4">
-        <v>1.05</v>
-      </c>
-      <c r="N4">
-        <v>4.3</v>
-      </c>
-      <c r="O4">
-        <v>1.27</v>
-      </c>
-      <c r="P4">
-        <v>2.1</v>
-      </c>
       <c r="Q4">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="R4">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="S4">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="T4">
         <v>1.68</v>
       </c>
       <c r="U4">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="V4">
-        <v>1.31</v>
+        <v>1.45</v>
       </c>
       <c r="W4">
-        <v>1.94</v>
+        <v>1.64</v>
       </c>
       <c r="X4">
+        <v>17.5</v>
+      </c>
+      <c r="Y4">
+        <v>14.5</v>
+      </c>
+      <c r="Z4">
+        <v>23</v>
+      </c>
+      <c r="AA4">
+        <v>60</v>
+      </c>
+      <c r="AB4">
+        <v>11.5</v>
+      </c>
+      <c r="AC4">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD4">
+        <v>14.5</v>
+      </c>
+      <c r="AE4">
+        <v>40</v>
+      </c>
+      <c r="AF4">
+        <v>17</v>
+      </c>
+      <c r="AG4">
+        <v>12</v>
+      </c>
+      <c r="AH4">
+        <v>17.5</v>
+      </c>
+      <c r="AI4">
+        <v>46</v>
+      </c>
+      <c r="AJ4">
+        <v>38</v>
+      </c>
+      <c r="AK4">
+        <v>29</v>
+      </c>
+      <c r="AL4">
+        <v>50</v>
+      </c>
+      <c r="AM4">
+        <v>100</v>
+      </c>
+      <c r="AN4">
+        <v>19.5</v>
+      </c>
+      <c r="AO4">
+        <v>32</v>
+      </c>
+      <c r="AP4">
+        <v>14</v>
+      </c>
+      <c r="AQ4">
+        <v>11.5</v>
+      </c>
+      <c r="AR4">
         <v>18</v>
       </c>
-      <c r="Y4">
-        <v>17</v>
-      </c>
-      <c r="Z4">
+      <c r="AS4">
         <v>40</v>
-      </c>
-      <c r="AA4">
-        <v>95</v>
-      </c>
-      <c r="AB4">
-        <v>11</v>
-      </c>
-      <c r="AC4">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD4">
-        <v>17</v>
-      </c>
-      <c r="AE4">
-        <v>65</v>
-      </c>
-      <c r="AF4">
-        <v>14</v>
-      </c>
-      <c r="AG4">
-        <v>11</v>
-      </c>
-      <c r="AH4">
-        <v>18</v>
-      </c>
-      <c r="AI4">
-        <v>75</v>
-      </c>
-      <c r="AJ4">
-        <v>26</v>
-      </c>
-      <c r="AK4">
-        <v>21</v>
-      </c>
-      <c r="AL4">
-        <v>40</v>
-      </c>
-      <c r="AM4">
-        <v>110</v>
-      </c>
-      <c r="AN4">
-        <v>13</v>
-      </c>
-      <c r="AO4">
-        <v>50</v>
-      </c>
-      <c r="AP4">
-        <v>14.5</v>
-      </c>
-      <c r="AQ4">
-        <v>13.5</v>
-      </c>
-      <c r="AR4">
-        <v>23</v>
-      </c>
-      <c r="AS4">
-        <v>50</v>
       </c>
       <c r="AT4">
         <v>9.199999999999999</v>
       </c>
       <c r="AU4">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AV4">
+        <v>11.5</v>
+      </c>
+      <c r="AW4">
+        <v>27</v>
+      </c>
+      <c r="AX4">
         <v>14</v>
       </c>
-      <c r="AW4">
-        <v>34</v>
-      </c>
-      <c r="AX4">
-        <v>10</v>
-      </c>
       <c r="AY4">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ4">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA4">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BB4">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="BC4">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="BD4">
         <v>27</v>
       </c>
       <c r="BE4">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BF4">
-        <v>9.4</v>
+        <v>15.5</v>
       </c>
       <c r="BG4">
-        <v>24</v>
+        <v>17.5</v>
       </c>
       <c r="BH4">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="BI4">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="BJ4">
         <v>9.6</v>
       </c>
       <c r="BK4">
-        <v>7.4</v>
+        <v>5.3</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BN4">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BO4">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BP4">
-        <v>14.5</v>
+        <v>19</v>
       </c>
       <c r="BQ4">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BR4">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="BS4">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BT4">
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="BU4">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="BV4">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BW4">
         <v>7.8</v>
       </c>
       <c r="BX4">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BY4">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ4">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="CA4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CB4" t="s">
         <v>118</v>
@@ -1693,13 +1693,13 @@
         <v>1.77</v>
       </c>
       <c r="G5">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="H5">
         <v>4.9</v>
       </c>
       <c r="I5">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J5">
         <v>4.1</v>
@@ -1708,7 +1708,7 @@
         <v>4.3</v>
       </c>
       <c r="L5">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="M5">
         <v>1.05</v>
@@ -1717,34 +1717,34 @@
         <v>5</v>
       </c>
       <c r="O5">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P5">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="Q5">
         <v>1.71</v>
       </c>
       <c r="R5">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S5">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="T5">
         <v>1.71</v>
       </c>
       <c r="U5">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V5">
         <v>1.24</v>
       </c>
       <c r="W5">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="X5">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y5">
         <v>22</v>
@@ -1756,118 +1756,118 @@
         <v>120</v>
       </c>
       <c r="AB5">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC5">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD5">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AE5">
         <v>60</v>
       </c>
       <c r="AF5">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG5">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AH5">
         <v>17.5</v>
       </c>
       <c r="AI5">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ5">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AK5">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AL5">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AM5">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AN5">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AO5">
         <v>55</v>
       </c>
       <c r="AP5">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AQ5">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AR5">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AS5">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="AT5">
         <v>10</v>
       </c>
       <c r="AU5">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV5">
+        <v>17.5</v>
+      </c>
+      <c r="AW5">
+        <v>50</v>
+      </c>
+      <c r="AX5">
+        <v>10.5</v>
+      </c>
+      <c r="AY5">
+        <v>9</v>
+      </c>
+      <c r="AZ5">
+        <v>16</v>
+      </c>
+      <c r="BA5">
+        <v>48</v>
+      </c>
+      <c r="BB5">
         <v>17</v>
-      </c>
-      <c r="AW5">
-        <v>40</v>
-      </c>
-      <c r="AX5">
-        <v>11</v>
-      </c>
-      <c r="AY5">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ5">
-        <v>15.5</v>
-      </c>
-      <c r="BA5">
-        <v>40</v>
-      </c>
-      <c r="BB5">
-        <v>16.5</v>
       </c>
       <c r="BC5">
         <v>15</v>
       </c>
       <c r="BD5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BE5">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="BF5">
         <v>8</v>
       </c>
       <c r="BG5">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="BH5">
         <v>4</v>
       </c>
       <c r="BI5">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BJ5">
         <v>9.800000000000001</v>
       </c>
       <c r="BK5">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BL5">
         <v>110</v>
       </c>
       <c r="BM5">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BN5">
         <v>4.8</v>
@@ -1876,40 +1876,40 @@
         <v>4.2</v>
       </c>
       <c r="BP5">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BQ5">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BR5">
         <v>24</v>
       </c>
       <c r="BS5">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT5">
         <v>8.800000000000001</v>
       </c>
       <c r="BU5">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BV5">
         <v>38</v>
       </c>
       <c r="BW5">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BX5">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BY5">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BZ5">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="CA5">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="CB5" t="s">
         <v>118</v>
@@ -1932,16 +1932,16 @@
         <v>112</v>
       </c>
       <c r="F6">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="G6">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="H6">
+        <v>2.74</v>
+      </c>
+      <c r="I6">
         <v>2.76</v>
-      </c>
-      <c r="I6">
-        <v>2.78</v>
       </c>
       <c r="J6">
         <v>3.7</v>
@@ -1977,16 +1977,16 @@
         <v>1.7</v>
       </c>
       <c r="U6">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="V6">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W6">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="X6">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Y6">
         <v>12.5</v>
@@ -2004,13 +2004,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD6">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE6">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AF6">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AG6">
         <v>12</v>
@@ -2046,7 +2046,7 @@
         <v>11</v>
       </c>
       <c r="AR6">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AS6">
         <v>38</v>
@@ -2058,25 +2058,25 @@
         <v>7.6</v>
       </c>
       <c r="AV6">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AW6">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AX6">
         <v>17</v>
       </c>
       <c r="AY6">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ6">
         <v>15</v>
       </c>
       <c r="BA6">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BB6">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BC6">
         <v>24</v>
@@ -2085,10 +2085,10 @@
         <v>32</v>
       </c>
       <c r="BE6">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BF6">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BG6">
         <v>21</v>
@@ -2097,19 +2097,19 @@
         <v>3.65</v>
       </c>
       <c r="BI6">
-        <v>2.98</v>
+        <v>3.35</v>
       </c>
       <c r="BJ6">
         <v>9</v>
       </c>
       <c r="BK6">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BL6">
         <v>100</v>
       </c>
       <c r="BM6">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BN6">
         <v>5.8</v>
@@ -2121,7 +2121,7 @@
         <v>19.5</v>
       </c>
       <c r="BQ6">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BR6">
         <v>30</v>
@@ -2130,7 +2130,7 @@
         <v>10.5</v>
       </c>
       <c r="BT6">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BU6">
         <v>5.3</v>
@@ -2139,19 +2139,19 @@
         <v>21</v>
       </c>
       <c r="BW6">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BX6">
         <v>32</v>
       </c>
       <c r="BY6">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BZ6">
         <v>24</v>
       </c>
       <c r="CA6">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="CB6" t="s">
         <v>118</v>
@@ -2174,16 +2174,16 @@
         <v>113</v>
       </c>
       <c r="F7">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="G7">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="H7">
         <v>6</v>
       </c>
       <c r="I7">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J7">
         <v>4</v>
@@ -2192,40 +2192,40 @@
         <v>4.5</v>
       </c>
       <c r="L7">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="M7">
         <v>1.06</v>
       </c>
       <c r="N7">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="O7">
         <v>1.32</v>
       </c>
       <c r="P7">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="Q7">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="R7">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S7">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="T7">
         <v>1.96</v>
       </c>
       <c r="U7">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="V7">
         <v>1.17</v>
       </c>
       <c r="W7">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="X7">
         <v>17</v>
@@ -2237,7 +2237,7 @@
         <v>55</v>
       </c>
       <c r="AA7">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AB7">
         <v>8.6</v>
@@ -2246,7 +2246,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD7">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE7">
         <v>120</v>
@@ -2255,13 +2255,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AG7">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AH7">
         <v>29</v>
       </c>
       <c r="AI7">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ7">
         <v>18</v>
@@ -2270,16 +2270,16 @@
         <v>23</v>
       </c>
       <c r="AL7">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM7">
         <v>160</v>
       </c>
       <c r="AN7">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AO7">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AP7">
         <v>12.5</v>
@@ -2291,7 +2291,7 @@
         <v>38</v>
       </c>
       <c r="AS7">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT7">
         <v>7</v>
@@ -2318,7 +2318,7 @@
         <v>55</v>
       </c>
       <c r="BB7">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BC7">
         <v>15.5</v>
@@ -2327,22 +2327,22 @@
         <v>27</v>
       </c>
       <c r="BE7">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BF7">
         <v>8.6</v>
       </c>
       <c r="BG7">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BH7">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BI7">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="BJ7">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK7">
         <v>6</v>
@@ -2351,7 +2351,7 @@
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BN7">
         <v>4.2</v>
@@ -2369,25 +2369,25 @@
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT7">
         <v>10</v>
       </c>
       <c r="BU7">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BV7">
         <v>1000</v>
       </c>
       <c r="BW7">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BZ7">
         <v>0</v>
@@ -2419,7 +2419,7 @@
         <v>1.61</v>
       </c>
       <c r="G8">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="H8">
         <v>6.4</v>
@@ -2428,7 +2428,7 @@
         <v>6.8</v>
       </c>
       <c r="J8">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K8">
         <v>4.5</v>
@@ -2443,7 +2443,7 @@
         <v>4.7</v>
       </c>
       <c r="O8">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P8">
         <v>2.26</v>
@@ -2455,58 +2455,58 @@
         <v>1.49</v>
       </c>
       <c r="S8">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="T8">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="U8">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V8">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W8">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="X8">
         <v>19.5</v>
       </c>
       <c r="Y8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Z8">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AA8">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="AB8">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC8">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD8">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE8">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AF8">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AG8">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH8">
         <v>21</v>
       </c>
       <c r="AI8">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AJ8">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AK8">
         <v>16</v>
@@ -2521,7 +2521,7 @@
         <v>7.8</v>
       </c>
       <c r="AO8">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AP8">
         <v>17</v>
@@ -2533,13 +2533,13 @@
         <v>46</v>
       </c>
       <c r="AS8">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AT8">
         <v>8.800000000000001</v>
       </c>
       <c r="AU8">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AV8">
         <v>21</v>
@@ -2548,7 +2548,7 @@
         <v>70</v>
       </c>
       <c r="AX8">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AY8">
         <v>9</v>
@@ -2557,7 +2557,7 @@
         <v>18.5</v>
       </c>
       <c r="BA8">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="BB8">
         <v>13.5</v>
@@ -2581,61 +2581,61 @@
         <v>4.7</v>
       </c>
       <c r="BI8">
-        <v>3.15</v>
+        <v>3.65</v>
       </c>
       <c r="BJ8">
         <v>10</v>
       </c>
       <c r="BK8">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>9.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BN8">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BO8">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BP8">
         <v>9.800000000000001</v>
       </c>
       <c r="BQ8">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="BR8">
         <v>23</v>
       </c>
       <c r="BS8">
-        <v>6.8</v>
+        <v>5.9</v>
       </c>
       <c r="BT8">
         <v>9.800000000000001</v>
       </c>
       <c r="BU8">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="BV8">
         <v>60</v>
       </c>
       <c r="BW8">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="BX8">
         <v>55</v>
       </c>
       <c r="BY8">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="BZ8">
         <v>16</v>
       </c>
       <c r="CA8">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="CB8" t="s">
         <v>118</v>
@@ -2664,7 +2664,7 @@
         <v>2.18</v>
       </c>
       <c r="H9">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="I9">
         <v>3.35</v>
@@ -2673,7 +2673,7 @@
         <v>4.3</v>
       </c>
       <c r="K9">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L9">
         <v>1.25</v>
@@ -2769,7 +2769,7 @@
         <v>23</v>
       </c>
       <c r="AQ9">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AR9">
         <v>19.5</v>
@@ -2802,7 +2802,7 @@
         <v>19.5</v>
       </c>
       <c r="BB9">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BC9">
         <v>14</v>
@@ -2900,13 +2900,13 @@
         <v>116</v>
       </c>
       <c r="F10">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="G10">
         <v>2.64</v>
       </c>
       <c r="H10">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="I10">
         <v>3.7</v>
@@ -2915,10 +2915,10 @@
         <v>2.98</v>
       </c>
       <c r="K10">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="L10">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="M10">
         <v>1.12</v>
@@ -2951,7 +2951,7 @@
         <v>1.37</v>
       </c>
       <c r="W10">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="X10">
         <v>8.6</v>
@@ -3062,64 +3062,64 @@
         <v>6.8</v>
       </c>
       <c r="BH10">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="BI10">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="BJ10">
         <v>12</v>
       </c>
       <c r="BK10">
-        <v>5.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BN10">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BO10">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BP10">
         <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR10">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BS10">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT10">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BU10">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BV10">
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BZ10">
         <v>1000</v>
       </c>
       <c r="CA10">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="CB10" t="s">
         <v>118</v>
@@ -3142,13 +3142,13 @@
         <v>117</v>
       </c>
       <c r="F11">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="G11">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H11">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="I11">
         <v>2.86</v>
@@ -3157,10 +3157,10 @@
         <v>3.15</v>
       </c>
       <c r="K11">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L11">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="M11">
         <v>1.09</v>
@@ -3169,7 +3169,7 @@
         <v>3.3</v>
       </c>
       <c r="O11">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P11">
         <v>1.76</v>
@@ -3178,7 +3178,7 @@
         <v>2.2</v>
       </c>
       <c r="R11">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S11">
         <v>4</v>
@@ -3193,7 +3193,7 @@
         <v>1.54</v>
       </c>
       <c r="W11">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="X11">
         <v>13.5</v>
@@ -3217,7 +3217,7 @@
         <v>12.5</v>
       </c>
       <c r="AE11">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AF11">
         <v>24</v>
@@ -3229,7 +3229,7 @@
         <v>23</v>
       </c>
       <c r="AI11">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ11">
         <v>60</v>
@@ -3247,7 +3247,7 @@
         <v>44</v>
       </c>
       <c r="AO11">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AP11">
         <v>10</v>
@@ -3259,7 +3259,7 @@
         <v>15</v>
       </c>
       <c r="AS11">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AT11">
         <v>9.4</v>
@@ -3271,7 +3271,7 @@
         <v>10.5</v>
       </c>
       <c r="AW11">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AX11">
         <v>17</v>
@@ -3283,31 +3283,31 @@
         <v>16</v>
       </c>
       <c r="BA11">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB11">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BC11">
         <v>29</v>
       </c>
       <c r="BD11">
+        <v>7.8</v>
+      </c>
+      <c r="BE11">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF11">
         <v>7.4</v>
-      </c>
-      <c r="BE11">
-        <v>7.8</v>
-      </c>
-      <c r="BF11">
-        <v>7</v>
       </c>
       <c r="BG11">
         <v>26</v>
       </c>
       <c r="BH11">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BI11">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="BJ11">
         <v>11.5</v>
@@ -3319,7 +3319,7 @@
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BN11">
         <v>6.8</v>
@@ -3337,7 +3337,7 @@
         <v>46</v>
       </c>
       <c r="BS11">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BT11">
         <v>6.4</v>
@@ -3346,7 +3346,7 @@
         <v>4.4</v>
       </c>
       <c r="BV11">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BW11">
         <v>4.7</v>
@@ -3361,7 +3361,7 @@
         <v>40</v>
       </c>
       <c r="CA11">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="CB11" t="s">
         <v>118</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-18.xlsx
@@ -370,7 +370,7 @@
     <t>Atletico GO</t>
   </si>
   <si>
-    <t>2026-08-17 18:08:56</t>
+    <t>2026-08-17 20:16:10</t>
   </si>
 </sst>
 </file>
@@ -964,172 +964,172 @@
         <v>108</v>
       </c>
       <c r="F2">
+        <v>3.8</v>
+      </c>
+      <c r="G2">
         <v>4.2</v>
       </c>
-      <c r="G2">
-        <v>4.5</v>
-      </c>
       <c r="H2">
-        <v>1.97</v>
+        <v>2.08</v>
       </c>
       <c r="I2">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="J2">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K2">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L2">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="M2">
         <v>1.09</v>
       </c>
       <c r="N2">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O2">
         <v>1.41</v>
       </c>
       <c r="P2">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="Q2">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="R2">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="S2">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="T2">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="U2">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="V2">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="W2">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="X2">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y2">
+        <v>8.4</v>
+      </c>
+      <c r="Z2">
+        <v>14</v>
+      </c>
+      <c r="AA2">
+        <v>28</v>
+      </c>
+      <c r="AB2">
+        <v>13</v>
+      </c>
+      <c r="AC2">
         <v>8.199999999999999</v>
-      </c>
-      <c r="Z2">
-        <v>12</v>
-      </c>
-      <c r="AA2">
-        <v>29</v>
-      </c>
-      <c r="AB2">
-        <v>14</v>
-      </c>
-      <c r="AC2">
-        <v>8</v>
       </c>
       <c r="AD2">
         <v>10.5</v>
       </c>
       <c r="AE2">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AF2">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AG2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AH2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI2">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AJ2">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AK2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AL2">
+        <v>85</v>
+      </c>
+      <c r="AM2">
+        <v>190</v>
+      </c>
+      <c r="AN2">
         <v>95</v>
       </c>
-      <c r="AM2">
-        <v>160</v>
-      </c>
-      <c r="AN2">
-        <v>110</v>
-      </c>
       <c r="AO2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AP2">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AQ2">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AR2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AS2">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AT2">
         <v>11</v>
       </c>
       <c r="AU2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV2">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AW2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AX2">
         <v>23</v>
       </c>
       <c r="AY2">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AZ2">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA2">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="BB2">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="BC2">
         <v>44</v>
       </c>
       <c r="BD2">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BE2">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="BF2">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BG2">
         <v>14</v>
       </c>
       <c r="BH2">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BI2">
-        <v>2.5</v>
+        <v>2.76</v>
       </c>
       <c r="BJ2">
         <v>13</v>
@@ -1141,49 +1141,49 @@
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>8.199999999999999</v>
+        <v>140</v>
       </c>
       <c r="BN2">
         <v>9.199999999999999</v>
       </c>
       <c r="BO2">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BP2">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BQ2">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="BR2">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BS2">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="BT2">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BU2">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BV2">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BW2">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BX2">
         <v>40</v>
       </c>
       <c r="BY2">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="BZ2">
         <v>40</v>
       </c>
       <c r="CA2">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="CB2" t="s">
         <v>118</v>
@@ -1209,61 +1209,61 @@
         <v>3.25</v>
       </c>
       <c r="G3">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="H3">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="I3">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="J3">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="K3">
         <v>3</v>
       </c>
       <c r="L3">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="M3">
         <v>1.14</v>
       </c>
       <c r="N3">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="O3">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="P3">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="Q3">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="R3">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S3">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="T3">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="U3">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="V3">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W3">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="X3">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y3">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z3">
         <v>15.5</v>
@@ -1272,28 +1272,28 @@
         <v>46</v>
       </c>
       <c r="AB3">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AC3">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AD3">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE3">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AF3">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AG3">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH3">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AI3">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ3">
         <v>65</v>
@@ -1302,22 +1302,22 @@
         <v>55</v>
       </c>
       <c r="AL3">
-        <v>970</v>
+        <v>80</v>
       </c>
       <c r="AM3">
         <v>1000</v>
       </c>
       <c r="AN3">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AO3">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AP3">
         <v>7.4</v>
       </c>
       <c r="AQ3">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AR3">
         <v>14</v>
@@ -1326,31 +1326,31 @@
         <v>40</v>
       </c>
       <c r="AT3">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AU3">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV3">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AW3">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AX3">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AY3">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AZ3">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BA3">
         <v>55</v>
       </c>
       <c r="BB3">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BC3">
         <v>46</v>
@@ -1359,31 +1359,31 @@
         <v>65</v>
       </c>
       <c r="BE3">
-        <v>95</v>
+        <v>140</v>
       </c>
       <c r="BF3">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="BG3">
         <v>42</v>
       </c>
       <c r="BH3">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="BI3">
         <v>2.48</v>
       </c>
       <c r="BJ3">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK3">
-        <v>7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>17.5</v>
+        <v>200</v>
       </c>
       <c r="BN3">
         <v>6.2</v>
@@ -1392,40 +1392,40 @@
         <v>5.5</v>
       </c>
       <c r="BP3">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="BQ3">
-        <v>11.5</v>
+        <v>15.5</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BT3">
         <v>5.3</v>
       </c>
       <c r="BU3">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BV3">
         <v>25</v>
       </c>
       <c r="BW3">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BX3">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY3">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BZ3">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="CA3">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="CB3" t="s">
         <v>118</v>
@@ -1448,16 +1448,16 @@
         <v>110</v>
       </c>
       <c r="F4">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="G4">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="H4">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="I4">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="J4">
         <v>3.6</v>
@@ -1472,58 +1472,58 @@
         <v>1.06</v>
       </c>
       <c r="N4">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O4">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="P4">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="Q4">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="R4">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S4">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="T4">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="U4">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="V4">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W4">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="X4">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Y4">
         <v>14.5</v>
       </c>
       <c r="Z4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA4">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB4">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC4">
         <v>8.800000000000001</v>
       </c>
       <c r="AD4">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE4">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AF4">
         <v>17</v>
@@ -1532,109 +1532,109 @@
         <v>12</v>
       </c>
       <c r="AH4">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI4">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AJ4">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AK4">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AL4">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="AM4">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AN4">
+        <v>18.5</v>
+      </c>
+      <c r="AO4">
+        <v>28</v>
+      </c>
+      <c r="AP4">
+        <v>14.5</v>
+      </c>
+      <c r="AQ4">
+        <v>12</v>
+      </c>
+      <c r="AR4">
         <v>19.5</v>
       </c>
-      <c r="AO4">
-        <v>32</v>
-      </c>
-      <c r="AP4">
-        <v>14</v>
-      </c>
-      <c r="AQ4">
-        <v>11.5</v>
-      </c>
-      <c r="AR4">
-        <v>18</v>
-      </c>
       <c r="AS4">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AT4">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AU4">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AV4">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW4">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AX4">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AY4">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ4">
         <v>14.5</v>
       </c>
       <c r="BA4">
+        <v>32</v>
+      </c>
+      <c r="BB4">
         <v>29</v>
-      </c>
-      <c r="BB4">
-        <v>23</v>
       </c>
       <c r="BC4">
         <v>21</v>
       </c>
       <c r="BD4">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BE4">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="BF4">
         <v>15.5</v>
       </c>
       <c r="BG4">
-        <v>17.5</v>
+        <v>22</v>
       </c>
       <c r="BH4">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="BI4">
-        <v>2.94</v>
+        <v>3.2</v>
       </c>
       <c r="BJ4">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BK4">
-        <v>5.3</v>
+        <v>7.6</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>10.5</v>
+        <v>75</v>
       </c>
       <c r="BN4">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BO4">
         <v>4.8</v>
       </c>
       <c r="BP4">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BQ4">
         <v>7.2</v>
@@ -1643,31 +1643,31 @@
         <v>32</v>
       </c>
       <c r="BS4">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="BT4">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BU4">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BV4">
         <v>24</v>
       </c>
       <c r="BW4">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="BX4">
         <v>36</v>
       </c>
       <c r="BY4">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="BZ4">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="CA4">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="CB4" t="s">
         <v>118</v>
@@ -1690,25 +1690,25 @@
         <v>111</v>
       </c>
       <c r="F5">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="G5">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="H5">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="I5">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="J5">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K5">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L5">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M5">
         <v>1.05</v>
@@ -1720,7 +1720,7 @@
         <v>1.23</v>
       </c>
       <c r="P5">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="Q5">
         <v>1.71</v>
@@ -1729,19 +1729,19 @@
         <v>1.53</v>
       </c>
       <c r="S5">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="T5">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="U5">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="V5">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="W5">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="X5">
         <v>20</v>
@@ -1762,7 +1762,7 @@
         <v>9.6</v>
       </c>
       <c r="AD5">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AE5">
         <v>60</v>
@@ -1771,13 +1771,13 @@
         <v>12</v>
       </c>
       <c r="AG5">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AH5">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AI5">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AJ5">
         <v>18</v>
@@ -1786,19 +1786,19 @@
         <v>16.5</v>
       </c>
       <c r="AL5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AM5">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AN5">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AO5">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AP5">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AQ5">
         <v>20</v>
@@ -1810,10 +1810,10 @@
         <v>85</v>
       </c>
       <c r="AT5">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU5">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV5">
         <v>17.5</v>
@@ -1825,16 +1825,16 @@
         <v>10.5</v>
       </c>
       <c r="AY5">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ5">
+        <v>16.5</v>
+      </c>
+      <c r="BA5">
+        <v>50</v>
+      </c>
+      <c r="BB5">
         <v>16</v>
-      </c>
-      <c r="BA5">
-        <v>48</v>
-      </c>
-      <c r="BB5">
-        <v>17</v>
       </c>
       <c r="BC5">
         <v>15</v>
@@ -1843,13 +1843,13 @@
         <v>26</v>
       </c>
       <c r="BE5">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BF5">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BG5">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="BH5">
         <v>4</v>
@@ -1861,25 +1861,25 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK5">
-        <v>5.6</v>
+        <v>8</v>
       </c>
       <c r="BL5">
         <v>110</v>
       </c>
       <c r="BM5">
-        <v>11</v>
+        <v>75</v>
       </c>
       <c r="BN5">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BO5">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BP5">
         <v>11.5</v>
       </c>
       <c r="BQ5">
-        <v>6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR5">
         <v>24</v>
@@ -1891,19 +1891,19 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BU5">
-        <v>5.2</v>
+        <v>7.6</v>
       </c>
       <c r="BV5">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BW5">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BX5">
         <v>42</v>
       </c>
       <c r="BY5">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BZ5">
         <v>17</v>
@@ -1932,13 +1932,13 @@
         <v>112</v>
       </c>
       <c r="F6">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="G6">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="H6">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="I6">
         <v>2.76</v>
@@ -1947,7 +1947,7 @@
         <v>3.7</v>
       </c>
       <c r="K6">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L6">
         <v>1.38</v>
@@ -1959,37 +1959,37 @@
         <v>4.3</v>
       </c>
       <c r="O6">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P6">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="Q6">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="R6">
         <v>1.43</v>
       </c>
       <c r="S6">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="T6">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="U6">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="V6">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="W6">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="X6">
         <v>17</v>
       </c>
       <c r="Y6">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Z6">
         <v>19</v>
@@ -1998,7 +1998,7 @@
         <v>42</v>
       </c>
       <c r="AB6">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AC6">
         <v>8.199999999999999</v>
@@ -2013,16 +2013,16 @@
         <v>19</v>
       </c>
       <c r="AG6">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH6">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI6">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ6">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AK6">
         <v>28</v>
@@ -2031,16 +2031,16 @@
         <v>38</v>
       </c>
       <c r="AM6">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN6">
         <v>22</v>
       </c>
       <c r="AO6">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AP6">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AQ6">
         <v>11</v>
@@ -2064,7 +2064,7 @@
         <v>25</v>
       </c>
       <c r="AX6">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AY6">
         <v>11</v>
@@ -2073,7 +2073,7 @@
         <v>15</v>
       </c>
       <c r="BA6">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BB6">
         <v>36</v>
@@ -2088,10 +2088,10 @@
         <v>55</v>
       </c>
       <c r="BF6">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BG6">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BH6">
         <v>3.65</v>
@@ -2100,58 +2100,58 @@
         <v>3.35</v>
       </c>
       <c r="BJ6">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK6">
-        <v>5.9</v>
+        <v>8</v>
       </c>
       <c r="BL6">
         <v>100</v>
       </c>
       <c r="BM6">
-        <v>14.5</v>
+        <v>75</v>
       </c>
       <c r="BN6">
         <v>5.8</v>
       </c>
       <c r="BO6">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BP6">
         <v>19.5</v>
       </c>
       <c r="BQ6">
-        <v>9</v>
+        <v>14.5</v>
       </c>
       <c r="BR6">
         <v>30</v>
       </c>
       <c r="BS6">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BT6">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BU6">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BV6">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BW6">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BX6">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BY6">
+        <v>12.5</v>
+      </c>
+      <c r="BZ6">
+        <v>23</v>
+      </c>
+      <c r="CA6">
         <v>11</v>
-      </c>
-      <c r="BZ6">
-        <v>24</v>
-      </c>
-      <c r="CA6">
-        <v>10</v>
       </c>
       <c r="CB6" t="s">
         <v>118</v>
@@ -2174,22 +2174,22 @@
         <v>113</v>
       </c>
       <c r="F7">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="G7">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="H7">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="I7">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="J7">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="K7">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L7">
         <v>1.42</v>
@@ -2198,34 +2198,34 @@
         <v>1.06</v>
       </c>
       <c r="N7">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="O7">
         <v>1.32</v>
       </c>
       <c r="P7">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="Q7">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="R7">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S7">
         <v>3.5</v>
       </c>
       <c r="T7">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="U7">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="V7">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W7">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="X7">
         <v>17</v>
@@ -2234,7 +2234,7 @@
         <v>22</v>
       </c>
       <c r="Z7">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AA7">
         <v>230</v>
@@ -2243,10 +2243,10 @@
         <v>8.6</v>
       </c>
       <c r="AC7">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AD7">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AE7">
         <v>120</v>
@@ -2258,10 +2258,10 @@
         <v>10.5</v>
       </c>
       <c r="AH7">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AI7">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AJ7">
         <v>18</v>
@@ -2276,10 +2276,10 @@
         <v>160</v>
       </c>
       <c r="AN7">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AO7">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="AP7">
         <v>12.5</v>
@@ -2288,10 +2288,10 @@
         <v>16.5</v>
       </c>
       <c r="AR7">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AS7">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT7">
         <v>7</v>
@@ -2300,13 +2300,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW7">
         <v>55</v>
       </c>
       <c r="AX7">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY7">
         <v>8.800000000000001</v>
@@ -2318,64 +2318,64 @@
         <v>55</v>
       </c>
       <c r="BB7">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BC7">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BD7">
         <v>27</v>
       </c>
       <c r="BE7">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF7">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG7">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH7">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BI7">
         <v>2.8</v>
       </c>
       <c r="BJ7">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BK7">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BN7">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BO7">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BP7">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BQ7">
         <v>8.199999999999999</v>
       </c>
       <c r="BR7">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BS7">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BT7">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BU7">
-        <v>5.8</v>
+        <v>7.8</v>
       </c>
       <c r="BV7">
         <v>1000</v>
@@ -2387,7 +2387,7 @@
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BZ7">
         <v>0</v>
@@ -2419,19 +2419,19 @@
         <v>1.61</v>
       </c>
       <c r="G8">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="H8">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="I8">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J8">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K8">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L8">
         <v>1.33</v>
@@ -2440,73 +2440,73 @@
         <v>1.05</v>
       </c>
       <c r="N8">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="O8">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P8">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="Q8">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="R8">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="S8">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="T8">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="U8">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="V8">
         <v>1.18</v>
       </c>
       <c r="W8">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="X8">
         <v>19.5</v>
       </c>
       <c r="Y8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Z8">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA8">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="AB8">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AC8">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD8">
         <v>24</v>
       </c>
       <c r="AE8">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AF8">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AG8">
         <v>10</v>
       </c>
       <c r="AH8">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI8">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AJ8">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AK8">
         <v>16</v>
@@ -2515,16 +2515,16 @@
         <v>32</v>
       </c>
       <c r="AM8">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="AN8">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AO8">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="AP8">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AQ8">
         <v>22</v>
@@ -2533,70 +2533,70 @@
         <v>46</v>
       </c>
       <c r="AS8">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AT8">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU8">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV8">
         <v>21</v>
       </c>
       <c r="AW8">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="AX8">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY8">
         <v>9</v>
       </c>
       <c r="AZ8">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA8">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="BB8">
         <v>13.5</v>
       </c>
       <c r="BC8">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BD8">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BE8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BF8">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BG8">
         <v>65</v>
       </c>
       <c r="BH8">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BI8">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="BJ8">
         <v>10</v>
       </c>
       <c r="BK8">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BL8">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="BM8">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="BN8">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="BO8">
         <v>3.85</v>
@@ -2605,37 +2605,37 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BQ8">
-        <v>4.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR8">
         <v>23</v>
       </c>
       <c r="BS8">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="BT8">
         <v>9.800000000000001</v>
       </c>
       <c r="BU8">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BV8">
         <v>60</v>
       </c>
       <c r="BW8">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX8">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BY8">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BZ8">
         <v>16</v>
       </c>
       <c r="CA8">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="CB8" t="s">
         <v>118</v>
@@ -2658,10 +2658,10 @@
         <v>115</v>
       </c>
       <c r="F9">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="G9">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="H9">
         <v>3.2</v>
@@ -2670,10 +2670,10 @@
         <v>3.35</v>
       </c>
       <c r="J9">
+        <v>4.1</v>
+      </c>
+      <c r="K9">
         <v>4.3</v>
-      </c>
-      <c r="K9">
-        <v>4.4</v>
       </c>
       <c r="L9">
         <v>1.25</v>
@@ -2682,52 +2682,52 @@
         <v>1.02</v>
       </c>
       <c r="N9">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="O9">
         <v>1.14</v>
       </c>
       <c r="P9">
+        <v>3.2</v>
+      </c>
+      <c r="Q9">
+        <v>1.43</v>
+      </c>
+      <c r="R9">
+        <v>1.91</v>
+      </c>
+      <c r="S9">
+        <v>2.04</v>
+      </c>
+      <c r="T9">
+        <v>1.42</v>
+      </c>
+      <c r="U9">
         <v>3.1</v>
       </c>
-      <c r="Q9">
-        <v>1.44</v>
-      </c>
-      <c r="R9">
-        <v>1.86</v>
-      </c>
-      <c r="S9">
-        <v>2.08</v>
-      </c>
-      <c r="T9">
-        <v>1.45</v>
-      </c>
-      <c r="U9">
-        <v>3.05</v>
-      </c>
       <c r="V9">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W9">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="X9">
         <v>80</v>
       </c>
       <c r="Y9">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Z9">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AA9">
-        <v>420</v>
+        <v>110</v>
       </c>
       <c r="AB9">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AC9">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD9">
         <v>17.5</v>
@@ -2736,16 +2736,16 @@
         <v>32</v>
       </c>
       <c r="AF9">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG9">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH9">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AI9">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AJ9">
         <v>32</v>
@@ -2757,28 +2757,28 @@
         <v>26</v>
       </c>
       <c r="AM9">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AN9">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AO9">
         <v>17</v>
       </c>
       <c r="AP9">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AQ9">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AR9">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AS9">
         <v>29</v>
       </c>
       <c r="AT9">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AU9">
         <v>10</v>
@@ -2787,37 +2787,37 @@
         <v>13</v>
       </c>
       <c r="AW9">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AX9">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AY9">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ9">
         <v>12.5</v>
       </c>
       <c r="BA9">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BB9">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BC9">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BD9">
         <v>20</v>
       </c>
       <c r="BE9">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BF9">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BG9">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BH9">
         <v>5.3</v>
@@ -2859,7 +2859,7 @@
         <v>7.4</v>
       </c>
       <c r="BU9">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BV9">
         <v>21</v>
@@ -2909,7 +2909,7 @@
         <v>3.45</v>
       </c>
       <c r="I10">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="J10">
         <v>2.98</v>
@@ -2924,7 +2924,7 @@
         <v>1.12</v>
       </c>
       <c r="N10">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="O10">
         <v>1.6</v>
@@ -2942,28 +2942,28 @@
         <v>5.9</v>
       </c>
       <c r="T10">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="U10">
         <v>1.73</v>
       </c>
       <c r="V10">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W10">
         <v>1.61</v>
       </c>
       <c r="X10">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="Y10">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z10">
         <v>24</v>
       </c>
       <c r="AA10">
-        <v>90</v>
+        <v>900</v>
       </c>
       <c r="AB10">
         <v>7.8</v>
@@ -2972,40 +2972,40 @@
         <v>7.6</v>
       </c>
       <c r="AD10">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE10">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AF10">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AG10">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AH10">
         <v>26</v>
       </c>
       <c r="AI10">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AJ10">
-        <v>44</v>
+        <v>250</v>
       </c>
       <c r="AK10">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="AL10">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="AM10">
-        <v>260</v>
+        <v>500</v>
       </c>
       <c r="AN10">
-        <v>48</v>
+        <v>500</v>
       </c>
       <c r="AO10">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AP10">
         <v>7</v>
@@ -3017,7 +3017,7 @@
         <v>19</v>
       </c>
       <c r="AS10">
-        <v>6.6</v>
+        <v>9</v>
       </c>
       <c r="AT10">
         <v>6.4</v>
@@ -3029,7 +3029,7 @@
         <v>12</v>
       </c>
       <c r="AW10">
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
       <c r="AX10">
         <v>12.5</v>
@@ -3041,34 +3041,34 @@
         <v>21</v>
       </c>
       <c r="BA10">
-        <v>6.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB10">
-        <v>6.2</v>
+        <v>16</v>
       </c>
       <c r="BC10">
         <v>32</v>
       </c>
       <c r="BD10">
-        <v>6.6</v>
+        <v>9</v>
       </c>
       <c r="BE10">
-        <v>7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF10">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="BG10">
-        <v>6.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH10">
         <v>2.72</v>
       </c>
       <c r="BI10">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="BJ10">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK10">
         <v>8.800000000000001</v>
@@ -3077,7 +3077,7 @@
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BN10">
         <v>5.3</v>
@@ -3089,13 +3089,13 @@
         <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BR10">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BS10">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BT10">
         <v>6.6</v>
@@ -3107,19 +3107,19 @@
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ10">
         <v>1000</v>
       </c>
       <c r="CA10">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="CB10" t="s">
         <v>118</v>
@@ -3142,7 +3142,7 @@
         <v>117</v>
       </c>
       <c r="F11">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="G11">
         <v>3.1</v>
@@ -3151,13 +3151,13 @@
         <v>2.64</v>
       </c>
       <c r="I11">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="J11">
         <v>3.15</v>
       </c>
       <c r="K11">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="L11">
         <v>1.4</v>
@@ -3181,7 +3181,7 @@
         <v>1.29</v>
       </c>
       <c r="S11">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="T11">
         <v>1.84</v>
@@ -3229,22 +3229,22 @@
         <v>23</v>
       </c>
       <c r="AI11">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AJ11">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AK11">
         <v>46</v>
       </c>
       <c r="AL11">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AM11">
-        <v>130</v>
+        <v>580</v>
       </c>
       <c r="AN11">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AO11">
         <v>36</v>
@@ -3259,7 +3259,7 @@
         <v>15</v>
       </c>
       <c r="AS11">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AT11">
         <v>9.4</v>
@@ -3271,7 +3271,7 @@
         <v>10.5</v>
       </c>
       <c r="AW11">
-        <v>7</v>
+        <v>14.5</v>
       </c>
       <c r="AX11">
         <v>17</v>
@@ -3286,19 +3286,19 @@
         <v>7.6</v>
       </c>
       <c r="BB11">
-        <v>7.8</v>
+        <v>20</v>
       </c>
       <c r="BC11">
         <v>29</v>
       </c>
       <c r="BD11">
-        <v>7.8</v>
+        <v>23</v>
       </c>
       <c r="BE11">
         <v>8.199999999999999</v>
       </c>
       <c r="BF11">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BG11">
         <v>26</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-18.xlsx
@@ -370,7 +370,7 @@
     <t>Atletico GO</t>
   </si>
   <si>
-    <t>2026-08-17 20:16:10</t>
+    <t>2026-08-17 22:23:24</t>
   </si>
 </sst>
 </file>
@@ -964,226 +964,226 @@
         <v>108</v>
       </c>
       <c r="F2">
-        <v>3.8</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>4.2</v>
+        <v>32</v>
       </c>
       <c r="H2">
-        <v>2.08</v>
+        <v>1.28</v>
       </c>
       <c r="I2">
-        <v>2.18</v>
+        <v>1.29</v>
       </c>
       <c r="J2">
-        <v>3.55</v>
+        <v>5.2</v>
       </c>
       <c r="K2">
-        <v>3.65</v>
+        <v>5.5</v>
       </c>
       <c r="L2">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="M2">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>3.2</v>
+        <v>2.62</v>
       </c>
       <c r="O2">
-        <v>1.41</v>
+        <v>1.6</v>
       </c>
       <c r="P2">
-        <v>1.77</v>
+        <v>1.32</v>
       </c>
       <c r="Q2">
-        <v>2.2</v>
+        <v>3.9</v>
       </c>
       <c r="R2">
-        <v>1.26</v>
+        <v>1.06</v>
       </c>
       <c r="S2">
+        <v>15</v>
+      </c>
+      <c r="T2">
+        <v>2.96</v>
+      </c>
+      <c r="U2">
+        <v>1.46</v>
+      </c>
+      <c r="V2">
+        <v>4.1</v>
+      </c>
+      <c r="W2">
+        <v>1.04</v>
+      </c>
+      <c r="X2">
+        <v>1000</v>
+      </c>
+      <c r="Y2">
+        <v>2.8</v>
+      </c>
+      <c r="Z2">
+        <v>4.7</v>
+      </c>
+      <c r="AA2">
+        <v>19.5</v>
+      </c>
+      <c r="AB2">
+        <v>1000</v>
+      </c>
+      <c r="AC2">
+        <v>6.2</v>
+      </c>
+      <c r="AD2">
+        <v>12</v>
+      </c>
+      <c r="AE2">
+        <v>1000</v>
+      </c>
+      <c r="AF2">
+        <v>1000</v>
+      </c>
+      <c r="AG2">
+        <v>1000</v>
+      </c>
+      <c r="AH2">
+        <v>990</v>
+      </c>
+      <c r="AI2">
+        <v>1000</v>
+      </c>
+      <c r="AJ2">
+        <v>1000</v>
+      </c>
+      <c r="AK2">
+        <v>1000</v>
+      </c>
+      <c r="AL2">
+        <v>1000</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>1000</v>
+      </c>
+      <c r="AO2">
+        <v>1000</v>
+      </c>
+      <c r="AP2">
+        <v>7.4</v>
+      </c>
+      <c r="AQ2">
+        <v>2.64</v>
+      </c>
+      <c r="AR2">
         <v>4.4</v>
       </c>
-      <c r="T2">
-        <v>1.94</v>
-      </c>
-      <c r="U2">
-        <v>1.94</v>
-      </c>
-      <c r="V2">
-        <v>1.68</v>
-      </c>
-      <c r="W2">
-        <v>1.26</v>
-      </c>
-      <c r="X2">
-        <v>11.5</v>
-      </c>
-      <c r="Y2">
-        <v>8.4</v>
-      </c>
-      <c r="Z2">
-        <v>14</v>
-      </c>
-      <c r="AA2">
-        <v>28</v>
-      </c>
-      <c r="AB2">
-        <v>13</v>
-      </c>
-      <c r="AC2">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD2">
-        <v>10.5</v>
-      </c>
-      <c r="AE2">
-        <v>27</v>
-      </c>
-      <c r="AF2">
-        <v>28</v>
-      </c>
-      <c r="AG2">
+      <c r="AS2">
         <v>16</v>
       </c>
-      <c r="AH2">
-        <v>23</v>
-      </c>
-      <c r="AI2">
-        <v>48</v>
-      </c>
-      <c r="AJ2">
-        <v>150</v>
-      </c>
-      <c r="AK2">
+      <c r="AT2">
+        <v>7.8</v>
+      </c>
+      <c r="AU2">
+        <v>5.4</v>
+      </c>
+      <c r="AV2">
+        <v>10</v>
+      </c>
+      <c r="AW2">
+        <v>30</v>
+      </c>
+      <c r="AX2">
+        <v>8</v>
+      </c>
+      <c r="AY2">
+        <v>19.5</v>
+      </c>
+      <c r="AZ2">
+        <v>32</v>
+      </c>
+      <c r="BA2">
+        <v>130</v>
+      </c>
+      <c r="BB2">
+        <v>7.4</v>
+      </c>
+      <c r="BC2">
+        <v>160</v>
+      </c>
+      <c r="BD2">
+        <v>220</v>
+      </c>
+      <c r="BE2">
+        <v>230</v>
+      </c>
+      <c r="BF2">
         <v>75</v>
       </c>
-      <c r="AL2">
-        <v>85</v>
-      </c>
-      <c r="AM2">
-        <v>190</v>
-      </c>
-      <c r="AN2">
-        <v>95</v>
-      </c>
-      <c r="AO2">
-        <v>22</v>
-      </c>
-      <c r="AP2">
-        <v>10.5</v>
-      </c>
-      <c r="AQ2">
-        <v>7.4</v>
-      </c>
-      <c r="AR2">
-        <v>11</v>
-      </c>
-      <c r="AS2">
-        <v>23</v>
-      </c>
-      <c r="AT2">
-        <v>11</v>
-      </c>
-      <c r="AU2">
-        <v>7</v>
-      </c>
-      <c r="AV2">
-        <v>9.4</v>
-      </c>
-      <c r="AW2">
-        <v>22</v>
-      </c>
-      <c r="AX2">
-        <v>23</v>
-      </c>
-      <c r="AY2">
-        <v>14</v>
-      </c>
-      <c r="AZ2">
-        <v>19</v>
-      </c>
-      <c r="BA2">
-        <v>40</v>
-      </c>
-      <c r="BB2">
-        <v>70</v>
-      </c>
-      <c r="BC2">
-        <v>44</v>
-      </c>
-      <c r="BD2">
-        <v>48</v>
-      </c>
-      <c r="BE2">
-        <v>110</v>
-      </c>
-      <c r="BF2">
-        <v>60</v>
-      </c>
       <c r="BG2">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="BH2">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="BI2">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="BJ2">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BK2">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BL2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM2">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="BN2">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BO2">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BP2">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="BQ2">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="BR2">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="BS2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BT2">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BU2">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BV2">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="BW2">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BX2">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BY2">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="BZ2">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="CA2">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="s">
         <v>118</v>
@@ -1206,226 +1206,226 @@
         <v>109</v>
       </c>
       <c r="F3">
-        <v>3.25</v>
+        <v>1.12</v>
       </c>
       <c r="G3">
-        <v>3.3</v>
+        <v>1.13</v>
       </c>
       <c r="H3">
-        <v>2.76</v>
+        <v>44</v>
       </c>
       <c r="I3">
-        <v>2.78</v>
+        <v>55</v>
       </c>
       <c r="J3">
-        <v>2.98</v>
+        <v>11</v>
       </c>
       <c r="K3">
-        <v>3</v>
+        <v>11.5</v>
       </c>
       <c r="L3">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="M3">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="N3">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O3">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="P3">
-        <v>1.53</v>
+        <v>4</v>
       </c>
       <c r="Q3">
-        <v>2.8</v>
+        <v>1.32</v>
       </c>
       <c r="R3">
-        <v>1.19</v>
+        <v>1.65</v>
       </c>
       <c r="S3">
-        <v>5.9</v>
+        <v>2.52</v>
       </c>
       <c r="T3">
-        <v>2.14</v>
+        <v>1.87</v>
       </c>
       <c r="U3">
-        <v>1.82</v>
+        <v>2.06</v>
       </c>
       <c r="V3">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="W3">
-        <v>1.43</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="X3">
+        <v>1000</v>
+      </c>
+      <c r="Y3">
+        <v>1000</v>
+      </c>
+      <c r="Z3">
+        <v>1000</v>
+      </c>
+      <c r="AA3">
+        <v>1000</v>
+      </c>
+      <c r="AB3">
+        <v>1000</v>
+      </c>
+      <c r="AC3">
+        <v>1000</v>
+      </c>
+      <c r="AD3">
+        <v>1000</v>
+      </c>
+      <c r="AE3">
+        <v>1000</v>
+      </c>
+      <c r="AF3">
+        <v>4.2</v>
+      </c>
+      <c r="AG3">
+        <v>5.4</v>
+      </c>
+      <c r="AH3">
+        <v>14</v>
+      </c>
+      <c r="AI3">
+        <v>75</v>
+      </c>
+      <c r="AJ3">
+        <v>6.4</v>
+      </c>
+      <c r="AK3">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AL3">
+        <v>27</v>
+      </c>
+      <c r="AM3">
+        <v>120</v>
+      </c>
+      <c r="AN3">
         <v>8.199999999999999</v>
       </c>
-      <c r="Y3">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Z3">
-        <v>15.5</v>
-      </c>
-      <c r="AA3">
-        <v>46</v>
-      </c>
-      <c r="AB3">
-        <v>9</v>
-      </c>
-      <c r="AC3">
-        <v>6.6</v>
-      </c>
-      <c r="AD3">
-        <v>13</v>
-      </c>
-      <c r="AE3">
-        <v>42</v>
-      </c>
-      <c r="AF3">
-        <v>20</v>
-      </c>
-      <c r="AG3">
-        <v>15</v>
-      </c>
-      <c r="AH3">
-        <v>23</v>
-      </c>
-      <c r="AI3">
-        <v>70</v>
-      </c>
-      <c r="AJ3">
-        <v>65</v>
-      </c>
-      <c r="AK3">
-        <v>55</v>
-      </c>
-      <c r="AL3">
-        <v>80</v>
-      </c>
-      <c r="AM3">
-        <v>1000</v>
-      </c>
-      <c r="AN3">
-        <v>1000</v>
-      </c>
       <c r="AO3">
-        <v>50</v>
+        <v>300</v>
       </c>
       <c r="AP3">
-        <v>7.4</v>
+        <v>19</v>
       </c>
       <c r="AQ3">
-        <v>7.6</v>
+        <v>19</v>
       </c>
       <c r="AR3">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AS3">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="AT3">
-        <v>8.4</v>
+        <v>19</v>
       </c>
       <c r="AU3">
-        <v>6.2</v>
+        <v>19</v>
       </c>
       <c r="AV3">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="AW3">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="AX3">
-        <v>18</v>
+        <v>3.95</v>
       </c>
       <c r="AY3">
-        <v>13.5</v>
+        <v>5</v>
       </c>
       <c r="AZ3">
-        <v>21</v>
+        <v>12.5</v>
       </c>
       <c r="BA3">
         <v>55</v>
       </c>
       <c r="BB3">
-        <v>50</v>
+        <v>5.9</v>
       </c>
       <c r="BC3">
-        <v>46</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD3">
+        <v>21</v>
+      </c>
+      <c r="BE3">
         <v>65</v>
       </c>
-      <c r="BE3">
-        <v>140</v>
-      </c>
       <c r="BF3">
-        <v>55</v>
+        <v>7.6</v>
       </c>
       <c r="BG3">
-        <v>42</v>
+        <v>150</v>
       </c>
       <c r="BH3">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="BI3">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="BJ3">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BK3">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BL3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="BN3">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BO3">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BP3">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="BQ3">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="BR3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS3">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="BT3">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="BU3">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="BV3">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="BW3">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BX3">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BY3">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BZ3">
-        <v>980</v>
+        <v>0</v>
       </c>
       <c r="CA3">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="s">
         <v>118</v>
@@ -1448,226 +1448,226 @@
         <v>110</v>
       </c>
       <c r="F4">
-        <v>2.34</v>
+        <v>6</v>
       </c>
       <c r="G4">
-        <v>2.5</v>
+        <v>6.8</v>
       </c>
       <c r="H4">
-        <v>3</v>
+        <v>1.71</v>
       </c>
       <c r="I4">
-        <v>3.25</v>
+        <v>1.77</v>
       </c>
       <c r="J4">
         <v>3.6</v>
       </c>
       <c r="K4">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="L4">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="M4">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="N4">
-        <v>4.3</v>
+        <v>5.9</v>
       </c>
       <c r="O4">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="P4">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="Q4">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="R4">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="S4">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="T4">
-        <v>1.66</v>
+        <v>1.54</v>
       </c>
       <c r="U4">
+        <v>2.66</v>
+      </c>
+      <c r="V4">
         <v>2.28</v>
       </c>
-      <c r="V4">
-        <v>1.44</v>
-      </c>
       <c r="W4">
-        <v>1.66</v>
+        <v>1.17</v>
       </c>
       <c r="X4">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Y4">
-        <v>14.5</v>
+        <v>6.4</v>
       </c>
       <c r="Z4">
-        <v>24</v>
+        <v>8.6</v>
       </c>
       <c r="AA4">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="AB4">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AC4">
-        <v>8.800000000000001</v>
+        <v>5.9</v>
       </c>
       <c r="AD4">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AE4">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="AF4">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AG4">
         <v>12</v>
       </c>
       <c r="AH4">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AI4">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="AJ4">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AK4">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="AL4">
+        <v>55</v>
+      </c>
+      <c r="AM4">
+        <v>170</v>
+      </c>
+      <c r="AN4">
+        <v>85</v>
+      </c>
+      <c r="AO4">
         <v>34</v>
       </c>
-      <c r="AM4">
-        <v>80</v>
-      </c>
-      <c r="AN4">
-        <v>18.5</v>
-      </c>
-      <c r="AO4">
-        <v>28</v>
-      </c>
       <c r="AP4">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="AQ4">
-        <v>12</v>
+        <v>5.9</v>
       </c>
       <c r="AR4">
-        <v>19.5</v>
+        <v>7</v>
       </c>
       <c r="AS4">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="AT4">
         <v>10.5</v>
       </c>
       <c r="AU4">
-        <v>7.4</v>
+        <v>5</v>
       </c>
       <c r="AV4">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AW4">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="AX4">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="AY4">
         <v>10</v>
       </c>
       <c r="AZ4">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BA4">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="BB4">
-        <v>29</v>
+        <v>10.5</v>
       </c>
       <c r="BC4">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="BD4">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="BE4">
-        <v>32</v>
+        <v>100</v>
       </c>
       <c r="BF4">
-        <v>15.5</v>
+        <v>55</v>
       </c>
       <c r="BG4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BH4">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="BI4">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BJ4">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="BK4">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="BL4">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM4">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="BN4">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BO4">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BP4">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="BQ4">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BR4">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BS4">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BT4">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="BU4">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="BV4">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="BW4">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BX4">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="BY4">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BZ4">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="CA4">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="CB4" t="s">
         <v>118</v>
@@ -1690,226 +1690,226 @@
         <v>111</v>
       </c>
       <c r="F5">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="G5">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="H5">
-        <v>5.2</v>
+        <v>7.2</v>
       </c>
       <c r="I5">
+        <v>7.4</v>
+      </c>
+      <c r="J5">
+        <v>3.15</v>
+      </c>
+      <c r="K5">
+        <v>3.25</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
         <v>5.5</v>
       </c>
-      <c r="J5">
+      <c r="Q5">
+        <v>1.21</v>
+      </c>
+      <c r="R5">
+        <v>2</v>
+      </c>
+      <c r="S5">
+        <v>1.99</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>1.15</v>
+      </c>
+      <c r="W5">
+        <v>2.18</v>
+      </c>
+      <c r="X5">
+        <v>1000</v>
+      </c>
+      <c r="Y5">
+        <v>1000</v>
+      </c>
+      <c r="Z5">
+        <v>1000</v>
+      </c>
+      <c r="AA5">
+        <v>1000</v>
+      </c>
+      <c r="AB5">
+        <v>1000</v>
+      </c>
+      <c r="AC5">
+        <v>5.8</v>
+      </c>
+      <c r="AD5">
+        <v>13</v>
+      </c>
+      <c r="AE5">
+        <v>70</v>
+      </c>
+      <c r="AF5">
+        <v>1000</v>
+      </c>
+      <c r="AG5">
         <v>4.2</v>
       </c>
-      <c r="K5">
-        <v>4.4</v>
-      </c>
-      <c r="L5">
-        <v>1.34</v>
-      </c>
-      <c r="M5">
-        <v>1.05</v>
-      </c>
-      <c r="N5">
-        <v>5</v>
-      </c>
-      <c r="O5">
-        <v>1.23</v>
-      </c>
-      <c r="P5">
-        <v>2.32</v>
-      </c>
-      <c r="Q5">
-        <v>1.71</v>
-      </c>
-      <c r="R5">
-        <v>1.53</v>
-      </c>
-      <c r="S5">
-        <v>2.82</v>
-      </c>
-      <c r="T5">
-        <v>1.73</v>
-      </c>
-      <c r="U5">
-        <v>2.28</v>
-      </c>
-      <c r="V5">
-        <v>1.22</v>
-      </c>
-      <c r="W5">
-        <v>2.34</v>
-      </c>
-      <c r="X5">
-        <v>20</v>
-      </c>
-      <c r="Y5">
-        <v>22</v>
-      </c>
-      <c r="Z5">
-        <v>42</v>
-      </c>
-      <c r="AA5">
-        <v>120</v>
-      </c>
-      <c r="AB5">
-        <v>11</v>
-      </c>
-      <c r="AC5">
-        <v>9.6</v>
-      </c>
-      <c r="AD5">
-        <v>20</v>
-      </c>
-      <c r="AE5">
-        <v>60</v>
-      </c>
-      <c r="AF5">
-        <v>12</v>
-      </c>
-      <c r="AG5">
-        <v>9.4</v>
-      </c>
       <c r="AH5">
-        <v>18.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AI5">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AJ5">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AK5">
-        <v>16.5</v>
+        <v>7.6</v>
       </c>
       <c r="AL5">
-        <v>30</v>
+        <v>15.5</v>
       </c>
       <c r="AM5">
         <v>80</v>
       </c>
       <c r="AN5">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="AO5">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="AP5">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AQ5">
         <v>20</v>
       </c>
       <c r="AR5">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="AS5">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="AT5">
-        <v>9.800000000000001</v>
+        <v>20</v>
       </c>
       <c r="AU5">
-        <v>8.800000000000001</v>
+        <v>5.5</v>
       </c>
       <c r="AV5">
-        <v>17.5</v>
+        <v>11.5</v>
       </c>
       <c r="AW5">
         <v>50</v>
       </c>
       <c r="AX5">
-        <v>10.5</v>
+        <v>20</v>
       </c>
       <c r="AY5">
-        <v>8.800000000000001</v>
+        <v>3.9</v>
       </c>
       <c r="AZ5">
-        <v>16.5</v>
+        <v>8</v>
       </c>
       <c r="BA5">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="BB5">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="BC5">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="BD5">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="BE5">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BF5">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="BG5">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="BH5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BI5">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="BJ5">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BK5">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BL5">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="BM5">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="BN5">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BO5">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BP5">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BQ5">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BR5">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="BS5">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BT5">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BU5">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="BV5">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="BW5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BX5">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="BY5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BZ5">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="CA5">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="CB5" t="s">
         <v>118</v>
@@ -1935,223 +1935,223 @@
         <v>2.72</v>
       </c>
       <c r="G6">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="H6">
-        <v>2.72</v>
+        <v>2.96</v>
       </c>
       <c r="I6">
-        <v>2.76</v>
+        <v>2.98</v>
       </c>
       <c r="J6">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="K6">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="L6">
-        <v>1.38</v>
+        <v>1.87</v>
       </c>
       <c r="M6">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="N6">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="O6">
-        <v>1.28</v>
+        <v>1.49</v>
       </c>
       <c r="P6">
-        <v>2.16</v>
+        <v>1.64</v>
       </c>
       <c r="Q6">
-        <v>1.85</v>
+        <v>2.52</v>
       </c>
       <c r="R6">
-        <v>1.43</v>
+        <v>1.23</v>
       </c>
       <c r="S6">
-        <v>3.15</v>
+        <v>5</v>
       </c>
       <c r="T6">
-        <v>1.68</v>
+        <v>2.02</v>
       </c>
       <c r="U6">
-        <v>2.4</v>
+        <v>1.91</v>
       </c>
       <c r="V6">
-        <v>1.56</v>
+        <v>1.48</v>
       </c>
       <c r="W6">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="X6">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="Y6">
-        <v>13</v>
+        <v>9.4</v>
       </c>
       <c r="Z6">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AA6">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="AB6">
-        <v>13</v>
+        <v>8.6</v>
       </c>
       <c r="AC6">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="AD6">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AE6">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="AF6">
-        <v>19</v>
+        <v>14.5</v>
       </c>
       <c r="AG6">
         <v>12.5</v>
       </c>
       <c r="AH6">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="AI6">
+        <v>70</v>
+      </c>
+      <c r="AJ6">
+        <v>60</v>
+      </c>
+      <c r="AK6">
         <v>36</v>
       </c>
-      <c r="AJ6">
-        <v>42</v>
-      </c>
-      <c r="AK6">
-        <v>28</v>
-      </c>
       <c r="AL6">
+        <v>65</v>
+      </c>
+      <c r="AM6">
+        <v>210</v>
+      </c>
+      <c r="AN6">
         <v>38</v>
       </c>
-      <c r="AM6">
-        <v>75</v>
-      </c>
-      <c r="AN6">
-        <v>22</v>
-      </c>
       <c r="AO6">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="AP6">
+        <v>9</v>
+      </c>
+      <c r="AQ6">
+        <v>8.6</v>
+      </c>
+      <c r="AR6">
         <v>15.5</v>
       </c>
-      <c r="AQ6">
-        <v>11</v>
-      </c>
-      <c r="AR6">
-        <v>17</v>
-      </c>
       <c r="AS6">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="AT6">
-        <v>11.5</v>
+        <v>7.8</v>
       </c>
       <c r="AU6">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="AV6">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AW6">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="AX6">
-        <v>17.5</v>
+        <v>13</v>
       </c>
       <c r="AY6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ6">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="BA6">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="BB6">
         <v>36</v>
       </c>
       <c r="BC6">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="BD6">
+        <v>60</v>
+      </c>
+      <c r="BE6">
+        <v>140</v>
+      </c>
+      <c r="BF6">
+        <v>34</v>
+      </c>
+      <c r="BG6">
+        <v>40</v>
+      </c>
+      <c r="BH6">
+        <v>2.16</v>
+      </c>
+      <c r="BI6">
+        <v>2.04</v>
+      </c>
+      <c r="BJ6">
+        <v>16</v>
+      </c>
+      <c r="BK6">
+        <v>13.5</v>
+      </c>
+      <c r="BL6">
+        <v>640</v>
+      </c>
+      <c r="BM6">
+        <v>13</v>
+      </c>
+      <c r="BN6">
+        <v>5.5</v>
+      </c>
+      <c r="BO6">
+        <v>4.9</v>
+      </c>
+      <c r="BP6">
+        <v>38</v>
+      </c>
+      <c r="BQ6">
+        <v>30</v>
+      </c>
+      <c r="BR6">
+        <v>110</v>
+      </c>
+      <c r="BS6">
+        <v>65</v>
+      </c>
+      <c r="BT6">
+        <v>6</v>
+      </c>
+      <c r="BU6">
+        <v>5.3</v>
+      </c>
+      <c r="BV6">
+        <v>42</v>
+      </c>
+      <c r="BW6">
         <v>32</v>
       </c>
-      <c r="BE6">
-        <v>55</v>
-      </c>
-      <c r="BF6">
-        <v>19.5</v>
-      </c>
-      <c r="BG6">
-        <v>19.5</v>
-      </c>
-      <c r="BH6">
-        <v>3.65</v>
-      </c>
-      <c r="BI6">
-        <v>3.35</v>
-      </c>
-      <c r="BJ6">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BK6">
-        <v>8</v>
-      </c>
-      <c r="BL6">
-        <v>100</v>
-      </c>
-      <c r="BM6">
+      <c r="BX6">
+        <v>110</v>
+      </c>
+      <c r="BY6">
         <v>75</v>
       </c>
-      <c r="BN6">
-        <v>5.8</v>
-      </c>
-      <c r="BO6">
-        <v>5.3</v>
-      </c>
-      <c r="BP6">
-        <v>19.5</v>
-      </c>
-      <c r="BQ6">
-        <v>14.5</v>
-      </c>
-      <c r="BR6">
-        <v>30</v>
-      </c>
-      <c r="BS6">
-        <v>12.5</v>
-      </c>
-      <c r="BT6">
-        <v>5.8</v>
-      </c>
-      <c r="BU6">
-        <v>5.4</v>
-      </c>
-      <c r="BV6">
-        <v>20</v>
-      </c>
-      <c r="BW6">
-        <v>10</v>
-      </c>
-      <c r="BX6">
-        <v>30</v>
-      </c>
-      <c r="BY6">
-        <v>12.5</v>
-      </c>
       <c r="BZ6">
-        <v>23</v>
+        <v>120</v>
       </c>
       <c r="CA6">
-        <v>11</v>
+        <v>80</v>
       </c>
       <c r="CB6" t="s">
         <v>118</v>
@@ -2174,7 +2174,7 @@
         <v>113</v>
       </c>
       <c r="F7">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="G7">
         <v>1.62</v>
@@ -2183,25 +2183,25 @@
         <v>6.4</v>
       </c>
       <c r="I7">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="J7">
         <v>4.2</v>
       </c>
       <c r="K7">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="L7">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="M7">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N7">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O7">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P7">
         <v>1.98</v>
@@ -2210,19 +2210,19 @@
         <v>1.96</v>
       </c>
       <c r="R7">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S7">
         <v>3.5</v>
       </c>
       <c r="T7">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U7">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="V7">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W7">
         <v>2.6</v>
@@ -2231,25 +2231,25 @@
         <v>17</v>
       </c>
       <c r="Y7">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z7">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="AA7">
-        <v>230</v>
+        <v>950</v>
       </c>
       <c r="AB7">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC7">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AD7">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AE7">
-        <v>120</v>
+        <v>210</v>
       </c>
       <c r="AF7">
         <v>9.800000000000001</v>
@@ -2261,97 +2261,97 @@
         <v>26</v>
       </c>
       <c r="AI7">
-        <v>120</v>
+        <v>190</v>
       </c>
       <c r="AJ7">
         <v>18</v>
       </c>
       <c r="AK7">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AL7">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AM7">
-        <v>160</v>
+        <v>560</v>
       </c>
       <c r="AN7">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AO7">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AP7">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AQ7">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AR7">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AS7">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AT7">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AU7">
         <v>8.199999999999999</v>
       </c>
       <c r="AV7">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AW7">
         <v>55</v>
       </c>
       <c r="AX7">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AY7">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ7">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BA7">
         <v>55</v>
       </c>
       <c r="BB7">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BC7">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BD7">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="BE7">
-        <v>7.6</v>
+        <v>120</v>
       </c>
       <c r="BF7">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BG7">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BH7">
         <v>3.55</v>
       </c>
       <c r="BI7">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="BJ7">
         <v>11.5</v>
       </c>
       <c r="BK7">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>12</v>
+        <v>140</v>
       </c>
       <c r="BN7">
         <v>4.1</v>
@@ -2363,10 +2363,10 @@
         <v>10.5</v>
       </c>
       <c r="BQ7">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BR7">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BS7">
         <v>9</v>
@@ -2375,7 +2375,7 @@
         <v>10.5</v>
       </c>
       <c r="BU7">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BV7">
         <v>1000</v>
@@ -2416,16 +2416,16 @@
         <v>114</v>
       </c>
       <c r="F8">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="G8">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="H8">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="I8">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J8">
         <v>4.4</v>
@@ -2440,25 +2440,25 @@
         <v>1.05</v>
       </c>
       <c r="N8">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O8">
         <v>1.24</v>
       </c>
       <c r="P8">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q8">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="R8">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S8">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="T8">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="U8">
         <v>2.16</v>
@@ -2467,16 +2467,16 @@
         <v>1.18</v>
       </c>
       <c r="W8">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="X8">
         <v>19.5</v>
       </c>
       <c r="Y8">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="Z8">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AA8">
         <v>170</v>
@@ -2485,13 +2485,13 @@
         <v>10.5</v>
       </c>
       <c r="AC8">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD8">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE8">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AF8">
         <v>10.5</v>
@@ -2503,7 +2503,7 @@
         <v>20</v>
       </c>
       <c r="AI8">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="AJ8">
         <v>15.5</v>
@@ -2521,19 +2521,19 @@
         <v>7.4</v>
       </c>
       <c r="AO8">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AP8">
+        <v>18.5</v>
+      </c>
+      <c r="AQ8">
+        <v>23</v>
+      </c>
+      <c r="AR8">
+        <v>44</v>
+      </c>
+      <c r="AS8">
         <v>17.5</v>
-      </c>
-      <c r="AQ8">
-        <v>22</v>
-      </c>
-      <c r="AR8">
-        <v>46</v>
-      </c>
-      <c r="AS8">
-        <v>14</v>
       </c>
       <c r="AT8">
         <v>9.199999999999999</v>
@@ -2542,13 +2542,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV8">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW8">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="AX8">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AY8">
         <v>9</v>
@@ -2557,10 +2557,10 @@
         <v>17.5</v>
       </c>
       <c r="BA8">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="BB8">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BC8">
         <v>14</v>
@@ -2569,7 +2569,7 @@
         <v>27</v>
       </c>
       <c r="BE8">
-        <v>13</v>
+        <v>80</v>
       </c>
       <c r="BF8">
         <v>6.8</v>
@@ -2578,64 +2578,64 @@
         <v>65</v>
       </c>
       <c r="BH8">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="BI8">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BJ8">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BK8">
-        <v>4.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL8">
         <v>130</v>
       </c>
       <c r="BM8">
-        <v>9</v>
+        <v>85</v>
       </c>
       <c r="BN8">
         <v>4.3</v>
       </c>
       <c r="BO8">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BP8">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BQ8">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BR8">
         <v>23</v>
       </c>
       <c r="BS8">
-        <v>6.8</v>
+        <v>12.5</v>
       </c>
       <c r="BT8">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BU8">
-        <v>4.8</v>
+        <v>8.6</v>
       </c>
       <c r="BV8">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="BW8">
-        <v>8.199999999999999</v>
+        <v>24</v>
       </c>
       <c r="BX8">
         <v>50</v>
       </c>
       <c r="BY8">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="BZ8">
         <v>16</v>
       </c>
       <c r="CA8">
-        <v>6</v>
+        <v>13.5</v>
       </c>
       <c r="CB8" t="s">
         <v>118</v>
@@ -2667,7 +2667,7 @@
         <v>3.2</v>
       </c>
       <c r="I9">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="J9">
         <v>4.1</v>
@@ -2682,28 +2682,28 @@
         <v>1.02</v>
       </c>
       <c r="N9">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="O9">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="P9">
+        <v>3.25</v>
+      </c>
+      <c r="Q9">
+        <v>1.41</v>
+      </c>
+      <c r="R9">
+        <v>1.92</v>
+      </c>
+      <c r="S9">
+        <v>2</v>
+      </c>
+      <c r="T9">
+        <v>1.41</v>
+      </c>
+      <c r="U9">
         <v>3.2</v>
-      </c>
-      <c r="Q9">
-        <v>1.43</v>
-      </c>
-      <c r="R9">
-        <v>1.91</v>
-      </c>
-      <c r="S9">
-        <v>2.04</v>
-      </c>
-      <c r="T9">
-        <v>1.42</v>
-      </c>
-      <c r="U9">
-        <v>3.1</v>
       </c>
       <c r="V9">
         <v>1.42</v>
@@ -2715,7 +2715,7 @@
         <v>80</v>
       </c>
       <c r="Y9">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Z9">
         <v>55</v>
@@ -2742,10 +2742,10 @@
         <v>12.5</v>
       </c>
       <c r="AH9">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI9">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="AJ9">
         <v>32</v>
@@ -2754,55 +2754,55 @@
         <v>21</v>
       </c>
       <c r="AL9">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AM9">
-        <v>48</v>
+        <v>90</v>
       </c>
       <c r="AN9">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO9">
         <v>17</v>
       </c>
       <c r="AP9">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AQ9">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR9">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AS9">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="AT9">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AU9">
         <v>10</v>
       </c>
       <c r="AV9">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AW9">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="AX9">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AY9">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ9">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BA9">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BB9">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BC9">
         <v>15</v>
@@ -2811,25 +2811,25 @@
         <v>20</v>
       </c>
       <c r="BE9">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BF9">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BG9">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BH9">
         <v>5.3</v>
       </c>
       <c r="BI9">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BJ9">
         <v>8.4</v>
       </c>
       <c r="BK9">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BL9">
         <v>1000</v>
@@ -2847,13 +2847,13 @@
         <v>13.5</v>
       </c>
       <c r="BQ9">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BR9">
         <v>1000</v>
       </c>
       <c r="BS9">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BT9">
         <v>7.4</v>
@@ -2865,19 +2865,19 @@
         <v>21</v>
       </c>
       <c r="BW9">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BX9">
         <v>24</v>
       </c>
       <c r="BY9">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BZ9">
         <v>11.5</v>
       </c>
       <c r="CA9">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="CB9" t="s">
         <v>118</v>
@@ -2900,13 +2900,13 @@
         <v>116</v>
       </c>
       <c r="F10">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="G10">
         <v>2.64</v>
       </c>
       <c r="H10">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="I10">
         <v>3.6</v>
@@ -2921,7 +2921,7 @@
         <v>1.57</v>
       </c>
       <c r="M10">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N10">
         <v>2.52</v>
@@ -2939,19 +2939,19 @@
         <v>1.18</v>
       </c>
       <c r="S10">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="T10">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="U10">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="V10">
         <v>1.38</v>
       </c>
       <c r="W10">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="X10">
         <v>8.4</v>
@@ -2960,7 +2960,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="Z10">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA10">
         <v>900</v>
@@ -2975,7 +2975,7 @@
         <v>16.5</v>
       </c>
       <c r="AE10">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AF10">
         <v>15.5</v>
@@ -2993,10 +2993,10 @@
         <v>250</v>
       </c>
       <c r="AK10">
-        <v>95</v>
+        <v>180</v>
       </c>
       <c r="AL10">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AM10">
         <v>500</v>
@@ -3011,13 +3011,13 @@
         <v>7</v>
       </c>
       <c r="AQ10">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AR10">
         <v>19</v>
       </c>
       <c r="AS10">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT10">
         <v>6.4</v>
@@ -3026,10 +3026,10 @@
         <v>6.2</v>
       </c>
       <c r="AV10">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AW10">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AX10">
         <v>12.5</v>
@@ -3041,7 +3041,7 @@
         <v>21</v>
       </c>
       <c r="BA10">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BB10">
         <v>16</v>
@@ -3050,16 +3050,16 @@
         <v>32</v>
       </c>
       <c r="BD10">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE10">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF10">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BG10">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BH10">
         <v>2.72</v>
@@ -3142,88 +3142,88 @@
         <v>117</v>
       </c>
       <c r="F11">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="G11">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="H11">
         <v>2.64</v>
       </c>
       <c r="I11">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="J11">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K11">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="L11">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="M11">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N11">
-        <v>3.3</v>
+        <v>2.92</v>
       </c>
       <c r="O11">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="P11">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="Q11">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="R11">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="S11">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="T11">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="U11">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="V11">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="W11">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="X11">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="Y11">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Z11">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AA11">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AB11">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC11">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AD11">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE11">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AF11">
         <v>24</v>
       </c>
       <c r="AG11">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH11">
         <v>23</v>
@@ -3232,10 +3232,10 @@
         <v>120</v>
       </c>
       <c r="AJ11">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="AK11">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AL11">
         <v>130</v>
@@ -3244,82 +3244,82 @@
         <v>580</v>
       </c>
       <c r="AN11">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="AO11">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AP11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AQ11">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AR11">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AS11">
-        <v>7.4</v>
+        <v>5</v>
       </c>
       <c r="AT11">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU11">
         <v>6.6</v>
       </c>
       <c r="AV11">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW11">
         <v>14.5</v>
       </c>
       <c r="AX11">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AY11">
         <v>11.5</v>
       </c>
       <c r="AZ11">
-        <v>16</v>
+        <v>10.5</v>
       </c>
       <c r="BA11">
-        <v>7.6</v>
+        <v>5</v>
       </c>
       <c r="BB11">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="BC11">
-        <v>29</v>
+        <v>4.9</v>
       </c>
       <c r="BD11">
-        <v>23</v>
+        <v>5.1</v>
       </c>
       <c r="BE11">
-        <v>8.199999999999999</v>
+        <v>5.3</v>
       </c>
       <c r="BF11">
-        <v>7.2</v>
+        <v>5</v>
       </c>
       <c r="BG11">
-        <v>26</v>
+        <v>6.2</v>
       </c>
       <c r="BH11">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="BI11">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="BJ11">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BK11">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BN11">
         <v>6.8</v>
@@ -3328,16 +3328,16 @@
         <v>4.7</v>
       </c>
       <c r="BP11">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BQ11">
         <v>4.8</v>
       </c>
       <c r="BR11">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BS11">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BT11">
         <v>6.4</v>
@@ -3346,22 +3346,22 @@
         <v>4.4</v>
       </c>
       <c r="BV11">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BW11">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BX11">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BY11">
         <v>5.1</v>
       </c>
       <c r="BZ11">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="CA11">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="CB11" t="s">
         <v>118</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-18.xlsx
@@ -295,7 +295,7 @@
     <t>Atletico GO</t>
   </si>
   <si>
-    <t>2026-08-18 02:39:46</t>
+    <t>2026-08-18 04:47:25</t>
   </si>
 </sst>
 </file>
@@ -889,22 +889,22 @@
         <v>90</v>
       </c>
       <c r="F2">
-        <v>2.34</v>
+        <v>2.16</v>
       </c>
       <c r="G2">
-        <v>2.42</v>
+        <v>2.2</v>
       </c>
       <c r="H2">
-        <v>2.86</v>
+        <v>3.2</v>
       </c>
       <c r="I2">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="J2">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K2">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L2">
         <v>1.23</v>
@@ -913,142 +913,142 @@
         <v>1.02</v>
       </c>
       <c r="N2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O2">
         <v>1.13</v>
       </c>
       <c r="P2">
+        <v>3.35</v>
+      </c>
+      <c r="Q2">
+        <v>1.4</v>
+      </c>
+      <c r="R2">
+        <v>1.96</v>
+      </c>
+      <c r="S2">
+        <v>2</v>
+      </c>
+      <c r="T2">
+        <v>1.41</v>
+      </c>
+      <c r="U2">
         <v>3.3</v>
       </c>
-      <c r="Q2">
-        <v>1.41</v>
-      </c>
-      <c r="R2">
-        <v>1.93</v>
-      </c>
-      <c r="S2">
-        <v>2.02</v>
-      </c>
-      <c r="T2">
-        <v>1.42</v>
-      </c>
-      <c r="U2">
-        <v>3.25</v>
-      </c>
       <c r="V2">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="W2">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="X2">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Y2">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Z2">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AA2">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AB2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AC2">
         <v>11.5</v>
       </c>
       <c r="AD2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AE2">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AF2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AG2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH2">
         <v>13.5</v>
       </c>
       <c r="AI2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AJ2">
+        <v>29</v>
+      </c>
+      <c r="AK2">
+        <v>19</v>
+      </c>
+      <c r="AL2">
+        <v>23</v>
+      </c>
+      <c r="AM2">
+        <v>40</v>
+      </c>
+      <c r="AN2">
+        <v>7.8</v>
+      </c>
+      <c r="AO2">
+        <v>14.5</v>
+      </c>
+      <c r="AP2">
         <v>34</v>
       </c>
-      <c r="AK2">
-        <v>21</v>
-      </c>
-      <c r="AL2">
+      <c r="AQ2">
         <v>24</v>
       </c>
-      <c r="AM2">
-        <v>44</v>
-      </c>
-      <c r="AN2">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AO2">
-        <v>12.5</v>
-      </c>
-      <c r="AP2">
-        <v>30</v>
-      </c>
-      <c r="AQ2">
-        <v>21</v>
-      </c>
       <c r="AR2">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AS2">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AT2">
         <v>19</v>
       </c>
       <c r="AU2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AV2">
+        <v>13.5</v>
+      </c>
+      <c r="AW2">
+        <v>25</v>
+      </c>
+      <c r="AX2">
+        <v>19</v>
+      </c>
+      <c r="AY2">
+        <v>11</v>
+      </c>
+      <c r="AZ2">
+        <v>12.5</v>
+      </c>
+      <c r="BA2">
+        <v>25</v>
+      </c>
+      <c r="BB2">
+        <v>27</v>
+      </c>
+      <c r="BC2">
+        <v>17</v>
+      </c>
+      <c r="BD2">
+        <v>20</v>
+      </c>
+      <c r="BE2">
+        <v>36</v>
+      </c>
+      <c r="BF2">
+        <v>7.2</v>
+      </c>
+      <c r="BG2">
         <v>13</v>
-      </c>
-      <c r="AW2">
-        <v>22</v>
-      </c>
-      <c r="AX2">
-        <v>20</v>
-      </c>
-      <c r="AY2">
-        <v>11.5</v>
-      </c>
-      <c r="AZ2">
-        <v>12</v>
-      </c>
-      <c r="BA2">
-        <v>23</v>
-      </c>
-      <c r="BB2">
-        <v>29</v>
-      </c>
-      <c r="BC2">
-        <v>18.5</v>
-      </c>
-      <c r="BD2">
-        <v>21</v>
-      </c>
-      <c r="BE2">
-        <v>32</v>
-      </c>
-      <c r="BF2">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BG2">
-        <v>11.5</v>
       </c>
       <c r="BH2">
         <v>5.3</v>
@@ -1060,55 +1060,55 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BK2">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BN2">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BO2">
         <v>5.2</v>
       </c>
       <c r="BP2">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BQ2">
         <v>10</v>
       </c>
       <c r="BR2">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BS2">
         <v>9.4</v>
       </c>
       <c r="BT2">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BU2">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BV2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BW2">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BY2">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BZ2">
         <v>11</v>
       </c>
       <c r="CA2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="CB2" t="s">
         <v>93</v>
@@ -1131,79 +1131,79 @@
         <v>91</v>
       </c>
       <c r="F3">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="G3">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="H3">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="I3">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="J3">
+        <v>2.88</v>
+      </c>
+      <c r="K3">
         <v>2.98</v>
       </c>
-      <c r="K3">
-        <v>3.05</v>
-      </c>
       <c r="L3">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="M3">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="N3">
-        <v>2.58</v>
+        <v>2.38</v>
       </c>
       <c r="O3">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="P3">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="Q3">
-        <v>2.92</v>
+        <v>3.15</v>
       </c>
       <c r="R3">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="S3">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="T3">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="U3">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="V3">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W3">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="X3">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="Y3">
         <v>9.6</v>
       </c>
       <c r="Z3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA3">
         <v>900</v>
       </c>
       <c r="AB3">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AC3">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD3">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="AE3">
         <v>500</v>
@@ -1212,7 +1212,7 @@
         <v>15.5</v>
       </c>
       <c r="AG3">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH3">
         <v>110</v>
@@ -1221,7 +1221,7 @@
         <v>500</v>
       </c>
       <c r="AJ3">
-        <v>250</v>
+        <v>48</v>
       </c>
       <c r="AK3">
         <v>180</v>
@@ -1239,40 +1239,40 @@
         <v>500</v>
       </c>
       <c r="AP3">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AQ3">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AR3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AS3">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT3">
         <v>6.4</v>
       </c>
       <c r="AU3">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AV3">
         <v>13.5</v>
       </c>
       <c r="AW3">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX3">
         <v>12.5</v>
       </c>
       <c r="AY3">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ3">
         <v>21</v>
       </c>
       <c r="BA3">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="BB3">
         <v>16</v>
@@ -1281,22 +1281,22 @@
         <v>32</v>
       </c>
       <c r="BD3">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BE3">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="BF3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BG3">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="BH3">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="BI3">
-        <v>2.48</v>
+        <v>2.24</v>
       </c>
       <c r="BJ3">
         <v>11.5</v>
@@ -1323,7 +1323,7 @@
         <v>8.6</v>
       </c>
       <c r="BR3">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS3">
         <v>10.5</v>
@@ -1347,10 +1347,10 @@
         <v>11</v>
       </c>
       <c r="BZ3">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="CA3">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="CB3" t="s">
         <v>93</v>
@@ -1373,7 +1373,7 @@
         <v>92</v>
       </c>
       <c r="F4">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="G4">
         <v>3.15</v>
@@ -1382,7 +1382,7 @@
         <v>2.66</v>
       </c>
       <c r="I4">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="J4">
         <v>3.15</v>
@@ -1421,7 +1421,7 @@
         <v>1.95</v>
       </c>
       <c r="V4">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W4">
         <v>1.46</v>
@@ -1433,7 +1433,7 @@
         <v>10.5</v>
       </c>
       <c r="Z4">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA4">
         <v>50</v>
@@ -1448,7 +1448,7 @@
         <v>14.5</v>
       </c>
       <c r="AE4">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF4">
         <v>24</v>
@@ -1481,13 +1481,13 @@
         <v>42</v>
       </c>
       <c r="AP4">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AQ4">
         <v>8</v>
       </c>
       <c r="AR4">
-        <v>8.4</v>
+        <v>15.5</v>
       </c>
       <c r="AS4">
         <v>5.1</v>
@@ -1499,10 +1499,10 @@
         <v>6.6</v>
       </c>
       <c r="AV4">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW4">
-        <v>14.5</v>
+        <v>5</v>
       </c>
       <c r="AX4">
         <v>9</v>
@@ -1514,22 +1514,22 @@
         <v>10.5</v>
       </c>
       <c r="BA4">
+        <v>5.2</v>
+      </c>
+      <c r="BB4">
+        <v>5.3</v>
+      </c>
+      <c r="BC4">
         <v>5.1</v>
       </c>
-      <c r="BB4">
+      <c r="BD4">
+        <v>5.3</v>
+      </c>
+      <c r="BE4">
+        <v>5.5</v>
+      </c>
+      <c r="BF4">
         <v>5.2</v>
-      </c>
-      <c r="BC4">
-        <v>5</v>
-      </c>
-      <c r="BD4">
-        <v>5.2</v>
-      </c>
-      <c r="BE4">
-        <v>5.4</v>
-      </c>
-      <c r="BF4">
-        <v>5.1</v>
       </c>
       <c r="BG4">
         <v>6.2</v>
@@ -1556,7 +1556,7 @@
         <v>6.8</v>
       </c>
       <c r="BO4">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BP4">
         <v>30</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-18.xlsx
@@ -295,7 +295,7 @@
     <t>Atletico GO</t>
   </si>
   <si>
-    <t>2026-08-18 04:47:25</t>
+    <t>2026-08-18 06:55:43</t>
   </si>
 </sst>
 </file>
@@ -889,22 +889,22 @@
         <v>90</v>
       </c>
       <c r="F2">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="G2">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="H2">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="I2">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="J2">
         <v>4.2</v>
       </c>
       <c r="K2">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L2">
         <v>1.23</v>
@@ -913,19 +913,19 @@
         <v>1.02</v>
       </c>
       <c r="N2">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="O2">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="P2">
         <v>3.35</v>
       </c>
       <c r="Q2">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="R2">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="S2">
         <v>2</v>
@@ -937,22 +937,22 @@
         <v>3.3</v>
       </c>
       <c r="V2">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W2">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="X2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Y2">
         <v>26</v>
       </c>
       <c r="Z2">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AA2">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AB2">
         <v>21</v>
@@ -961,13 +961,13 @@
         <v>11.5</v>
       </c>
       <c r="AD2">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AF2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG2">
         <v>12</v>
@@ -976,13 +976,13 @@
         <v>13.5</v>
       </c>
       <c r="AI2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AJ2">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AK2">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AL2">
         <v>23</v>
@@ -991,124 +991,124 @@
         <v>40</v>
       </c>
       <c r="AN2">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AO2">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AP2">
         <v>34</v>
       </c>
       <c r="AQ2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AR2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AS2">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AT2">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AU2">
         <v>10.5</v>
       </c>
       <c r="AV2">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AW2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AX2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AY2">
         <v>11</v>
       </c>
       <c r="AZ2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BA2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BB2">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BC2">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BD2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BE2">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BF2">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BG2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BH2">
         <v>5.3</v>
       </c>
       <c r="BI2">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BJ2">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BK2">
-        <v>5.8</v>
+        <v>7.4</v>
       </c>
       <c r="BL2">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BM2">
-        <v>14.5</v>
+        <v>44</v>
       </c>
       <c r="BN2">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BO2">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BP2">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BQ2">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="BR2">
+        <v>19</v>
+      </c>
+      <c r="BS2">
+        <v>17</v>
+      </c>
+      <c r="BT2">
+        <v>7</v>
+      </c>
+      <c r="BU2">
+        <v>6.4</v>
+      </c>
+      <c r="BV2">
         <v>18.5</v>
       </c>
-      <c r="BS2">
-        <v>9.4</v>
-      </c>
-      <c r="BT2">
-        <v>7.2</v>
-      </c>
-      <c r="BU2">
-        <v>5.6</v>
-      </c>
-      <c r="BV2">
-        <v>20</v>
-      </c>
       <c r="BW2">
-        <v>9.800000000000001</v>
+        <v>17</v>
       </c>
       <c r="BX2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BY2">
-        <v>10.5</v>
+        <v>19.5</v>
       </c>
       <c r="BZ2">
         <v>11</v>
       </c>
       <c r="CA2">
-        <v>7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB2" t="s">
         <v>93</v>
@@ -1134,7 +1134,7 @@
         <v>2.62</v>
       </c>
       <c r="G3">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="H3">
         <v>3.55</v>
@@ -1143,37 +1143,37 @@
         <v>3.6</v>
       </c>
       <c r="J3">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="K3">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="L3">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="M3">
         <v>1.17</v>
       </c>
       <c r="N3">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="O3">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="P3">
         <v>1.44</v>
       </c>
       <c r="Q3">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="R3">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="S3">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="T3">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="U3">
         <v>1.67</v>
@@ -1182,64 +1182,64 @@
         <v>1.38</v>
       </c>
       <c r="W3">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="X3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y3">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="Z3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA3">
-        <v>900</v>
+        <v>80</v>
       </c>
       <c r="AB3">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC3">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD3">
+        <v>17</v>
+      </c>
+      <c r="AE3">
+        <v>70</v>
+      </c>
+      <c r="AF3">
+        <v>15</v>
+      </c>
+      <c r="AG3">
+        <v>14</v>
+      </c>
+      <c r="AH3">
+        <v>29</v>
+      </c>
+      <c r="AI3">
+        <v>110</v>
+      </c>
+      <c r="AJ3">
+        <v>46</v>
+      </c>
+      <c r="AK3">
+        <v>46</v>
+      </c>
+      <c r="AL3">
+        <v>90</v>
+      </c>
+      <c r="AM3">
+        <v>300</v>
+      </c>
+      <c r="AN3">
         <v>55</v>
       </c>
-      <c r="AE3">
-        <v>500</v>
-      </c>
-      <c r="AF3">
-        <v>15.5</v>
-      </c>
-      <c r="AG3">
-        <v>14.5</v>
-      </c>
-      <c r="AH3">
+      <c r="AO3">
         <v>110</v>
       </c>
-      <c r="AI3">
-        <v>500</v>
-      </c>
-      <c r="AJ3">
-        <v>48</v>
-      </c>
-      <c r="AK3">
-        <v>180</v>
-      </c>
-      <c r="AL3">
-        <v>500</v>
-      </c>
-      <c r="AM3">
-        <v>500</v>
-      </c>
-      <c r="AN3">
-        <v>500</v>
-      </c>
-      <c r="AO3">
-        <v>500</v>
-      </c>
       <c r="AP3">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AQ3">
         <v>7.8</v>
@@ -1248,52 +1248,52 @@
         <v>18</v>
       </c>
       <c r="AS3">
-        <v>8.199999999999999</v>
+        <v>23</v>
       </c>
       <c r="AT3">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU3">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AV3">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AW3">
-        <v>8.199999999999999</v>
+        <v>55</v>
       </c>
       <c r="AX3">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AY3">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ3">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BA3">
-        <v>8.4</v>
+        <v>14.5</v>
       </c>
       <c r="BB3">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="BC3">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="BD3">
-        <v>8.4</v>
+        <v>38</v>
       </c>
       <c r="BE3">
-        <v>9</v>
+        <v>15.5</v>
       </c>
       <c r="BF3">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="BG3">
-        <v>8.4</v>
+        <v>14.5</v>
       </c>
       <c r="BH3">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="BI3">
         <v>2.24</v>
@@ -1308,7 +1308,7 @@
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BN3">
         <v>5.3</v>
@@ -1320,13 +1320,13 @@
         <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BR3">
         <v>60</v>
       </c>
       <c r="BS3">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BT3">
         <v>6.6</v>
@@ -1338,19 +1338,19 @@
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BZ3">
         <v>65</v>
       </c>
       <c r="CA3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="CB3" t="s">
         <v>93</v>
@@ -1376,13 +1376,13 @@
         <v>3</v>
       </c>
       <c r="G4">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H4">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="I4">
-        <v>2.78</v>
+        <v>2.86</v>
       </c>
       <c r="J4">
         <v>3.15</v>
@@ -1391,13 +1391,13 @@
         <v>3.3</v>
       </c>
       <c r="L4">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="M4">
         <v>1.1</v>
       </c>
       <c r="N4">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="O4">
         <v>1.45</v>
@@ -1406,13 +1406,13 @@
         <v>1.7</v>
       </c>
       <c r="Q4">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="R4">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S4">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="T4">
         <v>1.92</v>
@@ -1421,40 +1421,40 @@
         <v>1.95</v>
       </c>
       <c r="V4">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="W4">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="X4">
         <v>12</v>
       </c>
       <c r="Y4">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z4">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AA4">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AB4">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AC4">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD4">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AE4">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AF4">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG4">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH4">
         <v>23</v>
@@ -1466,7 +1466,7 @@
         <v>130</v>
       </c>
       <c r="AK4">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AL4">
         <v>130</v>
@@ -1478,61 +1478,61 @@
         <v>55</v>
       </c>
       <c r="AO4">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AP4">
         <v>9</v>
       </c>
       <c r="AQ4">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AR4">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AS4">
-        <v>5.1</v>
+        <v>18</v>
       </c>
       <c r="AT4">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AU4">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV4">
         <v>11</v>
       </c>
       <c r="AW4">
-        <v>5</v>
+        <v>14.5</v>
       </c>
       <c r="AX4">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="AY4">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AZ4">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="BA4">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB4">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="BC4">
-        <v>5.1</v>
+        <v>16</v>
       </c>
       <c r="BD4">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="BE4">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="BF4">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BG4">
-        <v>6.2</v>
+        <v>14</v>
       </c>
       <c r="BH4">
         <v>3.25</v>
@@ -1544,34 +1544,34 @@
         <v>12</v>
       </c>
       <c r="BK4">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="BN4">
         <v>6.8</v>
       </c>
       <c r="BO4">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BP4">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BQ4">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BR4">
         <v>50</v>
       </c>
       <c r="BS4">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="BT4">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BU4">
         <v>4.4</v>
@@ -1580,19 +1580,19 @@
         <v>26</v>
       </c>
       <c r="BW4">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BX4">
+        <v>48</v>
+      </c>
+      <c r="BY4">
+        <v>5.3</v>
+      </c>
+      <c r="BZ4">
         <v>46</v>
       </c>
-      <c r="BY4">
-        <v>5.5</v>
-      </c>
-      <c r="BZ4">
-        <v>44</v>
-      </c>
       <c r="CA4">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="CB4" t="s">
         <v>93</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-18.xlsx
@@ -295,7 +295,7 @@
     <t>Atletico GO</t>
   </si>
   <si>
-    <t>2026-08-18 06:55:43</t>
+    <t>2026-08-18 09:04:10</t>
   </si>
 </sst>
 </file>
@@ -889,226 +889,226 @@
         <v>90</v>
       </c>
       <c r="F2">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="G2">
-        <v>2.34</v>
+        <v>2.24</v>
       </c>
       <c r="H2">
-        <v>2.96</v>
+        <v>3.55</v>
       </c>
       <c r="I2">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="J2">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="K2">
+        <v>3.7</v>
+      </c>
+      <c r="L2">
+        <v>1.73</v>
+      </c>
+      <c r="M2">
+        <v>1.06</v>
+      </c>
+      <c r="N2">
         <v>4.4</v>
       </c>
-      <c r="L2">
-        <v>1.23</v>
-      </c>
-      <c r="M2">
-        <v>1.02</v>
-      </c>
-      <c r="N2">
-        <v>8.4</v>
-      </c>
       <c r="O2">
-        <v>1.12</v>
+        <v>1.28</v>
       </c>
       <c r="P2">
-        <v>3.35</v>
+        <v>2.14</v>
       </c>
       <c r="Q2">
-        <v>1.41</v>
+        <v>1.86</v>
       </c>
       <c r="R2">
-        <v>1.95</v>
+        <v>1.4</v>
       </c>
       <c r="S2">
-        <v>2</v>
+        <v>3.45</v>
       </c>
       <c r="T2">
-        <v>1.41</v>
+        <v>1.72</v>
       </c>
       <c r="U2">
-        <v>3.3</v>
+        <v>2.32</v>
       </c>
       <c r="V2">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="W2">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="X2">
+        <v>18</v>
+      </c>
+      <c r="Y2">
+        <v>15.5</v>
+      </c>
+      <c r="Z2">
+        <v>23</v>
+      </c>
+      <c r="AA2">
+        <v>55</v>
+      </c>
+      <c r="AB2">
+        <v>11</v>
+      </c>
+      <c r="AC2">
+        <v>8</v>
+      </c>
+      <c r="AD2">
+        <v>15</v>
+      </c>
+      <c r="AE2">
         <v>38</v>
       </c>
-      <c r="Y2">
-        <v>26</v>
-      </c>
-      <c r="Z2">
-        <v>29</v>
-      </c>
-      <c r="AA2">
-        <v>50</v>
-      </c>
-      <c r="AB2">
+      <c r="AF2">
+        <v>14</v>
+      </c>
+      <c r="AG2">
+        <v>10.5</v>
+      </c>
+      <c r="AH2">
+        <v>17</v>
+      </c>
+      <c r="AI2">
+        <v>55</v>
+      </c>
+      <c r="AJ2">
+        <v>27</v>
+      </c>
+      <c r="AK2">
+        <v>23</v>
+      </c>
+      <c r="AL2">
+        <v>38</v>
+      </c>
+      <c r="AM2">
+        <v>90</v>
+      </c>
+      <c r="AN2">
+        <v>16.5</v>
+      </c>
+      <c r="AO2">
+        <v>36</v>
+      </c>
+      <c r="AP2">
+        <v>16</v>
+      </c>
+      <c r="AQ2">
+        <v>14</v>
+      </c>
+      <c r="AR2">
         <v>21</v>
       </c>
-      <c r="AC2">
-        <v>11.5</v>
-      </c>
-      <c r="AD2">
-        <v>14.5</v>
-      </c>
-      <c r="AE2">
-        <v>27</v>
-      </c>
-      <c r="AF2">
-        <v>22</v>
-      </c>
-      <c r="AG2">
-        <v>12</v>
-      </c>
-      <c r="AH2">
-        <v>13.5</v>
-      </c>
-      <c r="AI2">
-        <v>27</v>
-      </c>
-      <c r="AJ2">
-        <v>34</v>
-      </c>
-      <c r="AK2">
-        <v>19.5</v>
-      </c>
-      <c r="AL2">
-        <v>23</v>
-      </c>
-      <c r="AM2">
-        <v>40</v>
-      </c>
-      <c r="AN2">
-        <v>8.4</v>
-      </c>
-      <c r="AO2">
-        <v>13.5</v>
-      </c>
-      <c r="AP2">
-        <v>34</v>
-      </c>
-      <c r="AQ2">
-        <v>23</v>
-      </c>
-      <c r="AR2">
-        <v>27</v>
-      </c>
       <c r="AS2">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AT2">
-        <v>19.5</v>
+        <v>10</v>
       </c>
       <c r="AU2">
-        <v>10.5</v>
+        <v>7.4</v>
       </c>
       <c r="AV2">
         <v>13</v>
       </c>
       <c r="AW2">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AX2">
+        <v>12.5</v>
+      </c>
+      <c r="AY2">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ2">
+        <v>15</v>
+      </c>
+      <c r="BA2">
+        <v>44</v>
+      </c>
+      <c r="BB2">
+        <v>25</v>
+      </c>
+      <c r="BC2">
         <v>20</v>
       </c>
-      <c r="AY2">
-        <v>11</v>
-      </c>
-      <c r="AZ2">
-        <v>12</v>
-      </c>
-      <c r="BA2">
-        <v>24</v>
-      </c>
-      <c r="BB2">
-        <v>30</v>
-      </c>
-      <c r="BC2">
-        <v>17.5</v>
-      </c>
       <c r="BD2">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="BE2">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="BF2">
-        <v>7.8</v>
+        <v>14.5</v>
       </c>
       <c r="BG2">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="BH2">
-        <v>5.3</v>
+        <v>2.36</v>
       </c>
       <c r="BI2">
-        <v>5</v>
+        <v>2.26</v>
       </c>
       <c r="BJ2">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="BK2">
-        <v>7.4</v>
+        <v>11.5</v>
       </c>
       <c r="BL2">
-        <v>55</v>
+        <v>700</v>
       </c>
       <c r="BM2">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="BN2">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="BO2">
-        <v>5.6</v>
+        <v>4.4</v>
       </c>
       <c r="BP2">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="BQ2">
-        <v>12.5</v>
+        <v>17</v>
       </c>
       <c r="BR2">
-        <v>19</v>
+        <v>95</v>
       </c>
       <c r="BS2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BT2">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BU2">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="BV2">
-        <v>18.5</v>
+        <v>46</v>
       </c>
       <c r="BW2">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="BX2">
-        <v>22</v>
+        <v>110</v>
       </c>
       <c r="BY2">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="BZ2">
-        <v>11</v>
+        <v>100</v>
       </c>
       <c r="CA2">
-        <v>9.800000000000001</v>
+        <v>16</v>
       </c>
       <c r="CB2" t="s">
         <v>93</v>
@@ -1131,70 +1131,70 @@
         <v>91</v>
       </c>
       <c r="F3">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="G3">
-        <v>2.66</v>
+        <v>2.76</v>
       </c>
       <c r="H3">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="I3">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="J3">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="K3">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="L3">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="M3">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="N3">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="O3">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="P3">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="Q3">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="R3">
         <v>1.15</v>
       </c>
       <c r="S3">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="T3">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="U3">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="V3">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W3">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="X3">
         <v>7</v>
       </c>
       <c r="Y3">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA3">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AB3">
         <v>7.4</v>
@@ -1203,10 +1203,10 @@
         <v>7</v>
       </c>
       <c r="AD3">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE3">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF3">
         <v>15</v>
@@ -1215,7 +1215,7 @@
         <v>14</v>
       </c>
       <c r="AH3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AI3">
         <v>110</v>
@@ -1230,31 +1230,31 @@
         <v>90</v>
       </c>
       <c r="AM3">
-        <v>300</v>
+        <v>260</v>
       </c>
       <c r="AN3">
         <v>55</v>
       </c>
       <c r="AO3">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AP3">
         <v>6.2</v>
       </c>
       <c r="AQ3">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR3">
         <v>18</v>
       </c>
       <c r="AS3">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="AT3">
         <v>6.6</v>
       </c>
       <c r="AU3">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV3">
         <v>15</v>
@@ -1272,7 +1272,7 @@
         <v>24</v>
       </c>
       <c r="BA3">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BB3">
         <v>38</v>
@@ -1281,64 +1281,64 @@
         <v>38</v>
       </c>
       <c r="BD3">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="BE3">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BF3">
         <v>48</v>
       </c>
       <c r="BG3">
-        <v>14.5</v>
+        <v>75</v>
       </c>
       <c r="BH3">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="BI3">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="BJ3">
         <v>11.5</v>
       </c>
       <c r="BK3">
-        <v>8.800000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BN3">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BO3">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BP3">
         <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BR3">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BS3">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BT3">
         <v>6.6</v>
       </c>
       <c r="BU3">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX3">
         <v>1000</v>
@@ -1347,10 +1347,10 @@
         <v>12</v>
       </c>
       <c r="BZ3">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="CA3">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="CB3" t="s">
         <v>93</v>
@@ -1376,46 +1376,46 @@
         <v>3</v>
       </c>
       <c r="G4">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="H4">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="I4">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="J4">
         <v>3.15</v>
       </c>
       <c r="K4">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L4">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="M4">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N4">
         <v>3.05</v>
       </c>
       <c r="O4">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P4">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="Q4">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="R4">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S4">
         <v>4.7</v>
       </c>
       <c r="T4">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="U4">
         <v>1.95</v>
@@ -1427,7 +1427,7 @@
         <v>1.47</v>
       </c>
       <c r="X4">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y4">
         <v>9.800000000000001</v>
@@ -1442,7 +1442,7 @@
         <v>10</v>
       </c>
       <c r="AC4">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD4">
         <v>15</v>
@@ -1454,7 +1454,7 @@
         <v>23</v>
       </c>
       <c r="AG4">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AH4">
         <v>23</v>
@@ -1481,7 +1481,7 @@
         <v>44</v>
       </c>
       <c r="AP4">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ4">
         <v>8.4</v>
@@ -1490,10 +1490,10 @@
         <v>16</v>
       </c>
       <c r="AS4">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AT4">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU4">
         <v>6.4</v>
@@ -1502,34 +1502,34 @@
         <v>11</v>
       </c>
       <c r="AW4">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AX4">
         <v>17</v>
       </c>
       <c r="AY4">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ4">
-        <v>13</v>
+        <v>17.5</v>
       </c>
       <c r="BA4">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BB4">
-        <v>6.4</v>
+        <v>20</v>
       </c>
       <c r="BC4">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BD4">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BE4">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BG4">
         <v>14</v>
@@ -1541,16 +1541,16 @@
         <v>2.48</v>
       </c>
       <c r="BJ4">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BK4">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BN4">
         <v>6.8</v>
@@ -1562,37 +1562,37 @@
         <v>32</v>
       </c>
       <c r="BQ4">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BR4">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BS4">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BT4">
         <v>6.4</v>
       </c>
       <c r="BU4">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BV4">
         <v>26</v>
       </c>
       <c r="BW4">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BX4">
         <v>48</v>
       </c>
       <c r="BY4">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BZ4">
         <v>46</v>
       </c>
       <c r="CA4">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="CB4" t="s">
         <v>93</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-18.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="90">
   <si>
     <t>League</t>
   </si>
@@ -256,9 +256,6 @@
     <t>SnapshotTS</t>
   </si>
   <si>
-    <t>Chinese Super League</t>
-  </si>
-  <si>
     <t>CONMEBOL Copa Libertadores</t>
   </si>
   <si>
@@ -268,34 +265,25 @@
     <t>2026-08-18</t>
   </si>
   <si>
-    <t>11:35:00</t>
-  </si>
-  <si>
     <t>22:00:00</t>
   </si>
   <si>
     <t>22:30:00</t>
   </si>
   <si>
-    <t>Shanghai Shenhua</t>
-  </si>
-  <si>
     <t>Independiente Rivadavia</t>
   </si>
   <si>
     <t>Londrina</t>
   </si>
   <si>
-    <t>Beijing Guoan</t>
-  </si>
-  <si>
     <t>Fluminense</t>
   </si>
   <si>
     <t>Atletico GO</t>
   </si>
   <si>
-    <t>2026-08-18 09:04:10</t>
+    <t>2026-08-18 11:12:28</t>
   </si>
 </sst>
 </file>
@@ -627,7 +615,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB4"/>
+  <dimension ref="A1:CB3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -877,241 +865,241 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C2" t="s">
         <v>83</v>
       </c>
-      <c r="C2" t="s">
-        <v>84</v>
-      </c>
       <c r="D2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E2" t="s">
         <v>87</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2">
+        <v>2.76</v>
+      </c>
+      <c r="G2">
+        <v>2.8</v>
+      </c>
+      <c r="H2">
+        <v>3.35</v>
+      </c>
+      <c r="I2">
+        <v>3.4</v>
+      </c>
+      <c r="J2">
+        <v>2.92</v>
+      </c>
+      <c r="K2">
+        <v>2.94</v>
+      </c>
+      <c r="L2">
+        <v>1.68</v>
+      </c>
+      <c r="M2">
+        <v>1.16</v>
+      </c>
+      <c r="N2">
+        <v>2.38</v>
+      </c>
+      <c r="O2">
+        <v>1.69</v>
+      </c>
+      <c r="P2">
+        <v>1.45</v>
+      </c>
+      <c r="Q2">
+        <v>3.15</v>
+      </c>
+      <c r="R2">
+        <v>1.15</v>
+      </c>
+      <c r="S2">
+        <v>7</v>
+      </c>
+      <c r="T2">
+        <v>2.34</v>
+      </c>
+      <c r="U2">
+        <v>1.69</v>
+      </c>
+      <c r="V2">
+        <v>1.41</v>
+      </c>
+      <c r="W2">
+        <v>1.56</v>
+      </c>
+      <c r="X2">
+        <v>7</v>
+      </c>
+      <c r="Y2">
+        <v>8.6</v>
+      </c>
+      <c r="Z2">
+        <v>20</v>
+      </c>
+      <c r="AA2">
+        <v>75</v>
+      </c>
+      <c r="AB2">
+        <v>7</v>
+      </c>
+      <c r="AC2">
+        <v>6.8</v>
+      </c>
+      <c r="AD2">
+        <v>16.5</v>
+      </c>
+      <c r="AE2">
+        <v>65</v>
+      </c>
+      <c r="AF2">
+        <v>15.5</v>
+      </c>
+      <c r="AG2">
+        <v>14</v>
+      </c>
+      <c r="AH2">
+        <v>28</v>
+      </c>
+      <c r="AI2">
+        <v>110</v>
+      </c>
+      <c r="AJ2">
+        <v>55</v>
+      </c>
+      <c r="AK2">
+        <v>46</v>
+      </c>
+      <c r="AL2">
         <v>90</v>
       </c>
-      <c r="F2">
-        <v>2.22</v>
-      </c>
-      <c r="G2">
-        <v>2.24</v>
-      </c>
-      <c r="H2">
-        <v>3.55</v>
-      </c>
-      <c r="I2">
-        <v>3.6</v>
-      </c>
-      <c r="J2">
-        <v>3.65</v>
-      </c>
-      <c r="K2">
-        <v>3.7</v>
-      </c>
-      <c r="L2">
-        <v>1.73</v>
-      </c>
-      <c r="M2">
-        <v>1.06</v>
-      </c>
-      <c r="N2">
-        <v>4.4</v>
-      </c>
-      <c r="O2">
-        <v>1.28</v>
-      </c>
-      <c r="P2">
+      <c r="AM2">
+        <v>260</v>
+      </c>
+      <c r="AN2">
+        <v>60</v>
+      </c>
+      <c r="AO2">
+        <v>95</v>
+      </c>
+      <c r="AP2">
+        <v>6.4</v>
+      </c>
+      <c r="AQ2">
+        <v>8</v>
+      </c>
+      <c r="AR2">
+        <v>18</v>
+      </c>
+      <c r="AS2">
+        <v>60</v>
+      </c>
+      <c r="AT2">
+        <v>6.6</v>
+      </c>
+      <c r="AU2">
+        <v>6.4</v>
+      </c>
+      <c r="AV2">
+        <v>14</v>
+      </c>
+      <c r="AW2">
+        <v>50</v>
+      </c>
+      <c r="AX2">
+        <v>14</v>
+      </c>
+      <c r="AY2">
+        <v>13</v>
+      </c>
+      <c r="AZ2">
+        <v>24</v>
+      </c>
+      <c r="BA2">
+        <v>80</v>
+      </c>
+      <c r="BB2">
+        <v>42</v>
+      </c>
+      <c r="BC2">
+        <v>38</v>
+      </c>
+      <c r="BD2">
+        <v>50</v>
+      </c>
+      <c r="BE2">
+        <v>170</v>
+      </c>
+      <c r="BF2">
+        <v>50</v>
+      </c>
+      <c r="BG2">
+        <v>70</v>
+      </c>
+      <c r="BH2">
+        <v>2.56</v>
+      </c>
+      <c r="BI2">
+        <v>2.42</v>
+      </c>
+      <c r="BJ2">
+        <v>11.5</v>
+      </c>
+      <c r="BK2">
+        <v>7</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>230</v>
+      </c>
+      <c r="BN2">
+        <v>5.5</v>
+      </c>
+      <c r="BO2">
+        <v>4.8</v>
+      </c>
+      <c r="BP2">
+        <v>26</v>
+      </c>
+      <c r="BQ2">
+        <v>10.5</v>
+      </c>
+      <c r="BR2">
+        <v>1000</v>
+      </c>
+      <c r="BS2">
         <v>2.14</v>
       </c>
-      <c r="Q2">
-        <v>1.86</v>
-      </c>
-      <c r="R2">
-        <v>1.4</v>
-      </c>
-      <c r="S2">
-        <v>3.45</v>
-      </c>
-      <c r="T2">
-        <v>1.72</v>
-      </c>
-      <c r="U2">
-        <v>2.32</v>
-      </c>
-      <c r="V2">
-        <v>1.38</v>
-      </c>
-      <c r="W2">
-        <v>1.8</v>
-      </c>
-      <c r="X2">
-        <v>18</v>
-      </c>
-      <c r="Y2">
-        <v>15.5</v>
-      </c>
-      <c r="Z2">
-        <v>23</v>
-      </c>
-      <c r="AA2">
-        <v>55</v>
-      </c>
-      <c r="AB2">
-        <v>11</v>
-      </c>
-      <c r="AC2">
-        <v>8</v>
-      </c>
-      <c r="AD2">
-        <v>15</v>
-      </c>
-      <c r="AE2">
-        <v>38</v>
-      </c>
-      <c r="AF2">
-        <v>14</v>
-      </c>
-      <c r="AG2">
-        <v>10.5</v>
-      </c>
-      <c r="AH2">
-        <v>17</v>
-      </c>
-      <c r="AI2">
-        <v>55</v>
-      </c>
-      <c r="AJ2">
-        <v>27</v>
-      </c>
-      <c r="AK2">
-        <v>23</v>
-      </c>
-      <c r="AL2">
-        <v>38</v>
-      </c>
-      <c r="AM2">
-        <v>90</v>
-      </c>
-      <c r="AN2">
-        <v>16.5</v>
-      </c>
-      <c r="AO2">
-        <v>36</v>
-      </c>
-      <c r="AP2">
-        <v>16</v>
-      </c>
-      <c r="AQ2">
-        <v>14</v>
-      </c>
-      <c r="AR2">
-        <v>21</v>
-      </c>
-      <c r="AS2">
-        <v>48</v>
-      </c>
-      <c r="AT2">
-        <v>10</v>
-      </c>
-      <c r="AU2">
-        <v>7.4</v>
-      </c>
-      <c r="AV2">
-        <v>13</v>
-      </c>
-      <c r="AW2">
+      <c r="BT2">
+        <v>6.2</v>
+      </c>
+      <c r="BU2">
+        <v>5.5</v>
+      </c>
+      <c r="BV2">
         <v>32</v>
       </c>
-      <c r="AX2">
-        <v>12.5</v>
-      </c>
-      <c r="AY2">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ2">
-        <v>15</v>
-      </c>
-      <c r="BA2">
-        <v>44</v>
-      </c>
-      <c r="BB2">
-        <v>25</v>
-      </c>
-      <c r="BC2">
-        <v>20</v>
-      </c>
-      <c r="BD2">
-        <v>32</v>
-      </c>
-      <c r="BE2">
-        <v>75</v>
-      </c>
-      <c r="BF2">
-        <v>14.5</v>
-      </c>
-      <c r="BG2">
-        <v>32</v>
-      </c>
-      <c r="BH2">
-        <v>2.36</v>
-      </c>
-      <c r="BI2">
-        <v>2.26</v>
-      </c>
-      <c r="BJ2">
-        <v>14</v>
-      </c>
-      <c r="BK2">
+      <c r="BW2">
         <v>11.5</v>
       </c>
-      <c r="BL2">
-        <v>700</v>
-      </c>
-      <c r="BM2">
-        <v>15</v>
-      </c>
-      <c r="BN2">
-        <v>4.8</v>
-      </c>
-      <c r="BO2">
-        <v>4.4</v>
-      </c>
-      <c r="BP2">
-        <v>23</v>
-      </c>
-      <c r="BQ2">
-        <v>17</v>
-      </c>
-      <c r="BR2">
-        <v>95</v>
-      </c>
-      <c r="BS2">
-        <v>16</v>
-      </c>
-      <c r="BT2">
-        <v>6.4</v>
-      </c>
-      <c r="BU2">
-        <v>5.8</v>
-      </c>
-      <c r="BV2">
-        <v>46</v>
-      </c>
-      <c r="BW2">
-        <v>26</v>
-      </c>
       <c r="BX2">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="BY2">
-        <v>16.5</v>
+        <v>2.16</v>
       </c>
       <c r="BZ2">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="CA2">
-        <v>16</v>
+        <v>2.16</v>
       </c>
       <c r="CB2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1119,483 +1107,241 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E3" t="s">
         <v>88</v>
       </c>
-      <c r="E3" t="s">
-        <v>91</v>
-      </c>
       <c r="F3">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>2.76</v>
+        <v>3.15</v>
       </c>
       <c r="H3">
-        <v>3.4</v>
+        <v>2.72</v>
       </c>
       <c r="I3">
-        <v>3.5</v>
+        <v>2.82</v>
       </c>
       <c r="J3">
-        <v>2.88</v>
+        <v>3.15</v>
       </c>
       <c r="K3">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="L3">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="M3">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="N3">
-        <v>2.38</v>
+        <v>3.05</v>
       </c>
       <c r="O3">
-        <v>1.69</v>
+        <v>1.47</v>
       </c>
       <c r="P3">
-        <v>1.45</v>
+        <v>1.66</v>
       </c>
       <c r="Q3">
-        <v>3.1</v>
+        <v>2.42</v>
       </c>
       <c r="R3">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="S3">
-        <v>7</v>
+        <v>4.7</v>
       </c>
       <c r="T3">
-        <v>2.32</v>
+        <v>1.94</v>
       </c>
       <c r="U3">
-        <v>1.69</v>
+        <v>1.95</v>
       </c>
       <c r="V3">
-        <v>1.4</v>
+        <v>1.54</v>
       </c>
       <c r="W3">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="X3">
-        <v>7</v>
+        <v>11.5</v>
       </c>
       <c r="Y3">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z3">
         <v>21</v>
       </c>
       <c r="AA3">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AB3">
-        <v>7.4</v>
+        <v>9.6</v>
       </c>
       <c r="AC3">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AD3">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AE3">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="AF3">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="AG3">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AH3">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="AI3">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AJ3">
-        <v>46</v>
+        <v>130</v>
       </c>
       <c r="AK3">
         <v>46</v>
       </c>
       <c r="AL3">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="AM3">
-        <v>260</v>
+        <v>500</v>
       </c>
       <c r="AN3">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AO3">
-        <v>95</v>
+        <v>44</v>
       </c>
       <c r="AP3">
-        <v>6.2</v>
+        <v>9</v>
       </c>
       <c r="AQ3">
         <v>8.199999999999999</v>
       </c>
       <c r="AR3">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AS3">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="AT3">
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
       <c r="AU3">
         <v>6.4</v>
       </c>
       <c r="AV3">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AW3">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="AX3">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="AY3">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AZ3">
-        <v>24</v>
+        <v>17.5</v>
       </c>
       <c r="BA3">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="BB3">
+        <v>20</v>
+      </c>
+      <c r="BC3">
+        <v>34</v>
+      </c>
+      <c r="BD3">
+        <v>23</v>
+      </c>
+      <c r="BE3">
+        <v>110</v>
+      </c>
+      <c r="BF3">
         <v>38</v>
       </c>
-      <c r="BC3">
-        <v>38</v>
-      </c>
-      <c r="BD3">
-        <v>28</v>
-      </c>
-      <c r="BE3">
-        <v>16.5</v>
-      </c>
-      <c r="BF3">
-        <v>48</v>
-      </c>
       <c r="BG3">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="BH3">
-        <v>2.56</v>
+        <v>3.25</v>
       </c>
       <c r="BI3">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="BJ3">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BK3">
-        <v>6.6</v>
+        <v>4.5</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>14.5</v>
+        <v>140</v>
       </c>
       <c r="BN3">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="BO3">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BP3">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BQ3">
-        <v>9.4</v>
+        <v>6.4</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>12</v>
+        <v>6.8</v>
       </c>
       <c r="BT3">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="BU3">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="BV3">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BW3">
-        <v>10.5</v>
+        <v>6</v>
       </c>
       <c r="BX3">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY3">
-        <v>12</v>
+        <v>6.8</v>
       </c>
       <c r="BZ3">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="CA3">
-        <v>12.5</v>
+        <v>6.8</v>
       </c>
       <c r="CB3" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="4" spans="1:80">
-      <c r="A4" t="s">
-        <v>82</v>
-      </c>
-      <c r="B4" t="s">
-        <v>83</v>
-      </c>
-      <c r="C4" t="s">
-        <v>86</v>
-      </c>
-      <c r="D4" t="s">
         <v>89</v>
-      </c>
-      <c r="E4" t="s">
-        <v>92</v>
-      </c>
-      <c r="F4">
-        <v>3</v>
-      </c>
-      <c r="G4">
-        <v>3.15</v>
-      </c>
-      <c r="H4">
-        <v>2.76</v>
-      </c>
-      <c r="I4">
-        <v>2.84</v>
-      </c>
-      <c r="J4">
-        <v>3.15</v>
-      </c>
-      <c r="K4">
-        <v>3.25</v>
-      </c>
-      <c r="L4">
-        <v>1.52</v>
-      </c>
-      <c r="M4">
-        <v>1.11</v>
-      </c>
-      <c r="N4">
-        <v>3.05</v>
-      </c>
-      <c r="O4">
-        <v>1.46</v>
-      </c>
-      <c r="P4">
-        <v>1.66</v>
-      </c>
-      <c r="Q4">
-        <v>2.42</v>
-      </c>
-      <c r="R4">
-        <v>1.24</v>
-      </c>
-      <c r="S4">
-        <v>4.7</v>
-      </c>
-      <c r="T4">
-        <v>1.94</v>
-      </c>
-      <c r="U4">
-        <v>1.95</v>
-      </c>
-      <c r="V4">
-        <v>1.54</v>
-      </c>
-      <c r="W4">
-        <v>1.47</v>
-      </c>
-      <c r="X4">
-        <v>11.5</v>
-      </c>
-      <c r="Y4">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="Z4">
-        <v>22</v>
-      </c>
-      <c r="AA4">
-        <v>55</v>
-      </c>
-      <c r="AB4">
-        <v>10</v>
-      </c>
-      <c r="AC4">
-        <v>7.2</v>
-      </c>
-      <c r="AD4">
-        <v>15</v>
-      </c>
-      <c r="AE4">
-        <v>44</v>
-      </c>
-      <c r="AF4">
-        <v>23</v>
-      </c>
-      <c r="AG4">
-        <v>15.5</v>
-      </c>
-      <c r="AH4">
-        <v>23</v>
-      </c>
-      <c r="AI4">
-        <v>120</v>
-      </c>
-      <c r="AJ4">
-        <v>130</v>
-      </c>
-      <c r="AK4">
-        <v>46</v>
-      </c>
-      <c r="AL4">
-        <v>130</v>
-      </c>
-      <c r="AM4">
-        <v>580</v>
-      </c>
-      <c r="AN4">
-        <v>55</v>
-      </c>
-      <c r="AO4">
-        <v>44</v>
-      </c>
-      <c r="AP4">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AQ4">
-        <v>8.4</v>
-      </c>
-      <c r="AR4">
-        <v>16</v>
-      </c>
-      <c r="AS4">
-        <v>18.5</v>
-      </c>
-      <c r="AT4">
-        <v>8.6</v>
-      </c>
-      <c r="AU4">
-        <v>6.4</v>
-      </c>
-      <c r="AV4">
-        <v>11</v>
-      </c>
-      <c r="AW4">
-        <v>15</v>
-      </c>
-      <c r="AX4">
-        <v>17</v>
-      </c>
-      <c r="AY4">
-        <v>11.5</v>
-      </c>
-      <c r="AZ4">
-        <v>17.5</v>
-      </c>
-      <c r="BA4">
-        <v>7.4</v>
-      </c>
-      <c r="BB4">
-        <v>20</v>
-      </c>
-      <c r="BC4">
-        <v>16.5</v>
-      </c>
-      <c r="BD4">
-        <v>7.4</v>
-      </c>
-      <c r="BE4">
-        <v>7.8</v>
-      </c>
-      <c r="BF4">
-        <v>7</v>
-      </c>
-      <c r="BG4">
-        <v>14</v>
-      </c>
-      <c r="BH4">
-        <v>3.25</v>
-      </c>
-      <c r="BI4">
-        <v>2.48</v>
-      </c>
-      <c r="BJ4">
-        <v>10.5</v>
-      </c>
-      <c r="BK4">
-        <v>4</v>
-      </c>
-      <c r="BL4">
-        <v>1000</v>
-      </c>
-      <c r="BM4">
-        <v>6.2</v>
-      </c>
-      <c r="BN4">
-        <v>6.8</v>
-      </c>
-      <c r="BO4">
-        <v>4.7</v>
-      </c>
-      <c r="BP4">
-        <v>32</v>
-      </c>
-      <c r="BQ4">
-        <v>5.4</v>
-      </c>
-      <c r="BR4">
-        <v>1000</v>
-      </c>
-      <c r="BS4">
-        <v>5.6</v>
-      </c>
-      <c r="BT4">
-        <v>6.4</v>
-      </c>
-      <c r="BU4">
-        <v>5</v>
-      </c>
-      <c r="BV4">
-        <v>26</v>
-      </c>
-      <c r="BW4">
-        <v>5.2</v>
-      </c>
-      <c r="BX4">
-        <v>48</v>
-      </c>
-      <c r="BY4">
-        <v>5.7</v>
-      </c>
-      <c r="BZ4">
-        <v>46</v>
-      </c>
-      <c r="CA4">
-        <v>5.7</v>
-      </c>
-      <c r="CB4" t="s">
-        <v>93</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-18.xlsx
@@ -283,7 +283,7 @@
     <t>Atletico GO</t>
   </si>
   <si>
-    <t>2026-08-18 11:12:28</t>
+    <t>2026-08-18 13:20:51</t>
   </si>
 </sst>
 </file>
@@ -877,16 +877,16 @@
         <v>87</v>
       </c>
       <c r="F2">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="G2">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="H2">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="I2">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="J2">
         <v>2.92</v>
@@ -895,76 +895,76 @@
         <v>2.94</v>
       </c>
       <c r="L2">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="M2">
         <v>1.16</v>
       </c>
       <c r="N2">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="O2">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="P2">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="Q2">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="R2">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="S2">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="T2">
         <v>2.34</v>
       </c>
       <c r="U2">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="V2">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="W2">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="X2">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="Y2">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="Z2">
         <v>20</v>
       </c>
       <c r="AA2">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AB2">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AC2">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AD2">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE2">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AF2">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG2">
         <v>14</v>
       </c>
       <c r="AH2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AI2">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AJ2">
         <v>55</v>
@@ -973,31 +973,31 @@
         <v>46</v>
       </c>
       <c r="AL2">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AM2">
-        <v>260</v>
+        <v>500</v>
       </c>
       <c r="AN2">
         <v>60</v>
       </c>
       <c r="AO2">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AP2">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AQ2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AR2">
         <v>18</v>
       </c>
       <c r="AS2">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AT2">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AU2">
         <v>6.4</v>
@@ -1015,16 +1015,16 @@
         <v>13</v>
       </c>
       <c r="AZ2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BB2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BC2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BD2">
         <v>50</v>
@@ -1036,19 +1036,19 @@
         <v>50</v>
       </c>
       <c r="BG2">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BH2">
-        <v>2.56</v>
+        <v>2.74</v>
       </c>
       <c r="BI2">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="BJ2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BL2">
         <v>1000</v>
@@ -1057,46 +1057,46 @@
         <v>230</v>
       </c>
       <c r="BN2">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BO2">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BP2">
         <v>26</v>
       </c>
       <c r="BQ2">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>2.14</v>
+        <v>10.5</v>
       </c>
       <c r="BT2">
         <v>6.2</v>
       </c>
       <c r="BU2">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BV2">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="BW2">
-        <v>11.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>2.16</v>
+        <v>10.5</v>
       </c>
       <c r="BZ2">
         <v>1000</v>
       </c>
       <c r="CA2">
-        <v>2.16</v>
+        <v>11</v>
       </c>
       <c r="CB2" t="s">
         <v>89</v>
@@ -1125,10 +1125,10 @@
         <v>3.15</v>
       </c>
       <c r="H3">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="I3">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="J3">
         <v>3.15</v>
@@ -1143,7 +1143,7 @@
         <v>1.11</v>
       </c>
       <c r="N3">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O3">
         <v>1.47</v>
@@ -1152,19 +1152,19 @@
         <v>1.66</v>
       </c>
       <c r="Q3">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="R3">
         <v>1.24</v>
       </c>
       <c r="S3">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T3">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="U3">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="V3">
         <v>1.54</v>
@@ -1176,67 +1176,67 @@
         <v>11.5</v>
       </c>
       <c r="Y3">
+        <v>9</v>
+      </c>
+      <c r="Z3">
+        <v>17.5</v>
+      </c>
+      <c r="AA3">
+        <v>70</v>
+      </c>
+      <c r="AB3">
         <v>9.800000000000001</v>
-      </c>
-      <c r="Z3">
-        <v>21</v>
-      </c>
-      <c r="AA3">
-        <v>55</v>
-      </c>
-      <c r="AB3">
-        <v>9.6</v>
       </c>
       <c r="AC3">
         <v>7.2</v>
       </c>
       <c r="AD3">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AE3">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AF3">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AG3">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AH3">
         <v>23</v>
       </c>
       <c r="AI3">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AJ3">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="AK3">
+        <v>50</v>
+      </c>
+      <c r="AL3">
+        <v>95</v>
+      </c>
+      <c r="AM3">
+        <v>160</v>
+      </c>
+      <c r="AN3">
+        <v>60</v>
+      </c>
+      <c r="AO3">
         <v>46</v>
       </c>
-      <c r="AL3">
-        <v>130</v>
-      </c>
-      <c r="AM3">
-        <v>500</v>
-      </c>
-      <c r="AN3">
-        <v>500</v>
-      </c>
-      <c r="AO3">
-        <v>44</v>
-      </c>
       <c r="AP3">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ3">
         <v>8.199999999999999</v>
       </c>
       <c r="AR3">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AS3">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AT3">
         <v>8.6</v>
@@ -1248,13 +1248,13 @@
         <v>11</v>
       </c>
       <c r="AW3">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AX3">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AY3">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ3">
         <v>17.5</v>
@@ -1269,7 +1269,7 @@
         <v>34</v>
       </c>
       <c r="BD3">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="BE3">
         <v>110</v>
@@ -1281,16 +1281,16 @@
         <v>32</v>
       </c>
       <c r="BH3">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BI3">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="BJ3">
         <v>10.5</v>
       </c>
       <c r="BK3">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="BL3">
         <v>1000</v>
@@ -1299,46 +1299,46 @@
         <v>140</v>
       </c>
       <c r="BN3">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="BO3">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BP3">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="BQ3">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BR3">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS3">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="BT3">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BU3">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BV3">
         <v>26</v>
       </c>
       <c r="BW3">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BX3">
         <v>48</v>
       </c>
       <c r="BY3">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="BZ3">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="CA3">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="CB3" t="s">
         <v>89</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-18.xlsx
@@ -283,7 +283,7 @@
     <t>Atletico GO</t>
   </si>
   <si>
-    <t>2026-08-18 13:20:51</t>
+    <t>2026-08-18 15:29:02</t>
   </si>
 </sst>
 </file>
@@ -877,118 +877,118 @@
         <v>87</v>
       </c>
       <c r="F2">
-        <v>2.82</v>
+        <v>2.72</v>
       </c>
       <c r="G2">
-        <v>2.86</v>
+        <v>2.76</v>
       </c>
       <c r="H2">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="I2">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="J2">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="K2">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="L2">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="M2">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="N2">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="O2">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="P2">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="Q2">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="R2">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="S2">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="T2">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="U2">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="V2">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="W2">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="X2">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="Y2">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="Z2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AA2">
         <v>70</v>
       </c>
       <c r="AB2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AC2">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AD2">
         <v>16</v>
       </c>
       <c r="AE2">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AF2">
         <v>15</v>
       </c>
       <c r="AG2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH2">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AI2">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AJ2">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AK2">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AL2">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AM2">
         <v>500</v>
       </c>
       <c r="AN2">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AO2">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="AP2">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AQ2">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AR2">
         <v>18</v>
@@ -1009,46 +1009,46 @@
         <v>50</v>
       </c>
       <c r="AX2">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AY2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BA2">
         <v>75</v>
       </c>
       <c r="BB2">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="BC2">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="BD2">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="BE2">
         <v>170</v>
       </c>
       <c r="BF2">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="BG2">
         <v>65</v>
       </c>
       <c r="BH2">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="BI2">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="BJ2">
         <v>11</v>
       </c>
       <c r="BK2">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BL2">
         <v>1000</v>
@@ -1063,16 +1063,16 @@
         <v>5</v>
       </c>
       <c r="BP2">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BQ2">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BT2">
         <v>6.2</v>
@@ -1081,22 +1081,22 @@
         <v>5.4</v>
       </c>
       <c r="BV2">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BW2">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BZ2">
         <v>1000</v>
       </c>
       <c r="CA2">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="CB2" t="s">
         <v>89</v>
@@ -1119,16 +1119,16 @@
         <v>88</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="G3">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="H3">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="I3">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="J3">
         <v>3.15</v>
@@ -1146,7 +1146,7 @@
         <v>3</v>
       </c>
       <c r="O3">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="P3">
         <v>1.66</v>
@@ -1158,19 +1158,19 @@
         <v>1.24</v>
       </c>
       <c r="S3">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="T3">
         <v>1.95</v>
       </c>
       <c r="U3">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="V3">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="W3">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="X3">
         <v>11.5</v>
@@ -1179,16 +1179,16 @@
         <v>9</v>
       </c>
       <c r="Z3">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AA3">
         <v>70</v>
       </c>
       <c r="AB3">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AC3">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD3">
         <v>13</v>
@@ -1200,7 +1200,7 @@
         <v>20</v>
       </c>
       <c r="AG3">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH3">
         <v>23</v>
@@ -1221,25 +1221,25 @@
         <v>160</v>
       </c>
       <c r="AN3">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AO3">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AP3">
         <v>8.800000000000001</v>
       </c>
       <c r="AQ3">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AR3">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AS3">
         <v>32</v>
       </c>
       <c r="AT3">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU3">
         <v>6.4</v>
@@ -1308,13 +1308,13 @@
         <v>27</v>
       </c>
       <c r="BQ3">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BR3">
         <v>55</v>
       </c>
       <c r="BS3">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT3">
         <v>5.5</v>
@@ -1323,7 +1323,7 @@
         <v>4.9</v>
       </c>
       <c r="BV3">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="BW3">
         <v>7.2</v>
@@ -1332,13 +1332,13 @@
         <v>48</v>
       </c>
       <c r="BY3">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ3">
         <v>40</v>
       </c>
       <c r="CA3">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="CB3" t="s">
         <v>89</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-18.xlsx
@@ -283,7 +283,7 @@
     <t>Atletico GO</t>
   </si>
   <si>
-    <t>2026-08-18 15:29:02</t>
+    <t>2026-08-18 17:37:54</t>
   </si>
 </sst>
 </file>
@@ -880,7 +880,7 @@
         <v>2.72</v>
       </c>
       <c r="G2">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="H2">
         <v>3.3</v>
@@ -889,55 +889,55 @@
         <v>3.4</v>
       </c>
       <c r="J2">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="K2">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="L2">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="M2">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="N2">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="O2">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="P2">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Q2">
-        <v>2.96</v>
+        <v>2.86</v>
       </c>
       <c r="R2">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S2">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="T2">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="U2">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="V2">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W2">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="X2">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="Y2">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA2">
         <v>70</v>
@@ -949,10 +949,10 @@
         <v>6.8</v>
       </c>
       <c r="AD2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE2">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF2">
         <v>15</v>
@@ -964,7 +964,7 @@
         <v>26</v>
       </c>
       <c r="AI2">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="AJ2">
         <v>48</v>
@@ -973,19 +973,19 @@
         <v>42</v>
       </c>
       <c r="AL2">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AM2">
-        <v>500</v>
+        <v>210</v>
       </c>
       <c r="AN2">
         <v>55</v>
       </c>
       <c r="AO2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AP2">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AQ2">
         <v>8.4</v>
@@ -1012,10 +1012,10 @@
         <v>13.5</v>
       </c>
       <c r="AY2">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA2">
         <v>75</v>
@@ -1024,16 +1024,16 @@
         <v>40</v>
       </c>
       <c r="BC2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BD2">
+        <v>60</v>
+      </c>
+      <c r="BE2">
         <v>65</v>
       </c>
-      <c r="BE2">
-        <v>170</v>
-      </c>
       <c r="BF2">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="BG2">
         <v>65</v>
@@ -1042,22 +1042,22 @@
         <v>2.66</v>
       </c>
       <c r="BI2">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="BJ2">
         <v>11</v>
       </c>
       <c r="BK2">
-        <v>6.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>230</v>
+        <v>16.5</v>
       </c>
       <c r="BN2">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BO2">
         <v>5</v>
@@ -1066,37 +1066,37 @@
         <v>24</v>
       </c>
       <c r="BQ2">
-        <v>9.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BT2">
         <v>6.2</v>
       </c>
       <c r="BU2">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BV2">
         <v>32</v>
       </c>
       <c r="BW2">
-        <v>10.5</v>
+        <v>16</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BZ2">
         <v>1000</v>
       </c>
       <c r="CA2">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="CB2" t="s">
         <v>89</v>
@@ -1119,73 +1119,73 @@
         <v>88</v>
       </c>
       <c r="F3">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="G3">
+        <v>3.15</v>
+      </c>
+      <c r="H3">
+        <v>2.74</v>
+      </c>
+      <c r="I3">
+        <v>2.84</v>
+      </c>
+      <c r="J3">
+        <v>3.1</v>
+      </c>
+      <c r="K3">
         <v>3.2</v>
       </c>
-      <c r="H3">
-        <v>2.68</v>
-      </c>
-      <c r="I3">
-        <v>2.78</v>
-      </c>
-      <c r="J3">
-        <v>3.15</v>
-      </c>
-      <c r="K3">
-        <v>3.25</v>
-      </c>
       <c r="L3">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="M3">
         <v>1.11</v>
       </c>
       <c r="N3">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="O3">
+        <v>1.49</v>
+      </c>
+      <c r="P3">
+        <v>1.64</v>
+      </c>
+      <c r="Q3">
+        <v>2.5</v>
+      </c>
+      <c r="R3">
+        <v>1.23</v>
+      </c>
+      <c r="S3">
+        <v>5.1</v>
+      </c>
+      <c r="T3">
+        <v>1.98</v>
+      </c>
+      <c r="U3">
+        <v>1.92</v>
+      </c>
+      <c r="V3">
+        <v>1.54</v>
+      </c>
+      <c r="W3">
         <v>1.46</v>
       </c>
-      <c r="P3">
-        <v>1.66</v>
-      </c>
-      <c r="Q3">
-        <v>2.44</v>
-      </c>
-      <c r="R3">
-        <v>1.24</v>
-      </c>
-      <c r="S3">
-        <v>4.9</v>
-      </c>
-      <c r="T3">
-        <v>1.95</v>
-      </c>
-      <c r="U3">
-        <v>1.93</v>
-      </c>
-      <c r="V3">
-        <v>1.56</v>
-      </c>
-      <c r="W3">
-        <v>1.45</v>
-      </c>
       <c r="X3">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y3">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z3">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AA3">
         <v>70</v>
       </c>
       <c r="AB3">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC3">
         <v>7</v>
@@ -1200,13 +1200,13 @@
         <v>20</v>
       </c>
       <c r="AG3">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AH3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI3">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="AJ3">
         <v>90</v>
@@ -1215,19 +1215,19 @@
         <v>50</v>
       </c>
       <c r="AL3">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="AM3">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AN3">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AO3">
         <v>44</v>
       </c>
       <c r="AP3">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AQ3">
         <v>8</v>
@@ -1257,13 +1257,13 @@
         <v>12</v>
       </c>
       <c r="AZ3">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA3">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="BB3">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="BC3">
         <v>34</v>
@@ -1272,7 +1272,7 @@
         <v>48</v>
       </c>
       <c r="BE3">
-        <v>110</v>
+        <v>28</v>
       </c>
       <c r="BF3">
         <v>38</v>
@@ -1281,10 +1281,10 @@
         <v>32</v>
       </c>
       <c r="BH3">
-        <v>3.2</v>
+        <v>2.86</v>
       </c>
       <c r="BI3">
-        <v>2.46</v>
+        <v>2.64</v>
       </c>
       <c r="BJ3">
         <v>10.5</v>
@@ -1296,7 +1296,7 @@
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>140</v>
+        <v>30</v>
       </c>
       <c r="BN3">
         <v>6</v>
@@ -1308,13 +1308,13 @@
         <v>27</v>
       </c>
       <c r="BQ3">
-        <v>7.6</v>
+        <v>11</v>
       </c>
       <c r="BR3">
         <v>55</v>
       </c>
       <c r="BS3">
-        <v>8.800000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="BT3">
         <v>5.5</v>
@@ -1326,19 +1326,19 @@
         <v>23</v>
       </c>
       <c r="BW3">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="BX3">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="BY3">
-        <v>8.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="BZ3">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="CA3">
-        <v>8.4</v>
+        <v>12.5</v>
       </c>
       <c r="CB3" t="s">
         <v>89</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-18.xlsx
@@ -283,7 +283,7 @@
     <t>Atletico GO</t>
   </si>
   <si>
-    <t>2026-08-18 17:37:54</t>
+    <t>2026-08-18 19:47:15</t>
   </si>
 </sst>
 </file>
@@ -877,226 +877,226 @@
         <v>87</v>
       </c>
       <c r="F2">
-        <v>2.72</v>
+        <v>3.4</v>
       </c>
       <c r="G2">
-        <v>2.74</v>
+        <v>3.45</v>
       </c>
       <c r="H2">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="I2">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="J2">
+        <v>2.16</v>
+      </c>
+      <c r="K2">
+        <v>2.18</v>
+      </c>
+      <c r="L2">
+        <v>7.2</v>
+      </c>
+      <c r="M2">
+        <v>1.5</v>
+      </c>
+      <c r="N2">
+        <v>1.49</v>
+      </c>
+      <c r="O2">
         <v>2.98</v>
       </c>
-      <c r="K2">
+      <c r="P2">
+        <v>1.12</v>
+      </c>
+      <c r="Q2">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="R2">
+        <v>1.02</v>
+      </c>
+      <c r="S2">
+        <v>32</v>
+      </c>
+      <c r="T2">
+        <v>4.8</v>
+      </c>
+      <c r="U2">
+        <v>1.23</v>
+      </c>
+      <c r="V2">
+        <v>1.33</v>
+      </c>
+      <c r="W2">
+        <v>1.42</v>
+      </c>
+      <c r="X2">
         <v>3.05</v>
       </c>
-      <c r="L2">
-        <v>1.61</v>
-      </c>
-      <c r="M2">
-        <v>1.14</v>
-      </c>
-      <c r="N2">
-        <v>2.6</v>
-      </c>
-      <c r="O2">
-        <v>1.59</v>
-      </c>
-      <c r="P2">
-        <v>1.51</v>
-      </c>
-      <c r="Q2">
-        <v>2.86</v>
-      </c>
-      <c r="R2">
-        <v>1.18</v>
-      </c>
-      <c r="S2">
-        <v>6</v>
-      </c>
-      <c r="T2">
-        <v>2.24</v>
-      </c>
-      <c r="U2">
-        <v>1.77</v>
-      </c>
-      <c r="V2">
-        <v>1.42</v>
-      </c>
-      <c r="W2">
-        <v>1.57</v>
-      </c>
-      <c r="X2">
-        <v>7.8</v>
-      </c>
       <c r="Y2">
-        <v>8.800000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="Z2">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AA2">
-        <v>70</v>
+        <v>200</v>
       </c>
       <c r="AB2">
-        <v>7.8</v>
+        <v>5.5</v>
       </c>
       <c r="AC2">
-        <v>6.8</v>
+        <v>9</v>
       </c>
       <c r="AD2">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="AE2">
-        <v>55</v>
+        <v>320</v>
       </c>
       <c r="AF2">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AG2">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="AH2">
-        <v>26</v>
+        <v>130</v>
       </c>
       <c r="AI2">
+        <v>1000</v>
+      </c>
+      <c r="AJ2">
+        <v>130</v>
+      </c>
+      <c r="AK2">
+        <v>210</v>
+      </c>
+      <c r="AL2">
+        <v>1000</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>600</v>
+      </c>
+      <c r="AO2">
+        <v>1000</v>
+      </c>
+      <c r="AP2">
+        <v>2.9</v>
+      </c>
+      <c r="AQ2">
+        <v>6.2</v>
+      </c>
+      <c r="AR2">
+        <v>23</v>
+      </c>
+      <c r="AS2">
+        <v>110</v>
+      </c>
+      <c r="AT2">
+        <v>5.2</v>
+      </c>
+      <c r="AU2">
+        <v>8.4</v>
+      </c>
+      <c r="AV2">
+        <v>32</v>
+      </c>
+      <c r="AW2">
+        <v>200</v>
+      </c>
+      <c r="AX2">
+        <v>17.5</v>
+      </c>
+      <c r="AY2">
+        <v>29</v>
+      </c>
+      <c r="AZ2">
         <v>85</v>
       </c>
-      <c r="AJ2">
-        <v>48</v>
-      </c>
-      <c r="AK2">
-        <v>42</v>
-      </c>
-      <c r="AL2">
-        <v>75</v>
-      </c>
-      <c r="AM2">
-        <v>210</v>
-      </c>
-      <c r="AN2">
-        <v>55</v>
-      </c>
-      <c r="AO2">
-        <v>75</v>
-      </c>
-      <c r="AP2">
-        <v>7.4</v>
-      </c>
-      <c r="AQ2">
-        <v>8.4</v>
-      </c>
-      <c r="AR2">
-        <v>18</v>
-      </c>
-      <c r="AS2">
-        <v>55</v>
-      </c>
-      <c r="AT2">
-        <v>7.2</v>
-      </c>
-      <c r="AU2">
-        <v>6.4</v>
-      </c>
-      <c r="AV2">
-        <v>14</v>
-      </c>
-      <c r="AW2">
-        <v>50</v>
-      </c>
-      <c r="AX2">
-        <v>13.5</v>
-      </c>
-      <c r="AY2">
-        <v>12.5</v>
-      </c>
-      <c r="AZ2">
-        <v>23</v>
-      </c>
       <c r="BA2">
-        <v>75</v>
+        <v>370</v>
       </c>
       <c r="BB2">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="BC2">
-        <v>38</v>
+        <v>150</v>
       </c>
       <c r="BD2">
-        <v>60</v>
+        <v>420</v>
       </c>
       <c r="BE2">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="BF2">
-        <v>25</v>
+        <v>120</v>
       </c>
       <c r="BG2">
-        <v>65</v>
+        <v>340</v>
       </c>
       <c r="BH2">
-        <v>2.66</v>
+        <v>1.15</v>
       </c>
       <c r="BI2">
-        <v>2.52</v>
+        <v>1.12</v>
       </c>
       <c r="BJ2">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK2">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>16.5</v>
+        <v>9.4</v>
       </c>
       <c r="BN2">
-        <v>5.4</v>
+        <v>60</v>
       </c>
       <c r="BO2">
-        <v>5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BP2">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>13</v>
+        <v>9.4</v>
       </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>13</v>
+        <v>9.4</v>
       </c>
       <c r="BT2">
-        <v>6.2</v>
+        <v>60</v>
       </c>
       <c r="BU2">
-        <v>5.6</v>
+        <v>8.6</v>
       </c>
       <c r="BV2">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BW2">
-        <v>16</v>
+        <v>9.4</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>13.5</v>
+        <v>9.4</v>
       </c>
       <c r="BZ2">
         <v>1000</v>
       </c>
       <c r="CA2">
-        <v>13.5</v>
+        <v>9.4</v>
       </c>
       <c r="CB2" t="s">
         <v>89</v>
@@ -1119,226 +1119,226 @@
         <v>88</v>
       </c>
       <c r="F3">
+        <v>3.55</v>
+      </c>
+      <c r="G3">
+        <v>3.65</v>
+      </c>
+      <c r="H3">
+        <v>2.56</v>
+      </c>
+      <c r="I3">
+        <v>2.6</v>
+      </c>
+      <c r="J3">
         <v>3</v>
       </c>
-      <c r="G3">
-        <v>3.15</v>
-      </c>
-      <c r="H3">
-        <v>2.74</v>
-      </c>
-      <c r="I3">
+      <c r="K3">
+        <v>3.1</v>
+      </c>
+      <c r="L3">
+        <v>1.78</v>
+      </c>
+      <c r="M3">
+        <v>1.14</v>
+      </c>
+      <c r="N3">
+        <v>2.52</v>
+      </c>
+      <c r="O3">
+        <v>1.64</v>
+      </c>
+      <c r="P3">
+        <v>1.54</v>
+      </c>
+      <c r="Q3">
         <v>2.84</v>
       </c>
-      <c r="J3">
-        <v>3.1</v>
-      </c>
-      <c r="K3">
-        <v>3.2</v>
-      </c>
-      <c r="L3">
-        <v>1.55</v>
-      </c>
-      <c r="M3">
-        <v>1.11</v>
-      </c>
-      <c r="N3">
-        <v>2.96</v>
-      </c>
-      <c r="O3">
-        <v>1.49</v>
-      </c>
-      <c r="P3">
-        <v>1.64</v>
-      </c>
-      <c r="Q3">
-        <v>2.5</v>
-      </c>
       <c r="R3">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="S3">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="T3">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="U3">
-        <v>1.92</v>
+        <v>1.74</v>
       </c>
       <c r="V3">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="W3">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="X3">
-        <v>10.5</v>
+        <v>8.4</v>
       </c>
       <c r="Y3">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="Z3">
-        <v>19.5</v>
+        <v>14.5</v>
       </c>
       <c r="AA3">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AB3">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AC3">
         <v>7</v>
       </c>
       <c r="AD3">
+        <v>13.5</v>
+      </c>
+      <c r="AE3">
+        <v>40</v>
+      </c>
+      <c r="AF3">
+        <v>23</v>
+      </c>
+      <c r="AG3">
+        <v>16.5</v>
+      </c>
+      <c r="AH3">
+        <v>25</v>
+      </c>
+      <c r="AI3">
+        <v>75</v>
+      </c>
+      <c r="AJ3">
+        <v>85</v>
+      </c>
+      <c r="AK3">
+        <v>65</v>
+      </c>
+      <c r="AL3">
+        <v>90</v>
+      </c>
+      <c r="AM3">
+        <v>230</v>
+      </c>
+      <c r="AN3">
+        <v>95</v>
+      </c>
+      <c r="AO3">
+        <v>46</v>
+      </c>
+      <c r="AP3">
+        <v>7.6</v>
+      </c>
+      <c r="AQ3">
+        <v>6.8</v>
+      </c>
+      <c r="AR3">
         <v>13</v>
       </c>
-      <c r="AE3">
-        <v>38</v>
-      </c>
-      <c r="AF3">
-        <v>20</v>
-      </c>
-      <c r="AG3">
-        <v>14</v>
-      </c>
-      <c r="AH3">
-        <v>24</v>
-      </c>
-      <c r="AI3">
-        <v>60</v>
-      </c>
-      <c r="AJ3">
-        <v>90</v>
-      </c>
-      <c r="AK3">
-        <v>50</v>
-      </c>
-      <c r="AL3">
-        <v>65</v>
-      </c>
-      <c r="AM3">
-        <v>170</v>
-      </c>
-      <c r="AN3">
-        <v>65</v>
-      </c>
-      <c r="AO3">
-        <v>44</v>
-      </c>
-      <c r="AP3">
+      <c r="AS3">
+        <v>34</v>
+      </c>
+      <c r="AT3">
         <v>8.6</v>
-      </c>
-      <c r="AQ3">
-        <v>8</v>
-      </c>
-      <c r="AR3">
-        <v>15</v>
-      </c>
-      <c r="AS3">
-        <v>32</v>
-      </c>
-      <c r="AT3">
-        <v>8.800000000000001</v>
       </c>
       <c r="AU3">
         <v>6.4</v>
       </c>
       <c r="AV3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW3">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AX3">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AY3">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AZ3">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="BA3">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="BB3">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="BC3">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="BD3">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="BE3">
-        <v>28</v>
+        <v>170</v>
       </c>
       <c r="BF3">
+        <v>75</v>
+      </c>
+      <c r="BG3">
         <v>38</v>
       </c>
-      <c r="BG3">
-        <v>32</v>
-      </c>
       <c r="BH3">
-        <v>2.86</v>
+        <v>2.32</v>
       </c>
       <c r="BI3">
-        <v>2.64</v>
+        <v>2.22</v>
       </c>
       <c r="BJ3">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="BK3">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="BL3">
-        <v>1000</v>
+        <v>960</v>
       </c>
       <c r="BM3">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="BN3">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BO3">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BP3">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="BQ3">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="BR3">
+        <v>100</v>
+      </c>
+      <c r="BS3">
+        <v>65</v>
+      </c>
+      <c r="BT3">
+        <v>5.2</v>
+      </c>
+      <c r="BU3">
+        <v>4.6</v>
+      </c>
+      <c r="BV3">
+        <v>29</v>
+      </c>
+      <c r="BW3">
+        <v>22</v>
+      </c>
+      <c r="BX3">
+        <v>75</v>
+      </c>
+      <c r="BY3">
         <v>55</v>
       </c>
-      <c r="BS3">
-        <v>13.5</v>
-      </c>
-      <c r="BT3">
-        <v>5.5</v>
-      </c>
-      <c r="BU3">
-        <v>4.9</v>
-      </c>
-      <c r="BV3">
-        <v>23</v>
-      </c>
-      <c r="BW3">
-        <v>10</v>
-      </c>
-      <c r="BX3">
-        <v>42</v>
-      </c>
-      <c r="BY3">
-        <v>12.5</v>
-      </c>
       <c r="BZ3">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="CA3">
-        <v>12.5</v>
+        <v>55</v>
       </c>
       <c r="CB3" t="s">
         <v>89</v>
